--- a/calc.xlsx
+++ b/calc.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\moex\calc_pos_moex\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mozart\Documents\calc_pos_moex\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="Лист4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="97">
   <si>
     <t>Депозит</t>
   </si>
@@ -253,9 +254,6 @@
     <t>TRNFP</t>
   </si>
   <si>
-    <t>Риск 1.2%</t>
-  </si>
-  <si>
     <t>SNGS</t>
   </si>
   <si>
@@ -284,6 +282,42 @@
   </si>
   <si>
     <t>BSPBP</t>
+  </si>
+  <si>
+    <t>Риск 0.6%</t>
+  </si>
+  <si>
+    <t>Утренние пробросы</t>
+  </si>
+  <si>
+    <t>TTF</t>
+  </si>
+  <si>
+    <t>SPYF</t>
+  </si>
+  <si>
+    <t>SRM6</t>
+  </si>
+  <si>
+    <t>GLM6</t>
+  </si>
+  <si>
+    <t>SiM6</t>
+  </si>
+  <si>
+    <t>MMM6</t>
+  </si>
+  <si>
+    <t>GL</t>
+  </si>
+  <si>
+    <t>FFJ6</t>
+  </si>
+  <si>
+    <t>SFM6</t>
+  </si>
+  <si>
+    <t>EuM6</t>
   </si>
 </sst>
 </file>
@@ -380,7 +414,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -455,11 +489,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -501,6 +544,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -789,19 +836,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" customWidth="1"/>
-    <col min="4" max="4" width="6.54296875" customWidth="1"/>
-    <col min="5" max="5" width="14.26953125" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" customWidth="1"/>
-    <col min="7" max="7" width="19.26953125" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -809,7 +856,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
         <v>1</v>
@@ -830,7 +877,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -855,7 +902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -880,7 +927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,7 +952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -930,7 +977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -955,7 +1002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -980,7 +1027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1005,7 +1052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1030,7 +1077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" t="s">
         <v>15</v>
@@ -1045,17 +1092,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.1796875" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" customWidth="1"/>
-    <col min="14" max="14" width="17.1796875" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" customWidth="1"/>
+    <col min="14" max="14" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
@@ -1070,7 +1117,7 @@
         <v>-9954.7800000000061</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
@@ -1085,7 +1132,7 @@
         <v>38.640000000000036</v>
       </c>
     </row>
-    <row r="5" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
@@ -1115,7 +1162,7 @@
       <c r="M5"/>
       <c r="N5"/>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
         <v>17</v>
       </c>
@@ -1141,7 +1188,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
         <v>17</v>
       </c>
@@ -1167,7 +1214,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
         <v>17</v>
       </c>
@@ -1193,7 +1240,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
         <v>17</v>
       </c>
@@ -1221,7 +1268,7 @@
       <c r="N9" s="23"/>
       <c r="O9" s="24"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
         <v>17</v>
       </c>
@@ -1254,7 +1301,7 @@
         <v>3.3543999999999996</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
         <v>17</v>
       </c>
@@ -1280,7 +1327,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
         <v>17</v>
       </c>
@@ -1316,7 +1363,7 @@
       </c>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
         <v>17</v>
       </c>
@@ -1352,7 +1399,7 @@
       </c>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
         <v>17</v>
       </c>
@@ -1388,7 +1435,7 @@
       </c>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
         <v>28</v>
       </c>
@@ -1424,7 +1471,7 @@
       </c>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="19" t="s">
         <v>28</v>
       </c>
@@ -1460,7 +1507,7 @@
       </c>
       <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="19" t="s">
         <v>28</v>
       </c>
@@ -1492,7 +1539,7 @@
       <c r="P17" s="11"/>
       <c r="Q17" s="1"/>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="19" t="s">
         <v>28</v>
       </c>
@@ -1524,7 +1571,7 @@
       <c r="P18" s="11"/>
       <c r="Q18" s="1"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="22" t="s">
         <v>28</v>
       </c>
@@ -1547,7 +1594,7 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="22" t="s">
         <v>28</v>
       </c>
@@ -1570,7 +1617,7 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="22" t="s">
         <v>28</v>
       </c>
@@ -1593,7 +1640,7 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
@@ -1602,7 +1649,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
@@ -1611,7 +1658,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" s="1"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
@@ -1620,7 +1667,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -1629,7 +1676,7 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
@@ -1638,7 +1685,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
@@ -1647,7 +1694,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" s="1"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -1656,7 +1703,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -1665,7 +1712,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
@@ -1674,7 +1721,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
@@ -1683,7 +1730,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -1692,7 +1739,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
@@ -1701,7 +1748,7 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="1"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
@@ -1710,7 +1757,7 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="1"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
@@ -1719,7 +1766,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="1"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
@@ -1728,7 +1775,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="1"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
@@ -1737,7 +1784,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="1"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
@@ -1755,58 +1802,58 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:U53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="15.26953125" customWidth="1"/>
-    <col min="5" max="5" width="10.54296875" customWidth="1"/>
-    <col min="6" max="6" width="18.26953125" customWidth="1"/>
-    <col min="8" max="8" width="13.7265625" customWidth="1"/>
-    <col min="9" max="9" width="8.54296875" customWidth="1"/>
-    <col min="10" max="10" width="11.54296875" customWidth="1"/>
-    <col min="12" max="16" width="10.26953125" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" customWidth="1"/>
+    <col min="12" max="16" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.35">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C4" s="31">
-        <f>C3*1.2/100</f>
-        <v>1560</v>
+        <f>C3*0.6/100</f>
+        <v>240</v>
       </c>
       <c r="D4" s="32"/>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="L6" s="5" t="str">
         <f ca="1">TEXT(L7,"ддд")</f>
-        <v>Пн</v>
+        <v>Вт</v>
       </c>
       <c r="M6" s="5" t="str">
         <f ca="1">TEXT(M7,"ддд")</f>
-        <v>Пт</v>
+        <v>Пн</v>
       </c>
       <c r="N6" s="5" t="str">
         <f t="shared" ref="N6:P6" ca="1" si="0">TEXT(N7,"ддд")</f>
-        <v>Чт</v>
+        <v>Пт</v>
       </c>
       <c r="O6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Ср</v>
+        <v>Чт</v>
       </c>
       <c r="P6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Вт</v>
-      </c>
-    </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.35">
+        <v>Ср</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>31</v>
       </c>
@@ -1830,30 +1877,30 @@
       </c>
       <c r="I7" s="24"/>
       <c r="J7" s="22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-1, "ГГГГ-ММ-ДД")</f>
-        <v>2026-02-16</v>
+        <v>2026-04-14</v>
       </c>
       <c r="M7" s="1" t="str">
-        <f ca="1">TEXT(TODAY()-4, "ГГГГ-ММ-ДД")</f>
-        <v>2026-02-13</v>
+        <f ca="1">TEXT(TODAY()-2, "ГГГГ-ММ-ДД")</f>
+        <v>2026-04-13</v>
       </c>
       <c r="N7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-5, "ГГГГ-ММ-ДД")</f>
-        <v>2026-02-12</v>
+        <v>2026-04-10</v>
       </c>
       <c r="O7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-6, "ГГГГ-ММ-ДД")</f>
-        <v>2026-02-11</v>
+        <v>2026-04-09</v>
       </c>
       <c r="P7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-7, "ГГГГ-ММ-ДД")</f>
-        <v>2026-02-10</v>
+        <v>2026-04-08</v>
       </c>
       <c r="R7" s="28">
         <v>45566</v>
@@ -1868,7 +1915,7 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B8" s="22" t="s">
         <v>46</v>
       </c>
@@ -1887,7 +1934,7 @@
       </c>
       <c r="G8" s="26">
         <f t="shared" ref="G8:G28" si="2">ROUND($C$4/(D8/E8*F8),0)</f>
-        <v>446</v>
+        <v>69</v>
       </c>
       <c r="H8" s="22">
         <f t="shared" ref="H8:H19" si="3">ROUND(D8/E8,0)</f>
@@ -1899,27 +1946,27 @@
       </c>
       <c r="K8">
         <f ca="1">ROUND(AVERAGE(L8:P8),2)</f>
-        <v>42.63</v>
+        <v>9339.66</v>
       </c>
       <c r="L8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.2580000000000009</v>
+        <v>42327.093999999997</v>
       </c>
       <c r="M8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>212</v>
+        <v>-34261.775999999998</v>
       </c>
       <c r="N8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.18299999999999983</v>
+        <v>13106.898999999999</v>
       </c>
       <c r="O8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.34799999999999898</v>
+        <v>0.42900000000000027</v>
       </c>
       <c r="P8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.34899999999999842</v>
+        <v>25525.673999999999</v>
       </c>
       <c r="R8" s="29">
         <v>54</v>
@@ -1932,7 +1979,7 @@
       </c>
       <c r="U8" s="1"/>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
@@ -1951,7 +1998,7 @@
       </c>
       <c r="G9" s="26">
         <f t="shared" si="2"/>
-        <v>1258</v>
+        <v>194</v>
       </c>
       <c r="H9" s="22">
         <f t="shared" si="3"/>
@@ -1963,27 +2010,27 @@
       </c>
       <c r="K9">
         <f ca="1">ROUND(AVERAGE(L9:P9),2)</f>
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="L9">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.2899999999999991</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="M9">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.99000000000000199</v>
+        <v>0.87000000000000455</v>
       </c>
       <c r="N9">
         <f t="shared" ref="N9:N50" ca="1" si="4">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.72999999999999687</v>
+        <v>1.0800000000000054</v>
       </c>
       <c r="O9">
         <f t="shared" ref="O9:O50" ca="1" si="5">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.2600000000000051</v>
+        <v>1.5799999999999983</v>
       </c>
       <c r="P9">
         <f t="shared" ref="P9:P50" ca="1" si="6">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.1000000000000014</v>
+        <v>1.7999999999999972</v>
       </c>
       <c r="R9" s="25">
         <v>-30</v>
@@ -1996,7 +2043,7 @@
       </c>
       <c r="U9" s="1"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B10" s="22" t="s">
         <v>57</v>
       </c>
@@ -2015,7 +2062,7 @@
       </c>
       <c r="G10" s="26">
         <f>ROUND($C$4/(D10/E10*F10),0)</f>
-        <v>1300</v>
+        <v>200</v>
       </c>
       <c r="H10" s="22">
         <f t="shared" si="3"/>
@@ -2024,27 +2071,27 @@
       <c r="I10" s="24"/>
       <c r="K10">
         <f ca="1">ROUND(AVERAGE(L10:P10),2)</f>
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="L10">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.89999999999999858</v>
+        <v>0.96000000000000085</v>
       </c>
       <c r="M10">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.92999999999999972</v>
+        <v>1.7899999999999991</v>
       </c>
       <c r="N10">
         <f t="shared" ca="1" si="4"/>
-        <v>0.83999999999999631</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="5"/>
-        <v>0.99000000000000199</v>
+        <v>0.55000000000000426</v>
       </c>
       <c r="P10">
         <f t="shared" ca="1" si="6"/>
-        <v>0.85999999999999943</v>
+        <v>0.92999999999999972</v>
       </c>
       <c r="R10" s="29">
         <v>39</v>
@@ -2057,9 +2104,9 @@
       </c>
       <c r="U10" s="1"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" s="22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" s="22">
         <v>8.77</v>
@@ -2076,7 +2123,7 @@
       </c>
       <c r="G11" s="26">
         <f>ROUND($C$4/(D11/E11*F11),0)</f>
-        <v>178</v>
+        <v>27</v>
       </c>
       <c r="H11" s="22">
         <f t="shared" si="3"/>
@@ -2088,36 +2135,36 @@
       </c>
       <c r="K11">
         <f ca="1">ROUND(AVERAGE(L11:P11),2)</f>
-        <v>8.77</v>
+        <v>4.5</v>
       </c>
       <c r="L11">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>19.970000000000027</v>
+        <v>5.9000000000000341</v>
       </c>
       <c r="M11">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>6.4199999999999591</v>
+        <v>3.8800000000000523</v>
       </c>
       <c r="N11">
         <f t="shared" ca="1" si="4"/>
-        <v>5.9700000000000273</v>
+        <v>3.1399999999999864</v>
       </c>
       <c r="O11">
         <f t="shared" ca="1" si="5"/>
-        <v>7.4800000000000182</v>
+        <v>6.57000000000005</v>
       </c>
       <c r="P11">
         <f t="shared" ca="1" si="6"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R11" s="29"/>
       <c r="S11" s="29"/>
       <c r="T11" s="25"/>
       <c r="U11" s="1"/>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B12" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C12" s="24">
         <v>2.83</v>
@@ -2134,7 +2181,7 @@
       </c>
       <c r="G12" s="26">
         <f>ROUND($C$4/(D12/E12*F12),0)</f>
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="H12" s="22">
         <f t="shared" si="3"/>
@@ -2146,34 +2193,34 @@
       </c>
       <c r="K12" s="24">
         <f ca="1">ROUND(AVERAGE(L12:P12),2)</f>
-        <v>2.83</v>
+        <v>1.35</v>
       </c>
       <c r="L12" s="24">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>11.149999999999999</v>
+        <v>0.94999999999999574</v>
       </c>
       <c r="M12" s="24">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.55000000000000426</v>
+        <v>1.6999999999999957</v>
       </c>
       <c r="N12" s="24">
         <f t="shared" ca="1" si="4"/>
-        <v>1.0499999999999972</v>
+        <v>1.8500000000000014</v>
       </c>
       <c r="O12" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>0.5</v>
+        <v>1.4499999999999957</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ca="1" si="6"/>
-        <v>0.89999999999999858</v>
+        <v>0.80000000000000426</v>
       </c>
       <c r="R12" s="29"/>
       <c r="S12" s="29"/>
       <c r="T12" s="25"/>
       <c r="U12" s="1"/>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>43</v>
       </c>
@@ -2192,7 +2239,7 @@
       </c>
       <c r="G13" s="26">
         <f t="shared" si="2"/>
-        <v>312</v>
+        <v>48</v>
       </c>
       <c r="H13" s="22">
         <f t="shared" si="3"/>
@@ -2201,27 +2248,27 @@
       <c r="I13" s="23"/>
       <c r="K13">
         <f t="shared" ref="K13:K50" ca="1" si="7">ROUND(AVERAGE(L13:P13),2)</f>
-        <v>24.2</v>
+        <v>19.760000000000002</v>
       </c>
       <c r="L13">
         <f t="shared" ref="L13:L50" ca="1" si="8">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>24</v>
+        <v>17.600000000000023</v>
       </c>
       <c r="M13">
         <f t="shared" ref="M13:M50" ca="1" si="9">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>30.399999999999977</v>
+        <v>22.600000000000023</v>
       </c>
       <c r="N13">
         <f t="shared" ca="1" si="4"/>
-        <v>21.799999999999955</v>
+        <v>16.600000000000023</v>
       </c>
       <c r="O13">
         <f t="shared" ca="1" si="5"/>
-        <v>28.799999999999955</v>
+        <v>20.200000000000045</v>
       </c>
       <c r="P13">
         <f t="shared" ca="1" si="6"/>
-        <v>16</v>
+        <v>21.800000000000068</v>
       </c>
       <c r="R13" s="29">
         <v>80</v>
@@ -2234,7 +2281,7 @@
       </c>
       <c r="U13" s="1"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" s="22" t="s">
         <v>68</v>
       </c>
@@ -2253,7 +2300,7 @@
       </c>
       <c r="G14" s="26">
         <f t="shared" ref="G14:G20" si="11">ROUND($C$4/(D14/E14*F14),0)</f>
-        <v>484</v>
+        <v>75</v>
       </c>
       <c r="H14" s="22">
         <f t="shared" si="3"/>
@@ -2262,27 +2309,27 @@
       <c r="I14" s="24"/>
       <c r="K14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="8"/>
-        <v>2.0600000000000023</v>
+        <v>2.019999999999996</v>
       </c>
       <c r="M14">
         <f t="shared" ca="1" si="9"/>
-        <v>1.5100000000000051</v>
+        <v>2.9099999999999966</v>
       </c>
       <c r="N14">
         <f t="shared" ca="1" si="4"/>
-        <v>1.2099999999999937</v>
+        <v>2.2200000000000131</v>
       </c>
       <c r="O14">
         <f t="shared" ca="1" si="5"/>
-        <v>2.5799999999999983</v>
+        <v>3.7999999999999972</v>
       </c>
       <c r="P14">
         <f t="shared" ca="1" si="6"/>
-        <v>1.8099999999999881</v>
+        <v>2.2800000000000011</v>
       </c>
       <c r="R14" s="29">
         <v>27</v>
@@ -2293,7 +2340,7 @@
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B15" s="22" t="s">
         <v>50</v>
       </c>
@@ -2312,7 +2359,7 @@
       </c>
       <c r="G15" s="26">
         <f t="shared" si="11"/>
-        <v>2889</v>
+        <v>444</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" si="3"/>
@@ -2321,34 +2368,34 @@
       <c r="I15" s="23"/>
       <c r="K15">
         <f t="shared" ca="1" si="7"/>
-        <v>3.62</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="8"/>
-        <v>3.5500000000000114</v>
+        <v>7.2000000000000028</v>
       </c>
       <c r="M15">
         <f t="shared" ca="1" si="9"/>
-        <v>3.5</v>
+        <v>16.599999999999994</v>
       </c>
       <c r="N15">
         <f t="shared" ca="1" si="4"/>
-        <v>2.4000000000000057</v>
+        <v>5.0999999999999943</v>
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="5"/>
-        <v>2.8000000000000114</v>
+        <v>3.4000000000000057</v>
       </c>
       <c r="P15">
         <f t="shared" ca="1" si="6"/>
-        <v>5.8499999999999943</v>
+        <v>8.3500000000000085</v>
       </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" s="22" t="s">
         <v>64</v>
       </c>
@@ -2367,7 +2414,7 @@
       </c>
       <c r="G16" s="26">
         <f t="shared" si="11"/>
-        <v>867</v>
+        <v>133</v>
       </c>
       <c r="H16" s="22">
         <f t="shared" si="3"/>
@@ -2379,27 +2426,27 @@
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="7"/>
-        <v>2.16</v>
+        <v>2.87</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="8"/>
-        <v>1.5</v>
+        <v>2.5999999999999943</v>
       </c>
       <c r="M16">
         <f t="shared" ca="1" si="9"/>
-        <v>2.9699999999999989</v>
+        <v>3.5499999999999829</v>
       </c>
       <c r="N16">
         <f t="shared" ca="1" si="4"/>
-        <v>1.5699999999999932</v>
+        <v>2.4400000000000119</v>
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="5"/>
-        <v>2.9000000000000057</v>
+        <v>3.4499999999999886</v>
       </c>
       <c r="P16">
         <f t="shared" ca="1" si="6"/>
-        <v>1.8700000000000045</v>
+        <v>2.3100000000000023</v>
       </c>
       <c r="R16" s="25">
         <v>-2</v>
@@ -2412,9 +2459,9 @@
       </c>
       <c r="U16" s="1"/>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" s="22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C17" s="22">
         <v>1.8600000000000001E-3</v>
@@ -2431,7 +2478,7 @@
       </c>
       <c r="G17" s="26">
         <f t="shared" si="11"/>
-        <v>839</v>
+        <v>129</v>
       </c>
       <c r="H17" s="22">
         <f t="shared" si="3"/>
@@ -2443,34 +2490,34 @@
       </c>
       <c r="K17">
         <f ca="1">ROUND(AVERAGE(L17:P17),5)</f>
-        <v>1.9E-3</v>
+        <v>2.0200000000000001E-3</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="8"/>
-        <v>1.7400000000000054E-3</v>
+        <v>2.140000000000003E-3</v>
       </c>
       <c r="M17">
         <f t="shared" ca="1" si="9"/>
-        <v>2.2599999999999981E-3</v>
+        <v>2.5599999999999928E-3</v>
       </c>
       <c r="N17">
         <f t="shared" ca="1" si="4"/>
-        <v>1.8200000000000022E-3</v>
+        <v>1.2000000000000066E-3</v>
       </c>
       <c r="O17">
         <f t="shared" ca="1" si="5"/>
-        <v>1.4799999999999952E-3</v>
+        <v>1.9799999999999957E-3</v>
       </c>
       <c r="P17">
         <f t="shared" ca="1" si="6"/>
-        <v>2.1800000000000014E-3</v>
+        <v>2.239999999999992E-3</v>
       </c>
       <c r="R17" s="25"/>
       <c r="S17" s="25"/>
       <c r="T17" s="29"/>
       <c r="U17" s="1"/>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" s="22" t="s">
         <v>56</v>
       </c>
@@ -2489,7 +2536,7 @@
       </c>
       <c r="G18" s="26">
         <f t="shared" si="11"/>
-        <v>355</v>
+        <v>55</v>
       </c>
       <c r="H18" s="22">
         <f t="shared" si="3"/>
@@ -2501,27 +2548,27 @@
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="7"/>
-        <v>4.6500000000000004</v>
+        <v>3.32</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="8"/>
-        <v>4.4200000000000159</v>
+        <v>4.539999999999992</v>
       </c>
       <c r="M18">
         <f t="shared" ca="1" si="9"/>
-        <v>6.8600000000000136</v>
+        <v>3.9000000000000057</v>
       </c>
       <c r="N18">
         <f t="shared" ca="1" si="4"/>
-        <v>3.4799999999999898</v>
+        <v>2.2600000000000193</v>
       </c>
       <c r="O18">
         <f t="shared" ca="1" si="5"/>
-        <v>6.3199999999999932</v>
+        <v>2.4000000000000057</v>
       </c>
       <c r="P18">
         <f t="shared" ca="1" si="6"/>
-        <v>2.1599999999999966</v>
+        <v>3.5</v>
       </c>
       <c r="R18" s="25">
         <v>-211</v>
@@ -2532,7 +2579,7 @@
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B19" s="22" t="s">
         <v>51</v>
       </c>
@@ -2551,7 +2598,7 @@
       </c>
       <c r="G19" s="26">
         <f t="shared" si="11"/>
-        <v>1987</v>
+        <v>306</v>
       </c>
       <c r="H19" s="22">
         <f t="shared" si="3"/>
@@ -2560,27 +2607,27 @@
       <c r="I19" s="24"/>
       <c r="K19">
         <f t="shared" ca="1" si="7"/>
-        <v>303466.46000000002</v>
+        <v>31361.14</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="8"/>
-        <v>394462</v>
+        <v>53018.834000000003</v>
       </c>
       <c r="M19">
         <f t="shared" ca="1" si="9"/>
-        <v>17954.636999999999</v>
+        <v>44252.837500000001</v>
       </c>
       <c r="N19">
         <f t="shared" ca="1" si="4"/>
-        <v>4.0999999999999925E-2</v>
+        <v>57708</v>
       </c>
       <c r="O19">
         <f t="shared" ca="1" si="5"/>
-        <v>874813.64300000004</v>
+        <v>-43156.788999999997</v>
       </c>
       <c r="P19">
         <f t="shared" ca="1" si="6"/>
-        <v>230102</v>
+        <v>44982.817499999997</v>
       </c>
       <c r="R19" s="1"/>
       <c r="S19" s="25">
@@ -2589,7 +2636,7 @@
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B20" s="22" t="s">
         <v>55</v>
       </c>
@@ -2608,7 +2655,7 @@
       </c>
       <c r="G20" s="26">
         <f t="shared" si="11"/>
-        <v>181</v>
+        <v>28</v>
       </c>
       <c r="H20" s="22">
         <f t="shared" ref="H20:H44" si="12">ROUND(D20/E20,0)</f>
@@ -2620,27 +2667,27 @@
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="7"/>
-        <v>86.3</v>
+        <v>112.6</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="8"/>
-        <v>58.5</v>
+        <v>54.5</v>
       </c>
       <c r="M20">
         <f t="shared" ca="1" si="9"/>
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="N20">
         <f t="shared" ca="1" si="4"/>
-        <v>75.5</v>
+        <v>83</v>
       </c>
       <c r="O20">
         <f t="shared" ca="1" si="5"/>
-        <v>98</v>
+        <v>94.5</v>
       </c>
       <c r="P20">
         <f t="shared" ca="1" si="6"/>
-        <v>130.5</v>
+        <v>162</v>
       </c>
       <c r="R20" s="25">
         <v>-741</v>
@@ -2653,7 +2700,7 @@
       </c>
       <c r="U20" s="1"/>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>38</v>
       </c>
@@ -2672,7 +2719,7 @@
       </c>
       <c r="G21" s="26">
         <f t="shared" si="2"/>
-        <v>1486</v>
+        <v>229</v>
       </c>
       <c r="H21" s="22">
         <f t="shared" si="12"/>
@@ -2684,27 +2731,27 @@
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="7"/>
-        <v>0.99</v>
+        <v>18445.27</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="8"/>
-        <v>0.85999999999999943</v>
+        <v>0.92499999999999716</v>
       </c>
       <c r="M21">
         <f t="shared" ca="1" si="9"/>
-        <v>1.4949999999999974</v>
+        <v>0.96499999999999986</v>
       </c>
       <c r="N21">
         <f t="shared" ca="1" si="4"/>
-        <v>0.61499999999999844</v>
+        <v>46081.334999999999</v>
       </c>
       <c r="O21">
         <f t="shared" ca="1" si="5"/>
-        <v>1.3400000000000034</v>
+        <v>46142.23</v>
       </c>
       <c r="P21">
         <f t="shared" ca="1" si="6"/>
-        <v>0.64999999999999858</v>
+        <v>0.90500000000000114</v>
       </c>
       <c r="R21" s="25">
         <v>-107</v>
@@ -2717,7 +2764,7 @@
       </c>
       <c r="U21" s="1"/>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>41</v>
       </c>
@@ -2736,7 +2783,7 @@
       </c>
       <c r="G22" s="26">
         <f t="shared" si="2"/>
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="H22" s="22">
         <f t="shared" si="12"/>
@@ -2746,27 +2793,27 @@
       <c r="J22" s="30"/>
       <c r="K22">
         <f t="shared" ca="1" si="7"/>
-        <v>76.3</v>
+        <v>59.3</v>
       </c>
       <c r="L22">
         <f t="shared" ca="1" si="8"/>
-        <v>125.5</v>
+        <v>54.5</v>
       </c>
       <c r="M22">
         <f t="shared" ca="1" si="9"/>
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="N22">
         <f t="shared" ca="1" si="4"/>
-        <v>64.5</v>
+        <v>38</v>
       </c>
       <c r="O22">
         <f t="shared" ca="1" si="5"/>
-        <v>56.5</v>
+        <v>76</v>
       </c>
       <c r="P22">
         <f t="shared" ca="1" si="6"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R22" s="29">
         <v>45</v>
@@ -2779,7 +2826,7 @@
       </c>
       <c r="U22" s="1"/>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" s="22" t="s">
         <v>53</v>
       </c>
@@ -2798,7 +2845,7 @@
       </c>
       <c r="G23" s="26">
         <f>ROUND($C$4/(D23/E23*F23),0)</f>
-        <v>274</v>
+        <v>42</v>
       </c>
       <c r="H23" s="22">
         <f t="shared" si="12"/>
@@ -2808,27 +2855,27 @@
       <c r="J23" s="30"/>
       <c r="K23">
         <f t="shared" ca="1" si="7"/>
-        <v>3.17</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="L23">
         <f t="shared" ca="1" si="8"/>
-        <v>4.4799999999999898</v>
+        <v>3.3400000000000034</v>
       </c>
       <c r="M23">
         <f t="shared" ca="1" si="9"/>
-        <v>3.789999999999992</v>
+        <v>2.410000000000025</v>
       </c>
       <c r="N23">
         <f t="shared" ca="1" si="4"/>
-        <v>2.6500000000000057</v>
+        <v>1.839999999999975</v>
       </c>
       <c r="O23">
         <f t="shared" ca="1" si="5"/>
-        <v>2.8100000000000023</v>
+        <v>2.7700000000000102</v>
       </c>
       <c r="P23">
         <f t="shared" ca="1" si="6"/>
-        <v>2.0999999999999943</v>
+        <v>2.4000000000000057</v>
       </c>
       <c r="R23" s="25">
         <v>-146</v>
@@ -2841,7 +2888,7 @@
       </c>
       <c r="U23" s="1"/>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="22" t="s">
         <v>45</v>
       </c>
@@ -2860,7 +2907,7 @@
       </c>
       <c r="G24" s="26">
         <f t="shared" si="2"/>
-        <v>2400</v>
+        <v>369</v>
       </c>
       <c r="H24" s="22">
         <f t="shared" si="12"/>
@@ -2870,27 +2917,27 @@
       <c r="J24" s="30"/>
       <c r="K24">
         <f t="shared" ca="1" si="7"/>
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="8"/>
-        <v>2.0900000000000034</v>
+        <v>1.3300000000000054</v>
       </c>
       <c r="M24">
         <f t="shared" ca="1" si="9"/>
-        <v>2.8399999999999892</v>
+        <v>2.7099999999999937</v>
       </c>
       <c r="N24">
         <f t="shared" ca="1" si="4"/>
-        <v>1.0899999999999892</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="O24">
         <f t="shared" ca="1" si="5"/>
-        <v>1.6000000000000085</v>
+        <v>2.1999999999999886</v>
       </c>
       <c r="P24">
         <f t="shared" ca="1" si="6"/>
-        <v>1.0699999999999932</v>
+        <v>1.4299999999999926</v>
       </c>
       <c r="R24" s="25">
         <v>-6</v>
@@ -2903,7 +2950,7 @@
       </c>
       <c r="U24" s="1"/>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>36</v>
       </c>
@@ -2922,7 +2969,7 @@
       </c>
       <c r="G25" s="26">
         <f t="shared" si="2"/>
-        <v>372</v>
+        <v>57</v>
       </c>
       <c r="H25" s="22">
         <f t="shared" si="12"/>
@@ -2934,27 +2981,27 @@
       </c>
       <c r="K25">
         <f t="shared" ca="1" si="7"/>
-        <v>5.26</v>
+        <v>3.06</v>
       </c>
       <c r="L25">
         <f t="shared" ca="1" si="8"/>
-        <v>5.5500000000000114</v>
+        <v>2.8999999999999773</v>
       </c>
       <c r="M25">
         <f t="shared" ca="1" si="9"/>
-        <v>8.0999999999999943</v>
+        <v>3.0499999999999829</v>
       </c>
       <c r="N25">
         <f t="shared" ca="1" si="4"/>
-        <v>5.1999999999999886</v>
+        <v>2.2000000000000171</v>
       </c>
       <c r="O25">
         <f t="shared" ca="1" si="5"/>
-        <v>2.9500000000000171</v>
+        <v>4.4000000000000057</v>
       </c>
       <c r="P25">
         <f t="shared" ca="1" si="6"/>
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="R25" s="25">
         <v>-149</v>
@@ -2967,7 +3014,7 @@
       </c>
       <c r="U25" s="1"/>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>42</v>
       </c>
@@ -2986,7 +3033,7 @@
       </c>
       <c r="G26" s="26">
         <f t="shared" si="2"/>
-        <v>390</v>
+        <v>60</v>
       </c>
       <c r="H26" s="22">
         <f t="shared" si="12"/>
@@ -2996,7 +3043,7 @@
       <c r="J26" s="30"/>
       <c r="K26">
         <f t="shared" ca="1" si="7"/>
-        <v>3.06</v>
+        <v>1.95</v>
       </c>
       <c r="L26">
         <f t="shared" ca="1" si="8"/>
@@ -3004,19 +3051,19 @@
       </c>
       <c r="M26">
         <f t="shared" ca="1" si="9"/>
-        <v>3.9599999999999937</v>
+        <v>2.4200000000000017</v>
       </c>
       <c r="N26">
         <f t="shared" ca="1" si="4"/>
-        <v>3.6400000000000006</v>
+        <v>1.5799999999999983</v>
       </c>
       <c r="O26">
         <f t="shared" ca="1" si="5"/>
-        <v>3.3599999999999994</v>
+        <v>1.3799999999999955</v>
       </c>
       <c r="P26">
         <f t="shared" ca="1" si="6"/>
-        <v>2.0600000000000023</v>
+        <v>2.0999999999999943</v>
       </c>
       <c r="R26" s="29">
         <v>23</v>
@@ -3029,7 +3076,7 @@
       </c>
       <c r="U26" s="1"/>
     </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" s="22" t="s">
         <v>66</v>
       </c>
@@ -3048,7 +3095,7 @@
       </c>
       <c r="G27" s="26">
         <f>ROUND($C$4/(D27/E27*F27),0)</f>
-        <v>692</v>
+        <v>106</v>
       </c>
       <c r="H27" s="22">
         <f t="shared" si="12"/>
@@ -3060,27 +3107,27 @@
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="7"/>
-        <v>26.6</v>
+        <v>34.380000000000003</v>
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="8"/>
-        <v>24.599999999999909</v>
+        <v>32.5</v>
       </c>
       <c r="M27">
         <f t="shared" ca="1" si="9"/>
-        <v>24.299999999999955</v>
+        <v>37</v>
       </c>
       <c r="N27">
         <f t="shared" ca="1" si="4"/>
-        <v>19.799999999999955</v>
+        <v>26.299999999999955</v>
       </c>
       <c r="O27">
         <f t="shared" ca="1" si="5"/>
-        <v>47.799999999999955</v>
+        <v>28.600000000000136</v>
       </c>
       <c r="P27">
         <f t="shared" ca="1" si="6"/>
-        <v>16.5</v>
+        <v>47.5</v>
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="29">
@@ -3089,7 +3136,7 @@
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>39</v>
       </c>
@@ -3108,7 +3155,7 @@
       </c>
       <c r="G28" s="26">
         <f t="shared" si="2"/>
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="H28" s="22">
         <f t="shared" si="12"/>
@@ -3120,27 +3167,27 @@
       </c>
       <c r="K28">
         <f t="shared" ca="1" si="7"/>
-        <v>120.7</v>
+        <v>99.6</v>
       </c>
       <c r="L28">
         <f t="shared" ca="1" si="8"/>
-        <v>62</v>
+        <v>86.5</v>
       </c>
       <c r="M28">
         <f t="shared" ca="1" si="9"/>
-        <v>129.5</v>
+        <v>116.5</v>
       </c>
       <c r="N28">
         <f t="shared" ca="1" si="4"/>
-        <v>85</v>
+        <v>54.5</v>
       </c>
       <c r="O28">
         <f t="shared" ca="1" si="5"/>
-        <v>228.5</v>
+        <v>134</v>
       </c>
       <c r="P28">
         <f t="shared" ca="1" si="6"/>
-        <v>98.5</v>
+        <v>106.5</v>
       </c>
       <c r="R28" s="25">
         <v>-6</v>
@@ -3153,7 +3200,7 @@
       </c>
       <c r="U28" s="1"/>
     </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" s="22" t="s">
         <v>72</v>
       </c>
@@ -3172,7 +3219,7 @@
       </c>
       <c r="G29" s="26">
         <f>ROUND($C$4/(D29/E29*F29),0)</f>
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="H29" s="22">
         <f t="shared" si="12"/>
@@ -3181,27 +3228,27 @@
       <c r="I29" s="24"/>
       <c r="K29">
         <f t="shared" ca="1" si="7"/>
-        <v>26.56</v>
+        <v>30.28</v>
       </c>
       <c r="L29">
         <f t="shared" ca="1" si="8"/>
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M29">
         <f t="shared" ca="1" si="9"/>
-        <v>23.799999999999955</v>
+        <v>37.599999999999909</v>
       </c>
       <c r="N29">
         <f t="shared" ca="1" si="4"/>
-        <v>33</v>
+        <v>39.399999999999864</v>
       </c>
       <c r="O29">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>27.399999999999864</v>
       </c>
       <c r="P29">
         <f t="shared" ca="1" si="6"/>
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="R29" s="1"/>
       <c r="S29" s="25">
@@ -3210,7 +3257,7 @@
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="22" t="s">
         <v>54</v>
       </c>
@@ -3229,7 +3276,7 @@
       </c>
       <c r="G30" s="26">
         <f t="shared" ref="G30:G43" si="14">ROUND($C$4/(D30/E30*F30),0)</f>
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="H30" s="22">
         <f t="shared" si="12"/>
@@ -3238,27 +3285,27 @@
       <c r="I30" s="24"/>
       <c r="K30">
         <f t="shared" ca="1" si="7"/>
-        <v>87.2</v>
+        <v>172.6</v>
       </c>
       <c r="L30">
         <f t="shared" ca="1" si="8"/>
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="M30">
         <f t="shared" ca="1" si="9"/>
-        <v>95</v>
+        <v>227</v>
       </c>
       <c r="N30">
         <f t="shared" ca="1" si="4"/>
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="O30">
         <f t="shared" ca="1" si="5"/>
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="P30">
         <f t="shared" ca="1" si="6"/>
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="R30" s="25">
         <v>-31</v>
@@ -3269,7 +3316,7 @@
       </c>
       <c r="U30" s="1"/>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="22" t="s">
         <v>70</v>
       </c>
@@ -3288,7 +3335,7 @@
       </c>
       <c r="G31" s="26">
         <f>ROUND($C$4/(D31/E31*F31),0)</f>
-        <v>1189</v>
+        <v>183</v>
       </c>
       <c r="H31" s="22">
         <f t="shared" si="12"/>
@@ -3300,27 +3347,27 @@
       </c>
       <c r="K31">
         <f t="shared" ca="1" si="7"/>
-        <v>13.04</v>
+        <v>4.32</v>
       </c>
       <c r="L31">
         <f t="shared" ca="1" si="8"/>
-        <v>8.5</v>
+        <v>5.9000000000000909</v>
       </c>
       <c r="M31">
         <f t="shared" ca="1" si="9"/>
-        <v>21.299999999999955</v>
+        <v>2.2999999999999545</v>
       </c>
       <c r="N31">
         <f t="shared" ca="1" si="4"/>
-        <v>9.6999999999999886</v>
+        <v>2.9000000000000909</v>
       </c>
       <c r="O31">
         <f t="shared" ca="1" si="5"/>
-        <v>17.5</v>
+        <v>3.7000000000000455</v>
       </c>
       <c r="P31">
         <f t="shared" ca="1" si="6"/>
-        <v>8.1999999999999886</v>
+        <v>6.7999999999999545</v>
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="29">
@@ -3331,7 +3378,7 @@
       </c>
       <c r="U31" s="1"/>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B32" s="22" t="s">
         <v>58</v>
       </c>
@@ -3350,7 +3397,7 @@
       </c>
       <c r="G32" s="26">
         <f t="shared" si="14"/>
-        <v>273</v>
+        <v>42</v>
       </c>
       <c r="H32" s="22">
         <f t="shared" si="12"/>
@@ -3362,27 +3409,27 @@
       </c>
       <c r="K32">
         <f t="shared" ca="1" si="7"/>
-        <v>70.44</v>
+        <v>74.040000000000006</v>
       </c>
       <c r="L32">
         <f t="shared" ca="1" si="8"/>
-        <v>76</v>
+        <v>87.800000000000182</v>
       </c>
       <c r="M32">
         <f t="shared" ca="1" si="9"/>
-        <v>92</v>
+        <v>46.199999999999818</v>
       </c>
       <c r="N32">
         <f t="shared" ca="1" si="4"/>
-        <v>108.19999999999982</v>
+        <v>79.400000000000091</v>
       </c>
       <c r="O32">
         <f t="shared" ca="1" si="5"/>
-        <v>41.800000000000182</v>
+        <v>69.800000000000182</v>
       </c>
       <c r="P32">
         <f t="shared" ca="1" si="6"/>
-        <v>34.199999999999818</v>
+        <v>87</v>
       </c>
       <c r="R32" s="25">
         <v>-68</v>
@@ -3393,7 +3440,7 @@
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B33" s="22" t="s">
         <v>63</v>
       </c>
@@ -3412,7 +3459,7 @@
       </c>
       <c r="G33" s="26">
         <f t="shared" si="14"/>
-        <v>1560</v>
+        <v>240</v>
       </c>
       <c r="H33" s="22">
         <f t="shared" si="12"/>
@@ -3421,27 +3468,27 @@
       <c r="I33" s="24"/>
       <c r="K33">
         <f t="shared" ca="1" si="7"/>
-        <v>3.35</v>
+        <v>4.97</v>
       </c>
       <c r="L33">
         <f t="shared" ca="1" si="8"/>
-        <v>2.2000000000000028</v>
+        <v>3</v>
       </c>
       <c r="M33">
         <f t="shared" ca="1" si="9"/>
-        <v>3.8000000000000114</v>
+        <v>6.3500000000000085</v>
       </c>
       <c r="N33">
         <f t="shared" ca="1" si="4"/>
-        <v>3.1500000000000057</v>
+        <v>6.2999999999999972</v>
       </c>
       <c r="O33">
         <f t="shared" ca="1" si="5"/>
-        <v>4.6499999999999915</v>
+        <v>3.5999999999999943</v>
       </c>
       <c r="P33">
         <f t="shared" ca="1" si="6"/>
-        <v>2.9499999999999886</v>
+        <v>5.5999999999999943</v>
       </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
@@ -3450,7 +3497,7 @@
       </c>
       <c r="U33" s="1"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B34" s="22" t="s">
         <v>49</v>
       </c>
@@ -3469,7 +3516,7 @@
       </c>
       <c r="G34" s="26">
         <f t="shared" si="14"/>
-        <v>2461</v>
+        <v>379</v>
       </c>
       <c r="H34" s="22">
         <f t="shared" si="12"/>
@@ -3481,27 +3528,27 @@
       </c>
       <c r="K34">
         <f t="shared" ca="1" si="7"/>
-        <v>6.62</v>
+        <v>14.96</v>
       </c>
       <c r="L34">
         <f t="shared" ca="1" si="8"/>
-        <v>3.8999999999999773</v>
+        <v>12</v>
       </c>
       <c r="M34">
         <f t="shared" ca="1" si="9"/>
-        <v>6.8000000000000114</v>
+        <v>17.75</v>
       </c>
       <c r="N34">
         <f t="shared" ca="1" si="4"/>
-        <v>4.4499999999999886</v>
+        <v>11.050000000000011</v>
       </c>
       <c r="O34">
         <f t="shared" ca="1" si="5"/>
-        <v>10.450000000000045</v>
+        <v>14.349999999999966</v>
       </c>
       <c r="P34">
         <f t="shared" ca="1" si="6"/>
-        <v>7.5</v>
+        <v>19.649999999999977</v>
       </c>
       <c r="R34" s="29">
         <v>342</v>
@@ -3514,7 +3561,7 @@
       </c>
       <c r="U34" s="1"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B35" s="22" t="s">
         <v>67</v>
       </c>
@@ -3533,7 +3580,7 @@
       </c>
       <c r="G35" s="26">
         <f>ROUND($C$4/(D35/E35*F35),0)</f>
-        <v>1381</v>
+        <v>212</v>
       </c>
       <c r="H35" s="22">
         <f t="shared" si="12"/>
@@ -3545,27 +3592,27 @@
       </c>
       <c r="K35">
         <f t="shared" ca="1" si="7"/>
-        <v>0.89</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L35">
         <f t="shared" ca="1" si="8"/>
-        <v>0.75500000000000256</v>
+        <v>1.7199999999999989</v>
       </c>
       <c r="M35">
         <f t="shared" ca="1" si="9"/>
-        <v>0.875</v>
+        <v>1.3599999999999994</v>
       </c>
       <c r="N35">
         <f t="shared" ca="1" si="4"/>
-        <v>0.91000000000000369</v>
+        <v>0.67999999999999972</v>
       </c>
       <c r="O35">
         <f t="shared" ca="1" si="5"/>
-        <v>1.0200000000000031</v>
+        <v>0.91000000000000369</v>
       </c>
       <c r="P35">
         <f t="shared" ca="1" si="6"/>
-        <v>0.88499999999999801</v>
+        <v>0.84999999999999432</v>
       </c>
       <c r="R35" s="1"/>
       <c r="S35" s="25">
@@ -3574,7 +3621,7 @@
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
@@ -3593,7 +3640,7 @@
       </c>
       <c r="G36" s="26">
         <f t="shared" si="14"/>
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="H36" s="22">
         <f t="shared" si="12"/>
@@ -3603,27 +3650,27 @@
       <c r="J36" s="30"/>
       <c r="K36">
         <f t="shared" ca="1" si="7"/>
-        <v>3.39</v>
+        <v>2.98</v>
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="8"/>
-        <v>3.5600000000000023</v>
+        <v>2.6000000000000227</v>
       </c>
       <c r="M36">
         <f t="shared" ca="1" si="9"/>
-        <v>4.5399999999999636</v>
+        <v>2.4399999999999977</v>
       </c>
       <c r="N36">
         <f t="shared" ca="1" si="4"/>
-        <v>2.5</v>
+        <v>2.2200000000000273</v>
       </c>
       <c r="O36">
         <f t="shared" ca="1" si="5"/>
-        <v>3.3799999999999955</v>
+        <v>4.8600000000000136</v>
       </c>
       <c r="P36">
         <f t="shared" ca="1" si="6"/>
-        <v>2.9800000000000182</v>
+        <v>2.7800000000000296</v>
       </c>
       <c r="R36" s="29">
         <v>32</v>
@@ -3636,7 +3683,7 @@
       </c>
       <c r="U36" s="1"/>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B37" s="22" t="s">
         <v>61</v>
       </c>
@@ -3655,7 +3702,7 @@
       </c>
       <c r="G37" s="26">
         <f t="shared" si="14"/>
-        <v>353</v>
+        <v>54</v>
       </c>
       <c r="H37" s="22">
         <f t="shared" si="12"/>
@@ -3667,27 +3714,27 @@
       </c>
       <c r="K37">
         <f t="shared" ca="1" si="7"/>
-        <v>22.6</v>
+        <v>58.4</v>
       </c>
       <c r="L37">
         <f t="shared" ca="1" si="8"/>
-        <v>8.3999999999999773</v>
+        <v>17.600000000000023</v>
       </c>
       <c r="M37">
         <f t="shared" ca="1" si="9"/>
-        <v>26.399999999999977</v>
+        <v>35.799999999999955</v>
       </c>
       <c r="N37">
         <f t="shared" ca="1" si="4"/>
-        <v>17.799999999999955</v>
+        <v>176</v>
       </c>
       <c r="O37">
         <f t="shared" ca="1" si="5"/>
-        <v>24.799999999999955</v>
+        <v>24</v>
       </c>
       <c r="P37">
         <f t="shared" ca="1" si="6"/>
-        <v>35.600000000000023</v>
+        <v>38.599999999999909</v>
       </c>
       <c r="R37" s="25">
         <v>-89</v>
@@ -3698,7 +3745,7 @@
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B38" s="22" t="s">
         <v>65</v>
       </c>
@@ -3717,7 +3764,7 @@
       </c>
       <c r="G38" s="26">
         <f>ROUND($C$4/(D38/E38*F38),0)</f>
-        <v>1114</v>
+        <v>171</v>
       </c>
       <c r="H38" s="22">
         <f t="shared" si="12"/>
@@ -3726,27 +3773,27 @@
       <c r="I38" s="24"/>
       <c r="K38">
         <f t="shared" ca="1" si="7"/>
-        <v>28489.22</v>
+        <v>438.04</v>
       </c>
       <c r="L38">
         <f t="shared" ca="1" si="8"/>
-        <v>-334197.69400000002</v>
+        <v>2.100000000000013E-2</v>
       </c>
       <c r="M38">
         <f t="shared" ca="1" si="9"/>
-        <v>399941.766</v>
+        <v>-41638.828500000003</v>
       </c>
       <c r="N38">
         <f t="shared" ca="1" si="4"/>
-        <v>76702</v>
+        <v>-42003.820500000002</v>
       </c>
       <c r="O38">
         <f t="shared" ca="1" si="5"/>
-        <v>2.100000000000013E-2</v>
+        <v>3.2000000000000028E-2</v>
       </c>
       <c r="P38">
         <f t="shared" ca="1" si="6"/>
-        <v>1.8000000000000016E-2</v>
+        <v>85832.812999999995</v>
       </c>
       <c r="R38" s="29">
         <v>71</v>
@@ -3755,7 +3802,7 @@
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B39" s="22" t="s">
         <v>71</v>
       </c>
@@ -3774,7 +3821,7 @@
       </c>
       <c r="G39" s="26">
         <f>ROUND($C$4/(D39/E39*F39),0)</f>
-        <v>839</v>
+        <v>129</v>
       </c>
       <c r="H39" s="22">
         <f t="shared" si="12"/>
@@ -3783,27 +3830,27 @@
       <c r="I39" s="24"/>
       <c r="K39">
         <f t="shared" ca="1" si="7"/>
-        <v>8.02</v>
+        <v>13.45</v>
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="8"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M39">
         <f t="shared" ca="1" si="9"/>
-        <v>5.9499999999999886</v>
+        <v>20.799999999999955</v>
       </c>
       <c r="N39">
         <f t="shared" ca="1" si="4"/>
-        <v>5.8999999999999773</v>
+        <v>11.399999999999977</v>
       </c>
       <c r="O39">
         <f t="shared" ca="1" si="5"/>
-        <v>8.5500000000000114</v>
+        <v>11.699999999999932</v>
       </c>
       <c r="P39">
         <f t="shared" ca="1" si="6"/>
-        <v>6.6999999999999886</v>
+        <v>14.350000000000023</v>
       </c>
       <c r="R39" s="25">
         <v>-9</v>
@@ -3814,7 +3861,7 @@
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B40" s="22" t="s">
         <v>69</v>
       </c>
@@ -3833,7 +3880,7 @@
       </c>
       <c r="G40" s="26">
         <f>ROUND($C$4/(D40/E40*F40),0)</f>
-        <v>347</v>
+        <v>53</v>
       </c>
       <c r="H40" s="22">
         <f t="shared" si="12"/>
@@ -3845,27 +3892,27 @@
       </c>
       <c r="K40">
         <f t="shared" ca="1" si="7"/>
-        <v>25.44</v>
+        <v>41.44</v>
       </c>
       <c r="L40">
         <f t="shared" ca="1" si="8"/>
-        <v>11</v>
+        <v>45.399999999999977</v>
       </c>
       <c r="M40">
         <f t="shared" ca="1" si="9"/>
-        <v>45</v>
+        <v>66.799999999999955</v>
       </c>
       <c r="N40">
         <f t="shared" ca="1" si="4"/>
-        <v>15.799999999999955</v>
+        <v>23.799999999999955</v>
       </c>
       <c r="O40">
         <f t="shared" ca="1" si="5"/>
-        <v>24.399999999999977</v>
+        <v>33</v>
       </c>
       <c r="P40">
         <f t="shared" ca="1" si="6"/>
-        <v>31</v>
+        <v>38.200000000000045</v>
       </c>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
@@ -3874,9 +3921,9 @@
       </c>
       <c r="U40" s="1"/>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C41" s="22">
         <v>690</v>
@@ -3902,30 +3949,30 @@
       <c r="I41" s="24"/>
       <c r="K41">
         <f t="shared" ca="1" si="7"/>
-        <v>0.36</v>
+        <v>9192.77</v>
       </c>
       <c r="L41">
         <f t="shared" ca="1" si="8"/>
-        <v>0.26999999999999957</v>
+        <v>0.34499999999999886</v>
       </c>
       <c r="M41">
         <f t="shared" ca="1" si="9"/>
-        <v>0.2900000000000027</v>
+        <v>46022.75</v>
       </c>
       <c r="N41">
         <f t="shared" ca="1" si="4"/>
-        <v>0.30999999999999872</v>
+        <v>0.32499999999999929</v>
       </c>
       <c r="O41">
         <f t="shared" ca="1" si="5"/>
-        <v>0.49499999999999744</v>
+        <v>0.42499999999999716</v>
       </c>
       <c r="P41">
         <f t="shared" ca="1" si="6"/>
-        <v>0.45000000000000284</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B42" s="22" t="s">
         <v>60</v>
       </c>
@@ -3944,7 +3991,7 @@
       </c>
       <c r="G42" s="26">
         <f t="shared" si="14"/>
-        <v>945</v>
+        <v>145</v>
       </c>
       <c r="H42" s="22">
         <f t="shared" si="12"/>
@@ -3953,27 +4000,27 @@
       <c r="I42" s="24"/>
       <c r="K42">
         <f t="shared" ca="1" si="7"/>
-        <v>0.76</v>
+        <v>1.24</v>
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="8"/>
-        <v>0.64999999999999858</v>
+        <v>1.0500000000000043</v>
       </c>
       <c r="M42">
         <f t="shared" ca="1" si="9"/>
-        <v>0.82999999999999829</v>
+        <v>1.5150000000000006</v>
       </c>
       <c r="N42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.64999999999999858</v>
+        <v>0.78000000000000114</v>
       </c>
       <c r="O42">
         <f t="shared" ca="1" si="5"/>
-        <v>0.79999999999999716</v>
+        <v>1.1599999999999966</v>
       </c>
       <c r="P42">
         <f t="shared" ca="1" si="6"/>
-        <v>0.89000000000000057</v>
+        <v>1.7000000000000028</v>
       </c>
       <c r="R42" s="25">
         <v>-18</v>
@@ -3986,7 +4033,7 @@
       </c>
       <c r="U42" s="1"/>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B43" s="22" t="s">
         <v>62</v>
       </c>
@@ -4005,7 +4052,7 @@
       </c>
       <c r="G43" s="26">
         <f t="shared" si="14"/>
-        <v>1300</v>
+        <v>200</v>
       </c>
       <c r="H43" s="22">
         <f t="shared" si="12"/>
@@ -4014,27 +4061,27 @@
       <c r="I43" s="24"/>
       <c r="K43">
         <f t="shared" ca="1" si="7"/>
-        <v>10.119999999999999</v>
+        <v>22.48</v>
       </c>
       <c r="L43">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B43&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B43&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>7</v>
+        <v>18.299999999999955</v>
       </c>
       <c r="M43">
         <f t="shared" ca="1" si="9"/>
-        <v>9.2999999999999545</v>
+        <v>30.299999999999955</v>
       </c>
       <c r="N43">
         <f t="shared" ca="1" si="4"/>
-        <v>12.399999999999977</v>
+        <v>17</v>
       </c>
       <c r="O43">
         <f t="shared" ca="1" si="5"/>
-        <v>10.200000000000045</v>
+        <v>19.5</v>
       </c>
       <c r="P43">
         <f t="shared" ca="1" si="6"/>
-        <v>11.700000000000045</v>
+        <v>27.299999999999955</v>
       </c>
       <c r="R43" s="25">
         <v>-114</v>
@@ -4045,7 +4092,7 @@
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B44" s="22" t="s">
         <v>52</v>
       </c>
@@ -4064,7 +4111,7 @@
       </c>
       <c r="G44" s="26">
         <f t="shared" ref="G44:G49" si="15">ROUND($C$4/(D44/E44*F44),0)</f>
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="H44" s="22">
         <f t="shared" si="12"/>
@@ -4073,27 +4120,27 @@
       <c r="I44" s="24"/>
       <c r="K44">
         <f t="shared" ca="1" si="7"/>
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="L44">
         <f t="shared" ca="1" si="8"/>
-        <v>2.6800000000000068</v>
+        <v>1.6199999999999903</v>
       </c>
       <c r="M44">
         <f t="shared" ca="1" si="9"/>
-        <v>2.7000000000000028</v>
+        <v>1.7999999999999972</v>
       </c>
       <c r="N44">
         <f t="shared" ca="1" si="4"/>
-        <v>1.1600000000000108</v>
+        <v>1.4399999999999977</v>
       </c>
       <c r="O44">
         <f t="shared" ca="1" si="5"/>
-        <v>1.3999999999999915</v>
+        <v>2.5799999999999983</v>
       </c>
       <c r="P44">
         <f t="shared" ca="1" si="6"/>
-        <v>1.5999999999999943</v>
+        <v>2.2199999999999989</v>
       </c>
       <c r="R44" s="29">
         <v>7</v>
@@ -4104,7 +4151,7 @@
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B45" s="22" t="s">
         <v>74</v>
       </c>
@@ -4123,7 +4170,7 @@
       </c>
       <c r="G45" s="26">
         <f t="shared" si="15"/>
-        <v>223</v>
+        <v>34</v>
       </c>
       <c r="H45" s="22">
         <f t="shared" ref="H45:H47" si="16">ROUND(D45/E45,0)</f>
@@ -4132,27 +4179,27 @@
       <c r="I45" s="24"/>
       <c r="K45">
         <f t="shared" ca="1" si="7"/>
-        <v>22.16</v>
+        <v>25.04</v>
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="8"/>
-        <v>22.399999999999864</v>
+        <v>19.400000000000091</v>
       </c>
       <c r="M45">
         <f t="shared" ca="1" si="9"/>
-        <v>30.599999999999909</v>
+        <v>25.799999999999955</v>
       </c>
       <c r="N45">
         <f t="shared" ca="1" si="4"/>
-        <v>11.200000000000045</v>
+        <v>17.599999999999909</v>
       </c>
       <c r="O45">
         <f t="shared" ca="1" si="5"/>
-        <v>23.400000000000091</v>
+        <v>24.200000000000045</v>
       </c>
       <c r="P45">
         <f t="shared" ca="1" si="6"/>
-        <v>23.200000000000045</v>
+        <v>38.200000000000045</v>
       </c>
       <c r="R45" s="1"/>
       <c r="S45" s="25">
@@ -4163,9 +4210,9 @@
       </c>
       <c r="U45" s="1"/>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B46" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C46" s="22">
         <v>5.1400000000000001E-2</v>
@@ -4182,7 +4229,7 @@
       </c>
       <c r="G46" s="26">
         <f t="shared" si="15"/>
-        <v>306</v>
+        <v>47</v>
       </c>
       <c r="H46" s="22">
         <f t="shared" si="16"/>
@@ -4194,34 +4241,34 @@
       </c>
       <c r="K46">
         <f ca="1">ROUND(AVERAGE(L46:P46),4)</f>
-        <v>2.46E-2</v>
+        <v>2.01E-2</v>
       </c>
       <c r="L46">
         <f t="shared" ca="1" si="8"/>
-        <v>3.0799999999999939E-2</v>
+        <v>2.5799999999999934E-2</v>
       </c>
       <c r="M46">
         <f t="shared" ca="1" si="9"/>
-        <v>1.8400000000000083E-2</v>
+        <v>1.4000000000000012E-2</v>
       </c>
       <c r="N46">
         <f t="shared" ca="1" si="4"/>
-        <v>2.2399999999999975E-2</v>
+        <v>2.1100000000000008E-2</v>
       </c>
       <c r="O46">
         <f t="shared" ca="1" si="5"/>
-        <v>3.1000000000000028E-2</v>
+        <v>1.7700000000000049E-2</v>
       </c>
       <c r="P46">
         <f t="shared" ca="1" si="6"/>
-        <v>2.0199999999999996E-2</v>
+        <v>2.2100000000000009E-2</v>
       </c>
       <c r="R46" s="1"/>
       <c r="S46" s="22"/>
       <c r="T46" s="22"/>
       <c r="U46" s="1"/>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>44</v>
       </c>
@@ -4240,7 +4287,7 @@
       </c>
       <c r="G47" s="26">
         <f t="shared" si="15"/>
-        <v>1753</v>
+        <v>270</v>
       </c>
       <c r="H47" s="22">
         <f t="shared" si="16"/>
@@ -4252,27 +4299,27 @@
       </c>
       <c r="K47">
         <f t="shared" ca="1" si="7"/>
-        <v>8.2899999999999991</v>
+        <v>8.19</v>
       </c>
       <c r="L47">
         <f t="shared" ca="1" si="8"/>
-        <v>6.8500000000000227</v>
+        <v>5.1000000000000227</v>
       </c>
       <c r="M47">
         <f t="shared" ca="1" si="9"/>
-        <v>6.3499999999999659</v>
+        <v>8.6499999999999773</v>
       </c>
       <c r="N47">
         <f t="shared" ca="1" si="4"/>
-        <v>3.6500000000000341</v>
+        <v>6.3999999999999773</v>
       </c>
       <c r="O47">
         <f t="shared" ca="1" si="5"/>
-        <v>7.8000000000000114</v>
+        <v>9.8000000000000114</v>
       </c>
       <c r="P47">
         <f t="shared" ca="1" si="6"/>
-        <v>16.800000000000011</v>
+        <v>11</v>
       </c>
       <c r="R47" s="1"/>
       <c r="S47" s="29">
@@ -4281,9 +4328,9 @@
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B48" s="22" t="s">
         <v>59</v>
@@ -4303,7 +4350,7 @@
       </c>
       <c r="G48" s="26">
         <f t="shared" si="15"/>
-        <v>5756</v>
+        <v>886</v>
       </c>
       <c r="H48" s="22">
         <f>ROUND(D48/E48,0)</f>
@@ -4315,27 +4362,27 @@
       </c>
       <c r="K48">
         <f t="shared" ca="1" si="7"/>
-        <v>2.5499999999999998</v>
+        <v>1.72</v>
       </c>
       <c r="L48">
         <f t="shared" ca="1" si="8"/>
-        <v>2.355000000000004</v>
+        <v>1.4399999999999977</v>
       </c>
       <c r="M48">
         <f t="shared" ca="1" si="9"/>
-        <v>4.125</v>
+        <v>1.644999999999996</v>
       </c>
       <c r="N48">
         <f t="shared" ca="1" si="4"/>
-        <v>0.98999999999999488</v>
+        <v>1.7000000000000028</v>
       </c>
       <c r="O48">
         <f t="shared" ca="1" si="5"/>
-        <v>3.5649999999999977</v>
+        <v>1.7900000000000063</v>
       </c>
       <c r="P48">
         <f t="shared" ca="1" si="6"/>
-        <v>1.7299999999999898</v>
+        <v>2.0150000000000006</v>
       </c>
       <c r="R48" s="29">
         <v>19</v>
@@ -4346,9 +4393,9 @@
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
     </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C49" s="22">
         <v>46.6</v>
@@ -4365,7 +4412,7 @@
       </c>
       <c r="G49" s="26">
         <f t="shared" si="15"/>
-        <v>335</v>
+        <v>52</v>
       </c>
       <c r="H49" s="22">
         <f>ROUND(D49/E49,0)</f>
@@ -4377,34 +4424,34 @@
       </c>
       <c r="K49">
         <f t="shared" ca="1" si="7"/>
-        <v>41.5</v>
+        <v>35.4</v>
       </c>
       <c r="L49">
         <f t="shared" ca="1" si="8"/>
-        <v>73</v>
+        <v>19.5</v>
       </c>
       <c r="M49">
         <f t="shared" ca="1" si="9"/>
-        <v>33.5</v>
+        <v>52.5</v>
       </c>
       <c r="N49">
         <f t="shared" ca="1" si="4"/>
-        <v>48</v>
+        <v>20.5</v>
       </c>
       <c r="O49">
         <f t="shared" ca="1" si="5"/>
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="P49">
         <f t="shared" ca="1" si="6"/>
-        <v>28</v>
+        <v>51.5</v>
       </c>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
     </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>37</v>
       </c>
@@ -4423,7 +4470,7 @@
       </c>
       <c r="G50" s="26">
         <f t="shared" ref="G50:G53" si="18">ROUND($C$4/(D50/E50*F50),0)</f>
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="H50" s="22">
         <f t="shared" ref="H50:H53" si="19">ROUND(D50/E50,0)</f>
@@ -4435,27 +4482,27 @@
       </c>
       <c r="K50">
         <f t="shared" ca="1" si="7"/>
-        <v>116.3</v>
+        <v>91.7</v>
       </c>
       <c r="L50">
         <f t="shared" ca="1" si="8"/>
-        <v>79</v>
+        <v>118.5</v>
       </c>
       <c r="M50">
         <f t="shared" ca="1" si="9"/>
-        <v>140.5</v>
+        <v>103</v>
       </c>
       <c r="N50">
         <f t="shared" ca="1" si="4"/>
-        <v>96</v>
+        <v>53.5</v>
       </c>
       <c r="O50">
         <f t="shared" ca="1" si="5"/>
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="P50">
         <f t="shared" ca="1" si="6"/>
-        <v>76</v>
+        <v>72.5</v>
       </c>
       <c r="R50" s="1">
         <v>-97</v>
@@ -4468,7 +4515,7 @@
       </c>
       <c r="U50" s="1"/>
     </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B51" s="27" t="s">
         <v>73</v>
       </c>
@@ -4487,7 +4534,7 @@
       </c>
       <c r="G51" s="26">
         <f t="shared" si="18"/>
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="H51" s="22">
         <f t="shared" si="19"/>
@@ -4503,7 +4550,7 @@
       </c>
       <c r="U51" s="1"/>
     </row>
-    <row r="52" spans="2:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="27" t="s">
         <v>11</v>
       </c>
@@ -4522,7 +4569,7 @@
       </c>
       <c r="G52" s="26">
         <f t="shared" si="18"/>
-        <v>156</v>
+        <v>24</v>
       </c>
       <c r="H52" s="22">
         <f t="shared" si="19"/>
@@ -4540,9 +4587,9 @@
       </c>
       <c r="U52" s="1"/>
     </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B53" s="27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C53" s="22">
         <v>550</v>
@@ -4559,16 +4606,16 @@
       </c>
       <c r="G53" s="26">
         <f t="shared" si="18"/>
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="H53" s="22">
         <f t="shared" si="19"/>
         <v>55</v>
       </c>
       <c r="I53" s="24"/>
-      <c r="M53">
+      <c r="M53" t="e">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/futures/markets/forts/securities/"&amp;B53&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/futures/markets/forts/securities/"&amp;B53&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>852</v>
+        <v>#VALUE!</v>
       </c>
       <c r="R53" s="29">
         <v>459</v>
@@ -4585,4 +4632,405 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:U16"/>
+  <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C2" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="34">
+        <v>46121</v>
+      </c>
+      <c r="E3" s="34">
+        <v>46122</v>
+      </c>
+      <c r="F3" s="34">
+        <v>46127</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46</v>
+      </c>
+      <c r="E4" s="1">
+        <v>157</v>
+      </c>
+      <c r="F4" s="1">
+        <v>91</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="1">
+        <v>50</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="1">
+        <v>60</v>
+      </c>
+      <c r="E6" s="1">
+        <v>44</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="1">
+        <v>61</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>73</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1">
+        <v>84</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>120</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <v>156</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C2:U2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/calc.xlsx
+++ b/calc.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -544,10 +544,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1834,23 +1834,23 @@
     <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="L6" s="5" t="str">
         <f ca="1">TEXT(L7,"ддд")</f>
-        <v>Вт</v>
+        <v>Ср</v>
       </c>
       <c r="M6" s="5" t="str">
         <f ca="1">TEXT(M7,"ддд")</f>
-        <v>Пн</v>
+        <v>Вт</v>
       </c>
       <c r="N6" s="5" t="str">
         <f t="shared" ref="N6:P6" ca="1" si="0">TEXT(N7,"ддд")</f>
-        <v>Пт</v>
+        <v>Пн</v>
       </c>
       <c r="O6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Чт</v>
+        <v>Пт</v>
       </c>
       <c r="P6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Ср</v>
+        <v>Чт</v>
       </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.25">
@@ -1884,23 +1884,23 @@
       </c>
       <c r="L7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-1, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-14</v>
+        <v>2026-04-15</v>
       </c>
       <c r="M7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-2, "ГГГГ-ММ-ДД")</f>
+        <v>2026-04-14</v>
+      </c>
+      <c r="N7" s="1" t="str">
+        <f ca="1">TEXT(TODAY()-3, "ГГГГ-ММ-ДД")</f>
         <v>2026-04-13</v>
-      </c>
-      <c r="N7" s="1" t="str">
-        <f ca="1">TEXT(TODAY()-5, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-10</v>
       </c>
       <c r="O7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-6, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="P7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-7, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="R7" s="28">
         <v>45566</v>
@@ -1946,27 +1946,27 @@
       </c>
       <c r="K8">
         <f ca="1">ROUND(AVERAGE(L8:P8),2)</f>
-        <v>9339.66</v>
+        <v>7075.15</v>
       </c>
       <c r="L8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>42327.093999999997</v>
+        <v>14203.084000000001</v>
       </c>
       <c r="M8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>-34261.775999999998</v>
+        <v>42327.093999999997</v>
       </c>
       <c r="N8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>13106.898999999999</v>
+        <v>-34261.775999999998</v>
       </c>
       <c r="O8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.42900000000000027</v>
+        <v>13106.898999999999</v>
       </c>
       <c r="P8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>25525.673999999999</v>
+        <v>0.42900000000000027</v>
       </c>
       <c r="R8" s="29">
         <v>54</v>
@@ -2010,27 +2010,27 @@
       </c>
       <c r="K9">
         <f ca="1">ROUND(AVERAGE(L9:P9),2)</f>
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="L9">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.92000000000000171</v>
+        <v>1.7100000000000009</v>
       </c>
       <c r="M9">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.87000000000000455</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="N9">
         <f t="shared" ref="N9:N50" ca="1" si="4">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.0800000000000054</v>
+        <v>0.87000000000000455</v>
       </c>
       <c r="O9">
         <f t="shared" ref="O9:O50" ca="1" si="5">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.5799999999999983</v>
+        <v>1.0800000000000054</v>
       </c>
       <c r="P9">
         <f t="shared" ref="P9:P50" ca="1" si="6">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.7999999999999972</v>
+        <v>1.5799999999999983</v>
       </c>
       <c r="R9" s="25">
         <v>-30</v>
@@ -2071,7 +2071,7 @@
       <c r="I10" s="24"/>
       <c r="K10">
         <f ca="1">ROUND(AVERAGE(L10:P10),2)</f>
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="L10">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
@@ -2079,19 +2079,19 @@
       </c>
       <c r="M10">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.7899999999999991</v>
+        <v>0.96000000000000085</v>
       </c>
       <c r="N10">
         <f t="shared" ca="1" si="4"/>
-        <v>0.64000000000000057</v>
+        <v>1.7899999999999991</v>
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="5"/>
-        <v>0.55000000000000426</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="P10">
         <f t="shared" ca="1" si="6"/>
-        <v>0.92999999999999972</v>
+        <v>0.55000000000000426</v>
       </c>
       <c r="R10" s="29">
         <v>39</v>
@@ -2135,27 +2135,27 @@
       </c>
       <c r="K11">
         <f ca="1">ROUND(AVERAGE(L11:P11),2)</f>
-        <v>4.5</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="L11">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>5.9000000000000341</v>
+        <v>4.8000000000000114</v>
       </c>
       <c r="M11">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>3.8800000000000523</v>
+        <v>5.9000000000000341</v>
       </c>
       <c r="N11">
         <f t="shared" ca="1" si="4"/>
-        <v>3.1399999999999864</v>
+        <v>3.8800000000000523</v>
       </c>
       <c r="O11">
         <f t="shared" ca="1" si="5"/>
-        <v>6.57000000000005</v>
+        <v>3.1399999999999864</v>
       </c>
       <c r="P11">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>6.57000000000005</v>
       </c>
       <c r="R11" s="29"/>
       <c r="S11" s="29"/>
@@ -2193,27 +2193,27 @@
       </c>
       <c r="K12" s="24">
         <f ca="1">ROUND(AVERAGE(L12:P12),2)</f>
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="L12" s="24">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.94999999999999574</v>
+        <v>0.64999999999999858</v>
       </c>
       <c r="M12" s="24">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.6999999999999957</v>
+        <v>0.94999999999999574</v>
       </c>
       <c r="N12" s="24">
         <f t="shared" ca="1" si="4"/>
-        <v>1.8500000000000014</v>
+        <v>1.6999999999999957</v>
       </c>
       <c r="O12" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>1.4499999999999957</v>
+        <v>1.8500000000000014</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ca="1" si="6"/>
-        <v>0.80000000000000426</v>
+        <v>1.4499999999999957</v>
       </c>
       <c r="R12" s="29"/>
       <c r="S12" s="29"/>
@@ -2248,27 +2248,27 @@
       <c r="I13" s="23"/>
       <c r="K13">
         <f t="shared" ref="K13:K50" ca="1" si="7">ROUND(AVERAGE(L13:P13),2)</f>
-        <v>19.760000000000002</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="L13">
         <f t="shared" ref="L13:L50" ca="1" si="8">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>17.600000000000023</v>
+        <v>25</v>
       </c>
       <c r="M13">
         <f t="shared" ref="M13:M50" ca="1" si="9">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>22.600000000000023</v>
+        <v>17.600000000000023</v>
       </c>
       <c r="N13">
         <f t="shared" ca="1" si="4"/>
-        <v>16.600000000000023</v>
+        <v>22.600000000000023</v>
       </c>
       <c r="O13">
         <f t="shared" ca="1" si="5"/>
-        <v>20.200000000000045</v>
+        <v>16.600000000000023</v>
       </c>
       <c r="P13">
         <f t="shared" ca="1" si="6"/>
-        <v>21.800000000000068</v>
+        <v>20.200000000000045</v>
       </c>
       <c r="R13" s="29">
         <v>80</v>
@@ -2309,27 +2309,27 @@
       <c r="I14" s="24"/>
       <c r="K14">
         <f t="shared" ca="1" si="7"/>
-        <v>2.65</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="8"/>
-        <v>2.019999999999996</v>
+        <v>1.4100000000000108</v>
       </c>
       <c r="M14">
         <f t="shared" ca="1" si="9"/>
-        <v>2.9099999999999966</v>
+        <v>2.019999999999996</v>
       </c>
       <c r="N14">
         <f t="shared" ca="1" si="4"/>
-        <v>2.2200000000000131</v>
+        <v>2.9099999999999966</v>
       </c>
       <c r="O14">
         <f t="shared" ca="1" si="5"/>
-        <v>3.7999999999999972</v>
+        <v>2.2200000000000131</v>
       </c>
       <c r="P14">
         <f t="shared" ca="1" si="6"/>
-        <v>2.2800000000000011</v>
+        <v>3.7999999999999972</v>
       </c>
       <c r="R14" s="29">
         <v>27</v>
@@ -2368,27 +2368,27 @@
       <c r="I15" s="23"/>
       <c r="K15">
         <f t="shared" ca="1" si="7"/>
-        <v>8.1300000000000008</v>
+        <v>6.97</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="8"/>
-        <v>7.2000000000000028</v>
+        <v>2.5499999999999972</v>
       </c>
       <c r="M15">
         <f t="shared" ca="1" si="9"/>
-        <v>16.599999999999994</v>
+        <v>7.2000000000000028</v>
       </c>
       <c r="N15">
         <f t="shared" ca="1" si="4"/>
-        <v>5.0999999999999943</v>
+        <v>16.599999999999994</v>
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="5"/>
-        <v>3.4000000000000057</v>
+        <v>5.0999999999999943</v>
       </c>
       <c r="P15">
         <f t="shared" ca="1" si="6"/>
-        <v>8.3500000000000085</v>
+        <v>3.4000000000000057</v>
       </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
@@ -2426,27 +2426,27 @@
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="7"/>
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="8"/>
-        <v>2.5999999999999943</v>
+        <v>2.1500000000000199</v>
       </c>
       <c r="M16">
         <f t="shared" ca="1" si="9"/>
-        <v>3.5499999999999829</v>
+        <v>2.5999999999999943</v>
       </c>
       <c r="N16">
         <f t="shared" ca="1" si="4"/>
-        <v>2.4400000000000119</v>
+        <v>3.5499999999999829</v>
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="5"/>
-        <v>3.4499999999999886</v>
+        <v>2.4400000000000119</v>
       </c>
       <c r="P16">
         <f t="shared" ca="1" si="6"/>
-        <v>2.3100000000000023</v>
+        <v>3.4499999999999886</v>
       </c>
       <c r="R16" s="25">
         <v>-2</v>
@@ -2490,27 +2490,27 @@
       </c>
       <c r="K17">
         <f ca="1">ROUND(AVERAGE(L17:P17),5)</f>
-        <v>2.0200000000000001E-3</v>
+        <v>1.9599999999999999E-3</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="8"/>
-        <v>2.140000000000003E-3</v>
+        <v>1.9000000000000128E-3</v>
       </c>
       <c r="M17">
         <f t="shared" ca="1" si="9"/>
-        <v>2.5599999999999928E-3</v>
+        <v>2.140000000000003E-3</v>
       </c>
       <c r="N17">
         <f t="shared" ca="1" si="4"/>
-        <v>1.2000000000000066E-3</v>
+        <v>2.5599999999999928E-3</v>
       </c>
       <c r="O17">
         <f t="shared" ca="1" si="5"/>
-        <v>1.9799999999999957E-3</v>
+        <v>1.2000000000000066E-3</v>
       </c>
       <c r="P17">
         <f t="shared" ca="1" si="6"/>
-        <v>2.239999999999992E-3</v>
+        <v>1.9799999999999957E-3</v>
       </c>
       <c r="R17" s="25"/>
       <c r="S17" s="25"/>
@@ -2548,27 +2548,27 @@
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="7"/>
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="8"/>
-        <v>4.539999999999992</v>
+        <v>3.5999999999999943</v>
       </c>
       <c r="M18">
         <f t="shared" ca="1" si="9"/>
-        <v>3.9000000000000057</v>
+        <v>4.539999999999992</v>
       </c>
       <c r="N18">
         <f t="shared" ca="1" si="4"/>
-        <v>2.2600000000000193</v>
+        <v>3.9000000000000057</v>
       </c>
       <c r="O18">
         <f t="shared" ca="1" si="5"/>
-        <v>2.4000000000000057</v>
+        <v>2.2600000000000193</v>
       </c>
       <c r="P18">
         <f t="shared" ca="1" si="6"/>
-        <v>3.5</v>
+        <v>2.4000000000000057</v>
       </c>
       <c r="R18" s="25">
         <v>-211</v>
@@ -2607,27 +2607,27 @@
       <c r="I19" s="24"/>
       <c r="K19">
         <f t="shared" ca="1" si="7"/>
-        <v>31361.14</v>
+        <v>13733.23</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="8"/>
-        <v>53018.834000000003</v>
+        <v>-43156.726999999999</v>
       </c>
       <c r="M19">
         <f t="shared" ca="1" si="9"/>
-        <v>44252.837500000001</v>
+        <v>53018.834000000003</v>
       </c>
       <c r="N19">
         <f t="shared" ca="1" si="4"/>
-        <v>57708</v>
+        <v>44252.837500000001</v>
       </c>
       <c r="O19">
         <f t="shared" ca="1" si="5"/>
-        <v>-43156.788999999997</v>
+        <v>57708</v>
       </c>
       <c r="P19">
         <f t="shared" ca="1" si="6"/>
-        <v>44982.817499999997</v>
+        <v>-43156.788999999997</v>
       </c>
       <c r="R19" s="1"/>
       <c r="S19" s="25">
@@ -2667,27 +2667,27 @@
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="7"/>
-        <v>112.6</v>
+        <v>95.2</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="8"/>
-        <v>54.5</v>
+        <v>75</v>
       </c>
       <c r="M20">
         <f t="shared" ca="1" si="9"/>
-        <v>169</v>
+        <v>54.5</v>
       </c>
       <c r="N20">
         <f t="shared" ca="1" si="4"/>
-        <v>83</v>
+        <v>169</v>
       </c>
       <c r="O20">
         <f t="shared" ca="1" si="5"/>
-        <v>94.5</v>
+        <v>83</v>
       </c>
       <c r="P20">
         <f t="shared" ca="1" si="6"/>
-        <v>162</v>
+        <v>94.5</v>
       </c>
       <c r="R20" s="25">
         <v>-741</v>
@@ -2731,27 +2731,27 @@
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="7"/>
-        <v>18445.27</v>
+        <v>27679.86</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="8"/>
-        <v>0.92499999999999716</v>
+        <v>46173.845000000001</v>
       </c>
       <c r="M21">
         <f t="shared" ca="1" si="9"/>
-        <v>0.96499999999999986</v>
+        <v>0.92499999999999716</v>
       </c>
       <c r="N21">
         <f t="shared" ca="1" si="4"/>
-        <v>46081.334999999999</v>
+        <v>0.96499999999999986</v>
       </c>
       <c r="O21">
         <f t="shared" ca="1" si="5"/>
-        <v>46142.23</v>
+        <v>46081.334999999999</v>
       </c>
       <c r="P21">
         <f t="shared" ca="1" si="6"/>
-        <v>0.90500000000000114</v>
+        <v>46142.23</v>
       </c>
       <c r="R21" s="25">
         <v>-107</v>
@@ -2793,27 +2793,27 @@
       <c r="J22" s="30"/>
       <c r="K22">
         <f t="shared" ca="1" si="7"/>
-        <v>59.3</v>
+        <v>57.9</v>
       </c>
       <c r="L22">
         <f t="shared" ca="1" si="8"/>
-        <v>54.5</v>
+        <v>52</v>
       </c>
       <c r="M22">
         <f t="shared" ca="1" si="9"/>
-        <v>69</v>
+        <v>54.5</v>
       </c>
       <c r="N22">
         <f t="shared" ca="1" si="4"/>
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="O22">
         <f t="shared" ca="1" si="5"/>
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="P22">
         <f t="shared" ca="1" si="6"/>
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="R22" s="29">
         <v>45</v>
@@ -2855,27 +2855,27 @@
       <c r="J23" s="30"/>
       <c r="K23">
         <f t="shared" ca="1" si="7"/>
-        <v>2.5499999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="L23">
         <f t="shared" ca="1" si="8"/>
-        <v>3.3400000000000034</v>
+        <v>3.6200000000000045</v>
       </c>
       <c r="M23">
         <f t="shared" ca="1" si="9"/>
-        <v>2.410000000000025</v>
+        <v>3.3400000000000034</v>
       </c>
       <c r="N23">
         <f t="shared" ca="1" si="4"/>
-        <v>1.839999999999975</v>
+        <v>2.410000000000025</v>
       </c>
       <c r="O23">
         <f t="shared" ca="1" si="5"/>
-        <v>2.7700000000000102</v>
+        <v>1.839999999999975</v>
       </c>
       <c r="P23">
         <f t="shared" ca="1" si="6"/>
-        <v>2.4000000000000057</v>
+        <v>2.7700000000000102</v>
       </c>
       <c r="R23" s="25">
         <v>-146</v>
@@ -2917,27 +2917,27 @@
       <c r="J24" s="30"/>
       <c r="K24">
         <f t="shared" ca="1" si="7"/>
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="8"/>
-        <v>1.3300000000000054</v>
+        <v>2.3600000000000065</v>
       </c>
       <c r="M24">
         <f t="shared" ca="1" si="9"/>
-        <v>2.7099999999999937</v>
+        <v>1.3300000000000054</v>
       </c>
       <c r="N24">
         <f t="shared" ca="1" si="4"/>
-        <v>0.76000000000000512</v>
+        <v>2.7099999999999937</v>
       </c>
       <c r="O24">
         <f t="shared" ca="1" si="5"/>
-        <v>2.1999999999999886</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="P24">
         <f t="shared" ca="1" si="6"/>
-        <v>1.4299999999999926</v>
+        <v>2.1999999999999886</v>
       </c>
       <c r="R24" s="25">
         <v>-6</v>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="K25">
         <f t="shared" ca="1" si="7"/>
-        <v>3.06</v>
+        <v>3.77</v>
       </c>
       <c r="L25">
         <f t="shared" ca="1" si="8"/>
-        <v>2.8999999999999773</v>
+        <v>6.2999999999999829</v>
       </c>
       <c r="M25">
         <f t="shared" ca="1" si="9"/>
-        <v>3.0499999999999829</v>
+        <v>2.8999999999999773</v>
       </c>
       <c r="N25">
         <f t="shared" ca="1" si="4"/>
-        <v>2.2000000000000171</v>
+        <v>3.0499999999999829</v>
       </c>
       <c r="O25">
         <f t="shared" ca="1" si="5"/>
-        <v>4.4000000000000057</v>
+        <v>2.2000000000000171</v>
       </c>
       <c r="P25">
         <f t="shared" ca="1" si="6"/>
-        <v>2.75</v>
+        <v>4.4000000000000057</v>
       </c>
       <c r="R25" s="25">
         <v>-149</v>
@@ -3043,27 +3043,27 @@
       <c r="J26" s="30"/>
       <c r="K26">
         <f t="shared" ca="1" si="7"/>
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="L26">
         <f t="shared" ca="1" si="8"/>
-        <v>2.2800000000000011</v>
+        <v>1.6800000000000068</v>
       </c>
       <c r="M26">
         <f t="shared" ca="1" si="9"/>
-        <v>2.4200000000000017</v>
+        <v>2.2800000000000011</v>
       </c>
       <c r="N26">
         <f t="shared" ca="1" si="4"/>
-        <v>1.5799999999999983</v>
+        <v>2.4200000000000017</v>
       </c>
       <c r="O26">
         <f t="shared" ca="1" si="5"/>
-        <v>1.3799999999999955</v>
+        <v>1.5799999999999983</v>
       </c>
       <c r="P26">
         <f t="shared" ca="1" si="6"/>
-        <v>2.0999999999999943</v>
+        <v>1.3799999999999955</v>
       </c>
       <c r="R26" s="29">
         <v>23</v>
@@ -3107,27 +3107,27 @@
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="7"/>
-        <v>34.380000000000003</v>
+        <v>28.98</v>
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="8"/>
-        <v>32.5</v>
+        <v>20.5</v>
       </c>
       <c r="M27">
         <f t="shared" ca="1" si="9"/>
-        <v>37</v>
+        <v>32.5</v>
       </c>
       <c r="N27">
         <f t="shared" ca="1" si="4"/>
-        <v>26.299999999999955</v>
+        <v>37</v>
       </c>
       <c r="O27">
         <f t="shared" ca="1" si="5"/>
-        <v>28.600000000000136</v>
+        <v>26.299999999999955</v>
       </c>
       <c r="P27">
         <f t="shared" ca="1" si="6"/>
-        <v>47.5</v>
+        <v>28.600000000000136</v>
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="29">
@@ -3167,27 +3167,27 @@
       </c>
       <c r="K28">
         <f t="shared" ca="1" si="7"/>
-        <v>99.6</v>
+        <v>107.4</v>
       </c>
       <c r="L28">
         <f t="shared" ca="1" si="8"/>
-        <v>86.5</v>
+        <v>145.5</v>
       </c>
       <c r="M28">
         <f t="shared" ca="1" si="9"/>
-        <v>116.5</v>
+        <v>86.5</v>
       </c>
       <c r="N28">
         <f t="shared" ca="1" si="4"/>
-        <v>54.5</v>
+        <v>116.5</v>
       </c>
       <c r="O28">
         <f t="shared" ca="1" si="5"/>
-        <v>134</v>
+        <v>54.5</v>
       </c>
       <c r="P28">
         <f t="shared" ca="1" si="6"/>
-        <v>106.5</v>
+        <v>134</v>
       </c>
       <c r="R28" s="25">
         <v>-6</v>
@@ -3228,27 +3228,27 @@
       <c r="I29" s="24"/>
       <c r="K29">
         <f t="shared" ca="1" si="7"/>
-        <v>30.28</v>
+        <v>30.48</v>
       </c>
       <c r="L29">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M29">
         <f t="shared" ca="1" si="9"/>
-        <v>37.599999999999909</v>
+        <v>22</v>
       </c>
       <c r="N29">
         <f t="shared" ca="1" si="4"/>
-        <v>39.399999999999864</v>
+        <v>37.599999999999909</v>
       </c>
       <c r="O29">
         <f t="shared" ca="1" si="5"/>
-        <v>27.399999999999864</v>
+        <v>39.399999999999864</v>
       </c>
       <c r="P29">
         <f t="shared" ca="1" si="6"/>
-        <v>25</v>
+        <v>27.399999999999864</v>
       </c>
       <c r="R29" s="1"/>
       <c r="S29" s="25">
@@ -3285,27 +3285,27 @@
       <c r="I30" s="24"/>
       <c r="K30">
         <f t="shared" ca="1" si="7"/>
-        <v>172.6</v>
+        <v>181.6</v>
       </c>
       <c r="L30">
         <f t="shared" ca="1" si="8"/>
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="M30">
         <f t="shared" ca="1" si="9"/>
-        <v>227</v>
+        <v>150</v>
       </c>
       <c r="N30">
         <f t="shared" ca="1" si="4"/>
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="O30">
         <f t="shared" ca="1" si="5"/>
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="P30">
         <f t="shared" ca="1" si="6"/>
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="R30" s="25">
         <v>-31</v>
@@ -3347,27 +3347,27 @@
       </c>
       <c r="K31">
         <f t="shared" ca="1" si="7"/>
-        <v>4.32</v>
+        <v>3.74</v>
       </c>
       <c r="L31">
         <f t="shared" ca="1" si="8"/>
-        <v>5.9000000000000909</v>
+        <v>3.8999999999999773</v>
       </c>
       <c r="M31">
         <f t="shared" ca="1" si="9"/>
-        <v>2.2999999999999545</v>
+        <v>5.9000000000000909</v>
       </c>
       <c r="N31">
         <f t="shared" ca="1" si="4"/>
-        <v>2.9000000000000909</v>
+        <v>2.2999999999999545</v>
       </c>
       <c r="O31">
         <f t="shared" ca="1" si="5"/>
-        <v>3.7000000000000455</v>
+        <v>2.9000000000000909</v>
       </c>
       <c r="P31">
         <f t="shared" ca="1" si="6"/>
-        <v>6.7999999999999545</v>
+        <v>3.7000000000000455</v>
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="29">
@@ -3409,27 +3409,27 @@
       </c>
       <c r="K32">
         <f t="shared" ca="1" si="7"/>
-        <v>74.040000000000006</v>
+        <v>67.680000000000007</v>
       </c>
       <c r="L32">
         <f t="shared" ca="1" si="8"/>
-        <v>87.800000000000182</v>
+        <v>55.200000000000273</v>
       </c>
       <c r="M32">
         <f t="shared" ca="1" si="9"/>
-        <v>46.199999999999818</v>
+        <v>87.800000000000182</v>
       </c>
       <c r="N32">
         <f t="shared" ca="1" si="4"/>
-        <v>79.400000000000091</v>
+        <v>46.199999999999818</v>
       </c>
       <c r="O32">
         <f t="shared" ca="1" si="5"/>
-        <v>69.800000000000182</v>
+        <v>79.400000000000091</v>
       </c>
       <c r="P32">
         <f t="shared" ca="1" si="6"/>
-        <v>87</v>
+        <v>69.800000000000182</v>
       </c>
       <c r="R32" s="25">
         <v>-68</v>
@@ -3468,27 +3468,27 @@
       <c r="I33" s="24"/>
       <c r="K33">
         <f t="shared" ca="1" si="7"/>
-        <v>4.97</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="L33">
         <f t="shared" ca="1" si="8"/>
-        <v>3</v>
+        <v>2.9499999999999886</v>
       </c>
       <c r="M33">
         <f t="shared" ca="1" si="9"/>
-        <v>6.3500000000000085</v>
+        <v>3</v>
       </c>
       <c r="N33">
         <f t="shared" ca="1" si="4"/>
-        <v>6.2999999999999972</v>
+        <v>6.3500000000000085</v>
       </c>
       <c r="O33">
         <f t="shared" ca="1" si="5"/>
-        <v>3.5999999999999943</v>
+        <v>6.2999999999999972</v>
       </c>
       <c r="P33">
         <f t="shared" ca="1" si="6"/>
-        <v>5.5999999999999943</v>
+        <v>3.5999999999999943</v>
       </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
@@ -3528,27 +3528,27 @@
       </c>
       <c r="K34">
         <f t="shared" ca="1" si="7"/>
-        <v>14.96</v>
+        <v>12.23</v>
       </c>
       <c r="L34">
         <f t="shared" ca="1" si="8"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <f t="shared" ca="1" si="9"/>
-        <v>17.75</v>
+        <v>12</v>
       </c>
       <c r="N34">
         <f t="shared" ca="1" si="4"/>
-        <v>11.050000000000011</v>
+        <v>17.75</v>
       </c>
       <c r="O34">
         <f t="shared" ca="1" si="5"/>
-        <v>14.349999999999966</v>
+        <v>11.050000000000011</v>
       </c>
       <c r="P34">
         <f t="shared" ca="1" si="6"/>
-        <v>19.649999999999977</v>
+        <v>14.349999999999966</v>
       </c>
       <c r="R34" s="29">
         <v>342</v>
@@ -3592,27 +3592,27 @@
       </c>
       <c r="K35">
         <f t="shared" ca="1" si="7"/>
-        <v>1.1000000000000001</v>
+        <v>1.23</v>
       </c>
       <c r="L35">
         <f t="shared" ca="1" si="8"/>
-        <v>1.7199999999999989</v>
+        <v>1.4549999999999983</v>
       </c>
       <c r="M35">
         <f t="shared" ca="1" si="9"/>
-        <v>1.3599999999999994</v>
+        <v>1.7199999999999989</v>
       </c>
       <c r="N35">
         <f t="shared" ca="1" si="4"/>
-        <v>0.67999999999999972</v>
+        <v>1.3599999999999994</v>
       </c>
       <c r="O35">
         <f t="shared" ca="1" si="5"/>
-        <v>0.91000000000000369</v>
+        <v>0.67999999999999972</v>
       </c>
       <c r="P35">
         <f t="shared" ca="1" si="6"/>
-        <v>0.84999999999999432</v>
+        <v>0.91000000000000369</v>
       </c>
       <c r="R35" s="1"/>
       <c r="S35" s="25">
@@ -3650,27 +3650,27 @@
       <c r="J36" s="30"/>
       <c r="K36">
         <f t="shared" ca="1" si="7"/>
-        <v>2.98</v>
+        <v>3.47</v>
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="8"/>
-        <v>2.6000000000000227</v>
+        <v>5.2100000000000364</v>
       </c>
       <c r="M36">
         <f t="shared" ca="1" si="9"/>
-        <v>2.4399999999999977</v>
+        <v>2.6000000000000227</v>
       </c>
       <c r="N36">
         <f t="shared" ca="1" si="4"/>
-        <v>2.2200000000000273</v>
+        <v>2.4399999999999977</v>
       </c>
       <c r="O36">
         <f t="shared" ca="1" si="5"/>
-        <v>4.8600000000000136</v>
+        <v>2.2200000000000273</v>
       </c>
       <c r="P36">
         <f t="shared" ca="1" si="6"/>
-        <v>2.7800000000000296</v>
+        <v>4.8600000000000136</v>
       </c>
       <c r="R36" s="29">
         <v>32</v>
@@ -3714,27 +3714,27 @@
       </c>
       <c r="K37">
         <f t="shared" ca="1" si="7"/>
-        <v>58.4</v>
+        <v>55.68</v>
       </c>
       <c r="L37">
         <f t="shared" ca="1" si="8"/>
-        <v>17.600000000000023</v>
+        <v>25</v>
       </c>
       <c r="M37">
         <f t="shared" ca="1" si="9"/>
-        <v>35.799999999999955</v>
+        <v>17.600000000000023</v>
       </c>
       <c r="N37">
         <f t="shared" ca="1" si="4"/>
-        <v>176</v>
+        <v>35.799999999999955</v>
       </c>
       <c r="O37">
         <f t="shared" ca="1" si="5"/>
-        <v>24</v>
+        <v>176</v>
       </c>
       <c r="P37">
         <f t="shared" ca="1" si="6"/>
-        <v>38.599999999999909</v>
+        <v>24</v>
       </c>
       <c r="R37" s="25">
         <v>-89</v>
@@ -3773,27 +3773,27 @@
       <c r="I38" s="24"/>
       <c r="K38">
         <f t="shared" ca="1" si="7"/>
-        <v>438.04</v>
+        <v>-16728.509999999998</v>
       </c>
       <c r="L38">
         <f t="shared" ca="1" si="8"/>
-        <v>2.100000000000013E-2</v>
+        <v>3.5499999999999865E-2</v>
       </c>
       <c r="M38">
         <f t="shared" ca="1" si="9"/>
-        <v>-41638.828500000003</v>
+        <v>2.100000000000013E-2</v>
       </c>
       <c r="N38">
         <f t="shared" ca="1" si="4"/>
-        <v>-42003.820500000002</v>
+        <v>-41638.828500000003</v>
       </c>
       <c r="O38">
         <f t="shared" ca="1" si="5"/>
-        <v>3.2000000000000028E-2</v>
+        <v>-42003.820500000002</v>
       </c>
       <c r="P38">
         <f t="shared" ca="1" si="6"/>
-        <v>85832.812999999995</v>
+        <v>3.2000000000000028E-2</v>
       </c>
       <c r="R38" s="29">
         <v>71</v>
@@ -3830,27 +3830,27 @@
       <c r="I39" s="24"/>
       <c r="K39">
         <f t="shared" ca="1" si="7"/>
-        <v>13.45</v>
+        <v>11.96</v>
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="8"/>
-        <v>9</v>
+        <v>6.8999999999999773</v>
       </c>
       <c r="M39">
         <f t="shared" ca="1" si="9"/>
-        <v>20.799999999999955</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <f t="shared" ca="1" si="4"/>
-        <v>11.399999999999977</v>
+        <v>20.799999999999955</v>
       </c>
       <c r="O39">
         <f t="shared" ca="1" si="5"/>
-        <v>11.699999999999932</v>
+        <v>11.399999999999977</v>
       </c>
       <c r="P39">
         <f t="shared" ca="1" si="6"/>
-        <v>14.350000000000023</v>
+        <v>11.699999999999932</v>
       </c>
       <c r="R39" s="25">
         <v>-9</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="K40">
         <f t="shared" ca="1" si="7"/>
-        <v>41.44</v>
+        <v>42.88</v>
       </c>
       <c r="L40">
         <f t="shared" ca="1" si="8"/>
@@ -3900,19 +3900,19 @@
       </c>
       <c r="M40">
         <f t="shared" ca="1" si="9"/>
-        <v>66.799999999999955</v>
+        <v>45.399999999999977</v>
       </c>
       <c r="N40">
         <f t="shared" ca="1" si="4"/>
-        <v>23.799999999999955</v>
+        <v>66.799999999999955</v>
       </c>
       <c r="O40">
         <f t="shared" ca="1" si="5"/>
-        <v>33</v>
+        <v>23.799999999999955</v>
       </c>
       <c r="P40">
         <f t="shared" ca="1" si="6"/>
-        <v>38.200000000000045</v>
+        <v>33</v>
       </c>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
@@ -3949,27 +3949,27 @@
       <c r="I41" s="24"/>
       <c r="K41">
         <f t="shared" ca="1" si="7"/>
-        <v>9192.77</v>
+        <v>9204.84</v>
       </c>
       <c r="L41">
         <f t="shared" ca="1" si="8"/>
-        <v>0.34499999999999886</v>
+        <v>0.34999999999999787</v>
       </c>
       <c r="M41">
         <f t="shared" ca="1" si="9"/>
-        <v>46022.75</v>
+        <v>0.34499999999999886</v>
       </c>
       <c r="N41">
         <f t="shared" ca="1" si="4"/>
-        <v>0.32499999999999929</v>
+        <v>46022.75</v>
       </c>
       <c r="O41">
         <f t="shared" ca="1" si="5"/>
-        <v>0.42499999999999716</v>
+        <v>0.32499999999999929</v>
       </c>
       <c r="P41">
         <f t="shared" ca="1" si="6"/>
-        <v>-60</v>
+        <v>0.42499999999999716</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4000,27 +4000,27 @@
       <c r="I42" s="24"/>
       <c r="K42">
         <f t="shared" ca="1" si="7"/>
-        <v>1.24</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="8"/>
-        <v>1.0500000000000043</v>
+        <v>0.99000000000000199</v>
       </c>
       <c r="M42">
         <f t="shared" ca="1" si="9"/>
-        <v>1.5150000000000006</v>
+        <v>1.0500000000000043</v>
       </c>
       <c r="N42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.78000000000000114</v>
+        <v>1.5150000000000006</v>
       </c>
       <c r="O42">
         <f t="shared" ca="1" si="5"/>
-        <v>1.1599999999999966</v>
+        <v>0.78000000000000114</v>
       </c>
       <c r="P42">
         <f t="shared" ca="1" si="6"/>
-        <v>1.7000000000000028</v>
+        <v>1.1599999999999966</v>
       </c>
       <c r="R42" s="25">
         <v>-18</v>
@@ -4061,27 +4061,27 @@
       <c r="I43" s="24"/>
       <c r="K43">
         <f t="shared" ca="1" si="7"/>
-        <v>22.48</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="L43">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B43&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B43&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>18.299999999999955</v>
+        <v>15.399999999999977</v>
       </c>
       <c r="M43">
         <f t="shared" ca="1" si="9"/>
-        <v>30.299999999999955</v>
+        <v>18.299999999999955</v>
       </c>
       <c r="N43">
         <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>30.299999999999955</v>
       </c>
       <c r="O43">
         <f t="shared" ca="1" si="5"/>
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="P43">
         <f t="shared" ca="1" si="6"/>
-        <v>27.299999999999955</v>
+        <v>19.5</v>
       </c>
       <c r="R43" s="25">
         <v>-114</v>
@@ -4120,27 +4120,27 @@
       <c r="I44" s="24"/>
       <c r="K44">
         <f t="shared" ca="1" si="7"/>
-        <v>1.93</v>
+        <v>2.37</v>
       </c>
       <c r="L44">
         <f t="shared" ca="1" si="8"/>
-        <v>1.6199999999999903</v>
+        <v>4.4200000000000017</v>
       </c>
       <c r="M44">
         <f t="shared" ca="1" si="9"/>
-        <v>1.7999999999999972</v>
+        <v>1.6199999999999903</v>
       </c>
       <c r="N44">
         <f t="shared" ca="1" si="4"/>
-        <v>1.4399999999999977</v>
+        <v>1.7999999999999972</v>
       </c>
       <c r="O44">
         <f t="shared" ca="1" si="5"/>
-        <v>2.5799999999999983</v>
+        <v>1.4399999999999977</v>
       </c>
       <c r="P44">
         <f t="shared" ca="1" si="6"/>
-        <v>2.2199999999999989</v>
+        <v>2.5799999999999983</v>
       </c>
       <c r="R44" s="29">
         <v>7</v>
@@ -4179,27 +4179,27 @@
       <c r="I45" s="24"/>
       <c r="K45">
         <f t="shared" ca="1" si="7"/>
-        <v>25.04</v>
+        <v>21.12</v>
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="8"/>
-        <v>19.400000000000091</v>
+        <v>18.599999999999909</v>
       </c>
       <c r="M45">
         <f t="shared" ca="1" si="9"/>
-        <v>25.799999999999955</v>
+        <v>19.400000000000091</v>
       </c>
       <c r="N45">
         <f t="shared" ca="1" si="4"/>
-        <v>17.599999999999909</v>
+        <v>25.799999999999955</v>
       </c>
       <c r="O45">
         <f t="shared" ca="1" si="5"/>
-        <v>24.200000000000045</v>
+        <v>17.599999999999909</v>
       </c>
       <c r="P45">
         <f t="shared" ca="1" si="6"/>
-        <v>38.200000000000045</v>
+        <v>24.200000000000045</v>
       </c>
       <c r="R45" s="1"/>
       <c r="S45" s="25">
@@ -4241,27 +4241,27 @@
       </c>
       <c r="K46">
         <f ca="1">ROUND(AVERAGE(L46:P46),4)</f>
-        <v>2.01E-2</v>
+        <v>1.83E-2</v>
       </c>
       <c r="L46">
         <f t="shared" ca="1" si="8"/>
-        <v>2.5799999999999934E-2</v>
+        <v>1.2800000000000034E-2</v>
       </c>
       <c r="M46">
         <f t="shared" ca="1" si="9"/>
-        <v>1.4000000000000012E-2</v>
+        <v>2.5799999999999934E-2</v>
       </c>
       <c r="N46">
         <f t="shared" ca="1" si="4"/>
-        <v>2.1100000000000008E-2</v>
+        <v>1.4000000000000012E-2</v>
       </c>
       <c r="O46">
         <f t="shared" ca="1" si="5"/>
-        <v>1.7700000000000049E-2</v>
+        <v>2.1100000000000008E-2</v>
       </c>
       <c r="P46">
         <f t="shared" ca="1" si="6"/>
-        <v>2.2100000000000009E-2</v>
+        <v>1.7700000000000049E-2</v>
       </c>
       <c r="R46" s="1"/>
       <c r="S46" s="22"/>
@@ -4299,27 +4299,27 @@
       </c>
       <c r="K47">
         <f t="shared" ca="1" si="7"/>
-        <v>8.19</v>
+        <v>7.4</v>
       </c>
       <c r="L47">
         <f t="shared" ca="1" si="8"/>
-        <v>5.1000000000000227</v>
+        <v>7.0500000000000114</v>
       </c>
       <c r="M47">
         <f t="shared" ca="1" si="9"/>
-        <v>8.6499999999999773</v>
+        <v>5.1000000000000227</v>
       </c>
       <c r="N47">
         <f t="shared" ca="1" si="4"/>
-        <v>6.3999999999999773</v>
+        <v>8.6499999999999773</v>
       </c>
       <c r="O47">
         <f t="shared" ca="1" si="5"/>
-        <v>9.8000000000000114</v>
+        <v>6.3999999999999773</v>
       </c>
       <c r="P47">
         <f t="shared" ca="1" si="6"/>
-        <v>11</v>
+        <v>9.8000000000000114</v>
       </c>
       <c r="R47" s="1"/>
       <c r="S47" s="29">
@@ -4362,27 +4362,27 @@
       </c>
       <c r="K48">
         <f t="shared" ca="1" si="7"/>
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="L48">
         <f t="shared" ca="1" si="8"/>
-        <v>1.4399999999999977</v>
+        <v>2.5799999999999983</v>
       </c>
       <c r="M48">
         <f t="shared" ca="1" si="9"/>
-        <v>1.644999999999996</v>
+        <v>1.4399999999999977</v>
       </c>
       <c r="N48">
         <f t="shared" ca="1" si="4"/>
-        <v>1.7000000000000028</v>
+        <v>1.644999999999996</v>
       </c>
       <c r="O48">
         <f t="shared" ca="1" si="5"/>
-        <v>1.7900000000000063</v>
+        <v>1.7000000000000028</v>
       </c>
       <c r="P48">
         <f t="shared" ca="1" si="6"/>
-        <v>2.0150000000000006</v>
+        <v>1.7900000000000063</v>
       </c>
       <c r="R48" s="29">
         <v>19</v>
@@ -4424,27 +4424,27 @@
       </c>
       <c r="K49">
         <f t="shared" ca="1" si="7"/>
-        <v>35.4</v>
+        <v>33.6</v>
       </c>
       <c r="L49">
         <f t="shared" ca="1" si="8"/>
-        <v>19.5</v>
+        <v>42.5</v>
       </c>
       <c r="M49">
         <f t="shared" ca="1" si="9"/>
-        <v>52.5</v>
+        <v>19.5</v>
       </c>
       <c r="N49">
         <f t="shared" ca="1" si="4"/>
-        <v>20.5</v>
+        <v>52.5</v>
       </c>
       <c r="O49">
         <f t="shared" ca="1" si="5"/>
-        <v>33</v>
+        <v>20.5</v>
       </c>
       <c r="P49">
         <f t="shared" ca="1" si="6"/>
-        <v>51.5</v>
+        <v>33</v>
       </c>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
@@ -4482,27 +4482,27 @@
       </c>
       <c r="K50">
         <f t="shared" ca="1" si="7"/>
-        <v>91.7</v>
+        <v>110</v>
       </c>
       <c r="L50">
         <f t="shared" ca="1" si="8"/>
-        <v>118.5</v>
+        <v>164</v>
       </c>
       <c r="M50">
         <f t="shared" ca="1" si="9"/>
-        <v>103</v>
+        <v>118.5</v>
       </c>
       <c r="N50">
         <f t="shared" ca="1" si="4"/>
-        <v>53.5</v>
+        <v>103</v>
       </c>
       <c r="O50">
         <f t="shared" ca="1" si="5"/>
-        <v>111</v>
+        <v>53.5</v>
       </c>
       <c r="P50">
         <f t="shared" ca="1" si="6"/>
-        <v>72.5</v>
+        <v>111</v>
       </c>
       <c r="R50" s="1">
         <v>-97</v>
@@ -4640,41 +4640,43 @@
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="34">
+      <c r="D3" s="33">
         <v>46121</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="33">
         <v>46122</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="33">
         <v>46127</v>
       </c>
-      <c r="G3" s="1"/>
+      <c r="G3" s="33">
+        <v>46128</v>
+      </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -4734,7 +4736,9 @@
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1">
+        <v>140</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -4764,7 +4768,9 @@
         <v>44</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1">
+        <v>43</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -4822,7 +4828,9 @@
         <v>84</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1">
+        <v>79</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -4878,7 +4886,9 @@
       <c r="F10" s="1">
         <v>156</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1">
+        <v>42</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>

--- a/calc.xlsx
+++ b/calc.xlsx
@@ -1834,23 +1834,23 @@
     <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="L6" s="5" t="str">
         <f ca="1">TEXT(L7,"ддд")</f>
-        <v>Ср</v>
+        <v>Сб</v>
       </c>
       <c r="M6" s="5" t="str">
         <f ca="1">TEXT(M7,"ддд")</f>
-        <v>Вт</v>
+        <v>Пт</v>
       </c>
       <c r="N6" s="5" t="str">
         <f t="shared" ref="N6:P6" ca="1" si="0">TEXT(N7,"ддд")</f>
-        <v>Пн</v>
+        <v>Чт</v>
       </c>
       <c r="O6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Пт</v>
+        <v>Ср</v>
       </c>
       <c r="P6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Чт</v>
+        <v>Вт</v>
       </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.25">
@@ -1883,24 +1883,24 @@
         <v>78</v>
       </c>
       <c r="L7" s="1" t="str">
-        <f ca="1">TEXT(TODAY()-1, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-15</v>
+        <f ca="1">TEXT(TODAY()-3, "ГГГГ-ММ-ДД")</f>
+        <v>2026-04-18</v>
       </c>
       <c r="M7" s="1" t="str">
-        <f ca="1">TEXT(TODAY()-2, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-14</v>
+        <f ca="1">TEXT(TODAY()-4, "ГГГГ-ММ-ДД")</f>
+        <v>2026-04-17</v>
       </c>
       <c r="N7" s="1" t="str">
-        <f ca="1">TEXT(TODAY()-3, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-13</v>
+        <f ca="1">TEXT(TODAY()-5, "ГГГГ-ММ-ДД")</f>
+        <v>2026-04-16</v>
       </c>
       <c r="O7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-6, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-10</v>
+        <v>2026-04-15</v>
       </c>
       <c r="P7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-7, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-09</v>
+        <v>2026-04-14</v>
       </c>
       <c r="R7" s="28">
         <v>45566</v>
@@ -1946,27 +1946,27 @@
       </c>
       <c r="K8">
         <f ca="1">ROUND(AVERAGE(L8:P8),2)</f>
-        <v>7075.15</v>
+        <v>15242.5</v>
       </c>
       <c r="L8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>14203.084000000001</v>
+        <v>5.099999999999838E-2</v>
       </c>
       <c r="M8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>42327.093999999997</v>
+        <v>19681.812999999998</v>
       </c>
       <c r="N8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>-34261.775999999998</v>
+        <v>0.4789999999999992</v>
       </c>
       <c r="O8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>13106.898999999999</v>
+        <v>14203.084000000001</v>
       </c>
       <c r="P8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.42900000000000027</v>
+        <v>42327.093999999997</v>
       </c>
       <c r="R8" s="29">
         <v>54</v>
@@ -2010,27 +2010,27 @@
       </c>
       <c r="K9">
         <f ca="1">ROUND(AVERAGE(L9:P9),2)</f>
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="L9">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.7100000000000009</v>
+        <v>0.57999999999999829</v>
       </c>
       <c r="M9">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.92000000000000171</v>
+        <v>1.7199999999999989</v>
       </c>
       <c r="N9">
         <f t="shared" ref="N9:N50" ca="1" si="4">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.87000000000000455</v>
+        <v>1.0900000000000034</v>
       </c>
       <c r="O9">
         <f t="shared" ref="O9:O50" ca="1" si="5">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.0800000000000054</v>
+        <v>1.7100000000000009</v>
       </c>
       <c r="P9">
         <f t="shared" ref="P9:P50" ca="1" si="6">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.5799999999999983</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="R9" s="25">
         <v>-30</v>
@@ -2071,27 +2071,27 @@
       <c r="I10" s="24"/>
       <c r="K10">
         <f ca="1">ROUND(AVERAGE(L10:P10),2)</f>
-        <v>0.98</v>
+        <v>0.76</v>
       </c>
       <c r="L10">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.96000000000000085</v>
+        <v>0.21999999999999886</v>
       </c>
       <c r="M10">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.96000000000000085</v>
+        <v>1.1499999999999986</v>
       </c>
       <c r="N10">
         <f t="shared" ca="1" si="4"/>
-        <v>1.7899999999999991</v>
+        <v>0.52000000000000313</v>
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="5"/>
-        <v>0.64000000000000057</v>
+        <v>0.96000000000000085</v>
       </c>
       <c r="P10">
         <f t="shared" ca="1" si="6"/>
-        <v>0.55000000000000426</v>
+        <v>0.96000000000000085</v>
       </c>
       <c r="R10" s="29">
         <v>39</v>
@@ -2135,27 +2135,27 @@
       </c>
       <c r="K11">
         <f ca="1">ROUND(AVERAGE(L11:P11),2)</f>
-        <v>4.8600000000000003</v>
+        <v>5.54</v>
       </c>
       <c r="L11">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>4.8000000000000114</v>
+        <v>1.8299999999999841</v>
       </c>
       <c r="M11">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>5.9000000000000341</v>
+        <v>7.089999999999975</v>
       </c>
       <c r="N11">
         <f t="shared" ca="1" si="4"/>
-        <v>3.8800000000000523</v>
+        <v>8.1000000000000227</v>
       </c>
       <c r="O11">
         <f t="shared" ca="1" si="5"/>
-        <v>3.1399999999999864</v>
+        <v>4.8000000000000114</v>
       </c>
       <c r="P11">
         <f t="shared" ca="1" si="6"/>
-        <v>6.57000000000005</v>
+        <v>5.9000000000000341</v>
       </c>
       <c r="R11" s="29"/>
       <c r="S11" s="29"/>
@@ -2193,27 +2193,27 @@
       </c>
       <c r="K12" s="24">
         <f ca="1">ROUND(AVERAGE(L12:P12),2)</f>
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="L12" s="24">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.64999999999999858</v>
+        <v>0.45000000000000284</v>
       </c>
       <c r="M12" s="24">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.94999999999999574</v>
+        <v>2.25</v>
       </c>
       <c r="N12" s="24">
         <f t="shared" ca="1" si="4"/>
-        <v>1.6999999999999957</v>
+        <v>3.0500000000000043</v>
       </c>
       <c r="O12" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>1.8500000000000014</v>
+        <v>0.64999999999999858</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ca="1" si="6"/>
-        <v>1.4499999999999957</v>
+        <v>0.94999999999999574</v>
       </c>
       <c r="R12" s="29"/>
       <c r="S12" s="29"/>
@@ -2248,27 +2248,27 @@
       <c r="I13" s="23"/>
       <c r="K13">
         <f t="shared" ref="K13:K50" ca="1" si="7">ROUND(AVERAGE(L13:P13),2)</f>
-        <v>20.399999999999999</v>
+        <v>17.079999999999998</v>
       </c>
       <c r="L13">
         <f t="shared" ref="L13:L50" ca="1" si="8">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>25</v>
+        <v>9.4000000000000909</v>
       </c>
       <c r="M13">
         <f t="shared" ref="M13:M50" ca="1" si="9">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>17.600000000000023</v>
+        <v>17</v>
       </c>
       <c r="N13">
         <f t="shared" ca="1" si="4"/>
-        <v>22.600000000000023</v>
+        <v>16.399999999999977</v>
       </c>
       <c r="O13">
         <f t="shared" ca="1" si="5"/>
-        <v>16.600000000000023</v>
+        <v>25</v>
       </c>
       <c r="P13">
         <f t="shared" ca="1" si="6"/>
-        <v>20.200000000000045</v>
+        <v>17.600000000000023</v>
       </c>
       <c r="R13" s="29">
         <v>80</v>
@@ -2309,27 +2309,27 @@
       <c r="I14" s="24"/>
       <c r="K14">
         <f t="shared" ca="1" si="7"/>
-        <v>2.4700000000000002</v>
+        <v>1.46</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="8"/>
-        <v>1.4100000000000108</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="M14">
         <f t="shared" ca="1" si="9"/>
-        <v>2.019999999999996</v>
+        <v>1.0600000000000023</v>
       </c>
       <c r="N14">
         <f t="shared" ca="1" si="4"/>
-        <v>2.9099999999999966</v>
+        <v>2.269999999999996</v>
       </c>
       <c r="O14">
         <f t="shared" ca="1" si="5"/>
-        <v>2.2200000000000131</v>
+        <v>1.4100000000000108</v>
       </c>
       <c r="P14">
         <f t="shared" ca="1" si="6"/>
-        <v>3.7999999999999972</v>
+        <v>2.019999999999996</v>
       </c>
       <c r="R14" s="29">
         <v>27</v>
@@ -2368,27 +2368,27 @@
       <c r="I15" s="23"/>
       <c r="K15">
         <f t="shared" ca="1" si="7"/>
-        <v>6.97</v>
+        <v>3.83</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="8"/>
-        <v>2.5499999999999972</v>
+        <v>0.85000000000000853</v>
       </c>
       <c r="M15">
         <f t="shared" ca="1" si="9"/>
-        <v>7.2000000000000028</v>
+        <v>3.8500000000000085</v>
       </c>
       <c r="N15">
         <f t="shared" ca="1" si="4"/>
-        <v>16.599999999999994</v>
+        <v>4.7000000000000028</v>
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="5"/>
-        <v>5.0999999999999943</v>
+        <v>2.5499999999999972</v>
       </c>
       <c r="P15">
         <f t="shared" ca="1" si="6"/>
-        <v>3.4000000000000057</v>
+        <v>7.2000000000000028</v>
       </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
@@ -2422,31 +2422,31 @@
       </c>
       <c r="I16" s="24"/>
       <c r="J16" s="30">
-        <v>46058</v>
+        <v>46133</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="7"/>
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="8"/>
-        <v>2.1500000000000199</v>
+        <v>1.0699999999999932</v>
       </c>
       <c r="M16">
         <f t="shared" ca="1" si="9"/>
-        <v>2.5999999999999943</v>
+        <v>4.7399999999999807</v>
       </c>
       <c r="N16">
         <f t="shared" ca="1" si="4"/>
-        <v>3.5499999999999829</v>
+        <v>1.9300000000000068</v>
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="5"/>
-        <v>2.4400000000000119</v>
+        <v>2.1500000000000199</v>
       </c>
       <c r="P16">
         <f t="shared" ca="1" si="6"/>
-        <v>3.4499999999999886</v>
+        <v>2.5999999999999943</v>
       </c>
       <c r="R16" s="25">
         <v>-2</v>
@@ -2490,27 +2490,27 @@
       </c>
       <c r="K17">
         <f ca="1">ROUND(AVERAGE(L17:P17),5)</f>
-        <v>1.9599999999999999E-3</v>
+        <v>1.6100000000000001E-3</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="8"/>
-        <v>1.9000000000000128E-3</v>
+        <v>5.3999999999999881E-4</v>
       </c>
       <c r="M17">
         <f t="shared" ca="1" si="9"/>
-        <v>2.140000000000003E-3</v>
+        <v>1.7599999999999977E-3</v>
       </c>
       <c r="N17">
         <f t="shared" ca="1" si="4"/>
-        <v>2.5599999999999928E-3</v>
+        <v>1.7199999999999993E-3</v>
       </c>
       <c r="O17">
         <f t="shared" ca="1" si="5"/>
-        <v>1.2000000000000066E-3</v>
+        <v>1.9000000000000128E-3</v>
       </c>
       <c r="P17">
         <f t="shared" ca="1" si="6"/>
-        <v>1.9799999999999957E-3</v>
+        <v>2.140000000000003E-3</v>
       </c>
       <c r="R17" s="25"/>
       <c r="S17" s="25"/>
@@ -2544,31 +2544,31 @@
       </c>
       <c r="I18" s="24"/>
       <c r="J18" s="30">
-        <v>46058</v>
+        <v>46133</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="7"/>
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="8"/>
-        <v>3.5999999999999943</v>
+        <v>2.1800000000000068</v>
       </c>
       <c r="M18">
         <f t="shared" ca="1" si="9"/>
-        <v>4.539999999999992</v>
+        <v>3.2800000000000011</v>
       </c>
       <c r="N18">
         <f t="shared" ca="1" si="4"/>
-        <v>3.9000000000000057</v>
+        <v>3.1399999999999864</v>
       </c>
       <c r="O18">
         <f t="shared" ca="1" si="5"/>
-        <v>2.2600000000000193</v>
+        <v>3.5999999999999943</v>
       </c>
       <c r="P18">
         <f t="shared" ca="1" si="6"/>
-        <v>2.4000000000000057</v>
+        <v>4.539999999999992</v>
       </c>
       <c r="R18" s="25">
         <v>-211</v>
@@ -2607,27 +2607,27 @@
       <c r="I19" s="24"/>
       <c r="K19">
         <f t="shared" ca="1" si="7"/>
-        <v>13733.23</v>
+        <v>39227.040000000001</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="8"/>
-        <v>-43156.726999999999</v>
+        <v>36524</v>
       </c>
       <c r="M19">
         <f t="shared" ca="1" si="9"/>
-        <v>53018.834000000003</v>
+        <v>414607.76500000001</v>
       </c>
       <c r="N19">
         <f t="shared" ca="1" si="4"/>
-        <v>44252.837500000001</v>
+        <v>-264858.68699999998</v>
       </c>
       <c r="O19">
         <f t="shared" ca="1" si="5"/>
-        <v>57708</v>
+        <v>-43156.726999999999</v>
       </c>
       <c r="P19">
         <f t="shared" ca="1" si="6"/>
-        <v>-43156.788999999997</v>
+        <v>53018.834000000003</v>
       </c>
       <c r="R19" s="1"/>
       <c r="S19" s="25">
@@ -2663,31 +2663,31 @@
       </c>
       <c r="I20" s="24"/>
       <c r="J20" s="30">
-        <v>46066</v>
+        <v>46133</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="7"/>
-        <v>95.2</v>
+        <v>76.7</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="8"/>
-        <v>75</v>
+        <v>41.5</v>
       </c>
       <c r="M20">
         <f t="shared" ca="1" si="9"/>
-        <v>54.5</v>
+        <v>149.5</v>
       </c>
       <c r="N20">
         <f t="shared" ca="1" si="4"/>
-        <v>169</v>
+        <v>63</v>
       </c>
       <c r="O20">
         <f t="shared" ca="1" si="5"/>
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="P20">
         <f t="shared" ca="1" si="6"/>
-        <v>94.5</v>
+        <v>54.5</v>
       </c>
       <c r="R20" s="25">
         <v>-741</v>
@@ -2727,31 +2727,31 @@
       </c>
       <c r="I21" s="23"/>
       <c r="J21" s="30">
-        <v>46063</v>
+        <v>46133</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="7"/>
-        <v>27679.86</v>
+        <v>18463.59</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="8"/>
-        <v>46173.845000000001</v>
+        <v>0.16000000000000014</v>
       </c>
       <c r="M21">
         <f t="shared" ca="1" si="9"/>
-        <v>0.92499999999999716</v>
+        <v>0.73499999999999943</v>
       </c>
       <c r="N21">
         <f t="shared" ca="1" si="4"/>
-        <v>0.96499999999999986</v>
+        <v>46142.264999999999</v>
       </c>
       <c r="O21">
         <f t="shared" ca="1" si="5"/>
-        <v>46081.334999999999</v>
+        <v>46173.845000000001</v>
       </c>
       <c r="P21">
         <f t="shared" ca="1" si="6"/>
-        <v>46142.23</v>
+        <v>0.92499999999999716</v>
       </c>
       <c r="R21" s="25">
         <v>-107</v>
@@ -2793,27 +2793,27 @@
       <c r="J22" s="30"/>
       <c r="K22">
         <f t="shared" ca="1" si="7"/>
-        <v>57.9</v>
+        <v>41.6</v>
       </c>
       <c r="L22">
         <f t="shared" ca="1" si="8"/>
-        <v>52</v>
+        <v>10.5</v>
       </c>
       <c r="M22">
         <f t="shared" ca="1" si="9"/>
-        <v>54.5</v>
+        <v>47</v>
       </c>
       <c r="N22">
         <f t="shared" ca="1" si="4"/>
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="O22">
         <f t="shared" ca="1" si="5"/>
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="P22">
         <f t="shared" ca="1" si="6"/>
-        <v>76</v>
+        <v>54.5</v>
       </c>
       <c r="R22" s="29">
         <v>45</v>
@@ -2855,27 +2855,27 @@
       <c r="J23" s="30"/>
       <c r="K23">
         <f t="shared" ca="1" si="7"/>
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="L23">
         <f t="shared" ca="1" si="8"/>
-        <v>3.6200000000000045</v>
+        <v>0.48999999999998067</v>
       </c>
       <c r="M23">
         <f t="shared" ca="1" si="9"/>
-        <v>3.3400000000000034</v>
+        <v>1.5800000000000125</v>
       </c>
       <c r="N23">
         <f t="shared" ca="1" si="4"/>
-        <v>2.410000000000025</v>
+        <v>2.9000000000000057</v>
       </c>
       <c r="O23">
         <f t="shared" ca="1" si="5"/>
-        <v>1.839999999999975</v>
+        <v>3.6200000000000045</v>
       </c>
       <c r="P23">
         <f t="shared" ca="1" si="6"/>
-        <v>2.7700000000000102</v>
+        <v>3.3400000000000034</v>
       </c>
       <c r="R23" s="25">
         <v>-146</v>
@@ -2917,27 +2917,27 @@
       <c r="J24" s="30"/>
       <c r="K24">
         <f t="shared" ca="1" si="7"/>
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="8"/>
-        <v>2.3600000000000065</v>
+        <v>0.65999999999999659</v>
       </c>
       <c r="M24">
         <f t="shared" ca="1" si="9"/>
-        <v>1.3300000000000054</v>
+        <v>1.5300000000000011</v>
       </c>
       <c r="N24">
         <f t="shared" ca="1" si="4"/>
-        <v>2.7099999999999937</v>
+        <v>1.8199999999999932</v>
       </c>
       <c r="O24">
         <f t="shared" ca="1" si="5"/>
-        <v>0.76000000000000512</v>
+        <v>2.3600000000000065</v>
       </c>
       <c r="P24">
         <f t="shared" ca="1" si="6"/>
-        <v>2.1999999999999886</v>
+        <v>1.3300000000000054</v>
       </c>
       <c r="R24" s="25">
         <v>-6</v>
@@ -2981,27 +2981,27 @@
       </c>
       <c r="K25">
         <f t="shared" ca="1" si="7"/>
-        <v>3.77</v>
+        <v>3.73</v>
       </c>
       <c r="L25">
         <f t="shared" ca="1" si="8"/>
-        <v>6.2999999999999829</v>
+        <v>0.75</v>
       </c>
       <c r="M25">
         <f t="shared" ca="1" si="9"/>
-        <v>2.8999999999999773</v>
+        <v>3.6500000000000057</v>
       </c>
       <c r="N25">
         <f t="shared" ca="1" si="4"/>
-        <v>3.0499999999999829</v>
+        <v>5.0500000000000114</v>
       </c>
       <c r="O25">
         <f t="shared" ca="1" si="5"/>
-        <v>2.2000000000000171</v>
+        <v>6.2999999999999829</v>
       </c>
       <c r="P25">
         <f t="shared" ca="1" si="6"/>
-        <v>4.4000000000000057</v>
+        <v>2.8999999999999773</v>
       </c>
       <c r="R25" s="25">
         <v>-149</v>
@@ -3043,27 +3043,27 @@
       <c r="J26" s="30"/>
       <c r="K26">
         <f t="shared" ca="1" si="7"/>
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="L26">
         <f t="shared" ca="1" si="8"/>
-        <v>1.6800000000000068</v>
+        <v>0.59999999999999432</v>
       </c>
       <c r="M26">
         <f t="shared" ca="1" si="9"/>
-        <v>2.2800000000000011</v>
+        <v>1.7000000000000028</v>
       </c>
       <c r="N26">
         <f t="shared" ca="1" si="4"/>
-        <v>2.4200000000000017</v>
+        <v>1.8200000000000074</v>
       </c>
       <c r="O26">
         <f t="shared" ca="1" si="5"/>
-        <v>1.5799999999999983</v>
+        <v>1.6800000000000068</v>
       </c>
       <c r="P26">
         <f t="shared" ca="1" si="6"/>
-        <v>1.3799999999999955</v>
+        <v>2.2800000000000011</v>
       </c>
       <c r="R26" s="29">
         <v>23</v>
@@ -3103,31 +3103,31 @@
       </c>
       <c r="I27" s="24"/>
       <c r="J27" s="30">
-        <v>46062</v>
+        <v>46133</v>
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="7"/>
-        <v>28.98</v>
+        <v>29.46</v>
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="8"/>
-        <v>20.5</v>
+        <v>15</v>
       </c>
       <c r="M27">
         <f t="shared" ca="1" si="9"/>
-        <v>32.5</v>
+        <v>52.700000000000045</v>
       </c>
       <c r="N27">
         <f t="shared" ca="1" si="4"/>
-        <v>37</v>
+        <v>26.600000000000136</v>
       </c>
       <c r="O27">
         <f t="shared" ca="1" si="5"/>
-        <v>26.299999999999955</v>
+        <v>20.5</v>
       </c>
       <c r="P27">
         <f t="shared" ca="1" si="6"/>
-        <v>28.600000000000136</v>
+        <v>32.5</v>
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="29">
@@ -3163,31 +3163,31 @@
       </c>
       <c r="I28" s="23"/>
       <c r="J28" s="30">
-        <v>46058</v>
+        <v>46133</v>
       </c>
       <c r="K28">
         <f t="shared" ca="1" si="7"/>
-        <v>107.4</v>
+        <v>90.8</v>
       </c>
       <c r="L28">
         <f t="shared" ca="1" si="8"/>
-        <v>145.5</v>
+        <v>19.5</v>
       </c>
       <c r="M28">
         <f t="shared" ca="1" si="9"/>
-        <v>86.5</v>
+        <v>50</v>
       </c>
       <c r="N28">
         <f t="shared" ca="1" si="4"/>
-        <v>116.5</v>
+        <v>152.5</v>
       </c>
       <c r="O28">
         <f t="shared" ca="1" si="5"/>
-        <v>54.5</v>
+        <v>145.5</v>
       </c>
       <c r="P28">
         <f t="shared" ca="1" si="6"/>
-        <v>134</v>
+        <v>86.5</v>
       </c>
       <c r="R28" s="25">
         <v>-6</v>
@@ -3228,27 +3228,27 @@
       <c r="I29" s="24"/>
       <c r="K29">
         <f t="shared" ca="1" si="7"/>
-        <v>30.48</v>
+        <v>20.440000000000001</v>
       </c>
       <c r="L29">
         <f t="shared" ca="1" si="8"/>
-        <v>26</v>
+        <v>6.6000000000001364</v>
       </c>
       <c r="M29">
         <f t="shared" ca="1" si="9"/>
-        <v>22</v>
+        <v>24.799999999999955</v>
       </c>
       <c r="N29">
         <f t="shared" ca="1" si="4"/>
-        <v>37.599999999999909</v>
+        <v>22.799999999999955</v>
       </c>
       <c r="O29">
         <f t="shared" ca="1" si="5"/>
-        <v>39.399999999999864</v>
+        <v>26</v>
       </c>
       <c r="P29">
         <f t="shared" ca="1" si="6"/>
-        <v>27.399999999999864</v>
+        <v>22</v>
       </c>
       <c r="R29" s="1"/>
       <c r="S29" s="25">
@@ -3285,27 +3285,27 @@
       <c r="I30" s="24"/>
       <c r="K30">
         <f t="shared" ca="1" si="7"/>
-        <v>181.6</v>
+        <v>154</v>
       </c>
       <c r="L30">
         <f t="shared" ca="1" si="8"/>
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="M30">
         <f t="shared" ca="1" si="9"/>
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="N30">
         <f t="shared" ca="1" si="4"/>
-        <v>227</v>
+        <v>145</v>
       </c>
       <c r="O30">
         <f t="shared" ca="1" si="5"/>
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="P30">
         <f t="shared" ca="1" si="6"/>
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="R30" s="25">
         <v>-31</v>
@@ -3347,27 +3347,27 @@
       </c>
       <c r="K31">
         <f t="shared" ca="1" si="7"/>
-        <v>3.74</v>
+        <v>3.86</v>
       </c>
       <c r="L31">
         <f t="shared" ca="1" si="8"/>
-        <v>3.8999999999999773</v>
+        <v>2.1000000000000227</v>
       </c>
       <c r="M31">
         <f t="shared" ca="1" si="9"/>
-        <v>5.9000000000000909</v>
+        <v>3.2999999999999545</v>
       </c>
       <c r="N31">
         <f t="shared" ca="1" si="4"/>
-        <v>2.2999999999999545</v>
+        <v>4.1000000000000227</v>
       </c>
       <c r="O31">
         <f t="shared" ca="1" si="5"/>
-        <v>2.9000000000000909</v>
+        <v>3.8999999999999773</v>
       </c>
       <c r="P31">
         <f t="shared" ca="1" si="6"/>
-        <v>3.7000000000000455</v>
+        <v>5.9000000000000909</v>
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="29">
@@ -3405,31 +3405,31 @@
       </c>
       <c r="I32" s="24"/>
       <c r="J32" s="30">
-        <v>46063</v>
+        <v>46133</v>
       </c>
       <c r="K32">
         <f t="shared" ca="1" si="7"/>
-        <v>67.680000000000007</v>
+        <v>57.08</v>
       </c>
       <c r="L32">
         <f t="shared" ca="1" si="8"/>
-        <v>55.200000000000273</v>
+        <v>34.400000000000091</v>
       </c>
       <c r="M32">
         <f t="shared" ca="1" si="9"/>
-        <v>87.800000000000182</v>
+        <v>71.599999999999909</v>
       </c>
       <c r="N32">
         <f t="shared" ca="1" si="4"/>
-        <v>46.199999999999818</v>
+        <v>36.400000000000091</v>
       </c>
       <c r="O32">
         <f t="shared" ca="1" si="5"/>
-        <v>79.400000000000091</v>
+        <v>55.200000000000273</v>
       </c>
       <c r="P32">
         <f t="shared" ca="1" si="6"/>
-        <v>69.800000000000182</v>
+        <v>87.800000000000182</v>
       </c>
       <c r="R32" s="25">
         <v>-68</v>
@@ -3468,27 +3468,27 @@
       <c r="I33" s="24"/>
       <c r="K33">
         <f t="shared" ca="1" si="7"/>
-        <v>4.4400000000000004</v>
+        <v>4.38</v>
       </c>
       <c r="L33">
         <f t="shared" ca="1" si="8"/>
-        <v>2.9499999999999886</v>
+        <v>2.9000000000000057</v>
       </c>
       <c r="M33">
         <f t="shared" ca="1" si="9"/>
-        <v>3</v>
+        <v>11.400000000000006</v>
       </c>
       <c r="N33">
         <f t="shared" ca="1" si="4"/>
-        <v>6.3500000000000085</v>
+        <v>1.6499999999999915</v>
       </c>
       <c r="O33">
         <f t="shared" ca="1" si="5"/>
-        <v>6.2999999999999972</v>
+        <v>2.9499999999999886</v>
       </c>
       <c r="P33">
         <f t="shared" ca="1" si="6"/>
-        <v>3.5999999999999943</v>
+        <v>3</v>
       </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
@@ -3524,31 +3524,31 @@
       </c>
       <c r="I34" s="23"/>
       <c r="J34" s="30">
-        <v>46062</v>
+        <v>46133</v>
       </c>
       <c r="K34">
         <f t="shared" ca="1" si="7"/>
-        <v>12.23</v>
+        <v>10.71</v>
       </c>
       <c r="L34">
         <f t="shared" ca="1" si="8"/>
-        <v>6</v>
+        <v>6.9499999999999886</v>
       </c>
       <c r="M34">
         <f t="shared" ca="1" si="9"/>
-        <v>12</v>
+        <v>24.600000000000023</v>
       </c>
       <c r="N34">
         <f t="shared" ca="1" si="4"/>
-        <v>17.75</v>
+        <v>4</v>
       </c>
       <c r="O34">
         <f t="shared" ca="1" si="5"/>
-        <v>11.050000000000011</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <f t="shared" ca="1" si="6"/>
-        <v>14.349999999999966</v>
+        <v>12</v>
       </c>
       <c r="R34" s="29">
         <v>342</v>
@@ -3588,31 +3588,31 @@
       </c>
       <c r="I35" s="24"/>
       <c r="J35" s="30">
-        <v>46062</v>
+        <v>46133</v>
       </c>
       <c r="K35">
         <f t="shared" ca="1" si="7"/>
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="L35">
         <f t="shared" ca="1" si="8"/>
-        <v>1.4549999999999983</v>
+        <v>0.81000000000000227</v>
       </c>
       <c r="M35">
         <f t="shared" ca="1" si="9"/>
-        <v>1.7199999999999989</v>
+        <v>1.9899999999999949</v>
       </c>
       <c r="N35">
         <f t="shared" ca="1" si="4"/>
-        <v>1.3599999999999994</v>
+        <v>0.99000000000000199</v>
       </c>
       <c r="O35">
         <f t="shared" ca="1" si="5"/>
-        <v>0.67999999999999972</v>
+        <v>1.4549999999999983</v>
       </c>
       <c r="P35">
         <f t="shared" ca="1" si="6"/>
-        <v>0.91000000000000369</v>
+        <v>1.7199999999999989</v>
       </c>
       <c r="R35" s="1"/>
       <c r="S35" s="25">
@@ -3636,41 +3636,43 @@
         <v>0.01</v>
       </c>
       <c r="F36" s="22">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G36" s="26">
         <f t="shared" si="14"/>
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="H36" s="22">
         <f t="shared" si="12"/>
         <v>60</v>
       </c>
       <c r="I36" s="23"/>
-      <c r="J36" s="30"/>
+      <c r="J36" s="30">
+        <v>46133</v>
+      </c>
       <c r="K36">
         <f t="shared" ca="1" si="7"/>
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="8"/>
-        <v>5.2100000000000364</v>
+        <v>1.2900000000000205</v>
       </c>
       <c r="M36">
         <f t="shared" ca="1" si="9"/>
-        <v>2.6000000000000227</v>
+        <v>3.5799999999999841</v>
       </c>
       <c r="N36">
         <f t="shared" ca="1" si="4"/>
-        <v>2.4399999999999977</v>
+        <v>4.7899999999999636</v>
       </c>
       <c r="O36">
         <f t="shared" ca="1" si="5"/>
-        <v>2.2200000000000273</v>
+        <v>5.2100000000000364</v>
       </c>
       <c r="P36">
         <f t="shared" ca="1" si="6"/>
-        <v>4.8600000000000136</v>
+        <v>2.6000000000000227</v>
       </c>
       <c r="R36" s="29">
         <v>32</v>
@@ -3714,27 +3716,27 @@
       </c>
       <c r="K37">
         <f t="shared" ca="1" si="7"/>
-        <v>55.68</v>
+        <v>15.12</v>
       </c>
       <c r="L37">
         <f t="shared" ca="1" si="8"/>
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="M37">
         <f t="shared" ca="1" si="9"/>
-        <v>17.600000000000023</v>
+        <v>14</v>
       </c>
       <c r="N37">
         <f t="shared" ca="1" si="4"/>
-        <v>35.799999999999955</v>
+        <v>13</v>
       </c>
       <c r="O37">
         <f t="shared" ca="1" si="5"/>
-        <v>176</v>
+        <v>25</v>
       </c>
       <c r="P37">
         <f t="shared" ca="1" si="6"/>
-        <v>24</v>
+        <v>17.600000000000023</v>
       </c>
       <c r="R37" s="25">
         <v>-89</v>
@@ -3773,27 +3775,27 @@
       <c r="I38" s="24"/>
       <c r="K38">
         <f t="shared" ca="1" si="7"/>
-        <v>-16728.509999999998</v>
+        <v>0.05</v>
       </c>
       <c r="L38">
         <f t="shared" ca="1" si="8"/>
-        <v>3.5499999999999865E-2</v>
+        <v>3.400000000000003E-2</v>
       </c>
       <c r="M38">
         <f t="shared" ca="1" si="9"/>
-        <v>2.100000000000013E-2</v>
+        <v>9.6999999999999975E-2</v>
       </c>
       <c r="N38">
         <f t="shared" ca="1" si="4"/>
-        <v>-41638.828500000003</v>
+        <v>6.9499999999999895E-2</v>
       </c>
       <c r="O38">
         <f t="shared" ca="1" si="5"/>
-        <v>-42003.820500000002</v>
+        <v>3.5499999999999865E-2</v>
       </c>
       <c r="P38">
         <f t="shared" ca="1" si="6"/>
-        <v>3.2000000000000028E-2</v>
+        <v>2.100000000000013E-2</v>
       </c>
       <c r="R38" s="29">
         <v>71</v>
@@ -3830,27 +3832,27 @@
       <c r="I39" s="24"/>
       <c r="K39">
         <f t="shared" ca="1" si="7"/>
-        <v>11.96</v>
+        <v>11.91</v>
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="8"/>
-        <v>6.8999999999999773</v>
+        <v>11.850000000000023</v>
       </c>
       <c r="M39">
         <f t="shared" ca="1" si="9"/>
-        <v>9</v>
+        <v>24.049999999999955</v>
       </c>
       <c r="N39">
         <f t="shared" ca="1" si="4"/>
-        <v>20.799999999999955</v>
+        <v>7.75</v>
       </c>
       <c r="O39">
         <f t="shared" ca="1" si="5"/>
-        <v>11.399999999999977</v>
+        <v>6.8999999999999773</v>
       </c>
       <c r="P39">
         <f t="shared" ca="1" si="6"/>
-        <v>11.699999999999932</v>
+        <v>9</v>
       </c>
       <c r="R39" s="25">
         <v>-9</v>
@@ -3888,31 +3890,31 @@
       </c>
       <c r="I40" s="24"/>
       <c r="J40" s="30">
-        <v>46058</v>
+        <v>46133</v>
       </c>
       <c r="K40">
         <f t="shared" ca="1" si="7"/>
-        <v>42.88</v>
+        <v>28.6</v>
       </c>
       <c r="L40">
         <f t="shared" ca="1" si="8"/>
-        <v>45.399999999999977</v>
+        <v>7.7999999999999545</v>
       </c>
       <c r="M40">
         <f t="shared" ca="1" si="9"/>
-        <v>45.399999999999977</v>
+        <v>17</v>
       </c>
       <c r="N40">
         <f t="shared" ca="1" si="4"/>
-        <v>66.799999999999955</v>
+        <v>27.399999999999977</v>
       </c>
       <c r="O40">
         <f t="shared" ca="1" si="5"/>
-        <v>23.799999999999955</v>
+        <v>45.399999999999977</v>
       </c>
       <c r="P40">
         <f t="shared" ca="1" si="6"/>
-        <v>33</v>
+        <v>45.399999999999977</v>
       </c>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
@@ -3949,27 +3951,27 @@
       <c r="I41" s="24"/>
       <c r="K41">
         <f t="shared" ca="1" si="7"/>
-        <v>9204.84</v>
+        <v>-9228.0400000000009</v>
       </c>
       <c r="L41">
         <f t="shared" ca="1" si="8"/>
-        <v>0.34999999999999787</v>
+        <v>0.19000000000000128</v>
       </c>
       <c r="M41">
         <f t="shared" ca="1" si="9"/>
-        <v>0.34499999999999886</v>
+        <v>-46141.48</v>
       </c>
       <c r="N41">
         <f t="shared" ca="1" si="4"/>
-        <v>46022.75</v>
+        <v>0.375</v>
       </c>
       <c r="O41">
         <f t="shared" ca="1" si="5"/>
-        <v>0.32499999999999929</v>
+        <v>0.34999999999999787</v>
       </c>
       <c r="P41">
         <f t="shared" ca="1" si="6"/>
-        <v>0.42499999999999716</v>
+        <v>0.34499999999999886</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -3998,29 +4000,32 @@
         <v>33</v>
       </c>
       <c r="I42" s="24"/>
+      <c r="J42" s="30">
+        <v>46133</v>
+      </c>
       <c r="K42">
         <f t="shared" ca="1" si="7"/>
-        <v>1.1000000000000001</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="8"/>
-        <v>0.99000000000000199</v>
+        <v>0.49000000000000199</v>
       </c>
       <c r="M42">
         <f t="shared" ca="1" si="9"/>
-        <v>1.0500000000000043</v>
+        <v>1.5</v>
       </c>
       <c r="N42">
         <f t="shared" ca="1" si="4"/>
-        <v>1.5150000000000006</v>
+        <v>1.6850000000000023</v>
       </c>
       <c r="O42">
         <f t="shared" ca="1" si="5"/>
-        <v>0.78000000000000114</v>
+        <v>0.99000000000000199</v>
       </c>
       <c r="P42">
         <f t="shared" ca="1" si="6"/>
-        <v>1.1599999999999966</v>
+        <v>1.0500000000000043</v>
       </c>
       <c r="R42" s="25">
         <v>-18</v>
@@ -4061,27 +4066,27 @@
       <c r="I43" s="24"/>
       <c r="K43">
         <f t="shared" ca="1" si="7"/>
-        <v>20.100000000000001</v>
+        <v>18.98</v>
       </c>
       <c r="L43">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B43&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B43&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>15.399999999999977</v>
+        <v>11.600000000000023</v>
       </c>
       <c r="M43">
         <f t="shared" ca="1" si="9"/>
-        <v>18.299999999999955</v>
+        <v>34.599999999999909</v>
       </c>
       <c r="N43">
         <f t="shared" ca="1" si="4"/>
-        <v>30.299999999999955</v>
+        <v>15</v>
       </c>
       <c r="O43">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>15.399999999999977</v>
       </c>
       <c r="P43">
         <f t="shared" ca="1" si="6"/>
-        <v>19.5</v>
+        <v>18.299999999999955</v>
       </c>
       <c r="R43" s="25">
         <v>-114</v>
@@ -4120,27 +4125,27 @@
       <c r="I44" s="24"/>
       <c r="K44">
         <f t="shared" ca="1" si="7"/>
-        <v>2.37</v>
+        <v>2.68</v>
       </c>
       <c r="L44">
         <f t="shared" ca="1" si="8"/>
-        <v>4.4200000000000017</v>
+        <v>0.90000000000000568</v>
       </c>
       <c r="M44">
         <f t="shared" ca="1" si="9"/>
-        <v>1.6199999999999903</v>
+        <v>2.1599999999999966</v>
       </c>
       <c r="N44">
         <f t="shared" ca="1" si="4"/>
-        <v>1.7999999999999972</v>
+        <v>4.3200000000000074</v>
       </c>
       <c r="O44">
         <f t="shared" ca="1" si="5"/>
-        <v>1.4399999999999977</v>
+        <v>4.4200000000000017</v>
       </c>
       <c r="P44">
         <f t="shared" ca="1" si="6"/>
-        <v>2.5799999999999983</v>
+        <v>1.6199999999999903</v>
       </c>
       <c r="R44" s="29">
         <v>7</v>
@@ -4179,27 +4184,27 @@
       <c r="I45" s="24"/>
       <c r="K45">
         <f t="shared" ca="1" si="7"/>
-        <v>21.12</v>
+        <v>16.32</v>
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="8"/>
-        <v>18.599999999999909</v>
+        <v>10.399999999999864</v>
       </c>
       <c r="M45">
         <f t="shared" ca="1" si="9"/>
-        <v>19.400000000000091</v>
+        <v>16.799999999999955</v>
       </c>
       <c r="N45">
         <f t="shared" ca="1" si="4"/>
-        <v>25.799999999999955</v>
+        <v>16.400000000000091</v>
       </c>
       <c r="O45">
         <f t="shared" ca="1" si="5"/>
-        <v>17.599999999999909</v>
+        <v>18.599999999999909</v>
       </c>
       <c r="P45">
         <f t="shared" ca="1" si="6"/>
-        <v>24.200000000000045</v>
+        <v>19.400000000000091</v>
       </c>
       <c r="R45" s="1"/>
       <c r="S45" s="25">
@@ -4237,31 +4242,31 @@
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="30">
-        <v>46057</v>
+        <v>46133</v>
       </c>
       <c r="K46">
         <f ca="1">ROUND(AVERAGE(L46:P46),4)</f>
-        <v>1.83E-2</v>
+        <v>3.2500000000000001E-2</v>
       </c>
       <c r="L46">
         <f t="shared" ca="1" si="8"/>
-        <v>1.2800000000000034E-2</v>
+        <v>2.3800000000000043E-2</v>
       </c>
       <c r="M46">
         <f t="shared" ca="1" si="9"/>
-        <v>2.5799999999999934E-2</v>
+        <v>4.3300000000000005E-2</v>
       </c>
       <c r="N46">
         <f t="shared" ca="1" si="4"/>
-        <v>1.4000000000000012E-2</v>
+        <v>5.699999999999994E-2</v>
       </c>
       <c r="O46">
         <f t="shared" ca="1" si="5"/>
-        <v>2.1100000000000008E-2</v>
+        <v>1.2800000000000034E-2</v>
       </c>
       <c r="P46">
         <f t="shared" ca="1" si="6"/>
-        <v>1.7700000000000049E-2</v>
+        <v>2.5799999999999934E-2</v>
       </c>
       <c r="R46" s="1"/>
       <c r="S46" s="22"/>
@@ -4299,27 +4304,27 @@
       </c>
       <c r="K47">
         <f t="shared" ca="1" si="7"/>
-        <v>7.4</v>
+        <v>6.21</v>
       </c>
       <c r="L47">
         <f t="shared" ca="1" si="8"/>
-        <v>7.0500000000000114</v>
+        <v>1.3000000000000114</v>
       </c>
       <c r="M47">
         <f t="shared" ca="1" si="9"/>
-        <v>5.1000000000000227</v>
+        <v>7.6499999999999773</v>
       </c>
       <c r="N47">
         <f t="shared" ca="1" si="4"/>
-        <v>8.6499999999999773</v>
+        <v>9.9500000000000455</v>
       </c>
       <c r="O47">
         <f t="shared" ca="1" si="5"/>
-        <v>6.3999999999999773</v>
+        <v>7.0500000000000114</v>
       </c>
       <c r="P47">
         <f t="shared" ca="1" si="6"/>
-        <v>9.8000000000000114</v>
+        <v>5.1000000000000227</v>
       </c>
       <c r="R47" s="1"/>
       <c r="S47" s="29">
@@ -4362,27 +4367,27 @@
       </c>
       <c r="K48">
         <f t="shared" ca="1" si="7"/>
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="L48">
         <f t="shared" ca="1" si="8"/>
-        <v>2.5799999999999983</v>
+        <v>0.43500000000000227</v>
       </c>
       <c r="M48">
         <f t="shared" ca="1" si="9"/>
-        <v>1.4399999999999977</v>
+        <v>1.8349999999999937</v>
       </c>
       <c r="N48">
         <f t="shared" ca="1" si="4"/>
-        <v>1.644999999999996</v>
+        <v>2.4100000000000108</v>
       </c>
       <c r="O48">
         <f t="shared" ca="1" si="5"/>
-        <v>1.7000000000000028</v>
+        <v>2.5799999999999983</v>
       </c>
       <c r="P48">
         <f t="shared" ca="1" si="6"/>
-        <v>1.7900000000000063</v>
+        <v>1.4399999999999977</v>
       </c>
       <c r="R48" s="29">
         <v>19</v>
@@ -4420,15 +4425,15 @@
       </c>
       <c r="I49" s="24"/>
       <c r="J49" s="30">
-        <v>46063</v>
+        <v>46133</v>
       </c>
       <c r="K49">
         <f t="shared" ca="1" si="7"/>
-        <v>33.6</v>
+        <v>28.6</v>
       </c>
       <c r="L49">
         <f t="shared" ca="1" si="8"/>
-        <v>42.5</v>
+        <v>11</v>
       </c>
       <c r="M49">
         <f t="shared" ca="1" si="9"/>
@@ -4436,15 +4441,15 @@
       </c>
       <c r="N49">
         <f t="shared" ca="1" si="4"/>
-        <v>52.5</v>
+        <v>50.5</v>
       </c>
       <c r="O49">
         <f t="shared" ca="1" si="5"/>
-        <v>20.5</v>
+        <v>42.5</v>
       </c>
       <c r="P49">
         <f t="shared" ca="1" si="6"/>
-        <v>33</v>
+        <v>19.5</v>
       </c>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
@@ -4478,31 +4483,31 @@
       </c>
       <c r="I50" s="23"/>
       <c r="J50" s="30">
-        <v>46069</v>
+        <v>46133</v>
       </c>
       <c r="K50">
         <f t="shared" ca="1" si="7"/>
-        <v>110</v>
+        <v>96.6</v>
       </c>
       <c r="L50">
         <f t="shared" ca="1" si="8"/>
-        <v>164</v>
+        <v>18</v>
       </c>
       <c r="M50">
         <f t="shared" ca="1" si="9"/>
-        <v>118.5</v>
+        <v>87.5</v>
       </c>
       <c r="N50">
         <f t="shared" ca="1" si="4"/>
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="O50">
         <f t="shared" ca="1" si="5"/>
-        <v>53.5</v>
+        <v>164</v>
       </c>
       <c r="P50">
         <f t="shared" ca="1" si="6"/>
-        <v>111</v>
+        <v>118.5</v>
       </c>
       <c r="R50" s="1">
         <v>-97</v>

--- a/calc.xlsx
+++ b/calc.xlsx
@@ -1834,23 +1834,23 @@
     <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="L6" s="5" t="str">
         <f ca="1">TEXT(L7,"ддд")</f>
-        <v>Сб</v>
+        <v>Ср</v>
       </c>
       <c r="M6" s="5" t="str">
         <f ca="1">TEXT(M7,"ддд")</f>
-        <v>Пт</v>
+        <v>Вт</v>
       </c>
       <c r="N6" s="5" t="str">
         <f t="shared" ref="N6:P6" ca="1" si="0">TEXT(N7,"ддд")</f>
-        <v>Чт</v>
+        <v>Пн</v>
       </c>
       <c r="O6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Ср</v>
+        <v>Пт</v>
       </c>
       <c r="P6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Вт</v>
+        <v>Чт</v>
       </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.25">
@@ -1883,24 +1883,24 @@
         <v>78</v>
       </c>
       <c r="L7" s="1" t="str">
+        <f ca="1">TEXT(TODAY()-1, "ГГГГ-ММ-ДД")</f>
+        <v>2026-04-22</v>
+      </c>
+      <c r="M7" s="1" t="str">
+        <f ca="1">TEXT(TODAY()-2, "ГГГГ-ММ-ДД")</f>
+        <v>2026-04-21</v>
+      </c>
+      <c r="N7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-3, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-18</v>
-      </c>
-      <c r="M7" s="1" t="str">
-        <f ca="1">TEXT(TODAY()-4, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-17</v>
-      </c>
-      <c r="N7" s="1" t="str">
-        <f ca="1">TEXT(TODAY()-5, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-16</v>
+        <v>2026-04-20</v>
       </c>
       <c r="O7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-6, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-15</v>
+        <v>2026-04-17</v>
       </c>
       <c r="P7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-7, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-14</v>
+        <v>2026-04-16</v>
       </c>
       <c r="R7" s="28">
         <v>45566</v>
@@ -1942,31 +1942,31 @@
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="30">
-        <v>46069</v>
+        <v>46135</v>
       </c>
       <c r="K8">
         <f ca="1">ROUND(AVERAGE(L8:P8),2)</f>
-        <v>15242.5</v>
+        <v>10382.74</v>
       </c>
       <c r="L8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>5.099999999999838E-2</v>
+        <v>17490.069</v>
       </c>
       <c r="M8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>19681.812999999998</v>
+        <v>14741</v>
       </c>
       <c r="N8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.4789999999999992</v>
+        <v>0.31900000000000084</v>
       </c>
       <c r="O8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>14203.084000000001</v>
+        <v>19681.812999999998</v>
       </c>
       <c r="P8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>42327.093999999997</v>
+        <v>0.4789999999999992</v>
       </c>
       <c r="R8" s="29">
         <v>54</v>
@@ -2010,27 +2010,27 @@
       </c>
       <c r="K9">
         <f ca="1">ROUND(AVERAGE(L9:P9),2)</f>
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="L9">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.57999999999999829</v>
+        <v>0.66000000000000369</v>
       </c>
       <c r="M9">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.7199999999999989</v>
+        <v>1.2700000000000031</v>
       </c>
       <c r="N9">
         <f t="shared" ref="N9:N50" ca="1" si="4">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.0900000000000034</v>
+        <v>1.6799999999999997</v>
       </c>
       <c r="O9">
         <f t="shared" ref="O9:O50" ca="1" si="5">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.7100000000000009</v>
+        <v>1.7199999999999989</v>
       </c>
       <c r="P9">
         <f t="shared" ref="P9:P50" ca="1" si="6">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.92000000000000171</v>
+        <v>1.0900000000000034</v>
       </c>
       <c r="R9" s="25">
         <v>-30</v>
@@ -2071,27 +2071,27 @@
       <c r="I10" s="24"/>
       <c r="K10">
         <f ca="1">ROUND(AVERAGE(L10:P10),2)</f>
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="L10">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.21999999999999886</v>
+        <v>0.92999999999999972</v>
       </c>
       <c r="M10">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.1499999999999986</v>
+        <v>0.83000000000000185</v>
       </c>
       <c r="N10">
         <f t="shared" ca="1" si="4"/>
-        <v>0.52000000000000313</v>
+        <v>0.80000000000000071</v>
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="5"/>
-        <v>0.96000000000000085</v>
+        <v>1.1499999999999986</v>
       </c>
       <c r="P10">
         <f t="shared" ca="1" si="6"/>
-        <v>0.96000000000000085</v>
+        <v>0.52000000000000313</v>
       </c>
       <c r="R10" s="29">
         <v>39</v>
@@ -2135,27 +2135,27 @@
       </c>
       <c r="K11">
         <f ca="1">ROUND(AVERAGE(L11:P11),2)</f>
-        <v>5.54</v>
+        <v>5.08</v>
       </c>
       <c r="L11">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.8299999999999841</v>
+        <v>2.2300000000000182</v>
       </c>
       <c r="M11">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>7.089999999999975</v>
+        <v>3.5600000000000023</v>
       </c>
       <c r="N11">
         <f t="shared" ca="1" si="4"/>
-        <v>8.1000000000000227</v>
+        <v>4.4300000000000068</v>
       </c>
       <c r="O11">
         <f t="shared" ca="1" si="5"/>
-        <v>4.8000000000000114</v>
+        <v>7.089999999999975</v>
       </c>
       <c r="P11">
         <f t="shared" ca="1" si="6"/>
-        <v>5.9000000000000341</v>
+        <v>8.1000000000000227</v>
       </c>
       <c r="R11" s="29"/>
       <c r="S11" s="29"/>
@@ -2193,27 +2193,27 @@
       </c>
       <c r="K12" s="24">
         <f ca="1">ROUND(AVERAGE(L12:P12),2)</f>
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="L12" s="24">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.45000000000000284</v>
+        <v>1</v>
       </c>
       <c r="M12" s="24">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>2.25</v>
+        <v>0.89999999999999858</v>
       </c>
       <c r="N12" s="24">
         <f t="shared" ca="1" si="4"/>
-        <v>3.0500000000000043</v>
+        <v>0.45000000000000284</v>
       </c>
       <c r="O12" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>0.64999999999999858</v>
+        <v>2.25</v>
       </c>
       <c r="P12" s="24">
         <f t="shared" ca="1" si="6"/>
-        <v>0.94999999999999574</v>
+        <v>3.0500000000000043</v>
       </c>
       <c r="R12" s="29"/>
       <c r="S12" s="29"/>
@@ -2246,29 +2246,32 @@
         <v>25</v>
       </c>
       <c r="I13" s="23"/>
+      <c r="J13" s="30">
+        <v>46135</v>
+      </c>
       <c r="K13">
         <f t="shared" ref="K13:K50" ca="1" si="7">ROUND(AVERAGE(L13:P13),2)</f>
-        <v>17.079999999999998</v>
+        <v>19</v>
       </c>
       <c r="L13">
         <f t="shared" ref="L13:L50" ca="1" si="8">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>9.4000000000000909</v>
+        <v>30.399999999999977</v>
       </c>
       <c r="M13">
         <f t="shared" ref="M13:M50" ca="1" si="9">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>17</v>
+        <v>13.799999999999955</v>
       </c>
       <c r="N13">
         <f t="shared" ca="1" si="4"/>
-        <v>16.399999999999977</v>
+        <v>17.399999999999977</v>
       </c>
       <c r="O13">
         <f t="shared" ca="1" si="5"/>
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="P13">
         <f t="shared" ca="1" si="6"/>
-        <v>17.600000000000023</v>
+        <v>16.399999999999977</v>
       </c>
       <c r="R13" s="29">
         <v>80</v>
@@ -2309,27 +2312,27 @@
       <c r="I14" s="24"/>
       <c r="K14">
         <f t="shared" ca="1" si="7"/>
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="8"/>
-        <v>0.56000000000000227</v>
+        <v>1.3900000000000006</v>
       </c>
       <c r="M14">
         <f t="shared" ca="1" si="9"/>
-        <v>1.0600000000000023</v>
+        <v>1.9000000000000057</v>
       </c>
       <c r="N14">
         <f t="shared" ca="1" si="4"/>
-        <v>2.269999999999996</v>
+        <v>1.6799999999999926</v>
       </c>
       <c r="O14">
         <f t="shared" ca="1" si="5"/>
-        <v>1.4100000000000108</v>
+        <v>1.0600000000000023</v>
       </c>
       <c r="P14">
         <f t="shared" ca="1" si="6"/>
-        <v>2.019999999999996</v>
+        <v>2.269999999999996</v>
       </c>
       <c r="R14" s="29">
         <v>27</v>
@@ -2368,27 +2371,27 @@
       <c r="I15" s="23"/>
       <c r="K15">
         <f t="shared" ca="1" si="7"/>
-        <v>3.83</v>
+        <v>10.36</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="8"/>
-        <v>0.85000000000000853</v>
+        <v>14.799999999999997</v>
       </c>
       <c r="M15">
         <f t="shared" ca="1" si="9"/>
-        <v>3.8500000000000085</v>
+        <v>12.350000000000001</v>
       </c>
       <c r="N15">
         <f t="shared" ca="1" si="4"/>
-        <v>4.7000000000000028</v>
+        <v>16.100000000000009</v>
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="5"/>
-        <v>2.5499999999999972</v>
+        <v>3.8500000000000085</v>
       </c>
       <c r="P15">
         <f t="shared" ca="1" si="6"/>
-        <v>7.2000000000000028</v>
+        <v>4.7000000000000028</v>
       </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
@@ -2426,27 +2429,27 @@
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="7"/>
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="8"/>
-        <v>1.0699999999999932</v>
+        <v>1.2099999999999937</v>
       </c>
       <c r="M16">
         <f t="shared" ca="1" si="9"/>
-        <v>4.7399999999999807</v>
+        <v>2.1400000000000006</v>
       </c>
       <c r="N16">
         <f t="shared" ca="1" si="4"/>
-        <v>1.9300000000000068</v>
+        <v>2.1700000000000017</v>
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="5"/>
-        <v>2.1500000000000199</v>
+        <v>4.7399999999999807</v>
       </c>
       <c r="P16">
         <f t="shared" ca="1" si="6"/>
-        <v>2.5999999999999943</v>
+        <v>1.9300000000000068</v>
       </c>
       <c r="R16" s="25">
         <v>-2</v>
@@ -2490,27 +2493,27 @@
       </c>
       <c r="K17">
         <f ca="1">ROUND(AVERAGE(L17:P17),5)</f>
-        <v>1.6100000000000001E-3</v>
+        <v>1.5499999999999999E-3</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="8"/>
-        <v>5.3999999999999881E-4</v>
+        <v>2.0000000000000018E-3</v>
       </c>
       <c r="M17">
         <f t="shared" ca="1" si="9"/>
-        <v>1.7599999999999977E-3</v>
+        <v>8.8000000000000578E-4</v>
       </c>
       <c r="N17">
         <f t="shared" ca="1" si="4"/>
-        <v>1.7199999999999993E-3</v>
+        <v>1.3799999999999923E-3</v>
       </c>
       <c r="O17">
         <f t="shared" ca="1" si="5"/>
-        <v>1.9000000000000128E-3</v>
+        <v>1.7599999999999977E-3</v>
       </c>
       <c r="P17">
         <f t="shared" ca="1" si="6"/>
-        <v>2.140000000000003E-3</v>
+        <v>1.7199999999999993E-3</v>
       </c>
       <c r="R17" s="25"/>
       <c r="S17" s="25"/>
@@ -2548,27 +2551,27 @@
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="7"/>
-        <v>3.35</v>
+        <v>3.69</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="8"/>
-        <v>2.1800000000000068</v>
+        <v>3.7199999999999989</v>
       </c>
       <c r="M18">
         <f t="shared" ca="1" si="9"/>
-        <v>3.2800000000000011</v>
+        <v>3.1800000000000068</v>
       </c>
       <c r="N18">
         <f t="shared" ca="1" si="4"/>
-        <v>3.1399999999999864</v>
+        <v>5.1400000000000148</v>
       </c>
       <c r="O18">
         <f t="shared" ca="1" si="5"/>
-        <v>3.5999999999999943</v>
+        <v>3.2800000000000011</v>
       </c>
       <c r="P18">
         <f t="shared" ca="1" si="6"/>
-        <v>4.539999999999992</v>
+        <v>3.1399999999999864</v>
       </c>
       <c r="R18" s="25">
         <v>-211</v>
@@ -2607,27 +2610,27 @@
       <c r="I19" s="24"/>
       <c r="K19">
         <f t="shared" ca="1" si="7"/>
-        <v>39227.040000000001</v>
+        <v>22791.03</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="8"/>
-        <v>36524</v>
+        <v>3.1000000000000139E-2</v>
       </c>
       <c r="M19">
         <f t="shared" ca="1" si="9"/>
-        <v>414607.76500000001</v>
+        <v>-35794</v>
       </c>
       <c r="N19">
         <f t="shared" ca="1" si="4"/>
-        <v>-264858.68699999998</v>
+        <v>5.500000000000016E-2</v>
       </c>
       <c r="O19">
         <f t="shared" ca="1" si="5"/>
-        <v>-43156.726999999999</v>
+        <v>414607.76500000001</v>
       </c>
       <c r="P19">
         <f t="shared" ca="1" si="6"/>
-        <v>53018.834000000003</v>
+        <v>-264858.68699999998</v>
       </c>
       <c r="R19" s="1"/>
       <c r="S19" s="25">
@@ -2667,27 +2670,27 @@
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="7"/>
-        <v>76.7</v>
+        <v>90.1</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="8"/>
-        <v>41.5</v>
+        <v>40.5</v>
       </c>
       <c r="M20">
         <f t="shared" ca="1" si="9"/>
-        <v>149.5</v>
+        <v>109.5</v>
       </c>
       <c r="N20">
         <f t="shared" ca="1" si="4"/>
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="O20">
         <f t="shared" ca="1" si="5"/>
-        <v>75</v>
+        <v>149.5</v>
       </c>
       <c r="P20">
         <f t="shared" ca="1" si="6"/>
-        <v>54.5</v>
+        <v>63</v>
       </c>
       <c r="R20" s="25">
         <v>-741</v>
@@ -2731,27 +2734,27 @@
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="7"/>
-        <v>18463.59</v>
+        <v>18433.419999999998</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="8"/>
-        <v>0.16000000000000014</v>
+        <v>0.98499999999999943</v>
       </c>
       <c r="M21">
         <f t="shared" ca="1" si="9"/>
-        <v>0.73499999999999943</v>
+        <v>0.45500000000000185</v>
       </c>
       <c r="N21">
         <f t="shared" ca="1" si="4"/>
-        <v>46142.264999999999</v>
+        <v>46022.635000000002</v>
       </c>
       <c r="O21">
         <f t="shared" ca="1" si="5"/>
-        <v>46173.845000000001</v>
+        <v>0.73499999999999943</v>
       </c>
       <c r="P21">
         <f t="shared" ca="1" si="6"/>
-        <v>0.92499999999999716</v>
+        <v>46142.264999999999</v>
       </c>
       <c r="R21" s="25">
         <v>-107</v>
@@ -2793,27 +2796,27 @@
       <c r="J22" s="30"/>
       <c r="K22">
         <f t="shared" ca="1" si="7"/>
-        <v>41.6</v>
+        <v>45.2</v>
       </c>
       <c r="L22">
         <f t="shared" ca="1" si="8"/>
-        <v>10.5</v>
+        <v>38.5</v>
       </c>
       <c r="M22">
         <f t="shared" ca="1" si="9"/>
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="N22">
         <f t="shared" ca="1" si="4"/>
-        <v>44</v>
+        <v>58.5</v>
       </c>
       <c r="O22">
         <f t="shared" ca="1" si="5"/>
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="P22">
         <f t="shared" ca="1" si="6"/>
-        <v>54.5</v>
+        <v>44</v>
       </c>
       <c r="R22" s="29">
         <v>45</v>
@@ -2855,27 +2858,27 @@
       <c r="J23" s="30"/>
       <c r="K23">
         <f t="shared" ca="1" si="7"/>
-        <v>2.39</v>
+        <v>3.18</v>
       </c>
       <c r="L23">
         <f t="shared" ca="1" si="8"/>
-        <v>0.48999999999998067</v>
+        <v>2.8000000000000114</v>
       </c>
       <c r="M23">
         <f t="shared" ca="1" si="9"/>
-        <v>1.5800000000000125</v>
+        <v>5.3899999999999864</v>
       </c>
       <c r="N23">
         <f t="shared" ca="1" si="4"/>
-        <v>2.9000000000000057</v>
+        <v>3.2199999999999989</v>
       </c>
       <c r="O23">
         <f t="shared" ca="1" si="5"/>
-        <v>3.6200000000000045</v>
+        <v>1.5800000000000125</v>
       </c>
       <c r="P23">
         <f t="shared" ca="1" si="6"/>
-        <v>3.3400000000000034</v>
+        <v>2.9000000000000057</v>
       </c>
       <c r="R23" s="25">
         <v>-146</v>
@@ -2917,27 +2920,27 @@
       <c r="J24" s="30"/>
       <c r="K24">
         <f t="shared" ca="1" si="7"/>
-        <v>1.54</v>
+        <v>2.13</v>
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="8"/>
-        <v>0.65999999999999659</v>
+        <v>2.0499999999999972</v>
       </c>
       <c r="M24">
         <f t="shared" ca="1" si="9"/>
-        <v>1.5300000000000011</v>
+        <v>2.1299999999999955</v>
       </c>
       <c r="N24">
         <f t="shared" ca="1" si="4"/>
-        <v>1.8199999999999932</v>
+        <v>3.1200000000000045</v>
       </c>
       <c r="O24">
         <f t="shared" ca="1" si="5"/>
-        <v>2.3600000000000065</v>
+        <v>1.5300000000000011</v>
       </c>
       <c r="P24">
         <f t="shared" ca="1" si="6"/>
-        <v>1.3300000000000054</v>
+        <v>1.8199999999999932</v>
       </c>
       <c r="R24" s="25">
         <v>-6</v>
@@ -2981,27 +2984,27 @@
       </c>
       <c r="K25">
         <f t="shared" ca="1" si="7"/>
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="L25">
         <f t="shared" ca="1" si="8"/>
-        <v>0.75</v>
+        <v>4.6499999999999773</v>
       </c>
       <c r="M25">
         <f t="shared" ca="1" si="9"/>
-        <v>3.6500000000000057</v>
+        <v>2.5499999999999829</v>
       </c>
       <c r="N25">
         <f t="shared" ca="1" si="4"/>
-        <v>5.0500000000000114</v>
+        <v>2.9499999999999886</v>
       </c>
       <c r="O25">
         <f t="shared" ca="1" si="5"/>
-        <v>6.2999999999999829</v>
+        <v>3.6500000000000057</v>
       </c>
       <c r="P25">
         <f t="shared" ca="1" si="6"/>
-        <v>2.8999999999999773</v>
+        <v>5.0500000000000114</v>
       </c>
       <c r="R25" s="25">
         <v>-149</v>
@@ -3043,27 +3046,27 @@
       <c r="J26" s="30"/>
       <c r="K26">
         <f t="shared" ca="1" si="7"/>
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="L26">
         <f t="shared" ca="1" si="8"/>
-        <v>0.59999999999999432</v>
+        <v>2.4599999999999937</v>
       </c>
       <c r="M26">
         <f t="shared" ca="1" si="9"/>
-        <v>1.7000000000000028</v>
+        <v>1.6599999999999966</v>
       </c>
       <c r="N26">
         <f t="shared" ca="1" si="4"/>
-        <v>1.8200000000000074</v>
+        <v>2.1199999999999903</v>
       </c>
       <c r="O26">
         <f t="shared" ca="1" si="5"/>
-        <v>1.6800000000000068</v>
+        <v>1.7000000000000028</v>
       </c>
       <c r="P26">
         <f t="shared" ca="1" si="6"/>
-        <v>2.2800000000000011</v>
+        <v>1.8200000000000074</v>
       </c>
       <c r="R26" s="29">
         <v>23</v>
@@ -3107,27 +3110,27 @@
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="7"/>
-        <v>29.46</v>
+        <v>33.1</v>
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="8"/>
-        <v>15</v>
+        <v>15.599999999999909</v>
       </c>
       <c r="M27">
         <f t="shared" ca="1" si="9"/>
-        <v>52.700000000000045</v>
+        <v>34.099999999999909</v>
       </c>
       <c r="N27">
         <f t="shared" ca="1" si="4"/>
-        <v>26.600000000000136</v>
+        <v>36.5</v>
       </c>
       <c r="O27">
         <f t="shared" ca="1" si="5"/>
-        <v>20.5</v>
+        <v>52.700000000000045</v>
       </c>
       <c r="P27">
         <f t="shared" ca="1" si="6"/>
-        <v>32.5</v>
+        <v>26.600000000000136</v>
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="29">
@@ -3167,27 +3170,27 @@
       </c>
       <c r="K28">
         <f t="shared" ca="1" si="7"/>
-        <v>90.8</v>
+        <v>92.1</v>
       </c>
       <c r="L28">
         <f t="shared" ca="1" si="8"/>
-        <v>19.5</v>
+        <v>76</v>
       </c>
       <c r="M28">
         <f t="shared" ca="1" si="9"/>
-        <v>50</v>
+        <v>67.5</v>
       </c>
       <c r="N28">
         <f t="shared" ca="1" si="4"/>
-        <v>152.5</v>
+        <v>114.5</v>
       </c>
       <c r="O28">
         <f t="shared" ca="1" si="5"/>
-        <v>145.5</v>
+        <v>50</v>
       </c>
       <c r="P28">
         <f t="shared" ca="1" si="6"/>
-        <v>86.5</v>
+        <v>152.5</v>
       </c>
       <c r="R28" s="25">
         <v>-6</v>
@@ -3228,27 +3231,27 @@
       <c r="I29" s="24"/>
       <c r="K29">
         <f t="shared" ca="1" si="7"/>
-        <v>20.440000000000001</v>
+        <v>23.92</v>
       </c>
       <c r="L29">
         <f t="shared" ca="1" si="8"/>
-        <v>6.6000000000001364</v>
+        <v>31</v>
       </c>
       <c r="M29">
         <f t="shared" ca="1" si="9"/>
-        <v>24.799999999999955</v>
+        <v>15.400000000000091</v>
       </c>
       <c r="N29">
         <f t="shared" ca="1" si="4"/>
-        <v>22.799999999999955</v>
+        <v>25.599999999999909</v>
       </c>
       <c r="O29">
         <f t="shared" ca="1" si="5"/>
-        <v>26</v>
+        <v>24.799999999999955</v>
       </c>
       <c r="P29">
         <f t="shared" ca="1" si="6"/>
-        <v>22</v>
+        <v>22.799999999999955</v>
       </c>
       <c r="R29" s="1"/>
       <c r="S29" s="25">
@@ -3285,27 +3288,27 @@
       <c r="I30" s="24"/>
       <c r="K30">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>151.4</v>
       </c>
       <c r="L30">
         <f t="shared" ca="1" si="8"/>
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="M30">
         <f t="shared" ca="1" si="9"/>
-        <v>221</v>
+        <v>150</v>
       </c>
       <c r="N30">
         <f t="shared" ca="1" si="4"/>
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="O30">
         <f t="shared" ca="1" si="5"/>
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="P30">
         <f t="shared" ca="1" si="6"/>
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="R30" s="25">
         <v>-31</v>
@@ -3347,27 +3350,27 @@
       </c>
       <c r="K31">
         <f t="shared" ca="1" si="7"/>
-        <v>3.86</v>
+        <v>2.94</v>
       </c>
       <c r="L31">
         <f t="shared" ca="1" si="8"/>
-        <v>2.1000000000000227</v>
+        <v>2.5</v>
       </c>
       <c r="M31">
         <f t="shared" ca="1" si="9"/>
-        <v>3.2999999999999545</v>
+        <v>2.3999999999999773</v>
       </c>
       <c r="N31">
         <f t="shared" ca="1" si="4"/>
-        <v>4.1000000000000227</v>
+        <v>2.3999999999999773</v>
       </c>
       <c r="O31">
         <f t="shared" ca="1" si="5"/>
-        <v>3.8999999999999773</v>
+        <v>3.2999999999999545</v>
       </c>
       <c r="P31">
         <f t="shared" ca="1" si="6"/>
-        <v>5.9000000000000909</v>
+        <v>4.1000000000000227</v>
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="29">
@@ -3409,27 +3412,27 @@
       </c>
       <c r="K32">
         <f t="shared" ca="1" si="7"/>
-        <v>57.08</v>
+        <v>54.52</v>
       </c>
       <c r="L32">
         <f t="shared" ca="1" si="8"/>
-        <v>34.400000000000091</v>
+        <v>35.800000000000182</v>
       </c>
       <c r="M32">
         <f t="shared" ca="1" si="9"/>
-        <v>71.599999999999909</v>
+        <v>44.800000000000182</v>
       </c>
       <c r="N32">
         <f t="shared" ca="1" si="4"/>
-        <v>36.400000000000091</v>
+        <v>84</v>
       </c>
       <c r="O32">
         <f t="shared" ca="1" si="5"/>
-        <v>55.200000000000273</v>
+        <v>71.599999999999909</v>
       </c>
       <c r="P32">
         <f t="shared" ca="1" si="6"/>
-        <v>87.800000000000182</v>
+        <v>36.400000000000091</v>
       </c>
       <c r="R32" s="25">
         <v>-68</v>
@@ -3468,27 +3471,27 @@
       <c r="I33" s="24"/>
       <c r="K33">
         <f t="shared" ca="1" si="7"/>
-        <v>4.38</v>
+        <v>5.16</v>
       </c>
       <c r="L33">
         <f t="shared" ca="1" si="8"/>
-        <v>2.9000000000000057</v>
+        <v>2.2000000000000028</v>
       </c>
       <c r="M33">
         <f t="shared" ca="1" si="9"/>
-        <v>11.400000000000006</v>
+        <v>6.0499999999999972</v>
       </c>
       <c r="N33">
         <f t="shared" ca="1" si="4"/>
-        <v>1.6499999999999915</v>
+        <v>4.5</v>
       </c>
       <c r="O33">
         <f t="shared" ca="1" si="5"/>
-        <v>2.9499999999999886</v>
+        <v>11.400000000000006</v>
       </c>
       <c r="P33">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>1.6499999999999915</v>
       </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
@@ -3528,27 +3531,27 @@
       </c>
       <c r="K34">
         <f t="shared" ca="1" si="7"/>
-        <v>10.71</v>
+        <v>11.79</v>
       </c>
       <c r="L34">
         <f t="shared" ca="1" si="8"/>
-        <v>6.9499999999999886</v>
+        <v>5.4000000000000341</v>
       </c>
       <c r="M34">
         <f t="shared" ca="1" si="9"/>
-        <v>24.600000000000023</v>
+        <v>11.850000000000023</v>
       </c>
       <c r="N34">
         <f t="shared" ca="1" si="4"/>
-        <v>4</v>
+        <v>13.100000000000023</v>
       </c>
       <c r="O34">
         <f t="shared" ca="1" si="5"/>
-        <v>6</v>
+        <v>24.600000000000023</v>
       </c>
       <c r="P34">
         <f t="shared" ca="1" si="6"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R34" s="29">
         <v>342</v>
@@ -3592,27 +3595,27 @@
       </c>
       <c r="K35">
         <f t="shared" ca="1" si="7"/>
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="L35">
         <f t="shared" ca="1" si="8"/>
-        <v>0.81000000000000227</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="M35">
         <f t="shared" ca="1" si="9"/>
-        <v>1.9899999999999949</v>
+        <v>1.0949999999999989</v>
       </c>
       <c r="N35">
         <f t="shared" ca="1" si="4"/>
-        <v>0.99000000000000199</v>
+        <v>1.5899999999999963</v>
       </c>
       <c r="O35">
         <f t="shared" ca="1" si="5"/>
-        <v>1.4549999999999983</v>
+        <v>1.9899999999999949</v>
       </c>
       <c r="P35">
         <f t="shared" ca="1" si="6"/>
-        <v>1.7199999999999989</v>
+        <v>0.99000000000000199</v>
       </c>
       <c r="R35" s="1"/>
       <c r="S35" s="25">
@@ -3652,27 +3655,27 @@
       </c>
       <c r="K36">
         <f t="shared" ca="1" si="7"/>
-        <v>3.49</v>
+        <v>3.83</v>
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="8"/>
-        <v>1.2900000000000205</v>
+        <v>3.9599999999999795</v>
       </c>
       <c r="M36">
         <f t="shared" ca="1" si="9"/>
-        <v>3.5799999999999841</v>
+        <v>3.7099999999999795</v>
       </c>
       <c r="N36">
         <f t="shared" ca="1" si="4"/>
-        <v>4.7899999999999636</v>
+        <v>3.1299999999999955</v>
       </c>
       <c r="O36">
         <f t="shared" ca="1" si="5"/>
-        <v>5.2100000000000364</v>
+        <v>3.5799999999999841</v>
       </c>
       <c r="P36">
         <f t="shared" ca="1" si="6"/>
-        <v>2.6000000000000227</v>
+        <v>4.7899999999999636</v>
       </c>
       <c r="R36" s="29">
         <v>32</v>
@@ -3716,27 +3719,27 @@
       </c>
       <c r="K37">
         <f t="shared" ca="1" si="7"/>
-        <v>15.12</v>
+        <v>17.559999999999999</v>
       </c>
       <c r="L37">
         <f t="shared" ca="1" si="8"/>
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="M37">
         <f t="shared" ca="1" si="9"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N37">
         <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>14.800000000000068</v>
       </c>
       <c r="O37">
         <f t="shared" ca="1" si="5"/>
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="P37">
         <f t="shared" ca="1" si="6"/>
-        <v>17.600000000000023</v>
+        <v>13</v>
       </c>
       <c r="R37" s="25">
         <v>-89</v>
@@ -3775,27 +3778,27 @@
       <c r="I38" s="24"/>
       <c r="K38">
         <f t="shared" ca="1" si="7"/>
-        <v>0.05</v>
+        <v>9222.4699999999993</v>
       </c>
       <c r="L38">
         <f t="shared" ca="1" si="8"/>
-        <v>3.400000000000003E-2</v>
+        <v>46112.035499999998</v>
       </c>
       <c r="M38">
         <f t="shared" ca="1" si="9"/>
-        <v>9.6999999999999975E-2</v>
+        <v>9.8499999999999921E-2</v>
       </c>
       <c r="N38">
         <f t="shared" ca="1" si="4"/>
-        <v>6.9499999999999895E-2</v>
+        <v>3.8499999999999979E-2</v>
       </c>
       <c r="O38">
         <f t="shared" ca="1" si="5"/>
-        <v>3.5499999999999865E-2</v>
+        <v>9.6999999999999975E-2</v>
       </c>
       <c r="P38">
         <f t="shared" ca="1" si="6"/>
-        <v>2.100000000000013E-2</v>
+        <v>6.9499999999999895E-2</v>
       </c>
       <c r="R38" s="29">
         <v>71</v>
@@ -3832,27 +3835,27 @@
       <c r="I39" s="24"/>
       <c r="K39">
         <f t="shared" ca="1" si="7"/>
-        <v>11.91</v>
+        <v>12.36</v>
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="8"/>
-        <v>11.850000000000023</v>
+        <v>5.0499999999999545</v>
       </c>
       <c r="M39">
         <f t="shared" ca="1" si="9"/>
-        <v>24.049999999999955</v>
+        <v>13.25</v>
       </c>
       <c r="N39">
         <f t="shared" ca="1" si="4"/>
-        <v>7.75</v>
+        <v>11.700000000000045</v>
       </c>
       <c r="O39">
         <f t="shared" ca="1" si="5"/>
-        <v>6.8999999999999773</v>
+        <v>24.049999999999955</v>
       </c>
       <c r="P39">
         <f t="shared" ca="1" si="6"/>
-        <v>9</v>
+        <v>7.75</v>
       </c>
       <c r="R39" s="25">
         <v>-9</v>
@@ -3894,27 +3897,27 @@
       </c>
       <c r="K40">
         <f t="shared" ca="1" si="7"/>
-        <v>28.6</v>
+        <v>28.48</v>
       </c>
       <c r="L40">
         <f t="shared" ca="1" si="8"/>
-        <v>7.7999999999999545</v>
+        <v>60</v>
       </c>
       <c r="M40">
         <f t="shared" ca="1" si="9"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N40">
         <f t="shared" ca="1" si="4"/>
-        <v>27.399999999999977</v>
+        <v>20</v>
       </c>
       <c r="O40">
         <f t="shared" ca="1" si="5"/>
-        <v>45.399999999999977</v>
+        <v>17</v>
       </c>
       <c r="P40">
         <f t="shared" ca="1" si="6"/>
-        <v>45.399999999999977</v>
+        <v>27.399999999999977</v>
       </c>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
@@ -3951,27 +3954,27 @@
       <c r="I41" s="24"/>
       <c r="K41">
         <f t="shared" ca="1" si="7"/>
-        <v>-9228.0400000000009</v>
+        <v>6.44</v>
       </c>
       <c r="L41">
         <f t="shared" ca="1" si="8"/>
-        <v>0.19000000000000128</v>
+        <v>0.22000000000000242</v>
       </c>
       <c r="M41">
         <f t="shared" ca="1" si="9"/>
-        <v>-46141.48</v>
+        <v>0.34499999999999886</v>
       </c>
       <c r="N41">
         <f t="shared" ca="1" si="4"/>
-        <v>0.375</v>
+        <v>46172.764999999999</v>
       </c>
       <c r="O41">
         <f t="shared" ca="1" si="5"/>
-        <v>0.34999999999999787</v>
+        <v>-46141.48</v>
       </c>
       <c r="P41">
         <f t="shared" ca="1" si="6"/>
-        <v>0.34499999999999886</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4005,27 +4008,27 @@
       </c>
       <c r="K42">
         <f t="shared" ca="1" si="7"/>
-        <v>1.1399999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="8"/>
-        <v>0.49000000000000199</v>
+        <v>1.4200000000000017</v>
       </c>
       <c r="M42">
         <f t="shared" ca="1" si="9"/>
-        <v>1.5</v>
+        <v>1.1400000000000006</v>
       </c>
       <c r="N42">
         <f t="shared" ca="1" si="4"/>
-        <v>1.6850000000000023</v>
+        <v>1.0649999999999977</v>
       </c>
       <c r="O42">
         <f t="shared" ca="1" si="5"/>
-        <v>0.99000000000000199</v>
+        <v>1.5</v>
       </c>
       <c r="P42">
         <f t="shared" ca="1" si="6"/>
-        <v>1.0500000000000043</v>
+        <v>1.6850000000000023</v>
       </c>
       <c r="R42" s="25">
         <v>-18</v>
@@ -4066,27 +4069,27 @@
       <c r="I43" s="24"/>
       <c r="K43">
         <f t="shared" ca="1" si="7"/>
-        <v>18.98</v>
+        <v>19.059999999999999</v>
       </c>
       <c r="L43">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B43&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B43&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>11.600000000000023</v>
+        <v>14.700000000000045</v>
       </c>
       <c r="M43">
         <f t="shared" ca="1" si="9"/>
-        <v>34.599999999999909</v>
+        <v>17</v>
       </c>
       <c r="N43">
         <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O43">
         <f t="shared" ca="1" si="5"/>
-        <v>15.399999999999977</v>
+        <v>34.599999999999909</v>
       </c>
       <c r="P43">
         <f t="shared" ca="1" si="6"/>
-        <v>18.299999999999955</v>
+        <v>15</v>
       </c>
       <c r="R43" s="25">
         <v>-114</v>
@@ -4125,11 +4128,11 @@
       <c r="I44" s="24"/>
       <c r="K44">
         <f t="shared" ca="1" si="7"/>
-        <v>2.68</v>
+        <v>2.87</v>
       </c>
       <c r="L44">
         <f t="shared" ca="1" si="8"/>
-        <v>0.90000000000000568</v>
+        <v>2.8799999999999955</v>
       </c>
       <c r="M44">
         <f t="shared" ca="1" si="9"/>
@@ -4137,15 +4140,15 @@
       </c>
       <c r="N44">
         <f t="shared" ca="1" si="4"/>
-        <v>4.3200000000000074</v>
+        <v>2.8200000000000074</v>
       </c>
       <c r="O44">
         <f t="shared" ca="1" si="5"/>
-        <v>4.4200000000000017</v>
+        <v>2.1599999999999966</v>
       </c>
       <c r="P44">
         <f t="shared" ca="1" si="6"/>
-        <v>1.6199999999999903</v>
+        <v>4.3200000000000074</v>
       </c>
       <c r="R44" s="29">
         <v>7</v>
@@ -4184,27 +4187,27 @@
       <c r="I45" s="24"/>
       <c r="K45">
         <f t="shared" ca="1" si="7"/>
-        <v>16.32</v>
+        <v>17.559999999999999</v>
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="8"/>
-        <v>10.399999999999864</v>
+        <v>14.200000000000045</v>
       </c>
       <c r="M45">
         <f t="shared" ca="1" si="9"/>
-        <v>16.799999999999955</v>
+        <v>14.400000000000091</v>
       </c>
       <c r="N45">
         <f t="shared" ca="1" si="4"/>
-        <v>16.400000000000091</v>
+        <v>26</v>
       </c>
       <c r="O45">
         <f t="shared" ca="1" si="5"/>
-        <v>18.599999999999909</v>
+        <v>16.799999999999955</v>
       </c>
       <c r="P45">
         <f t="shared" ca="1" si="6"/>
-        <v>19.400000000000091</v>
+        <v>16.400000000000091</v>
       </c>
       <c r="R45" s="1"/>
       <c r="S45" s="25">
@@ -4246,27 +4249,27 @@
       </c>
       <c r="K46">
         <f ca="1">ROUND(AVERAGE(L46:P46),4)</f>
-        <v>3.2500000000000001E-2</v>
+        <v>7.5399999999999995E-2</v>
       </c>
       <c r="L46">
         <f t="shared" ca="1" si="8"/>
-        <v>2.3800000000000043E-2</v>
+        <v>2.2299999999999986E-2</v>
       </c>
       <c r="M46">
         <f t="shared" ca="1" si="9"/>
-        <v>4.3300000000000005E-2</v>
+        <v>2.4900000000000033E-2</v>
       </c>
       <c r="N46">
         <f t="shared" ca="1" si="4"/>
-        <v>5.699999999999994E-2</v>
+        <v>0.22949999999999993</v>
       </c>
       <c r="O46">
         <f t="shared" ca="1" si="5"/>
-        <v>1.2800000000000034E-2</v>
+        <v>4.3300000000000005E-2</v>
       </c>
       <c r="P46">
         <f t="shared" ca="1" si="6"/>
-        <v>2.5799999999999934E-2</v>
+        <v>5.699999999999994E-2</v>
       </c>
       <c r="R46" s="1"/>
       <c r="S46" s="22"/>
@@ -4304,27 +4307,27 @@
       </c>
       <c r="K47">
         <f t="shared" ca="1" si="7"/>
-        <v>6.21</v>
+        <v>6.16</v>
       </c>
       <c r="L47">
         <f t="shared" ca="1" si="8"/>
-        <v>1.3000000000000114</v>
+        <v>4.25</v>
       </c>
       <c r="M47">
         <f t="shared" ca="1" si="9"/>
-        <v>7.6499999999999773</v>
+        <v>3.5</v>
       </c>
       <c r="N47">
         <f t="shared" ca="1" si="4"/>
-        <v>9.9500000000000455</v>
+        <v>5.4499999999999886</v>
       </c>
       <c r="O47">
         <f t="shared" ca="1" si="5"/>
-        <v>7.0500000000000114</v>
+        <v>7.6499999999999773</v>
       </c>
       <c r="P47">
         <f t="shared" ca="1" si="6"/>
-        <v>5.1000000000000227</v>
+        <v>9.9500000000000455</v>
       </c>
       <c r="R47" s="1"/>
       <c r="S47" s="29">
@@ -4367,27 +4370,27 @@
       </c>
       <c r="K48">
         <f t="shared" ca="1" si="7"/>
-        <v>1.74</v>
+        <v>3.03</v>
       </c>
       <c r="L48">
         <f t="shared" ca="1" si="8"/>
-        <v>0.43500000000000227</v>
+        <v>3.125</v>
       </c>
       <c r="M48">
         <f t="shared" ca="1" si="9"/>
-        <v>1.8349999999999937</v>
+        <v>5.2649999999999864</v>
       </c>
       <c r="N48">
         <f t="shared" ca="1" si="4"/>
-        <v>2.4100000000000108</v>
+        <v>2.5349999999999966</v>
       </c>
       <c r="O48">
         <f t="shared" ca="1" si="5"/>
-        <v>2.5799999999999983</v>
+        <v>1.8349999999999937</v>
       </c>
       <c r="P48">
         <f t="shared" ca="1" si="6"/>
-        <v>1.4399999999999977</v>
+        <v>2.4100000000000108</v>
       </c>
       <c r="R48" s="29">
         <v>19</v>
@@ -4429,27 +4432,27 @@
       </c>
       <c r="K49">
         <f t="shared" ca="1" si="7"/>
-        <v>28.6</v>
+        <v>28.2</v>
       </c>
       <c r="L49">
         <f t="shared" ca="1" si="8"/>
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="M49">
         <f t="shared" ca="1" si="9"/>
-        <v>19.5</v>
+        <v>33.5</v>
       </c>
       <c r="N49">
         <f t="shared" ca="1" si="4"/>
-        <v>50.5</v>
+        <v>19</v>
       </c>
       <c r="O49">
         <f t="shared" ca="1" si="5"/>
-        <v>42.5</v>
+        <v>19.5</v>
       </c>
       <c r="P49">
         <f t="shared" ca="1" si="6"/>
-        <v>19.5</v>
+        <v>50.5</v>
       </c>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
@@ -4487,27 +4490,27 @@
       </c>
       <c r="K50">
         <f t="shared" ca="1" si="7"/>
-        <v>96.6</v>
+        <v>80.8</v>
       </c>
       <c r="L50">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="M50">
         <f t="shared" ca="1" si="9"/>
-        <v>87.5</v>
+        <v>89</v>
       </c>
       <c r="N50">
         <f t="shared" ca="1" si="4"/>
-        <v>95</v>
+        <v>76.5</v>
       </c>
       <c r="O50">
         <f t="shared" ca="1" si="5"/>
-        <v>164</v>
+        <v>87.5</v>
       </c>
       <c r="P50">
         <f t="shared" ca="1" si="6"/>
-        <v>118.5</v>
+        <v>95</v>
       </c>
       <c r="R50" s="1">
         <v>-97</v>
@@ -4682,8 +4685,12 @@
       <c r="G3" s="33">
         <v>46128</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="H3" s="33">
+        <v>46134</v>
+      </c>
+      <c r="I3" s="33">
+        <v>46135</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -4714,8 +4721,12 @@
         <v>91</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="H4" s="1">
+        <v>62</v>
+      </c>
+      <c r="I4" s="1">
+        <v>46</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -4776,7 +4787,9 @@
       <c r="G6" s="1">
         <v>43</v>
       </c>
-      <c r="H6" s="1"/>
+      <c r="H6" s="1">
+        <v>45</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -4837,7 +4850,9 @@
         <v>79</v>
       </c>
       <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1">
+        <v>47</v>
+      </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -4865,7 +4880,9 @@
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1">
+        <v>89</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -4894,7 +4911,9 @@
       <c r="G10" s="1">
         <v>42</v>
       </c>
-      <c r="H10" s="1"/>
+      <c r="H10" s="1">
+        <v>151</v>
+      </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>

--- a/calc.xlsx
+++ b/calc.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="98">
   <si>
     <t>Депозит</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t>EuM6</t>
+  </si>
+  <si>
+    <t>ASTR</t>
   </si>
 </sst>
 </file>
@@ -1801,7 +1804,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:U53"/>
+  <dimension ref="A3:U54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="15.28515625" customWidth="1"/>
@@ -1818,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="1">
-        <v>40000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.25">
@@ -1826,31 +1829,31 @@
         <v>85</v>
       </c>
       <c r="C4" s="31">
-        <f>C3*0.6/100</f>
-        <v>240</v>
+        <f>C3*1/100</f>
+        <v>250</v>
       </c>
       <c r="D4" s="32"/>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="L6" s="5" t="str">
         <f ca="1">TEXT(L7,"ддд")</f>
-        <v>Ср</v>
+        <v>Пт</v>
       </c>
       <c r="M6" s="5" t="str">
         <f ca="1">TEXT(M7,"ддд")</f>
-        <v>Вт</v>
+        <v>Сб</v>
       </c>
       <c r="N6" s="5" t="str">
         <f t="shared" ref="N6:P6" ca="1" si="0">TEXT(N7,"ддд")</f>
-        <v>Пн</v>
+        <v>Вт</v>
       </c>
       <c r="O6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Пт</v>
+        <v>Чт</v>
       </c>
       <c r="P6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Чт</v>
+        <v>Ср</v>
       </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.25">
@@ -1883,24 +1886,24 @@
         <v>78</v>
       </c>
       <c r="L7" s="1" t="str">
+        <f ca="1">TEXT(TODAY()-5, "ГГГГ-ММ-ДД")</f>
+        <v>2026-04-24</v>
+      </c>
+      <c r="M7" s="1" t="str">
+        <f ca="1">TEXT(TODAY()-4, "ГГГГ-ММ-ДД")</f>
+        <v>2026-04-25</v>
+      </c>
+      <c r="N7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-1, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-22</v>
-      </c>
-      <c r="M7" s="1" t="str">
-        <f ca="1">TEXT(TODAY()-2, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-21</v>
-      </c>
-      <c r="N7" s="1" t="str">
-        <f ca="1">TEXT(TODAY()-3, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-20</v>
+        <v>2026-04-28</v>
       </c>
       <c r="O7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-6, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-17</v>
+        <v>2026-04-23</v>
       </c>
       <c r="P7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-7, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-16</v>
+        <v>2026-04-22</v>
       </c>
       <c r="R7" s="28">
         <v>45566</v>
@@ -1923,7 +1926,7 @@
         <v>0.35</v>
       </c>
       <c r="D8" s="25">
-        <f t="shared" ref="D8:D28" si="1">C8/10</f>
+        <f t="shared" ref="D8:D29" si="1">C8/10</f>
         <v>3.4999999999999996E-2</v>
       </c>
       <c r="E8" s="22">
@@ -1933,11 +1936,11 @@
         <v>0.1</v>
       </c>
       <c r="G8" s="26">
-        <f t="shared" ref="G8:G28" si="2">ROUND($C$4/(D8/E8*F8),0)</f>
-        <v>69</v>
+        <f t="shared" ref="G8:G29" si="2">ROUND($C$4/(D8/E8*F8),0)</f>
+        <v>71</v>
       </c>
       <c r="H8" s="22">
-        <f t="shared" ref="H8:H19" si="3">ROUND(D8/E8,0)</f>
+        <f t="shared" ref="H8:H20" si="3">ROUND(D8/E8,0)</f>
         <v>35</v>
       </c>
       <c r="I8" s="23"/>
@@ -1945,28 +1948,28 @@
         <v>46135</v>
       </c>
       <c r="K8">
-        <f ca="1">ROUND(AVERAGE(L8:P8),2)</f>
-        <v>10382.74</v>
+        <f t="shared" ref="K8:K13" ca="1" si="4">ROUND(AVERAGE(L8:P8),2)</f>
+        <v>10350.68</v>
       </c>
       <c r="L8">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>17490.069</v>
+        <f t="shared" ref="L8:L13" ca="1" si="5">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <v>0.54600000000000115</v>
       </c>
       <c r="M8">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>14741</v>
+        <f t="shared" ref="M8:M13" ca="1" si="6">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <v>3.5000000000000142E-2</v>
       </c>
       <c r="N8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.31900000000000084</v>
+        <v>34262.447</v>
       </c>
       <c r="O8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>19681.812999999998</v>
+        <v>0.29299999999999926</v>
       </c>
       <c r="P8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.4789999999999992</v>
+        <v>17490.069</v>
       </c>
       <c r="R8" s="29">
         <v>54</v>
@@ -1998,7 +2001,7 @@
       </c>
       <c r="G9" s="26">
         <f t="shared" si="2"/>
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="H9" s="22">
         <f t="shared" si="3"/>
@@ -2009,28 +2012,28 @@
         <v>46062</v>
       </c>
       <c r="K9">
-        <f ca="1">ROUND(AVERAGE(L9:P9),2)</f>
-        <v>1.28</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>0.84</v>
       </c>
       <c r="L9">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <f t="shared" ca="1" si="5"/>
+        <v>1.5400000000000063</v>
+      </c>
+      <c r="M9">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.21999999999999886</v>
+      </c>
+      <c r="N9">
+        <f t="shared" ref="N9:N51" ca="1" si="7">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <v>0.78000000000000114</v>
+      </c>
+      <c r="O9">
+        <f t="shared" ref="O9:O51" ca="1" si="8">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <v>1.009999999999998</v>
+      </c>
+      <c r="P9">
+        <f t="shared" ref="P9:P51" ca="1" si="9">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
         <v>0.66000000000000369</v>
-      </c>
-      <c r="M9">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.2700000000000031</v>
-      </c>
-      <c r="N9">
-        <f t="shared" ref="N9:N50" ca="1" si="4">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.6799999999999997</v>
-      </c>
-      <c r="O9">
-        <f t="shared" ref="O9:O50" ca="1" si="5">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.7199999999999989</v>
-      </c>
-      <c r="P9">
-        <f t="shared" ref="P9:P50" ca="1" si="6">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.0900000000000034</v>
       </c>
       <c r="R9" s="25">
         <v>-30</v>
@@ -2062,7 +2065,7 @@
       </c>
       <c r="G10" s="26">
         <f>ROUND($C$4/(D10/E10*F10),0)</f>
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="H10" s="22">
         <f t="shared" si="3"/>
@@ -2070,28 +2073,28 @@
       </c>
       <c r="I10" s="24"/>
       <c r="K10">
-        <f ca="1">ROUND(AVERAGE(L10:P10),2)</f>
-        <v>0.85</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>-18467.87</v>
       </c>
       <c r="L10">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <f t="shared" ca="1" si="5"/>
+        <v>1.5300000000000011</v>
+      </c>
+      <c r="M10">
+        <f t="shared" ca="1" si="6"/>
+        <v>-46201.98</v>
+      </c>
+      <c r="N10">
+        <f t="shared" ca="1" si="7"/>
+        <v>-46140.38</v>
+      </c>
+      <c r="O10">
+        <f t="shared" ca="1" si="8"/>
+        <v>0.55000000000000071</v>
+      </c>
+      <c r="P10">
+        <f t="shared" ca="1" si="9"/>
         <v>0.92999999999999972</v>
-      </c>
-      <c r="M10">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B10&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.83000000000000185</v>
-      </c>
-      <c r="N10">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.80000000000000071</v>
-      </c>
-      <c r="O10">
-        <f t="shared" ca="1" si="5"/>
-        <v>1.1499999999999986</v>
-      </c>
-      <c r="P10">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.52000000000000313</v>
       </c>
       <c r="R10" s="29">
         <v>39</v>
@@ -2106,56 +2109,56 @@
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" s="22" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C11" s="22">
-        <v>8.77</v>
+        <v>7.9</v>
       </c>
       <c r="D11" s="25">
         <f>C11/10</f>
-        <v>0.877</v>
+        <v>0.79</v>
       </c>
       <c r="E11" s="22">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="F11" s="22">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G11" s="26">
         <f>ROUND($C$4/(D11/E11*F11),0)</f>
-        <v>27</v>
+        <v>316</v>
       </c>
       <c r="H11" s="22">
         <f t="shared" si="3"/>
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="30">
-        <v>46070</v>
+        <v>46140</v>
       </c>
       <c r="K11">
-        <f ca="1">ROUND(AVERAGE(L11:P11),2)</f>
-        <v>5.08</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>5.95</v>
       </c>
       <c r="L11">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>2.2300000000000182</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>8.5999999999999659</v>
       </c>
       <c r="M11">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B11&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>3.5600000000000023</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1.3999999999999773</v>
       </c>
       <c r="N11">
-        <f t="shared" ca="1" si="4"/>
-        <v>4.4300000000000068</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>12.100000000000023</v>
       </c>
       <c r="O11">
-        <f t="shared" ca="1" si="5"/>
-        <v>7.089999999999975</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>4.25</v>
       </c>
       <c r="P11">
-        <f t="shared" ca="1" si="6"/>
-        <v>8.1000000000000227</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>3.3999999999999773</v>
       </c>
       <c r="R11" s="29"/>
       <c r="S11" s="29"/>
@@ -2164,56 +2167,56 @@
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B12" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="24">
-        <v>2.83</v>
+        <v>83</v>
+      </c>
+      <c r="C12" s="22">
+        <v>8.77</v>
       </c>
       <c r="D12" s="25">
         <f>C12/10</f>
-        <v>0.28300000000000003</v>
+        <v>0.877</v>
       </c>
       <c r="E12" s="22">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F12" s="22">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="G12" s="26">
         <f>ROUND($C$4/(D12/E12*F12),0)</f>
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H12" s="22">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="I12" s="24"/>
       <c r="J12" s="30">
-        <v>46071</v>
-      </c>
-      <c r="K12" s="24">
-        <f ca="1">ROUND(AVERAGE(L12:P12),2)</f>
-        <v>1.53</v>
-      </c>
-      <c r="L12" s="24">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1</v>
-      </c>
-      <c r="M12" s="24">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B12&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.89999999999999858</v>
-      </c>
-      <c r="N12" s="24">
+        <v>46070</v>
+      </c>
+      <c r="K12">
         <f t="shared" ca="1" si="4"/>
-        <v>0.45000000000000284</v>
-      </c>
-      <c r="O12" s="24">
+        <v>2.6</v>
+      </c>
+      <c r="L12">
         <f t="shared" ca="1" si="5"/>
-        <v>2.25</v>
-      </c>
-      <c r="P12" s="24">
+        <v>3.5</v>
+      </c>
+      <c r="M12">
         <f t="shared" ca="1" si="6"/>
-        <v>3.0500000000000043</v>
+        <v>0.92000000000001592</v>
+      </c>
+      <c r="N12">
+        <f t="shared" ca="1" si="7"/>
+        <v>3.4900000000000091</v>
+      </c>
+      <c r="O12">
+        <f t="shared" ca="1" si="8"/>
+        <v>2.8799999999999955</v>
+      </c>
+      <c r="P12">
+        <f t="shared" ca="1" si="9"/>
+        <v>2.2300000000000182</v>
       </c>
       <c r="R12" s="29"/>
       <c r="S12" s="29"/>
@@ -2221,1295 +2224,1296 @@
       <c r="U12" s="1"/>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="24">
+        <v>2.83</v>
+      </c>
+      <c r="D13" s="25">
+        <f>C13/10</f>
+        <v>0.28300000000000003</v>
+      </c>
+      <c r="E13" s="22">
+        <v>0.05</v>
+      </c>
+      <c r="F13" s="22">
+        <v>5</v>
+      </c>
+      <c r="G13" s="26">
+        <f>ROUND($C$4/(D13/E13*F13),0)</f>
+        <v>9</v>
+      </c>
+      <c r="H13" s="22">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="I13" s="24"/>
+      <c r="J13" s="30">
+        <v>46071</v>
+      </c>
+      <c r="K13" s="24">
+        <f t="shared" ca="1" si="4"/>
+        <v>1.27</v>
+      </c>
+      <c r="L13" s="24">
+        <f t="shared" ca="1" si="5"/>
+        <v>1.2000000000000028</v>
+      </c>
+      <c r="M13" s="24">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.54999999999999716</v>
+      </c>
+      <c r="N13" s="24">
+        <f t="shared" ca="1" si="7"/>
+        <v>2.5500000000000043</v>
+      </c>
+      <c r="O13" s="24">
+        <f t="shared" ca="1" si="8"/>
+        <v>1.0499999999999972</v>
+      </c>
+      <c r="P13" s="24">
+        <f t="shared" ca="1" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="1"/>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C14" s="1">
         <v>50</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D14" s="25">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E14" s="1">
         <v>0.2</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F14" s="1">
         <v>0.2</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G14" s="26">
         <f t="shared" si="2"/>
-        <v>48</v>
-      </c>
-      <c r="H13" s="22">
+        <v>50</v>
+      </c>
+      <c r="H14" s="22">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="I13" s="23"/>
-      <c r="J13" s="30">
+      <c r="I14" s="23"/>
+      <c r="J14" s="30">
         <v>46135</v>
       </c>
-      <c r="K13">
-        <f t="shared" ref="K13:K50" ca="1" si="7">ROUND(AVERAGE(L13:P13),2)</f>
-        <v>19</v>
-      </c>
-      <c r="L13">
-        <f t="shared" ref="L13:L50" ca="1" si="8">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+      <c r="K14">
+        <f t="shared" ref="K14:K51" ca="1" si="10">ROUND(AVERAGE(L14:P14),2)</f>
+        <v>20.84</v>
+      </c>
+      <c r="L14">
+        <f t="shared" ref="L14:L51" ca="1" si="11">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <v>32.599999999999909</v>
+      </c>
+      <c r="M14">
+        <f t="shared" ref="M14:M51" ca="1" si="12">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <v>3</v>
+      </c>
+      <c r="N14">
+        <f t="shared" ca="1" si="7"/>
+        <v>21.600000000000023</v>
+      </c>
+      <c r="O14">
+        <f t="shared" ca="1" si="8"/>
+        <v>16.600000000000023</v>
+      </c>
+      <c r="P14">
+        <f t="shared" ca="1" si="9"/>
         <v>30.399999999999977</v>
       </c>
-      <c r="M13">
-        <f t="shared" ref="M13:M50" ca="1" si="9">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B13&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>13.799999999999955</v>
-      </c>
-      <c r="N13">
-        <f t="shared" ca="1" si="4"/>
-        <v>17.399999999999977</v>
-      </c>
-      <c r="O13">
-        <f t="shared" ca="1" si="5"/>
-        <v>17</v>
-      </c>
-      <c r="P13">
-        <f t="shared" ca="1" si="6"/>
-        <v>16.399999999999977</v>
-      </c>
-      <c r="R13" s="29">
+      <c r="R14" s="29">
         <v>80</v>
       </c>
-      <c r="S13" s="25">
+      <c r="S14" s="25">
         <v>-6</v>
       </c>
-      <c r="T13" s="29">
+      <c r="T14" s="29">
         <v>12</v>
       </c>
-      <c r="U13" s="1"/>
-    </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B14" s="22" t="s">
+      <c r="U14" s="1"/>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B15" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C15" s="22">
         <v>3.22</v>
       </c>
-      <c r="D14" s="25">
-        <f t="shared" ref="D14:D20" si="10">C14/10</f>
+      <c r="D15" s="25">
+        <f t="shared" ref="D15:D21" si="13">C15/10</f>
         <v>0.32200000000000001</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E15" s="22">
         <v>0.01</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F15" s="22">
         <v>0.1</v>
       </c>
-      <c r="G14" s="26">
-        <f t="shared" ref="G14:G20" si="11">ROUND($C$4/(D14/E14*F14),0)</f>
-        <v>75</v>
-      </c>
-      <c r="H14" s="22">
+      <c r="G15" s="26">
+        <f t="shared" ref="G15:G21" si="14">ROUND($C$4/(D15/E15*F15),0)</f>
+        <v>78</v>
+      </c>
+      <c r="H15" s="22">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
-      <c r="I14" s="24"/>
-      <c r="K14">
+      <c r="I15" s="24"/>
+      <c r="K15">
+        <f t="shared" ca="1" si="10"/>
+        <v>1.62</v>
+      </c>
+      <c r="L15">
+        <f t="shared" ca="1" si="11"/>
+        <v>2.3900000000000006</v>
+      </c>
+      <c r="M15">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.59000000000000341</v>
+      </c>
+      <c r="N15">
         <f t="shared" ca="1" si="7"/>
-        <v>1.66</v>
-      </c>
-      <c r="L14">
+        <v>2.6400000000000006</v>
+      </c>
+      <c r="O15">
         <f t="shared" ca="1" si="8"/>
+        <v>1.1099999999999994</v>
+      </c>
+      <c r="P15">
+        <f t="shared" ca="1" si="9"/>
         <v>1.3900000000000006</v>
       </c>
-      <c r="M14">
-        <f t="shared" ca="1" si="9"/>
-        <v>1.9000000000000057</v>
-      </c>
-      <c r="N14">
-        <f t="shared" ca="1" si="4"/>
-        <v>1.6799999999999926</v>
-      </c>
-      <c r="O14">
-        <f t="shared" ca="1" si="5"/>
-        <v>1.0600000000000023</v>
-      </c>
-      <c r="P14">
-        <f t="shared" ca="1" si="6"/>
-        <v>2.269999999999996</v>
-      </c>
-      <c r="R14" s="29">
+      <c r="R15" s="29">
         <v>27</v>
       </c>
-      <c r="S14" s="25">
+      <c r="S15" s="25">
         <v>-172</v>
       </c>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B16" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C16" s="22">
         <v>5.4</v>
       </c>
-      <c r="D15" s="25">
-        <f t="shared" si="10"/>
+      <c r="D16" s="25">
+        <f t="shared" si="13"/>
         <v>0.54</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E16" s="22">
         <v>0.05</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F16" s="22">
         <v>0.05</v>
       </c>
-      <c r="G15" s="26">
-        <f t="shared" si="11"/>
-        <v>444</v>
-      </c>
-      <c r="H15" s="22">
+      <c r="G16" s="26">
+        <f t="shared" si="14"/>
+        <v>463</v>
+      </c>
+      <c r="H16" s="22">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="I15" s="23"/>
-      <c r="K15">
+      <c r="I16" s="23"/>
+      <c r="K16">
+        <f t="shared" ca="1" si="10"/>
+        <v>8.64</v>
+      </c>
+      <c r="L16">
+        <f t="shared" ca="1" si="11"/>
+        <v>10.599999999999994</v>
+      </c>
+      <c r="M16">
+        <f t="shared" ca="1" si="12"/>
+        <v>2.2000000000000028</v>
+      </c>
+      <c r="N16">
         <f t="shared" ca="1" si="7"/>
-        <v>10.36</v>
-      </c>
-      <c r="L15">
+        <v>7.2000000000000028</v>
+      </c>
+      <c r="O16">
         <f t="shared" ca="1" si="8"/>
+        <v>8.4000000000000057</v>
+      </c>
+      <c r="P16">
+        <f t="shared" ca="1" si="9"/>
         <v>14.799999999999997</v>
       </c>
-      <c r="M15">
-        <f t="shared" ca="1" si="9"/>
-        <v>12.350000000000001</v>
-      </c>
-      <c r="N15">
-        <f t="shared" ca="1" si="4"/>
-        <v>16.100000000000009</v>
-      </c>
-      <c r="O15">
-        <f t="shared" ca="1" si="5"/>
-        <v>3.8500000000000085</v>
-      </c>
-      <c r="P15">
-        <f t="shared" ca="1" si="6"/>
-        <v>4.7000000000000028</v>
-      </c>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B16" s="22" t="s">
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B17" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C17" s="22">
         <v>1.8</v>
       </c>
-      <c r="D16" s="25">
-        <f t="shared" si="10"/>
+      <c r="D17" s="25">
+        <f t="shared" si="13"/>
         <v>0.18</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E17" s="22">
         <v>0.01</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F17" s="22">
         <v>0.1</v>
       </c>
-      <c r="G16" s="26">
-        <f t="shared" si="11"/>
-        <v>133</v>
-      </c>
-      <c r="H16" s="22">
+      <c r="G17" s="26">
+        <f t="shared" si="14"/>
+        <v>139</v>
+      </c>
+      <c r="H17" s="22">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="I16" s="24"/>
-      <c r="J16" s="30">
+      <c r="I17" s="24"/>
+      <c r="J17" s="30">
         <v>46133</v>
       </c>
-      <c r="K16">
+      <c r="K17">
+        <f t="shared" ca="1" si="10"/>
+        <v>1.87</v>
+      </c>
+      <c r="L17">
+        <f t="shared" ca="1" si="11"/>
+        <v>2.5499999999999972</v>
+      </c>
+      <c r="M17">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.42999999999999261</v>
+      </c>
+      <c r="N17">
         <f t="shared" ca="1" si="7"/>
-        <v>2.44</v>
-      </c>
-      <c r="L16">
+        <v>4.0600000000000023</v>
+      </c>
+      <c r="O17">
         <f t="shared" ca="1" si="8"/>
+        <v>1.0799999999999983</v>
+      </c>
+      <c r="P17">
+        <f t="shared" ca="1" si="9"/>
         <v>1.2099999999999937</v>
       </c>
-      <c r="M16">
-        <f t="shared" ca="1" si="9"/>
-        <v>2.1400000000000006</v>
-      </c>
-      <c r="N16">
-        <f t="shared" ca="1" si="4"/>
-        <v>2.1700000000000017</v>
-      </c>
-      <c r="O16">
-        <f t="shared" ca="1" si="5"/>
-        <v>4.7399999999999807</v>
-      </c>
-      <c r="P16">
-        <f t="shared" ca="1" si="6"/>
-        <v>1.9300000000000068</v>
-      </c>
-      <c r="R16" s="25">
+      <c r="R17" s="25">
         <v>-2</v>
       </c>
-      <c r="S16" s="25">
+      <c r="S17" s="25">
         <v>-117</v>
       </c>
-      <c r="T16" s="29">
+      <c r="T17" s="29">
         <v>88</v>
       </c>
-      <c r="U16" s="1"/>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B17" s="22" t="s">
+      <c r="U17" s="1"/>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B18" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C18" s="22">
         <v>1.8600000000000001E-3</v>
       </c>
-      <c r="D17" s="25">
-        <f t="shared" si="10"/>
+      <c r="D18" s="25">
+        <f t="shared" si="13"/>
         <v>1.8600000000000002E-4</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E18" s="22">
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F18" s="22">
         <v>0.2</v>
       </c>
-      <c r="G17" s="26">
-        <f t="shared" si="11"/>
-        <v>129</v>
-      </c>
-      <c r="H17" s="22">
+      <c r="G18" s="26">
+        <f t="shared" si="14"/>
+        <v>134</v>
+      </c>
+      <c r="H18" s="22">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="I17" s="24"/>
-      <c r="J17" s="30">
+      <c r="I18" s="24"/>
+      <c r="J18" s="30">
         <v>46062</v>
       </c>
-      <c r="K17">
-        <f ca="1">ROUND(AVERAGE(L17:P17),5)</f>
-        <v>1.5499999999999999E-3</v>
-      </c>
-      <c r="L17">
+      <c r="K18">
+        <f ca="1">ROUND(AVERAGE(L18:P18),5)</f>
+        <v>1.9E-3</v>
+      </c>
+      <c r="L18">
+        <f t="shared" ca="1" si="11"/>
+        <v>2.1199999999999969E-3</v>
+      </c>
+      <c r="M18">
+        <f t="shared" ca="1" si="12"/>
+        <v>4.200000000000037E-4</v>
+      </c>
+      <c r="N18">
+        <f t="shared" ca="1" si="7"/>
+        <v>2.9600000000000043E-3</v>
+      </c>
+      <c r="O18">
         <f t="shared" ca="1" si="8"/>
         <v>2.0000000000000018E-3</v>
       </c>
-      <c r="M17">
+      <c r="P18">
         <f t="shared" ca="1" si="9"/>
-        <v>8.8000000000000578E-4</v>
-      </c>
-      <c r="N17">
-        <f t="shared" ca="1" si="4"/>
-        <v>1.3799999999999923E-3</v>
-      </c>
-      <c r="O17">
-        <f t="shared" ca="1" si="5"/>
-        <v>1.7599999999999977E-3</v>
-      </c>
-      <c r="P17">
-        <f t="shared" ca="1" si="6"/>
-        <v>1.7199999999999993E-3</v>
-      </c>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="1"/>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B18" s="22" t="s">
+        <v>2.0000000000000018E-3</v>
+      </c>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="1"/>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B19" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C19" s="22">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D18" s="25">
-        <f t="shared" si="10"/>
+      <c r="D19" s="25">
+        <f t="shared" si="13"/>
         <v>0.44000000000000006</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E19" s="22">
         <v>0.02</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F19" s="22">
         <v>0.2</v>
       </c>
-      <c r="G18" s="26">
-        <f t="shared" si="11"/>
-        <v>55</v>
-      </c>
-      <c r="H18" s="22">
+      <c r="G19" s="26">
+        <f t="shared" si="14"/>
+        <v>57</v>
+      </c>
+      <c r="H19" s="22">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="I18" s="24"/>
-      <c r="J18" s="30">
+      <c r="I19" s="24"/>
+      <c r="J19" s="30">
         <v>46133</v>
       </c>
-      <c r="K18">
+      <c r="K19">
+        <f t="shared" ca="1" si="10"/>
+        <v>2.79</v>
+      </c>
+      <c r="L19">
+        <f t="shared" ca="1" si="11"/>
+        <v>3.3799999999999955</v>
+      </c>
+      <c r="M19">
+        <f t="shared" ca="1" si="12"/>
+        <v>1.2400000000000091</v>
+      </c>
+      <c r="N19">
         <f t="shared" ca="1" si="7"/>
-        <v>3.69</v>
-      </c>
-      <c r="L18">
+        <v>3.2400000000000091</v>
+      </c>
+      <c r="O19">
         <f t="shared" ca="1" si="8"/>
+        <v>2.3600000000000136</v>
+      </c>
+      <c r="P19">
+        <f t="shared" ca="1" si="9"/>
         <v>3.7199999999999989</v>
       </c>
-      <c r="M18">
-        <f t="shared" ca="1" si="9"/>
-        <v>3.1800000000000068</v>
-      </c>
-      <c r="N18">
-        <f t="shared" ca="1" si="4"/>
-        <v>5.1400000000000148</v>
-      </c>
-      <c r="O18">
-        <f t="shared" ca="1" si="5"/>
-        <v>3.2800000000000011</v>
-      </c>
-      <c r="P18">
-        <f t="shared" ca="1" si="6"/>
-        <v>3.1399999999999864</v>
-      </c>
-      <c r="R18" s="25">
+      <c r="R19" s="25">
         <v>-211</v>
       </c>
-      <c r="S18" s="25">
+      <c r="S19" s="25">
         <v>-701</v>
       </c>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="22" t="s">
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B20" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C20" s="22">
         <v>7.85E-2</v>
       </c>
-      <c r="D19" s="25">
-        <f t="shared" si="10"/>
+      <c r="D20" s="25">
+        <f t="shared" si="13"/>
         <v>7.8499999999999993E-3</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E20" s="22">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F20" s="22">
         <v>0.05</v>
       </c>
-      <c r="G19" s="26">
-        <f t="shared" si="11"/>
-        <v>306</v>
-      </c>
-      <c r="H19" s="22">
+      <c r="G20" s="26">
+        <f t="shared" si="14"/>
+        <v>318</v>
+      </c>
+      <c r="H20" s="22">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="I19" s="24"/>
-      <c r="K19">
+      <c r="I20" s="24"/>
+      <c r="K20">
+        <f t="shared" ca="1" si="10"/>
+        <v>127931.33</v>
+      </c>
+      <c r="L20">
+        <f t="shared" ca="1" si="11"/>
+        <v>227546</v>
+      </c>
+      <c r="M20">
+        <f t="shared" ca="1" si="12"/>
+        <v>199115.76699999999</v>
+      </c>
+      <c r="N20">
         <f t="shared" ca="1" si="7"/>
-        <v>22791.03</v>
-      </c>
-      <c r="L19">
+        <v>44982.854500000001</v>
+      </c>
+      <c r="O20">
         <f t="shared" ca="1" si="8"/>
+        <v>168012</v>
+      </c>
+      <c r="P20">
+        <f t="shared" ca="1" si="9"/>
         <v>3.1000000000000139E-2</v>
       </c>
-      <c r="M19">
+      <c r="R20" s="1"/>
+      <c r="S20" s="25">
+        <v>-488</v>
+      </c>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B21" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="22">
+        <v>86.3</v>
+      </c>
+      <c r="D21" s="25">
+        <f t="shared" si="13"/>
+        <v>8.629999999999999</v>
+      </c>
+      <c r="E21" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="G21" s="26">
+        <f t="shared" si="14"/>
+        <v>29</v>
+      </c>
+      <c r="H21" s="22">
+        <f t="shared" ref="H21:H45" si="15">ROUND(D21/E21,0)</f>
+        <v>17</v>
+      </c>
+      <c r="I21" s="24"/>
+      <c r="J21" s="30">
+        <v>46133</v>
+      </c>
+      <c r="K21">
+        <f t="shared" ca="1" si="10"/>
+        <v>67.400000000000006</v>
+      </c>
+      <c r="L21">
+        <f t="shared" ca="1" si="11"/>
+        <v>118.5</v>
+      </c>
+      <c r="M21">
+        <f t="shared" ca="1" si="12"/>
+        <v>27.5</v>
+      </c>
+      <c r="N21">
+        <f t="shared" ca="1" si="7"/>
+        <v>83</v>
+      </c>
+      <c r="O21">
+        <f t="shared" ca="1" si="8"/>
+        <v>67.5</v>
+      </c>
+      <c r="P21">
         <f t="shared" ca="1" si="9"/>
-        <v>-35794</v>
-      </c>
-      <c r="N19">
-        <f t="shared" ca="1" si="4"/>
-        <v>5.500000000000016E-2</v>
-      </c>
-      <c r="O19">
-        <f t="shared" ca="1" si="5"/>
-        <v>414607.76500000001</v>
-      </c>
-      <c r="P19">
-        <f t="shared" ca="1" si="6"/>
-        <v>-264858.68699999998</v>
-      </c>
-      <c r="R19" s="1"/>
-      <c r="S19" s="25">
-        <v>-488</v>
-      </c>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B20" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="22">
-        <v>86.3</v>
-      </c>
-      <c r="D20" s="25">
-        <f t="shared" si="10"/>
-        <v>8.629999999999999</v>
-      </c>
-      <c r="E20" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="F20" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="G20" s="26">
-        <f t="shared" si="11"/>
-        <v>28</v>
-      </c>
-      <c r="H20" s="22">
-        <f t="shared" ref="H20:H44" si="12">ROUND(D20/E20,0)</f>
-        <v>17</v>
-      </c>
-      <c r="I20" s="24"/>
-      <c r="J20" s="30">
-        <v>46133</v>
-      </c>
-      <c r="K20">
-        <f t="shared" ca="1" si="7"/>
-        <v>90.1</v>
-      </c>
-      <c r="L20">
-        <f t="shared" ca="1" si="8"/>
         <v>40.5</v>
       </c>
-      <c r="M20">
-        <f t="shared" ca="1" si="9"/>
-        <v>109.5</v>
-      </c>
-      <c r="N20">
-        <f t="shared" ca="1" si="4"/>
-        <v>88</v>
-      </c>
-      <c r="O20">
-        <f t="shared" ca="1" si="5"/>
-        <v>149.5</v>
-      </c>
-      <c r="P20">
-        <f t="shared" ca="1" si="6"/>
-        <v>63</v>
-      </c>
-      <c r="R20" s="25">
+      <c r="R21" s="25">
         <v>-741</v>
       </c>
-      <c r="S20" s="25">
+      <c r="S21" s="25">
         <v>-475</v>
       </c>
-      <c r="T20" s="29">
+      <c r="T21" s="29">
         <v>34</v>
       </c>
-      <c r="U20" s="1"/>
-    </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
+      <c r="U21" s="1"/>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C21">
+      <c r="C22">
         <v>1.05</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D22" s="25">
         <f t="shared" si="1"/>
         <v>0.10500000000000001</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E22" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F22" s="1">
         <v>0.05</v>
       </c>
-      <c r="G21" s="26">
+      <c r="G22" s="26">
         <f t="shared" si="2"/>
-        <v>229</v>
-      </c>
-      <c r="H21" s="22">
-        <f t="shared" si="12"/>
+        <v>238</v>
+      </c>
+      <c r="H22" s="22">
+        <f t="shared" si="15"/>
         <v>21</v>
       </c>
-      <c r="I21" s="23"/>
-      <c r="J21" s="30">
+      <c r="I22" s="23"/>
+      <c r="J22" s="30">
         <v>46133</v>
       </c>
-      <c r="K21">
+      <c r="K22">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.84</v>
+      </c>
+      <c r="L22">
+        <f t="shared" ca="1" si="11"/>
+        <v>1.4500000000000028</v>
+      </c>
+      <c r="M22">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.28000000000000114</v>
+      </c>
+      <c r="N22">
         <f t="shared" ca="1" si="7"/>
-        <v>18433.419999999998</v>
-      </c>
-      <c r="L21">
+        <v>0.72499999999999787</v>
+      </c>
+      <c r="O22">
         <f t="shared" ca="1" si="8"/>
+        <v>0.74500000000000099</v>
+      </c>
+      <c r="P22">
+        <f t="shared" ca="1" si="9"/>
         <v>0.98499999999999943</v>
       </c>
-      <c r="M21">
-        <f t="shared" ca="1" si="9"/>
-        <v>0.45500000000000185</v>
-      </c>
-      <c r="N21">
-        <f t="shared" ca="1" si="4"/>
-        <v>46022.635000000002</v>
-      </c>
-      <c r="O21">
-        <f t="shared" ca="1" si="5"/>
-        <v>0.73499999999999943</v>
-      </c>
-      <c r="P21">
-        <f t="shared" ca="1" si="6"/>
-        <v>46142.264999999999</v>
-      </c>
-      <c r="R21" s="25">
+      <c r="R22" s="25">
         <v>-107</v>
       </c>
-      <c r="S21" s="25">
+      <c r="S22" s="25">
         <v>-169</v>
       </c>
-      <c r="T21" s="29">
+      <c r="T22" s="29">
         <v>24</v>
       </c>
-      <c r="U21" s="1"/>
-    </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
+      <c r="U22" s="1"/>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C23" s="1">
         <v>150</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D23" s="25">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E23" s="1">
         <v>0.5</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F23" s="1">
         <v>0.5</v>
       </c>
-      <c r="G22" s="26">
+      <c r="G23" s="26">
         <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-      <c r="H22" s="22">
-        <f t="shared" si="12"/>
+        <v>17</v>
+      </c>
+      <c r="H23" s="22">
+        <f t="shared" si="15"/>
         <v>30</v>
       </c>
-      <c r="I22" s="23"/>
-      <c r="J22" s="30"/>
-      <c r="K22">
-        <f t="shared" ca="1" si="7"/>
-        <v>45.2</v>
-      </c>
-      <c r="L22">
-        <f t="shared" ca="1" si="8"/>
-        <v>38.5</v>
-      </c>
-      <c r="M22">
-        <f t="shared" ca="1" si="9"/>
-        <v>38</v>
-      </c>
-      <c r="N22">
-        <f t="shared" ca="1" si="4"/>
-        <v>58.5</v>
-      </c>
-      <c r="O22">
-        <f t="shared" ca="1" si="5"/>
-        <v>47</v>
-      </c>
-      <c r="P22">
-        <f t="shared" ca="1" si="6"/>
-        <v>44</v>
-      </c>
-      <c r="R22" s="29">
-        <v>45</v>
-      </c>
-      <c r="S22" s="29">
-        <v>10</v>
-      </c>
-      <c r="T22" s="29">
-        <v>44</v>
-      </c>
-      <c r="U22" s="1"/>
-    </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B23" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="22">
-        <v>5.7</v>
-      </c>
-      <c r="D23" s="25">
-        <f>C23/10</f>
-        <v>0.57000000000000006</v>
-      </c>
-      <c r="E23" s="22">
-        <v>0.01</v>
-      </c>
-      <c r="F23" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="G23" s="26">
-        <f>ROUND($C$4/(D23/E23*F23),0)</f>
-        <v>42</v>
-      </c>
-      <c r="H23" s="22">
-        <f t="shared" si="12"/>
-        <v>57</v>
-      </c>
-      <c r="I23" s="24"/>
+      <c r="I23" s="23"/>
       <c r="J23" s="30"/>
       <c r="K23">
+        <f t="shared" ca="1" si="10"/>
+        <v>67</v>
+      </c>
+      <c r="L23">
+        <f t="shared" ca="1" si="11"/>
+        <v>74</v>
+      </c>
+      <c r="M23">
+        <f t="shared" ca="1" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="N23">
         <f t="shared" ca="1" si="7"/>
-        <v>3.18</v>
-      </c>
-      <c r="L23">
+        <v>157</v>
+      </c>
+      <c r="O23">
         <f t="shared" ca="1" si="8"/>
-        <v>2.8000000000000114</v>
-      </c>
-      <c r="M23">
+        <v>50.5</v>
+      </c>
+      <c r="P23">
         <f t="shared" ca="1" si="9"/>
-        <v>5.3899999999999864</v>
-      </c>
-      <c r="N23">
-        <f t="shared" ca="1" si="4"/>
-        <v>3.2199999999999989</v>
-      </c>
-      <c r="O23">
-        <f t="shared" ca="1" si="5"/>
-        <v>1.5800000000000125</v>
-      </c>
-      <c r="P23">
-        <f t="shared" ca="1" si="6"/>
-        <v>2.9000000000000057</v>
-      </c>
-      <c r="R23" s="25">
-        <v>-146</v>
-      </c>
-      <c r="S23" s="25">
-        <v>-28</v>
+        <v>38.5</v>
+      </c>
+      <c r="R23" s="29">
+        <v>45</v>
+      </c>
+      <c r="S23" s="29">
+        <v>10</v>
       </c>
       <c r="T23" s="29">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="U23" s="1"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="22">
+        <v>5.7</v>
+      </c>
+      <c r="D24" s="25">
+        <f>C24/10</f>
+        <v>0.57000000000000006</v>
+      </c>
+      <c r="E24" s="22">
+        <v>0.01</v>
+      </c>
+      <c r="F24" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="G24" s="26">
+        <f>ROUND($C$4/(D24/E24*F24),0)</f>
+        <v>44</v>
+      </c>
+      <c r="H24" s="22">
+        <f t="shared" si="15"/>
+        <v>57</v>
+      </c>
+      <c r="I24" s="24"/>
+      <c r="J24" s="30"/>
+      <c r="K24">
+        <f t="shared" ca="1" si="10"/>
+        <v>3.02</v>
+      </c>
+      <c r="L24">
+        <f t="shared" ca="1" si="11"/>
+        <v>4.9399999999999977</v>
+      </c>
+      <c r="M24">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.69999999999998863</v>
+      </c>
+      <c r="N24">
+        <f t="shared" ca="1" si="7"/>
+        <v>3.7999999999999829</v>
+      </c>
+      <c r="O24">
+        <f t="shared" ca="1" si="8"/>
+        <v>2.8499999999999943</v>
+      </c>
+      <c r="P24">
+        <f t="shared" ca="1" si="9"/>
+        <v>2.8000000000000114</v>
+      </c>
+      <c r="R24" s="25">
+        <v>-146</v>
+      </c>
+      <c r="S24" s="25">
+        <v>-28</v>
+      </c>
+      <c r="T24" s="29">
+        <v>31</v>
+      </c>
+      <c r="U24" s="1"/>
+    </row>
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B25" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C25" s="22">
         <v>6.5</v>
       </c>
-      <c r="D24" s="25">
+      <c r="D25" s="25">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E25" s="22">
         <v>0.01</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F25" s="22">
         <v>0.01</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G25" s="26">
         <f t="shared" si="2"/>
-        <v>369</v>
-      </c>
-      <c r="H24" s="22">
-        <f t="shared" si="12"/>
+        <v>385</v>
+      </c>
+      <c r="H25" s="22">
+        <f t="shared" si="15"/>
         <v>65</v>
       </c>
-      <c r="I24" s="23"/>
-      <c r="J24" s="30"/>
-      <c r="K24">
+      <c r="I25" s="23"/>
+      <c r="J25" s="30"/>
+      <c r="K25">
+        <f t="shared" ca="1" si="10"/>
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="L25">
+        <f t="shared" ca="1" si="11"/>
+        <v>4.2899999999999991</v>
+      </c>
+      <c r="M25">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.4199999999999946</v>
+      </c>
+      <c r="N25">
         <f t="shared" ca="1" si="7"/>
-        <v>2.13</v>
-      </c>
-      <c r="L24">
+        <v>3.6799999999999997</v>
+      </c>
+      <c r="O25">
         <f t="shared" ca="1" si="8"/>
+        <v>1.1800000000000068</v>
+      </c>
+      <c r="P25">
+        <f t="shared" ca="1" si="9"/>
         <v>2.0499999999999972</v>
       </c>
-      <c r="M24">
-        <f t="shared" ca="1" si="9"/>
-        <v>2.1299999999999955</v>
-      </c>
-      <c r="N24">
-        <f t="shared" ca="1" si="4"/>
-        <v>3.1200000000000045</v>
-      </c>
-      <c r="O24">
-        <f t="shared" ca="1" si="5"/>
-        <v>1.5300000000000011</v>
-      </c>
-      <c r="P24">
-        <f t="shared" ca="1" si="6"/>
-        <v>1.8199999999999932</v>
-      </c>
-      <c r="R24" s="25">
+      <c r="R25" s="25">
         <v>-6</v>
       </c>
-      <c r="S24" s="29">
+      <c r="S25" s="29">
         <v>142</v>
       </c>
-      <c r="T24" s="29">
+      <c r="T25" s="29">
         <v>62</v>
       </c>
-      <c r="U24" s="1"/>
-    </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
+      <c r="U25" s="1"/>
+    </row>
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C26" s="1">
         <v>4.1900000000000004</v>
       </c>
-      <c r="D25" s="25">
+      <c r="D26" s="25">
         <f t="shared" si="1"/>
         <v>0.41900000000000004</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E26" s="1">
         <v>0.05</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F26" s="1">
         <v>0.5</v>
-      </c>
-      <c r="G25" s="26">
-        <f t="shared" si="2"/>
-        <v>57</v>
-      </c>
-      <c r="H25" s="22">
-        <f t="shared" si="12"/>
-        <v>8</v>
-      </c>
-      <c r="I25" s="23"/>
-      <c r="J25" s="30">
-        <v>46063</v>
-      </c>
-      <c r="K25">
-        <f t="shared" ca="1" si="7"/>
-        <v>3.77</v>
-      </c>
-      <c r="L25">
-        <f t="shared" ca="1" si="8"/>
-        <v>4.6499999999999773</v>
-      </c>
-      <c r="M25">
-        <f t="shared" ca="1" si="9"/>
-        <v>2.5499999999999829</v>
-      </c>
-      <c r="N25">
-        <f t="shared" ca="1" si="4"/>
-        <v>2.9499999999999886</v>
-      </c>
-      <c r="O25">
-        <f t="shared" ca="1" si="5"/>
-        <v>3.6500000000000057</v>
-      </c>
-      <c r="P25">
-        <f t="shared" ca="1" si="6"/>
-        <v>5.0500000000000114</v>
-      </c>
-      <c r="R25" s="25">
-        <v>-149</v>
-      </c>
-      <c r="S25" s="29">
-        <v>46</v>
-      </c>
-      <c r="T25" s="29">
-        <v>59</v>
-      </c>
-      <c r="U25" s="1"/>
-    </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="1">
-        <v>4</v>
-      </c>
-      <c r="D26" s="25">
-        <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="F26" s="1">
-        <v>0.2</v>
       </c>
       <c r="G26" s="26">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="H26" s="22">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
+        <v>8</v>
+      </c>
+      <c r="I26" s="23"/>
+      <c r="J26" s="30">
+        <v>46063</v>
+      </c>
+      <c r="K26">
+        <f t="shared" ca="1" si="10"/>
+        <v>3.15</v>
+      </c>
+      <c r="L26">
+        <f t="shared" ca="1" si="11"/>
+        <v>4.6500000000000057</v>
+      </c>
+      <c r="M26">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.75</v>
+      </c>
+      <c r="N26">
+        <f t="shared" ca="1" si="7"/>
+        <v>3.0999999999999943</v>
+      </c>
+      <c r="O26">
+        <f t="shared" ca="1" si="8"/>
+        <v>2.5999999999999943</v>
+      </c>
+      <c r="P26">
+        <f t="shared" ca="1" si="9"/>
+        <v>4.6499999999999773</v>
+      </c>
+      <c r="R26" s="25">
+        <v>-149</v>
+      </c>
+      <c r="S26" s="29">
+        <v>46</v>
+      </c>
+      <c r="T26" s="29">
+        <v>59</v>
+      </c>
+      <c r="U26" s="1"/>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="25">
+        <f t="shared" si="1"/>
+        <v>0.4</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G27" s="26">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="H27" s="22">
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
-      <c r="I26" s="23"/>
-      <c r="J26" s="30"/>
-      <c r="K26">
+      <c r="I27" s="23"/>
+      <c r="J27" s="30"/>
+      <c r="K27">
+        <f t="shared" ca="1" si="10"/>
+        <v>1.91</v>
+      </c>
+      <c r="L27">
+        <f t="shared" ca="1" si="11"/>
+        <v>3.1599999999999966</v>
+      </c>
+      <c r="M27">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.42000000000000171</v>
+      </c>
+      <c r="N27">
         <f t="shared" ca="1" si="7"/>
-        <v>1.95</v>
-      </c>
-      <c r="L26">
+        <v>1.480000000000004</v>
+      </c>
+      <c r="O27">
         <f t="shared" ca="1" si="8"/>
+        <v>2.039999999999992</v>
+      </c>
+      <c r="P27">
+        <f t="shared" ca="1" si="9"/>
         <v>2.4599999999999937</v>
       </c>
-      <c r="M26">
+      <c r="R27" s="29">
+        <v>23</v>
+      </c>
+      <c r="S27" s="29">
+        <v>241</v>
+      </c>
+      <c r="T27" s="29">
+        <v>13</v>
+      </c>
+      <c r="U27" s="1"/>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B28" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="22">
+        <v>22.54</v>
+      </c>
+      <c r="D28" s="25">
+        <f>C28/10</f>
+        <v>2.254</v>
+      </c>
+      <c r="E28" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="F28" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="G28" s="26">
+        <f>ROUND($C$4/(D28/E28*F28),0)</f>
+        <v>111</v>
+      </c>
+      <c r="H28" s="22">
+        <f t="shared" si="15"/>
+        <v>23</v>
+      </c>
+      <c r="I28" s="24"/>
+      <c r="J28" s="30">
+        <v>46133</v>
+      </c>
+      <c r="K28">
+        <f t="shared" ca="1" si="10"/>
+        <v>19.78</v>
+      </c>
+      <c r="L28">
+        <f t="shared" ca="1" si="11"/>
+        <v>39.299999999999955</v>
+      </c>
+      <c r="M28">
+        <f t="shared" ca="1" si="12"/>
+        <v>3.2000000000000455</v>
+      </c>
+      <c r="N28">
+        <f t="shared" ca="1" si="7"/>
+        <v>23.299999999999955</v>
+      </c>
+      <c r="O28">
+        <f t="shared" ca="1" si="8"/>
+        <v>17.5</v>
+      </c>
+      <c r="P28">
         <f t="shared" ca="1" si="9"/>
-        <v>1.6599999999999966</v>
-      </c>
-      <c r="N26">
-        <f t="shared" ca="1" si="4"/>
-        <v>2.1199999999999903</v>
-      </c>
-      <c r="O26">
-        <f t="shared" ca="1" si="5"/>
-        <v>1.7000000000000028</v>
-      </c>
-      <c r="P26">
-        <f t="shared" ca="1" si="6"/>
-        <v>1.8200000000000074</v>
-      </c>
-      <c r="R26" s="29">
-        <v>23</v>
-      </c>
-      <c r="S26" s="29">
-        <v>241</v>
-      </c>
-      <c r="T26" s="29">
-        <v>13</v>
-      </c>
-      <c r="U26" s="1"/>
-    </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B27" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="22">
-        <v>22.54</v>
-      </c>
-      <c r="D27" s="25">
-        <f>C27/10</f>
-        <v>2.254</v>
-      </c>
-      <c r="E27" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="F27" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="G27" s="26">
-        <f>ROUND($C$4/(D27/E27*F27),0)</f>
-        <v>106</v>
-      </c>
-      <c r="H27" s="22">
-        <f t="shared" si="12"/>
-        <v>23</v>
-      </c>
-      <c r="I27" s="24"/>
-      <c r="J27" s="30">
-        <v>46133</v>
-      </c>
-      <c r="K27">
-        <f t="shared" ca="1" si="7"/>
-        <v>33.1</v>
-      </c>
-      <c r="L27">
-        <f t="shared" ca="1" si="8"/>
         <v>15.599999999999909</v>
       </c>
-      <c r="M27">
-        <f t="shared" ca="1" si="9"/>
-        <v>34.099999999999909</v>
-      </c>
-      <c r="N27">
-        <f t="shared" ca="1" si="4"/>
-        <v>36.5</v>
-      </c>
-      <c r="O27">
-        <f t="shared" ca="1" si="5"/>
-        <v>52.700000000000045</v>
-      </c>
-      <c r="P27">
-        <f t="shared" ca="1" si="6"/>
-        <v>26.600000000000136</v>
-      </c>
-      <c r="R27" s="1"/>
-      <c r="S27" s="29">
+      <c r="R28" s="1"/>
+      <c r="S28" s="29">
         <v>55</v>
       </c>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-    </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C29" s="1">
         <v>125.5</v>
       </c>
-      <c r="D28" s="25">
+      <c r="D29" s="25">
         <f t="shared" si="1"/>
         <v>12.55</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E29" s="1">
         <v>0.5</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F29" s="1">
         <v>0.5</v>
       </c>
-      <c r="G28" s="26">
+      <c r="G29" s="26">
         <f t="shared" si="2"/>
-        <v>19</v>
-      </c>
-      <c r="H28" s="22">
-        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="H29" s="22">
+        <f t="shared" si="15"/>
         <v>25</v>
       </c>
-      <c r="I28" s="23"/>
-      <c r="J28" s="30">
+      <c r="I29" s="23"/>
+      <c r="J29" s="30">
         <v>46133</v>
       </c>
-      <c r="K28">
+      <c r="K29">
+        <f t="shared" ca="1" si="10"/>
+        <v>117.3</v>
+      </c>
+      <c r="L29">
+        <f t="shared" ca="1" si="11"/>
+        <v>164</v>
+      </c>
+      <c r="M29">
+        <f t="shared" ca="1" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="N29">
         <f t="shared" ca="1" si="7"/>
-        <v>92.1</v>
-      </c>
-      <c r="L28">
+        <v>249</v>
+      </c>
+      <c r="O29">
         <f t="shared" ca="1" si="8"/>
+        <v>69.5</v>
+      </c>
+      <c r="P29">
+        <f t="shared" ca="1" si="9"/>
         <v>76</v>
       </c>
-      <c r="M28">
-        <f t="shared" ca="1" si="9"/>
-        <v>67.5</v>
-      </c>
-      <c r="N28">
-        <f t="shared" ca="1" si="4"/>
-        <v>114.5</v>
-      </c>
-      <c r="O28">
-        <f t="shared" ca="1" si="5"/>
-        <v>50</v>
-      </c>
-      <c r="P28">
-        <f t="shared" ca="1" si="6"/>
-        <v>152.5</v>
-      </c>
-      <c r="R28" s="25">
+      <c r="R29" s="25">
         <v>-6</v>
       </c>
-      <c r="S28" s="25">
+      <c r="S29" s="25">
         <v>-340</v>
       </c>
-      <c r="T28" s="29">
+      <c r="T29" s="29">
         <v>22</v>
       </c>
-      <c r="U28" s="1"/>
-    </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B29" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="22">
-        <v>140</v>
-      </c>
-      <c r="D29" s="25">
-        <f>C29/10</f>
-        <v>14</v>
-      </c>
-      <c r="E29" s="22">
-        <v>0.2</v>
-      </c>
-      <c r="F29" s="22">
-        <v>0.2</v>
-      </c>
-      <c r="G29" s="26">
-        <f>ROUND($C$4/(D29/E29*F29),0)</f>
-        <v>17</v>
-      </c>
-      <c r="H29" s="22">
-        <f t="shared" si="12"/>
-        <v>70</v>
-      </c>
-      <c r="I29" s="24"/>
-      <c r="K29">
-        <f t="shared" ca="1" si="7"/>
-        <v>23.92</v>
-      </c>
-      <c r="L29">
-        <f t="shared" ca="1" si="8"/>
-        <v>31</v>
-      </c>
-      <c r="M29">
-        <f t="shared" ca="1" si="9"/>
-        <v>15.400000000000091</v>
-      </c>
-      <c r="N29">
-        <f t="shared" ca="1" si="4"/>
-        <v>25.599999999999909</v>
-      </c>
-      <c r="O29">
-        <f t="shared" ca="1" si="5"/>
-        <v>24.799999999999955</v>
-      </c>
-      <c r="P29">
-        <f t="shared" ca="1" si="6"/>
-        <v>22.799999999999955</v>
-      </c>
-      <c r="R29" s="1"/>
-      <c r="S29" s="25">
-        <v>-426</v>
-      </c>
-      <c r="T29" s="1"/>
       <c r="U29" s="1"/>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="22" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C30" s="22">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="D30" s="25">
-        <f t="shared" ref="D30:D43" si="13">C30/10</f>
-        <v>11.2</v>
+        <f>C30/10</f>
+        <v>14</v>
       </c>
       <c r="E30" s="22">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="F30" s="22">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G30" s="26">
-        <f t="shared" ref="G30:G43" si="14">ROUND($C$4/(D30/E30*F30),0)</f>
-        <v>21</v>
+        <f>ROUND($C$4/(D30/E30*F30),0)</f>
+        <v>18</v>
       </c>
       <c r="H30" s="22">
-        <f t="shared" si="12"/>
-        <v>11</v>
+        <f t="shared" si="15"/>
+        <v>70</v>
       </c>
       <c r="I30" s="24"/>
       <c r="K30">
+        <f t="shared" ca="1" si="10"/>
+        <v>22.48</v>
+      </c>
+      <c r="L30">
+        <f t="shared" ca="1" si="11"/>
+        <v>16</v>
+      </c>
+      <c r="M30">
+        <f t="shared" ca="1" si="12"/>
+        <v>23</v>
+      </c>
+      <c r="N30">
         <f t="shared" ca="1" si="7"/>
-        <v>151.4</v>
-      </c>
-      <c r="L30">
+        <v>30</v>
+      </c>
+      <c r="O30">
         <f t="shared" ca="1" si="8"/>
-        <v>102</v>
-      </c>
-      <c r="M30">
+        <v>12.400000000000091</v>
+      </c>
+      <c r="P30">
         <f t="shared" ca="1" si="9"/>
-        <v>150</v>
-      </c>
-      <c r="N30">
-        <f t="shared" ca="1" si="4"/>
-        <v>139</v>
-      </c>
-      <c r="O30">
-        <f t="shared" ca="1" si="5"/>
-        <v>221</v>
-      </c>
-      <c r="P30">
-        <f t="shared" ca="1" si="6"/>
-        <v>145</v>
-      </c>
-      <c r="R30" s="25">
-        <v>-31</v>
-      </c>
-      <c r="S30" s="1"/>
-      <c r="T30" s="29">
-        <v>35</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="R30" s="1"/>
+      <c r="S30" s="25">
+        <v>-426</v>
+      </c>
+      <c r="T30" s="1"/>
       <c r="U30" s="1"/>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="22" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C31" s="22">
-        <v>13.12</v>
+        <v>112</v>
       </c>
       <c r="D31" s="25">
-        <f>C31/10</f>
-        <v>1.3119999999999998</v>
+        <f t="shared" ref="D31:D44" si="16">C31/10</f>
+        <v>11.2</v>
       </c>
       <c r="E31" s="22">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F31" s="22">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G31" s="26">
-        <f>ROUND($C$4/(D31/E31*F31),0)</f>
-        <v>183</v>
+        <f t="shared" ref="G31:G44" si="17">ROUND($C$4/(D31/E31*F31),0)</f>
+        <v>22</v>
       </c>
       <c r="H31" s="22">
-        <f t="shared" si="12"/>
-        <v>13</v>
+        <f t="shared" si="15"/>
+        <v>11</v>
       </c>
       <c r="I31" s="24"/>
-      <c r="J31" s="30">
-        <v>46066</v>
-      </c>
       <c r="K31">
+        <f t="shared" ca="1" si="10"/>
+        <v>109.2</v>
+      </c>
+      <c r="L31">
+        <f t="shared" ca="1" si="11"/>
+        <v>188</v>
+      </c>
+      <c r="M31">
+        <f t="shared" ca="1" si="12"/>
+        <v>18</v>
+      </c>
+      <c r="N31">
         <f t="shared" ca="1" si="7"/>
-        <v>2.94</v>
-      </c>
-      <c r="L31">
+        <v>108</v>
+      </c>
+      <c r="O31">
         <f t="shared" ca="1" si="8"/>
-        <v>2.5</v>
-      </c>
-      <c r="M31">
+        <v>130</v>
+      </c>
+      <c r="P31">
         <f t="shared" ca="1" si="9"/>
-        <v>2.3999999999999773</v>
-      </c>
-      <c r="N31">
-        <f t="shared" ca="1" si="4"/>
-        <v>2.3999999999999773</v>
-      </c>
-      <c r="O31">
-        <f t="shared" ca="1" si="5"/>
-        <v>3.2999999999999545</v>
-      </c>
-      <c r="P31">
-        <f t="shared" ca="1" si="6"/>
-        <v>4.1000000000000227</v>
-      </c>
-      <c r="R31" s="1"/>
-      <c r="S31" s="29">
-        <v>61</v>
-      </c>
-      <c r="T31" s="25">
-        <v>-11</v>
+        <v>102</v>
+      </c>
+      <c r="R31" s="25">
+        <v>-31</v>
+      </c>
+      <c r="S31" s="1"/>
+      <c r="T31" s="29">
+        <v>35</v>
       </c>
       <c r="U31" s="1"/>
     </row>
     <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B32" s="22" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C32" s="22">
-        <v>57.2</v>
+        <v>13.12</v>
       </c>
       <c r="D32" s="25">
-        <f t="shared" si="13"/>
-        <v>5.7200000000000006</v>
+        <f>C32/10</f>
+        <v>1.3119999999999998</v>
       </c>
       <c r="E32" s="22">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F32" s="22">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G32" s="26">
-        <f t="shared" si="14"/>
-        <v>42</v>
+        <f>ROUND($C$4/(D32/E32*F32),0)</f>
+        <v>191</v>
       </c>
       <c r="H32" s="22">
-        <f t="shared" si="12"/>
-        <v>29</v>
+        <f t="shared" si="15"/>
+        <v>13</v>
       </c>
       <c r="I32" s="24"/>
       <c r="J32" s="30">
+        <v>46066</v>
+      </c>
+      <c r="K32">
+        <f t="shared" ca="1" si="10"/>
+        <v>2.46</v>
+      </c>
+      <c r="L32">
+        <f t="shared" ca="1" si="11"/>
+        <v>3.7999999999999545</v>
+      </c>
+      <c r="M32">
+        <f t="shared" ca="1" si="12"/>
+        <v>1.3999999999999773</v>
+      </c>
+      <c r="N32">
+        <f t="shared" ca="1" si="7"/>
+        <v>1.8999999999999773</v>
+      </c>
+      <c r="O32">
+        <f t="shared" ca="1" si="8"/>
+        <v>2.6999999999999318</v>
+      </c>
+      <c r="P32">
+        <f t="shared" ca="1" si="9"/>
+        <v>2.5</v>
+      </c>
+      <c r="R32" s="1"/>
+      <c r="S32" s="29">
+        <v>61</v>
+      </c>
+      <c r="T32" s="25">
+        <v>-11</v>
+      </c>
+      <c r="U32" s="1"/>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B33" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="22">
+        <v>57.2</v>
+      </c>
+      <c r="D33" s="25">
+        <f t="shared" si="16"/>
+        <v>5.7200000000000006</v>
+      </c>
+      <c r="E33" s="22">
+        <v>0.2</v>
+      </c>
+      <c r="F33" s="22">
+        <v>0.2</v>
+      </c>
+      <c r="G33" s="26">
+        <f t="shared" si="17"/>
+        <v>44</v>
+      </c>
+      <c r="H33" s="22">
+        <f t="shared" si="15"/>
+        <v>29</v>
+      </c>
+      <c r="I33" s="24"/>
+      <c r="J33" s="30">
         <v>46133</v>
       </c>
-      <c r="K32">
+      <c r="K33">
+        <f t="shared" ca="1" si="10"/>
+        <v>42.88</v>
+      </c>
+      <c r="L33">
+        <f t="shared" ca="1" si="11"/>
+        <v>32.800000000000182</v>
+      </c>
+      <c r="M33">
+        <f t="shared" ca="1" si="12"/>
+        <v>11</v>
+      </c>
+      <c r="N33">
         <f t="shared" ca="1" si="7"/>
-        <v>54.52</v>
-      </c>
-      <c r="L32">
+        <v>104.40000000000009</v>
+      </c>
+      <c r="O33">
         <f t="shared" ca="1" si="8"/>
+        <v>30.400000000000091</v>
+      </c>
+      <c r="P33">
+        <f t="shared" ca="1" si="9"/>
         <v>35.800000000000182</v>
       </c>
-      <c r="M32">
-        <f t="shared" ca="1" si="9"/>
-        <v>44.800000000000182</v>
-      </c>
-      <c r="N32">
-        <f t="shared" ca="1" si="4"/>
-        <v>84</v>
-      </c>
-      <c r="O32">
-        <f t="shared" ca="1" si="5"/>
-        <v>71.599999999999909</v>
-      </c>
-      <c r="P32">
-        <f t="shared" ca="1" si="6"/>
-        <v>36.400000000000091</v>
-      </c>
-      <c r="R32" s="25">
+      <c r="R33" s="25">
         <v>-68</v>
       </c>
-      <c r="S32" s="25">
+      <c r="S33" s="25">
         <v>-291</v>
       </c>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B33" s="22" t="s">
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B34" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C34" s="22">
         <v>10</v>
       </c>
-      <c r="D33" s="25">
-        <f t="shared" si="13"/>
+      <c r="D34" s="25">
+        <f t="shared" si="16"/>
         <v>1</v>
-      </c>
-      <c r="E33" s="22">
-        <v>0.05</v>
-      </c>
-      <c r="F33" s="22">
-        <v>0.05</v>
-      </c>
-      <c r="G33" s="26">
-        <f t="shared" si="14"/>
-        <v>240</v>
-      </c>
-      <c r="H33" s="22">
-        <f t="shared" si="12"/>
-        <v>20</v>
-      </c>
-      <c r="I33" s="24"/>
-      <c r="K33">
-        <f t="shared" ca="1" si="7"/>
-        <v>5.16</v>
-      </c>
-      <c r="L33">
-        <f t="shared" ca="1" si="8"/>
-        <v>2.2000000000000028</v>
-      </c>
-      <c r="M33">
-        <f t="shared" ca="1" si="9"/>
-        <v>6.0499999999999972</v>
-      </c>
-      <c r="N33">
-        <f t="shared" ca="1" si="4"/>
-        <v>4.5</v>
-      </c>
-      <c r="O33">
-        <f t="shared" ca="1" si="5"/>
-        <v>11.400000000000006</v>
-      </c>
-      <c r="P33">
-        <f t="shared" ca="1" si="6"/>
-        <v>1.6499999999999915</v>
-      </c>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="29">
-        <v>33</v>
-      </c>
-      <c r="U33" s="1"/>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B34" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="22">
-        <v>6.34</v>
-      </c>
-      <c r="D34" s="25">
-        <f t="shared" si="13"/>
-        <v>0.63400000000000001</v>
       </c>
       <c r="E34" s="22">
         <v>0.05</v>
@@ -3518,1123 +3522,1180 @@
         <v>0.05</v>
       </c>
       <c r="G34" s="26">
-        <f t="shared" si="14"/>
-        <v>379</v>
+        <f t="shared" si="17"/>
+        <v>250</v>
       </c>
       <c r="H34" s="22">
-        <f t="shared" si="12"/>
-        <v>13</v>
-      </c>
-      <c r="I34" s="23"/>
-      <c r="J34" s="30">
-        <v>46133</v>
-      </c>
+        <f t="shared" si="15"/>
+        <v>20</v>
+      </c>
+      <c r="I34" s="24"/>
       <c r="K34">
+        <f t="shared" ca="1" si="10"/>
+        <v>3.15</v>
+      </c>
+      <c r="L34">
+        <f t="shared" ca="1" si="11"/>
+        <v>2.5999999999999943</v>
+      </c>
+      <c r="M34">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.94999999999998863</v>
+      </c>
+      <c r="N34">
         <f t="shared" ca="1" si="7"/>
-        <v>11.79</v>
-      </c>
-      <c r="L34">
+        <v>6.6500000000000057</v>
+      </c>
+      <c r="O34">
         <f t="shared" ca="1" si="8"/>
-        <v>5.4000000000000341</v>
-      </c>
-      <c r="M34">
+        <v>3.3499999999999943</v>
+      </c>
+      <c r="P34">
         <f t="shared" ca="1" si="9"/>
-        <v>11.850000000000023</v>
-      </c>
-      <c r="N34">
-        <f t="shared" ca="1" si="4"/>
-        <v>13.100000000000023</v>
-      </c>
-      <c r="O34">
-        <f t="shared" ca="1" si="5"/>
-        <v>24.600000000000023</v>
-      </c>
-      <c r="P34">
-        <f t="shared" ca="1" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="R34" s="29">
-        <v>342</v>
-      </c>
-      <c r="S34" s="25">
-        <v>-106</v>
-      </c>
-      <c r="T34" s="25">
-        <v>-93</v>
+        <v>2.2000000000000028</v>
+      </c>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="29">
+        <v>33</v>
       </c>
       <c r="U34" s="1"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B35" s="22" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C35" s="22">
-        <v>1.1299999999999999</v>
+        <v>6.34</v>
       </c>
       <c r="D35" s="25">
-        <f>C35/10</f>
-        <v>0.11299999999999999</v>
+        <f t="shared" si="16"/>
+        <v>0.63400000000000001</v>
       </c>
       <c r="E35" s="22">
-        <v>5.0000000000000001E-3</v>
+        <v>0.05</v>
       </c>
       <c r="F35" s="22">
         <v>0.05</v>
       </c>
       <c r="G35" s="26">
-        <f>ROUND($C$4/(D35/E35*F35),0)</f>
-        <v>212</v>
+        <f t="shared" si="17"/>
+        <v>394</v>
       </c>
       <c r="H35" s="22">
-        <f t="shared" si="12"/>
-        <v>23</v>
-      </c>
-      <c r="I35" s="24"/>
+        <f t="shared" si="15"/>
+        <v>13</v>
+      </c>
+      <c r="I35" s="23"/>
       <c r="J35" s="30">
         <v>46133</v>
       </c>
       <c r="K35">
+        <f t="shared" ca="1" si="10"/>
+        <v>7.83</v>
+      </c>
+      <c r="L35">
+        <f t="shared" ca="1" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="M35">
+        <f t="shared" ca="1" si="12"/>
+        <v>2.3500000000000227</v>
+      </c>
+      <c r="N35">
         <f t="shared" ca="1" si="7"/>
-        <v>1.32</v>
-      </c>
-      <c r="L35">
+        <v>14.25</v>
+      </c>
+      <c r="O35">
         <f t="shared" ca="1" si="8"/>
-        <v>0.92000000000000171</v>
-      </c>
-      <c r="M35">
+        <v>9.1499999999999773</v>
+      </c>
+      <c r="P35">
         <f t="shared" ca="1" si="9"/>
-        <v>1.0949999999999989</v>
-      </c>
-      <c r="N35">
-        <f t="shared" ca="1" si="4"/>
-        <v>1.5899999999999963</v>
-      </c>
-      <c r="O35">
-        <f t="shared" ca="1" si="5"/>
-        <v>1.9899999999999949</v>
-      </c>
-      <c r="P35">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.99000000000000199</v>
-      </c>
-      <c r="R35" s="1"/>
+        <v>5.4000000000000341</v>
+      </c>
+      <c r="R35" s="29">
+        <v>342</v>
+      </c>
       <c r="S35" s="25">
-        <v>-143</v>
-      </c>
-      <c r="T35" s="1"/>
+        <v>-106</v>
+      </c>
+      <c r="T35" s="25">
+        <v>-93</v>
+      </c>
       <c r="U35" s="1"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B36" s="22" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C36" s="22">
-        <v>6</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D36" s="25">
-        <f t="shared" si="13"/>
-        <v>0.6</v>
+        <f>C36/10</f>
+        <v>0.11299999999999999</v>
       </c>
       <c r="E36" s="22">
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F36" s="22">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="G36" s="26">
-        <f t="shared" si="14"/>
-        <v>400</v>
+        <f>ROUND($C$4/(D36/E36*F36),0)</f>
+        <v>221</v>
       </c>
       <c r="H36" s="22">
-        <f t="shared" si="12"/>
-        <v>60</v>
-      </c>
-      <c r="I36" s="23"/>
+        <f t="shared" si="15"/>
+        <v>23</v>
+      </c>
+      <c r="I36" s="24"/>
       <c r="J36" s="30">
         <v>46133</v>
       </c>
       <c r="K36">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.81</v>
+      </c>
+      <c r="L36">
+        <f t="shared" ca="1" si="11"/>
+        <v>1.0949999999999989</v>
+      </c>
+      <c r="M36">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.29500000000000171</v>
+      </c>
+      <c r="N36">
         <f t="shared" ca="1" si="7"/>
-        <v>3.83</v>
-      </c>
-      <c r="L36">
+        <v>0.98000000000000398</v>
+      </c>
+      <c r="O36">
         <f t="shared" ca="1" si="8"/>
+        <v>0.77499999999999858</v>
+      </c>
+      <c r="P36">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.92000000000000171</v>
+      </c>
+      <c r="R36" s="1"/>
+      <c r="S36" s="25">
+        <v>-143</v>
+      </c>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B37" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="22">
+        <v>6</v>
+      </c>
+      <c r="D37" s="25">
+        <f t="shared" si="16"/>
+        <v>0.6</v>
+      </c>
+      <c r="E37" s="22">
+        <v>0.01</v>
+      </c>
+      <c r="F37" s="22">
+        <v>0.01</v>
+      </c>
+      <c r="G37" s="26">
+        <f t="shared" si="17"/>
+        <v>417</v>
+      </c>
+      <c r="H37" s="22">
+        <f t="shared" si="15"/>
+        <v>60</v>
+      </c>
+      <c r="I37" s="23"/>
+      <c r="J37" s="30">
+        <v>46133</v>
+      </c>
+      <c r="K37">
+        <f t="shared" ca="1" si="10"/>
+        <v>2.87</v>
+      </c>
+      <c r="L37">
+        <f t="shared" ca="1" si="11"/>
+        <v>3.9399999999999977</v>
+      </c>
+      <c r="M37">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="N37">
+        <f t="shared" ca="1" si="7"/>
+        <v>3.4900000000000091</v>
+      </c>
+      <c r="O37">
+        <f t="shared" ca="1" si="8"/>
+        <v>2.4399999999999977</v>
+      </c>
+      <c r="P37">
+        <f t="shared" ca="1" si="9"/>
         <v>3.9599999999999795</v>
       </c>
-      <c r="M36">
+      <c r="R37" s="29">
+        <v>32</v>
+      </c>
+      <c r="S37" s="25">
+        <v>-139</v>
+      </c>
+      <c r="T37" s="29">
+        <v>40</v>
+      </c>
+      <c r="U37" s="1"/>
+    </row>
+    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B38" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="22">
+        <v>44.16</v>
+      </c>
+      <c r="D38" s="25">
+        <f t="shared" si="16"/>
+        <v>4.4159999999999995</v>
+      </c>
+      <c r="E38" s="22">
+        <v>0.2</v>
+      </c>
+      <c r="F38" s="22">
+        <v>0.2</v>
+      </c>
+      <c r="G38" s="26">
+        <f t="shared" si="17"/>
+        <v>57</v>
+      </c>
+      <c r="H38" s="22">
+        <f t="shared" si="15"/>
+        <v>22</v>
+      </c>
+      <c r="I38" s="24"/>
+      <c r="J38" s="30">
+        <v>46058</v>
+      </c>
+      <c r="K38">
+        <f t="shared" ca="1" si="10"/>
+        <v>27.28</v>
+      </c>
+      <c r="L38">
+        <f t="shared" ca="1" si="11"/>
+        <v>26</v>
+      </c>
+      <c r="M38">
+        <f t="shared" ca="1" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="N38">
+        <f t="shared" ca="1" si="7"/>
+        <v>24.799999999999955</v>
+      </c>
+      <c r="O38">
+        <f t="shared" ca="1" si="8"/>
+        <v>42.600000000000023</v>
+      </c>
+      <c r="P38">
         <f t="shared" ca="1" si="9"/>
-        <v>3.7099999999999795</v>
-      </c>
-      <c r="N36">
-        <f t="shared" ca="1" si="4"/>
-        <v>3.1299999999999955</v>
-      </c>
-      <c r="O36">
-        <f t="shared" ca="1" si="5"/>
-        <v>3.5799999999999841</v>
-      </c>
-      <c r="P36">
-        <f t="shared" ca="1" si="6"/>
-        <v>4.7899999999999636</v>
-      </c>
-      <c r="R36" s="29">
-        <v>32</v>
-      </c>
-      <c r="S36" s="25">
-        <v>-139</v>
-      </c>
-      <c r="T36" s="29">
-        <v>40</v>
-      </c>
-      <c r="U36" s="1"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B37" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="22">
-        <v>44.16</v>
-      </c>
-      <c r="D37" s="25">
-        <f t="shared" si="13"/>
-        <v>4.4159999999999995</v>
-      </c>
-      <c r="E37" s="22">
-        <v>0.2</v>
-      </c>
-      <c r="F37" s="22">
-        <v>0.2</v>
-      </c>
-      <c r="G37" s="26">
-        <f t="shared" si="14"/>
-        <v>54</v>
-      </c>
-      <c r="H37" s="22">
-        <f t="shared" si="12"/>
-        <v>22</v>
-      </c>
-      <c r="I37" s="24"/>
-      <c r="J37" s="30">
-        <v>46058</v>
-      </c>
-      <c r="K37">
-        <f t="shared" ca="1" si="7"/>
-        <v>17.559999999999999</v>
-      </c>
-      <c r="L37">
-        <f t="shared" ca="1" si="8"/>
         <v>31</v>
       </c>
-      <c r="M37">
-        <f t="shared" ca="1" si="9"/>
-        <v>15</v>
-      </c>
-      <c r="N37">
-        <f t="shared" ca="1" si="4"/>
-        <v>14.800000000000068</v>
-      </c>
-      <c r="O37">
-        <f t="shared" ca="1" si="5"/>
-        <v>14</v>
-      </c>
-      <c r="P37">
-        <f t="shared" ca="1" si="6"/>
-        <v>13</v>
-      </c>
-      <c r="R37" s="25">
+      <c r="R38" s="25">
         <v>-89</v>
       </c>
-      <c r="S37" s="25">
+      <c r="S38" s="25">
         <v>-300</v>
       </c>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B38" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38" s="22">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D38" s="25">
-        <f>C38/10</f>
-        <v>1.4000000000000002E-2</v>
-      </c>
-      <c r="E38" s="22">
-        <v>1E-3</v>
-      </c>
-      <c r="F38" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="G38" s="26">
-        <f>ROUND($C$4/(D38/E38*F38),0)</f>
-        <v>171</v>
-      </c>
-      <c r="H38" s="22">
-        <f t="shared" si="12"/>
-        <v>14</v>
-      </c>
-      <c r="I38" s="24"/>
-      <c r="K38">
-        <f t="shared" ca="1" si="7"/>
-        <v>9222.4699999999993</v>
-      </c>
-      <c r="L38">
-        <f t="shared" ca="1" si="8"/>
-        <v>46112.035499999998</v>
-      </c>
-      <c r="M38">
-        <f t="shared" ca="1" si="9"/>
-        <v>9.8499999999999921E-2</v>
-      </c>
-      <c r="N38">
-        <f t="shared" ca="1" si="4"/>
-        <v>3.8499999999999979E-2</v>
-      </c>
-      <c r="O38">
-        <f t="shared" ca="1" si="5"/>
-        <v>9.6999999999999975E-2</v>
-      </c>
-      <c r="P38">
-        <f t="shared" ca="1" si="6"/>
-        <v>6.9499999999999895E-2</v>
-      </c>
-      <c r="R38" s="29">
-        <v>71</v>
-      </c>
-      <c r="S38" s="22"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B39" s="22" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C39" s="22">
-        <v>18.600000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D39" s="25">
         <f>C39/10</f>
-        <v>1.86</v>
+        <v>1.4000000000000002E-2</v>
       </c>
       <c r="E39" s="22">
-        <v>0.05</v>
+        <v>1E-3</v>
       </c>
       <c r="F39" s="22">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G39" s="26">
         <f>ROUND($C$4/(D39/E39*F39),0)</f>
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="H39" s="22">
-        <f t="shared" si="12"/>
-        <v>37</v>
+        <f t="shared" si="15"/>
+        <v>14</v>
       </c>
       <c r="I39" s="24"/>
       <c r="K39">
+        <f t="shared" ca="1" si="10"/>
+        <v>18.05</v>
+      </c>
+      <c r="L39">
+        <f t="shared" ca="1" si="11"/>
+        <v>6.9499999999999895E-2</v>
+      </c>
+      <c r="M39">
+        <f t="shared" ca="1" si="12"/>
+        <v>1.5000000000000013E-2</v>
+      </c>
+      <c r="N39">
         <f t="shared" ca="1" si="7"/>
-        <v>12.36</v>
-      </c>
-      <c r="L39">
+        <v>6.3999999999999946E-2</v>
+      </c>
+      <c r="O39">
         <f t="shared" ca="1" si="8"/>
-        <v>5.0499999999999545</v>
-      </c>
-      <c r="M39">
+        <v>-46021.955499999996</v>
+      </c>
+      <c r="P39">
         <f t="shared" ca="1" si="9"/>
-        <v>13.25</v>
-      </c>
-      <c r="N39">
-        <f t="shared" ca="1" si="4"/>
-        <v>11.700000000000045</v>
-      </c>
-      <c r="O39">
-        <f t="shared" ca="1" si="5"/>
-        <v>24.049999999999955</v>
-      </c>
-      <c r="P39">
-        <f t="shared" ca="1" si="6"/>
-        <v>7.75</v>
-      </c>
-      <c r="R39" s="25">
-        <v>-9</v>
-      </c>
-      <c r="S39" s="29">
-        <v>42</v>
-      </c>
+        <v>46112.035499999998</v>
+      </c>
+      <c r="R39" s="29">
+        <v>71</v>
+      </c>
+      <c r="S39" s="22"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B40" s="22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C40" s="22">
-        <v>45</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="D40" s="25">
         <f>C40/10</f>
-        <v>4.5</v>
+        <v>1.86</v>
       </c>
       <c r="E40" s="22">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="F40" s="22">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G40" s="26">
         <f>ROUND($C$4/(D40/E40*F40),0)</f>
-        <v>53</v>
+        <v>134</v>
       </c>
       <c r="H40" s="22">
-        <f t="shared" si="12"/>
-        <v>23</v>
+        <f t="shared" si="15"/>
+        <v>37</v>
       </c>
       <c r="I40" s="24"/>
-      <c r="J40" s="30">
-        <v>46133</v>
-      </c>
       <c r="K40">
+        <f t="shared" ca="1" si="10"/>
+        <v>8.84</v>
+      </c>
+      <c r="L40">
+        <f t="shared" ca="1" si="11"/>
+        <v>11.75</v>
+      </c>
+      <c r="M40">
+        <f t="shared" ca="1" si="12"/>
+        <v>2.5499999999999545</v>
+      </c>
+      <c r="N40">
         <f t="shared" ca="1" si="7"/>
-        <v>28.48</v>
-      </c>
-      <c r="L40">
+        <v>16.450000000000045</v>
+      </c>
+      <c r="O40">
         <f t="shared" ca="1" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="M40">
+        <v>8.4000000000000909</v>
+      </c>
+      <c r="P40">
         <f t="shared" ca="1" si="9"/>
-        <v>18</v>
-      </c>
-      <c r="N40">
-        <f t="shared" ca="1" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="O40">
-        <f t="shared" ca="1" si="5"/>
-        <v>17</v>
-      </c>
-      <c r="P40">
-        <f t="shared" ca="1" si="6"/>
-        <v>27.399999999999977</v>
-      </c>
-      <c r="R40" s="1"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="29">
-        <v>22</v>
-      </c>
+        <v>5.0499999999999545</v>
+      </c>
+      <c r="R40" s="25">
+        <v>-9</v>
+      </c>
+      <c r="S40" s="29">
+        <v>42</v>
+      </c>
+      <c r="T40" s="1"/>
       <c r="U40" s="1"/>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B41" s="1" t="s">
-        <v>75</v>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B41" s="22" t="s">
+        <v>69</v>
       </c>
       <c r="C41" s="22">
-        <v>690</v>
+        <v>45</v>
       </c>
       <c r="D41" s="25">
         <f>C41/10</f>
-        <v>69</v>
+        <v>4.5</v>
       </c>
       <c r="E41" s="22">
-        <v>5.0000000000000001E-3</v>
+        <v>0.2</v>
       </c>
       <c r="F41" s="22">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G41" s="26">
         <f>ROUND($C$4/(D41/E41*F41),0)</f>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H41" s="22">
-        <f t="shared" si="12"/>
-        <v>13800</v>
+        <f t="shared" si="15"/>
+        <v>23</v>
       </c>
       <c r="I41" s="24"/>
+      <c r="J41" s="30">
+        <v>46133</v>
+      </c>
       <c r="K41">
+        <f t="shared" ca="1" si="10"/>
+        <v>40.28</v>
+      </c>
+      <c r="L41">
+        <f t="shared" ca="1" si="11"/>
+        <v>55.799999999999955</v>
+      </c>
+      <c r="M41">
+        <f t="shared" ca="1" si="12"/>
+        <v>11.599999999999909</v>
+      </c>
+      <c r="N41">
         <f t="shared" ca="1" si="7"/>
-        <v>6.44</v>
-      </c>
-      <c r="L41">
+        <v>53.799999999999955</v>
+      </c>
+      <c r="O41">
         <f t="shared" ca="1" si="8"/>
-        <v>0.22000000000000242</v>
-      </c>
-      <c r="M41">
+        <v>20.200000000000045</v>
+      </c>
+      <c r="P41">
         <f t="shared" ca="1" si="9"/>
-        <v>0.34499999999999886</v>
-      </c>
-      <c r="N41">
-        <f t="shared" ca="1" si="4"/>
-        <v>46172.764999999999</v>
-      </c>
-      <c r="O41">
-        <f t="shared" ca="1" si="5"/>
-        <v>-46141.48</v>
-      </c>
-      <c r="P41">
-        <f t="shared" ca="1" si="6"/>
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B42" s="22" t="s">
         <v>60</v>
       </c>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="29">
+        <v>22</v>
+      </c>
+      <c r="U41" s="1"/>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="C42" s="22">
-        <v>1.65</v>
+        <v>690</v>
       </c>
       <c r="D42" s="25">
-        <f t="shared" si="13"/>
-        <v>0.16499999999999998</v>
+        <f>C42/10</f>
+        <v>69</v>
       </c>
       <c r="E42" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F42" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="G42" s="26">
+        <f>ROUND($C$4/(D42/E42*F42),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="22">
+        <f t="shared" si="15"/>
+        <v>13800</v>
+      </c>
+      <c r="I42" s="24"/>
+      <c r="K42">
+        <f t="shared" ca="1" si="10"/>
+        <v>0.27</v>
+      </c>
+      <c r="L42">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.4599999999999973</v>
+      </c>
+      <c r="M42">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.14000000000000057</v>
+      </c>
+      <c r="N42">
+        <f t="shared" ca="1" si="7"/>
+        <v>0.33999999999999986</v>
+      </c>
+      <c r="O42">
+        <f t="shared" ca="1" si="8"/>
+        <v>0.18500000000000227</v>
+      </c>
+      <c r="P42">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.22000000000000242</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B43" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="22">
+        <v>1.65</v>
+      </c>
+      <c r="D43" s="25">
+        <f t="shared" si="16"/>
+        <v>0.16499999999999998</v>
+      </c>
+      <c r="E43" s="22">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F43" s="22">
         <v>0.05</v>
       </c>
-      <c r="G42" s="26">
-        <f t="shared" si="14"/>
-        <v>145</v>
-      </c>
-      <c r="H42" s="22">
-        <f t="shared" si="12"/>
+      <c r="G43" s="26">
+        <f t="shared" si="17"/>
+        <v>152</v>
+      </c>
+      <c r="H43" s="22">
+        <f t="shared" si="15"/>
         <v>33</v>
       </c>
-      <c r="I42" s="24"/>
-      <c r="J42" s="30">
+      <c r="I43" s="24"/>
+      <c r="J43" s="30">
         <v>46133</v>
       </c>
-      <c r="K42">
+      <c r="K43">
+        <f t="shared" ca="1" si="10"/>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="L43">
+        <f t="shared" ca="1" si="11"/>
+        <v>1.240000000000002</v>
+      </c>
+      <c r="M43">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.18999999999999773</v>
+      </c>
+      <c r="N43">
         <f t="shared" ca="1" si="7"/>
-        <v>1.36</v>
-      </c>
-      <c r="L42">
+        <v>1.1749999999999972</v>
+      </c>
+      <c r="O43">
         <f t="shared" ca="1" si="8"/>
+        <v>1.7600000000000051</v>
+      </c>
+      <c r="P43">
+        <f t="shared" ca="1" si="9"/>
         <v>1.4200000000000017</v>
       </c>
-      <c r="M42">
-        <f t="shared" ca="1" si="9"/>
-        <v>1.1400000000000006</v>
-      </c>
-      <c r="N42">
-        <f t="shared" ca="1" si="4"/>
-        <v>1.0649999999999977</v>
-      </c>
-      <c r="O42">
-        <f t="shared" ca="1" si="5"/>
-        <v>1.5</v>
-      </c>
-      <c r="P42">
-        <f t="shared" ca="1" si="6"/>
-        <v>1.6850000000000023</v>
-      </c>
-      <c r="R42" s="25">
+      <c r="R43" s="25">
         <v>-18</v>
       </c>
-      <c r="S42" s="25">
+      <c r="S43" s="25">
         <v>-76</v>
       </c>
-      <c r="T42" s="25">
+      <c r="T43" s="25">
         <v>-116</v>
       </c>
-      <c r="U42" s="1"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B43" s="22" t="s">
+      <c r="U43" s="1"/>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B44" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C43" s="22">
+      <c r="C44" s="22">
         <v>12</v>
       </c>
-      <c r="D43" s="25">
-        <f t="shared" si="13"/>
+      <c r="D44" s="25">
+        <f t="shared" si="16"/>
         <v>1.2</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E44" s="22">
         <v>0.1</v>
       </c>
-      <c r="F43" s="22">
+      <c r="F44" s="22">
         <v>0.1</v>
       </c>
-      <c r="G43" s="26">
-        <f t="shared" si="14"/>
-        <v>200</v>
-      </c>
-      <c r="H43" s="22">
-        <f t="shared" si="12"/>
+      <c r="G44" s="26">
+        <f t="shared" si="17"/>
+        <v>208</v>
+      </c>
+      <c r="H44" s="22">
+        <f t="shared" si="15"/>
         <v>12</v>
-      </c>
-      <c r="I43" s="24"/>
-      <c r="K43">
-        <f t="shared" ca="1" si="7"/>
-        <v>19.059999999999999</v>
-      </c>
-      <c r="L43">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B43&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B43&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>14.700000000000045</v>
-      </c>
-      <c r="M43">
-        <f t="shared" ca="1" si="9"/>
-        <v>17</v>
-      </c>
-      <c r="N43">
-        <f t="shared" ca="1" si="4"/>
-        <v>14</v>
-      </c>
-      <c r="O43">
-        <f t="shared" ca="1" si="5"/>
-        <v>34.599999999999909</v>
-      </c>
-      <c r="P43">
-        <f t="shared" ca="1" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="R43" s="25">
-        <v>-114</v>
-      </c>
-      <c r="S43" s="29">
-        <v>6</v>
-      </c>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B44" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C44" s="22">
-        <v>6</v>
-      </c>
-      <c r="D44" s="25">
-        <f>C44/10</f>
-        <v>0.6</v>
-      </c>
-      <c r="E44" s="22">
-        <v>0.02</v>
-      </c>
-      <c r="F44" s="22">
-        <v>0.2</v>
-      </c>
-      <c r="G44" s="26">
-        <f t="shared" ref="G44:G49" si="15">ROUND($C$4/(D44/E44*F44),0)</f>
-        <v>40</v>
-      </c>
-      <c r="H44" s="22">
-        <f t="shared" si="12"/>
-        <v>30</v>
       </c>
       <c r="I44" s="24"/>
       <c r="K44">
+        <f t="shared" ca="1" si="10"/>
+        <v>13.14</v>
+      </c>
+      <c r="L44">
+        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B44&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B44&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <v>19.399999999999977</v>
+      </c>
+      <c r="M44">
+        <f t="shared" ca="1" si="12"/>
+        <v>3.6000000000000227</v>
+      </c>
+      <c r="N44">
         <f t="shared" ca="1" si="7"/>
-        <v>2.87</v>
-      </c>
-      <c r="L44">
+        <v>19.100000000000023</v>
+      </c>
+      <c r="O44">
         <f t="shared" ca="1" si="8"/>
-        <v>2.8799999999999955</v>
-      </c>
-      <c r="M44">
+        <v>8.8999999999999773</v>
+      </c>
+      <c r="P44">
         <f t="shared" ca="1" si="9"/>
-        <v>2.1599999999999966</v>
-      </c>
-      <c r="N44">
-        <f t="shared" ca="1" si="4"/>
-        <v>2.8200000000000074</v>
-      </c>
-      <c r="O44">
-        <f t="shared" ca="1" si="5"/>
-        <v>2.1599999999999966</v>
-      </c>
-      <c r="P44">
-        <f t="shared" ca="1" si="6"/>
-        <v>4.3200000000000074</v>
-      </c>
-      <c r="R44" s="29">
-        <v>7</v>
-      </c>
-      <c r="S44" s="25">
-        <v>-262</v>
+        <v>14.700000000000045</v>
+      </c>
+      <c r="R44" s="25">
+        <v>-114</v>
+      </c>
+      <c r="S44" s="29">
+        <v>6</v>
       </c>
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B45" s="22" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="C45" s="22">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="D45" s="25">
         <f>C45/10</f>
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="E45" s="22">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
       <c r="F45" s="22">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G45" s="26">
+        <f t="shared" ref="G45:G50" si="18">ROUND($C$4/(D45/E45*F45),0)</f>
+        <v>42</v>
+      </c>
+      <c r="H45" s="22">
         <f t="shared" si="15"/>
-        <v>34</v>
-      </c>
-      <c r="H45" s="22">
-        <f t="shared" ref="H45:H47" si="16">ROUND(D45/E45,0)</f>
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I45" s="24"/>
       <c r="K45">
+        <f t="shared" ca="1" si="10"/>
+        <v>2.41</v>
+      </c>
+      <c r="L45">
+        <f t="shared" ca="1" si="11"/>
+        <v>2.8199999999999932</v>
+      </c>
+      <c r="M45">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.37999999999999545</v>
+      </c>
+      <c r="N45">
         <f t="shared" ca="1" si="7"/>
-        <v>17.559999999999999</v>
-      </c>
-      <c r="L45">
+        <v>4.3799999999999955</v>
+      </c>
+      <c r="O45">
         <f t="shared" ca="1" si="8"/>
+        <v>1.5999999999999943</v>
+      </c>
+      <c r="P45">
+        <f t="shared" ca="1" si="9"/>
+        <v>2.8799999999999955</v>
+      </c>
+      <c r="R45" s="29">
+        <v>7</v>
+      </c>
+      <c r="S45" s="25">
+        <v>-262</v>
+      </c>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B46" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C46" s="22">
+        <v>70</v>
+      </c>
+      <c r="D46" s="25">
+        <f>C46/10</f>
+        <v>7</v>
+      </c>
+      <c r="E46" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="F46" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="G46" s="26">
+        <f t="shared" si="18"/>
+        <v>36</v>
+      </c>
+      <c r="H46" s="22">
+        <f t="shared" ref="H46:H48" si="19">ROUND(D46/E46,0)</f>
+        <v>14</v>
+      </c>
+      <c r="I46" s="24"/>
+      <c r="K46">
+        <f t="shared" ca="1" si="10"/>
+        <v>15.76</v>
+      </c>
+      <c r="L46">
+        <f t="shared" ca="1" si="11"/>
+        <v>18.200000000000045</v>
+      </c>
+      <c r="M46">
+        <f t="shared" ca="1" si="12"/>
+        <v>6.2000000000000455</v>
+      </c>
+      <c r="N46">
+        <f t="shared" ca="1" si="7"/>
+        <v>22.399999999999864</v>
+      </c>
+      <c r="O46">
+        <f t="shared" ca="1" si="8"/>
+        <v>17.799999999999955</v>
+      </c>
+      <c r="P46">
+        <f t="shared" ca="1" si="9"/>
         <v>14.200000000000045</v>
       </c>
-      <c r="M45">
+      <c r="R46" s="1"/>
+      <c r="S46" s="25">
+        <v>-8</v>
+      </c>
+      <c r="T46" s="29">
+        <v>5</v>
+      </c>
+      <c r="U46" s="1"/>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B47" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" s="22">
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="D47" s="25">
+        <f>ROUND(C47/10,4)</f>
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G47" s="26">
+        <f t="shared" si="18"/>
+        <v>49</v>
+      </c>
+      <c r="H47" s="22">
+        <f t="shared" si="19"/>
+        <v>51</v>
+      </c>
+      <c r="I47" s="24"/>
+      <c r="J47" s="30">
+        <v>46133</v>
+      </c>
+      <c r="K47">
+        <f ca="1">ROUND(AVERAGE(L47:P47),4)</f>
+        <v>1.8800000000000001E-2</v>
+      </c>
+      <c r="L47">
+        <f t="shared" ca="1" si="11"/>
+        <v>1.3900000000000023E-2</v>
+      </c>
+      <c r="M47">
+        <f t="shared" ca="1" si="12"/>
+        <v>2.9000000000000137E-3</v>
+      </c>
+      <c r="N47">
+        <f t="shared" ca="1" si="7"/>
+        <v>3.1100000000000017E-2</v>
+      </c>
+      <c r="O47">
+        <f t="shared" ca="1" si="8"/>
+        <v>2.3799999999999932E-2</v>
+      </c>
+      <c r="P47">
         <f t="shared" ca="1" si="9"/>
-        <v>14.400000000000091</v>
-      </c>
-      <c r="N45">
-        <f t="shared" ca="1" si="4"/>
-        <v>26</v>
-      </c>
-      <c r="O45">
-        <f t="shared" ca="1" si="5"/>
-        <v>16.799999999999955</v>
-      </c>
-      <c r="P45">
-        <f t="shared" ca="1" si="6"/>
-        <v>16.400000000000091</v>
-      </c>
-      <c r="R45" s="1"/>
-      <c r="S45" s="25">
-        <v>-8</v>
-      </c>
-      <c r="T45" s="29">
-        <v>5</v>
-      </c>
-      <c r="U45" s="1"/>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B46" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" s="22">
-        <v>5.1400000000000001E-2</v>
-      </c>
-      <c r="D46" s="25">
-        <f>ROUND(C46/10,4)</f>
-        <v>5.1000000000000004E-3</v>
-      </c>
-      <c r="E46" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="F46" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="G46" s="26">
-        <f t="shared" si="15"/>
-        <v>47</v>
-      </c>
-      <c r="H46" s="22">
-        <f t="shared" si="16"/>
-        <v>51</v>
-      </c>
-      <c r="I46" s="24"/>
-      <c r="J46" s="30">
-        <v>46133</v>
-      </c>
-      <c r="K46">
-        <f ca="1">ROUND(AVERAGE(L46:P46),4)</f>
-        <v>7.5399999999999995E-2</v>
-      </c>
-      <c r="L46">
-        <f t="shared" ca="1" si="8"/>
         <v>2.2299999999999986E-2</v>
       </c>
-      <c r="M46">
-        <f t="shared" ca="1" si="9"/>
-        <v>2.4900000000000033E-2</v>
-      </c>
-      <c r="N46">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.22949999999999993</v>
-      </c>
-      <c r="O46">
-        <f t="shared" ca="1" si="5"/>
-        <v>4.3300000000000005E-2</v>
-      </c>
-      <c r="P46">
-        <f t="shared" ca="1" si="6"/>
-        <v>5.699999999999994E-2</v>
-      </c>
-      <c r="R46" s="1"/>
-      <c r="S46" s="22"/>
-      <c r="T46" s="22"/>
-      <c r="U46" s="1"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B47" s="1" t="s">
+      <c r="R47" s="1"/>
+      <c r="S47" s="22"/>
+      <c r="T47" s="22"/>
+      <c r="U47" s="1"/>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C48" s="1">
         <v>8.9</v>
-      </c>
-      <c r="D47" s="25">
-        <f>C47/10</f>
-        <v>0.89</v>
-      </c>
-      <c r="E47" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="F47" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="G47" s="26">
-        <f t="shared" si="15"/>
-        <v>270</v>
-      </c>
-      <c r="H47" s="22">
-        <f t="shared" si="16"/>
-        <v>18</v>
-      </c>
-      <c r="I47" s="23"/>
-      <c r="J47" s="30">
-        <v>46063</v>
-      </c>
-      <c r="K47">
-        <f t="shared" ca="1" si="7"/>
-        <v>6.16</v>
-      </c>
-      <c r="L47">
-        <f t="shared" ca="1" si="8"/>
-        <v>4.25</v>
-      </c>
-      <c r="M47">
-        <f t="shared" ca="1" si="9"/>
-        <v>3.5</v>
-      </c>
-      <c r="N47">
-        <f t="shared" ca="1" si="4"/>
-        <v>5.4499999999999886</v>
-      </c>
-      <c r="O47">
-        <f t="shared" ca="1" si="5"/>
-        <v>7.6499999999999773</v>
-      </c>
-      <c r="P47">
-        <f t="shared" ca="1" si="6"/>
-        <v>9.9500000000000455</v>
-      </c>
-      <c r="R47" s="1"/>
-      <c r="S47" s="29">
-        <v>24</v>
-      </c>
-      <c r="T47" s="1"/>
-      <c r="U47" s="1"/>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>77</v>
-      </c>
-      <c r="B48" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C48" s="22">
-        <v>2.71</v>
       </c>
       <c r="D48" s="25">
         <f>C48/10</f>
-        <v>0.27100000000000002</v>
-      </c>
-      <c r="E48" s="22">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="F48" s="22">
-        <v>5.0000000000000001E-3</v>
+        <v>0.89</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0.05</v>
       </c>
       <c r="G48" s="26">
-        <f t="shared" si="15"/>
-        <v>886</v>
+        <f t="shared" si="18"/>
+        <v>281</v>
       </c>
       <c r="H48" s="22">
-        <f>ROUND(D48/E48,0)</f>
-        <v>54</v>
-      </c>
-      <c r="I48" s="24"/>
+        <f t="shared" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="I48" s="23"/>
       <c r="J48" s="30">
-        <v>46069</v>
+        <v>46063</v>
       </c>
       <c r="K48">
+        <f t="shared" ca="1" si="10"/>
+        <v>6.07</v>
+      </c>
+      <c r="L48">
+        <f t="shared" ca="1" si="11"/>
+        <v>10.399999999999977</v>
+      </c>
+      <c r="M48">
+        <f t="shared" ca="1" si="12"/>
+        <v>1.6000000000000227</v>
+      </c>
+      <c r="N48">
         <f t="shared" ca="1" si="7"/>
-        <v>3.03</v>
-      </c>
-      <c r="L48">
+        <v>8.4999999999999716</v>
+      </c>
+      <c r="O48">
         <f t="shared" ca="1" si="8"/>
-        <v>3.125</v>
-      </c>
-      <c r="M48">
+        <v>5.5999999999999659</v>
+      </c>
+      <c r="P48">
         <f t="shared" ca="1" si="9"/>
-        <v>5.2649999999999864</v>
-      </c>
-      <c r="N48">
-        <f t="shared" ca="1" si="4"/>
-        <v>2.5349999999999966</v>
-      </c>
-      <c r="O48">
-        <f t="shared" ca="1" si="5"/>
-        <v>1.8349999999999937</v>
-      </c>
-      <c r="P48">
-        <f t="shared" ca="1" si="6"/>
-        <v>2.4100000000000108</v>
-      </c>
-      <c r="R48" s="29">
-        <v>19</v>
-      </c>
+        <v>4.25</v>
+      </c>
+      <c r="R48" s="1"/>
       <c r="S48" s="29">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
     </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B49" s="1" t="s">
-        <v>76</v>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>77</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>59</v>
       </c>
       <c r="C49" s="22">
-        <v>46.6</v>
+        <v>2.71</v>
       </c>
       <c r="D49" s="25">
         <f>C49/10</f>
-        <v>4.66</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="E49" s="22">
-        <v>0.5</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F49" s="22">
-        <v>0.5</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G49" s="26">
-        <f t="shared" si="15"/>
-        <v>52</v>
+        <f t="shared" si="18"/>
+        <v>923</v>
       </c>
       <c r="H49" s="22">
         <f>ROUND(D49/E49,0)</f>
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="I49" s="24"/>
       <c r="J49" s="30">
+        <v>46069</v>
+      </c>
+      <c r="K49">
+        <f t="shared" ca="1" si="10"/>
+        <v>1.78</v>
+      </c>
+      <c r="L49">
+        <f t="shared" ca="1" si="11"/>
+        <v>2.2800000000000011</v>
+      </c>
+      <c r="M49">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.40999999999999659</v>
+      </c>
+      <c r="N49">
+        <f t="shared" ca="1" si="7"/>
+        <v>1.5600000000000023</v>
+      </c>
+      <c r="O49">
+        <f t="shared" ca="1" si="8"/>
+        <v>1.5400000000000063</v>
+      </c>
+      <c r="P49">
+        <f t="shared" ca="1" si="9"/>
+        <v>3.125</v>
+      </c>
+      <c r="R49" s="29">
+        <v>19</v>
+      </c>
+      <c r="S49" s="29">
+        <v>122</v>
+      </c>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C50" s="22">
+        <v>46.6</v>
+      </c>
+      <c r="D50" s="25">
+        <f>C50/10</f>
+        <v>4.66</v>
+      </c>
+      <c r="E50" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="F50" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="G50" s="26">
+        <f t="shared" si="18"/>
+        <v>54</v>
+      </c>
+      <c r="H50" s="22">
+        <f>ROUND(D50/E50,0)</f>
+        <v>9</v>
+      </c>
+      <c r="I50" s="24"/>
+      <c r="J50" s="30">
         <v>46133</v>
       </c>
-      <c r="K49">
+      <c r="K50">
+        <f t="shared" ca="1" si="10"/>
+        <v>26</v>
+      </c>
+      <c r="L50">
+        <f t="shared" ca="1" si="11"/>
+        <v>40.5</v>
+      </c>
+      <c r="M50">
+        <f t="shared" ca="1" si="12"/>
+        <v>12.5</v>
+      </c>
+      <c r="N50">
         <f t="shared" ca="1" si="7"/>
-        <v>28.2</v>
-      </c>
-      <c r="L49">
+        <v>40</v>
+      </c>
+      <c r="O50">
         <f t="shared" ca="1" si="8"/>
         <v>18.5</v>
       </c>
-      <c r="M49">
+      <c r="P50">
         <f t="shared" ca="1" si="9"/>
-        <v>33.5</v>
-      </c>
-      <c r="N49">
-        <f t="shared" ca="1" si="4"/>
-        <v>19</v>
-      </c>
-      <c r="O49">
-        <f t="shared" ca="1" si="5"/>
-        <v>19.5</v>
-      </c>
-      <c r="P49">
-        <f t="shared" ca="1" si="6"/>
-        <v>50.5</v>
-      </c>
-      <c r="R49" s="1"/>
-      <c r="S49" s="1"/>
-      <c r="T49" s="1"/>
-      <c r="U49" s="1"/>
-    </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B50" s="1" t="s">
+        <v>18.5</v>
+      </c>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B51" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C51" s="1">
         <v>120.3</v>
       </c>
-      <c r="D50" s="25">
-        <f t="shared" ref="D50:D53" si="17">C50/10</f>
+      <c r="D51" s="25">
+        <f t="shared" ref="D51:D54" si="20">C51/10</f>
         <v>12.03</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E51" s="1">
         <v>0.5</v>
-      </c>
-      <c r="F50" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G50" s="26">
-        <f t="shared" ref="G50:G53" si="18">ROUND($C$4/(D50/E50*F50),0)</f>
-        <v>20</v>
-      </c>
-      <c r="H50" s="22">
-        <f t="shared" ref="H50:H53" si="19">ROUND(D50/E50,0)</f>
-        <v>24</v>
-      </c>
-      <c r="I50" s="23"/>
-      <c r="J50" s="30">
-        <v>46133</v>
-      </c>
-      <c r="K50">
-        <f t="shared" ca="1" si="7"/>
-        <v>80.8</v>
-      </c>
-      <c r="L50">
-        <f t="shared" ca="1" si="8"/>
-        <v>56</v>
-      </c>
-      <c r="M50">
-        <f t="shared" ca="1" si="9"/>
-        <v>89</v>
-      </c>
-      <c r="N50">
-        <f t="shared" ca="1" si="4"/>
-        <v>76.5</v>
-      </c>
-      <c r="O50">
-        <f t="shared" ca="1" si="5"/>
-        <v>87.5</v>
-      </c>
-      <c r="P50">
-        <f t="shared" ca="1" si="6"/>
-        <v>95</v>
-      </c>
-      <c r="R50" s="1">
-        <v>-97</v>
-      </c>
-      <c r="S50" s="25">
-        <v>-176</v>
-      </c>
-      <c r="T50" s="29">
-        <v>11</v>
-      </c>
-      <c r="U50" s="1"/>
-    </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B51" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" s="22">
-        <v>60</v>
-      </c>
-      <c r="D51" s="25">
-        <f t="shared" si="17"/>
-        <v>6</v>
-      </c>
-      <c r="E51" s="1">
-        <v>0.05</v>
       </c>
       <c r="F51" s="1">
         <v>0.5</v>
       </c>
       <c r="G51" s="26">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G51:G54" si="21">ROUND($C$4/(D51/E51*F51),0)</f>
+        <v>21</v>
+      </c>
+      <c r="H51" s="22">
+        <f t="shared" ref="H51:H54" si="22">ROUND(D51/E51,0)</f>
+        <v>24</v>
+      </c>
+      <c r="I51" s="23"/>
+      <c r="J51" s="30">
+        <v>46133</v>
+      </c>
+      <c r="K51">
+        <f t="shared" ca="1" si="10"/>
+        <v>90.4</v>
+      </c>
+      <c r="L51">
+        <f t="shared" ca="1" si="11"/>
+        <v>140.5</v>
+      </c>
+      <c r="M51">
+        <f t="shared" ca="1" si="12"/>
+        <v>24</v>
+      </c>
+      <c r="N51">
+        <f t="shared" ca="1" si="7"/>
+        <v>167</v>
+      </c>
+      <c r="O51">
+        <f t="shared" ca="1" si="8"/>
+        <v>64.5</v>
+      </c>
+      <c r="P51">
+        <f t="shared" ca="1" si="9"/>
+        <v>56</v>
+      </c>
+      <c r="R51" s="1">
+        <v>-97</v>
+      </c>
+      <c r="S51" s="25">
+        <v>-176</v>
+      </c>
+      <c r="T51" s="29">
+        <v>11</v>
+      </c>
+      <c r="U51" s="1"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B52" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" s="22">
+        <v>60</v>
+      </c>
+      <c r="D52" s="25">
+        <f t="shared" si="20"/>
+        <v>6</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G52" s="26">
+        <f t="shared" si="21"/>
         <v>4</v>
       </c>
-      <c r="H51" s="22">
-        <f t="shared" si="19"/>
+      <c r="H52" s="22">
+        <f t="shared" si="22"/>
         <v>120</v>
       </c>
-      <c r="I51" s="23"/>
-      <c r="R51" s="1"/>
-      <c r="S51" s="25">
+      <c r="I52" s="23"/>
+      <c r="R52" s="1"/>
+      <c r="S52" s="25">
         <v>-489</v>
       </c>
-      <c r="T51" s="29">
+      <c r="T52" s="29">
         <v>255</v>
       </c>
-      <c r="U51" s="1"/>
-    </row>
-    <row r="52" spans="2:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="27" t="s">
+      <c r="U52" s="1"/>
+    </row>
+    <row r="53" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C52" s="22">
+      <c r="C53" s="22">
         <v>0.1</v>
       </c>
-      <c r="D52" s="25">
-        <f t="shared" si="17"/>
+      <c r="D53" s="25">
+        <f t="shared" si="20"/>
         <v>0.01</v>
       </c>
-      <c r="E52" s="22">
+      <c r="E53" s="22">
         <v>1E-3</v>
-      </c>
-      <c r="F52" s="22">
-        <v>1</v>
-      </c>
-      <c r="G52" s="26">
-        <f t="shared" si="18"/>
-        <v>24</v>
-      </c>
-      <c r="H52" s="22">
-        <f t="shared" si="19"/>
-        <v>10</v>
-      </c>
-      <c r="I52" s="24"/>
-      <c r="R52" s="29">
-        <v>445</v>
-      </c>
-      <c r="S52" s="25">
-        <v>-21</v>
-      </c>
-      <c r="T52" s="29">
-        <v>125</v>
-      </c>
-      <c r="U52" s="1"/>
-    </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B53" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C53" s="22">
-        <v>550</v>
-      </c>
-      <c r="D53" s="25">
-        <f t="shared" si="17"/>
-        <v>55</v>
-      </c>
-      <c r="E53" s="22">
-        <v>1</v>
       </c>
       <c r="F53" s="22">
         <v>1</v>
       </c>
       <c r="G53" s="26">
-        <f t="shared" si="18"/>
-        <v>4</v>
+        <f t="shared" si="21"/>
+        <v>25</v>
       </c>
       <c r="H53" s="22">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
+        <v>10</v>
+      </c>
+      <c r="I53" s="24"/>
+      <c r="R53" s="29">
+        <v>445</v>
+      </c>
+      <c r="S53" s="25">
+        <v>-21</v>
+      </c>
+      <c r="T53" s="29">
+        <v>125</v>
+      </c>
+      <c r="U53" s="1"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B54" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C54" s="22">
+        <v>550</v>
+      </c>
+      <c r="D54" s="25">
+        <f t="shared" si="20"/>
         <v>55</v>
       </c>
-      <c r="I53" s="24"/>
-      <c r="M53" t="e">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/futures/markets/forts/securities/"&amp;B53&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/futures/markets/forts/securities/"&amp;B53&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+      <c r="E54" s="22">
+        <v>1</v>
+      </c>
+      <c r="F54" s="22">
+        <v>1</v>
+      </c>
+      <c r="G54" s="26">
+        <f t="shared" si="21"/>
+        <v>5</v>
+      </c>
+      <c r="H54" s="22">
+        <f t="shared" si="22"/>
+        <v>55</v>
+      </c>
+      <c r="I54" s="24"/>
+      <c r="M54" t="e">
+        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/futures/markets/forts/securities/"&amp;B54&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/futures/markets/forts/securities/"&amp;B54&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R53" s="29">
+      <c r="R54" s="29">
         <v>459</v>
       </c>
-      <c r="S53" s="29">
+      <c r="S54" s="29">
         <v>596</v>
       </c>
-      <c r="T53" s="25">
+      <c r="T54" s="25">
         <v>-455</v>
       </c>
-      <c r="U53" s="1"/>
+      <c r="U54" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/calc.xlsx
+++ b/calc.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="99">
   <si>
     <t>Депозит</t>
   </si>
@@ -284,9 +284,6 @@
     <t>BSPBP</t>
   </si>
   <si>
-    <t>Риск 0.6%</t>
-  </si>
-  <si>
     <t>Утренние пробросы</t>
   </si>
   <si>
@@ -321,6 +318,12 @@
   </si>
   <si>
     <t>ASTR</t>
+  </si>
+  <si>
+    <t>Риск 1.0%</t>
+  </si>
+  <si>
+    <t>DOMRF</t>
   </si>
 </sst>
 </file>
@@ -1804,7 +1807,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:U54"/>
+  <dimension ref="A3:U55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="15.28515625" customWidth="1"/>
@@ -1826,7 +1829,7 @@
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C4" s="31">
         <f>C3*1/100</f>
@@ -1837,23 +1840,23 @@
     <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="L6" s="5" t="str">
         <f ca="1">TEXT(L7,"ддд")</f>
-        <v>Пт</v>
+        <v>Чт</v>
       </c>
       <c r="M6" s="5" t="str">
         <f ca="1">TEXT(M7,"ддд")</f>
-        <v>Сб</v>
+        <v>Пт</v>
       </c>
       <c r="N6" s="5" t="str">
         <f t="shared" ref="N6:P6" ca="1" si="0">TEXT(N7,"ддд")</f>
-        <v>Вт</v>
+        <v>Пн</v>
       </c>
       <c r="O6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Чт</v>
+        <v>Ср</v>
       </c>
       <c r="P6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Ср</v>
+        <v>Вт</v>
       </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.25">
@@ -1887,23 +1890,23 @@
       </c>
       <c r="L7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-5, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-24</v>
+        <v>2026-05-28</v>
       </c>
       <c r="M7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-4, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="N7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-1, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-28</v>
+        <v>2026-06-01</v>
       </c>
       <c r="O7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-6, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="P7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-7, "ГГГГ-ММ-ДД")</f>
-        <v>2026-04-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="R7" s="28">
         <v>45566</v>
@@ -1926,7 +1929,7 @@
         <v>0.35</v>
       </c>
       <c r="D8" s="25">
-        <f t="shared" ref="D8:D29" si="1">C8/10</f>
+        <f t="shared" ref="D8:D30" si="1">C8/10</f>
         <v>3.4999999999999996E-2</v>
       </c>
       <c r="E8" s="22">
@@ -1936,11 +1939,11 @@
         <v>0.1</v>
       </c>
       <c r="G8" s="26">
-        <f t="shared" ref="G8:G29" si="2">ROUND($C$4/(D8/E8*F8),0)</f>
+        <f t="shared" ref="G8:G30" si="2">ROUND($C$4/(D8/E8*F8),0)</f>
         <v>71</v>
       </c>
       <c r="H8" s="22">
-        <f t="shared" ref="H8:H20" si="3">ROUND(D8/E8,0)</f>
+        <f t="shared" ref="H8:H21" si="3">ROUND(D8/E8,0)</f>
         <v>35</v>
       </c>
       <c r="I8" s="23"/>
@@ -1949,27 +1952,27 @@
       </c>
       <c r="K8">
         <f t="shared" ref="K8:K13" ca="1" si="4">ROUND(AVERAGE(L8:P8),2)</f>
-        <v>10350.68</v>
+        <v>5895.08</v>
       </c>
       <c r="L8">
         <f t="shared" ref="L8:L13" ca="1" si="5">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.54600000000000115</v>
+        <v>0.90200000000000102</v>
       </c>
       <c r="M8">
         <f t="shared" ref="M8:M13" ca="1" si="6">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>3.5000000000000142E-2</v>
+        <v>-16729.837</v>
       </c>
       <c r="N8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>34262.447</v>
+        <v>46203.107000000004</v>
       </c>
       <c r="O8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.29299999999999926</v>
+        <v>0.46200000000000152</v>
       </c>
       <c r="P8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>17490.069</v>
+        <v>0.77500000000000036</v>
       </c>
       <c r="R8" s="29">
         <v>54</v>
@@ -2013,27 +2016,27 @@
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="4"/>
-        <v>0.84</v>
+        <v>1.51</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="5"/>
-        <v>1.5400000000000063</v>
+        <v>1.0399999999999991</v>
       </c>
       <c r="M9">
         <f t="shared" ca="1" si="6"/>
-        <v>0.21999999999999886</v>
+        <v>2.5200000000000031</v>
       </c>
       <c r="N9">
-        <f t="shared" ref="N9:N51" ca="1" si="7">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.78000000000000114</v>
+        <f t="shared" ref="N9:N52" ca="1" si="7">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <v>1.5300000000000011</v>
       </c>
       <c r="O9">
-        <f t="shared" ref="O9:O51" ca="1" si="8">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.009999999999998</v>
+        <f t="shared" ref="O9:O52" ca="1" si="8">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <v>0.94000000000000483</v>
       </c>
       <c r="P9">
-        <f t="shared" ref="P9:P51" ca="1" si="9">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.66000000000000369</v>
+        <f t="shared" ref="P9:P52" ca="1" si="9">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <v>1.5300000000000011</v>
       </c>
       <c r="R9" s="25">
         <v>-30</v>
@@ -2074,27 +2077,27 @@
       <c r="I10" s="24"/>
       <c r="K10">
         <f t="shared" ca="1" si="4"/>
-        <v>-18467.87</v>
+        <v>9180.76</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="5"/>
-        <v>1.5300000000000011</v>
+        <v>1.1999999999999993</v>
       </c>
       <c r="M10">
         <f t="shared" ca="1" si="6"/>
-        <v>-46201.98</v>
+        <v>1.4200000000000017</v>
       </c>
       <c r="N10">
         <f t="shared" ca="1" si="7"/>
-        <v>-46140.38</v>
+        <v>46053.59</v>
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="8"/>
-        <v>0.55000000000000071</v>
+        <v>-153</v>
       </c>
       <c r="P10">
         <f t="shared" ca="1" si="9"/>
-        <v>0.92999999999999972</v>
+        <v>0.58000000000000185</v>
       </c>
       <c r="R10" s="29">
         <v>39</v>
@@ -2109,7 +2112,7 @@
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" s="22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C11" s="22">
         <v>7.9</v>
@@ -2138,27 +2141,27 @@
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="4"/>
-        <v>5.95</v>
+        <v>15.63</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="5"/>
-        <v>8.5999999999999659</v>
+        <v>2.25</v>
       </c>
       <c r="M11">
         <f t="shared" ca="1" si="6"/>
-        <v>1.3999999999999773</v>
+        <v>12.550000000000011</v>
       </c>
       <c r="N11">
         <f t="shared" ca="1" si="7"/>
-        <v>12.100000000000023</v>
+        <v>51.849999999999994</v>
       </c>
       <c r="O11">
         <f t="shared" ca="1" si="8"/>
-        <v>4.25</v>
+        <v>5.75</v>
       </c>
       <c r="P11">
         <f t="shared" ca="1" si="9"/>
-        <v>3.3999999999999773</v>
+        <v>5.75</v>
       </c>
       <c r="R11" s="29"/>
       <c r="S11" s="29"/>
@@ -2196,27 +2199,27 @@
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="4"/>
-        <v>2.6</v>
+        <v>4.29</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="5"/>
-        <v>3.5</v>
+        <v>6.589999999999975</v>
       </c>
       <c r="M12">
         <f t="shared" ca="1" si="6"/>
-        <v>0.92000000000001592</v>
+        <v>3</v>
       </c>
       <c r="N12">
         <f t="shared" ca="1" si="7"/>
-        <v>3.4900000000000091</v>
+        <v>2.3899999999999864</v>
       </c>
       <c r="O12">
         <f t="shared" ca="1" si="8"/>
-        <v>2.8799999999999955</v>
+        <v>3.8100000000000023</v>
       </c>
       <c r="P12">
         <f t="shared" ca="1" si="9"/>
-        <v>2.2300000000000182</v>
+        <v>5.6700000000000159</v>
       </c>
       <c r="R12" s="29"/>
       <c r="S12" s="29"/>
@@ -2254,11 +2257,11 @@
       </c>
       <c r="K13" s="24">
         <f t="shared" ca="1" si="4"/>
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="L13" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>1.2000000000000028</v>
+        <v>1</v>
       </c>
       <c r="M13" s="24">
         <f t="shared" ca="1" si="6"/>
@@ -2266,15 +2269,15 @@
       </c>
       <c r="N13" s="24">
         <f t="shared" ca="1" si="7"/>
-        <v>2.5500000000000043</v>
+        <v>2.7999999999999972</v>
       </c>
       <c r="O13" s="24">
         <f t="shared" ca="1" si="8"/>
-        <v>1.0499999999999972</v>
+        <v>0.75</v>
       </c>
       <c r="P13" s="24">
         <f t="shared" ca="1" si="9"/>
-        <v>1</v>
+        <v>2.1999999999999957</v>
       </c>
       <c r="R13" s="29"/>
       <c r="S13" s="29"/>
@@ -2286,11 +2289,11 @@
         <v>43</v>
       </c>
       <c r="C14" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="1">
         <v>0.2</v>
@@ -2300,39 +2303,39 @@
       </c>
       <c r="G14" s="26">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="H14" s="22">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I14" s="23"/>
       <c r="J14" s="30">
         <v>46135</v>
       </c>
       <c r="K14">
-        <f t="shared" ref="K14:K51" ca="1" si="10">ROUND(AVERAGE(L14:P14),2)</f>
-        <v>20.84</v>
+        <f t="shared" ref="K14:K52" ca="1" si="10">ROUND(AVERAGE(L14:P14),2)</f>
+        <v>18.079999999999998</v>
       </c>
       <c r="L14">
-        <f t="shared" ref="L14:L51" ca="1" si="11">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>32.599999999999909</v>
+        <f t="shared" ref="L14:L52" ca="1" si="11">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <v>24</v>
       </c>
       <c r="M14">
-        <f t="shared" ref="M14:M51" ca="1" si="12">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>3</v>
+        <f t="shared" ref="M14:M52" ca="1" si="12">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <v>12.399999999999977</v>
       </c>
       <c r="N14">
         <f t="shared" ca="1" si="7"/>
-        <v>21.600000000000023</v>
+        <v>14</v>
       </c>
       <c r="O14">
         <f t="shared" ca="1" si="8"/>
-        <v>16.600000000000023</v>
+        <v>13.200000000000045</v>
       </c>
       <c r="P14">
         <f t="shared" ca="1" si="9"/>
-        <v>30.399999999999977</v>
+        <v>26.799999999999955</v>
       </c>
       <c r="R14" s="29">
         <v>80</v>
@@ -2346,2356 +2349,2414 @@
       <c r="U14" s="1"/>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="22">
-        <v>3.22</v>
+      <c r="B15" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="1">
+        <v>50</v>
       </c>
       <c r="D15" s="25">
-        <f t="shared" ref="D15:D21" si="13">C15/10</f>
-        <v>0.32200000000000001</v>
-      </c>
-      <c r="E15" s="22">
-        <v>0.01</v>
-      </c>
-      <c r="F15" s="22">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="E15" s="1">
         <v>0.1</v>
       </c>
+      <c r="F15" s="1">
+        <v>0.1</v>
+      </c>
       <c r="G15" s="26">
-        <f t="shared" ref="G15:G21" si="14">ROUND($C$4/(D15/E15*F15),0)</f>
-        <v>78</v>
+        <f t="shared" si="2"/>
+        <v>50</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-      <c r="I15" s="24"/>
+        <v>50</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="30">
+        <v>46175</v>
+      </c>
       <c r="K15">
         <f t="shared" ca="1" si="10"/>
-        <v>1.62</v>
+        <v>47.64</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="11"/>
-        <v>2.3900000000000006</v>
+        <v>57.800000000000182</v>
       </c>
       <c r="M15">
         <f t="shared" ca="1" si="12"/>
-        <v>0.59000000000000341</v>
+        <v>48.599999999999909</v>
       </c>
       <c r="N15">
         <f t="shared" ca="1" si="7"/>
-        <v>2.6400000000000006</v>
+        <v>21.599999999999909</v>
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="8"/>
-        <v>1.1099999999999994</v>
+        <v>47.300000000000182</v>
       </c>
       <c r="P15">
         <f t="shared" ca="1" si="9"/>
-        <v>1.3900000000000006</v>
-      </c>
-      <c r="R15" s="29">
-        <v>27</v>
-      </c>
-      <c r="S15" s="25">
-        <v>-172</v>
-      </c>
-      <c r="T15" s="1"/>
+        <v>62.900000000000091</v>
+      </c>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
       <c r="U15" s="1"/>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="22">
+        <v>3.22</v>
+      </c>
+      <c r="D16" s="25">
+        <f t="shared" ref="D16:D22" si="13">C16/10</f>
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="E16" s="22">
+        <v>0.01</v>
+      </c>
+      <c r="F16" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="26">
+        <f t="shared" ref="G16:G22" si="14">ROUND($C$4/(D16/E16*F16),0)</f>
+        <v>78</v>
+      </c>
+      <c r="H16" s="22">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="I16" s="24"/>
+      <c r="K16">
+        <f t="shared" ca="1" si="10"/>
+        <v>2.37</v>
+      </c>
+      <c r="L16">
+        <f t="shared" ca="1" si="11"/>
+        <v>1.8199999999999932</v>
+      </c>
+      <c r="M16">
+        <f t="shared" ca="1" si="12"/>
+        <v>2.7599999999999909</v>
+      </c>
+      <c r="N16">
+        <f t="shared" ca="1" si="7"/>
+        <v>2.4699999999999989</v>
+      </c>
+      <c r="O16">
+        <f t="shared" ca="1" si="8"/>
+        <v>2.4300000000000068</v>
+      </c>
+      <c r="P16">
+        <f t="shared" ca="1" si="9"/>
+        <v>2.3599999999999994</v>
+      </c>
+      <c r="R16" s="29">
+        <v>27</v>
+      </c>
+      <c r="S16" s="25">
+        <v>-172</v>
+      </c>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B17" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C17" s="22">
         <v>5.4</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D17" s="25">
         <f t="shared" si="13"/>
         <v>0.54</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E17" s="22">
         <v>0.05</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F17" s="22">
         <v>0.05</v>
       </c>
-      <c r="G16" s="26">
+      <c r="G17" s="26">
         <f t="shared" si="14"/>
         <v>463</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H17" s="22">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="I16" s="23"/>
-      <c r="K16">
+      <c r="I17" s="23"/>
+      <c r="K17">
         <f t="shared" ca="1" si="10"/>
-        <v>8.64</v>
-      </c>
-      <c r="L16">
+        <v>2.19</v>
+      </c>
+      <c r="L17">
         <f t="shared" ca="1" si="11"/>
-        <v>10.599999999999994</v>
-      </c>
-      <c r="M16">
+        <v>2.3499999999999943</v>
+      </c>
+      <c r="M17">
         <f t="shared" ca="1" si="12"/>
-        <v>2.2000000000000028</v>
-      </c>
-      <c r="N16">
+        <v>2.6500000000000057</v>
+      </c>
+      <c r="N17">
         <f t="shared" ca="1" si="7"/>
-        <v>7.2000000000000028</v>
-      </c>
-      <c r="O16">
+        <v>2.1000000000000085</v>
+      </c>
+      <c r="O17">
         <f t="shared" ca="1" si="8"/>
-        <v>8.4000000000000057</v>
-      </c>
-      <c r="P16">
+        <v>1.5999999999999943</v>
+      </c>
+      <c r="P17">
         <f t="shared" ca="1" si="9"/>
-        <v>14.799999999999997</v>
-      </c>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B17" s="22" t="s">
+        <v>2.25</v>
+      </c>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B18" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C18" s="22">
         <v>1.8</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D18" s="25">
         <f t="shared" si="13"/>
         <v>0.18</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E18" s="22">
         <v>0.01</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F18" s="22">
         <v>0.1</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G18" s="26">
         <f t="shared" si="14"/>
         <v>139</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H18" s="22">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="I17" s="24"/>
-      <c r="J17" s="30">
+      <c r="I18" s="24"/>
+      <c r="J18" s="30">
         <v>46133</v>
       </c>
-      <c r="K17">
+      <c r="K18">
         <f t="shared" ca="1" si="10"/>
-        <v>1.87</v>
-      </c>
-      <c r="L17">
+        <v>1.84</v>
+      </c>
+      <c r="L18">
         <f t="shared" ca="1" si="11"/>
-        <v>2.5499999999999972</v>
-      </c>
-      <c r="M17">
+        <v>1.6299999999999955</v>
+      </c>
+      <c r="M18">
         <f t="shared" ca="1" si="12"/>
-        <v>0.42999999999999261</v>
-      </c>
-      <c r="N17">
+        <v>1.8999999999999915</v>
+      </c>
+      <c r="N18">
         <f t="shared" ca="1" si="7"/>
-        <v>4.0600000000000023</v>
-      </c>
-      <c r="O17">
+        <v>1.8400000000000034</v>
+      </c>
+      <c r="O18">
         <f t="shared" ca="1" si="8"/>
-        <v>1.0799999999999983</v>
-      </c>
-      <c r="P17">
+        <v>1.9500000000000028</v>
+      </c>
+      <c r="P18">
         <f t="shared" ca="1" si="9"/>
-        <v>1.2099999999999937</v>
-      </c>
-      <c r="R17" s="25">
+        <v>1.9000000000000057</v>
+      </c>
+      <c r="R18" s="25">
         <v>-2</v>
       </c>
-      <c r="S17" s="25">
+      <c r="S18" s="25">
         <v>-117</v>
       </c>
-      <c r="T17" s="29">
+      <c r="T18" s="29">
         <v>88</v>
       </c>
-      <c r="U17" s="1"/>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B18" s="22" t="s">
+      <c r="U18" s="1"/>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B19" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C19" s="22">
         <v>1.8600000000000001E-3</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D19" s="25">
         <f t="shared" si="13"/>
         <v>1.8600000000000002E-4</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E19" s="22">
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F19" s="22">
         <v>0.2</v>
       </c>
-      <c r="G18" s="26">
+      <c r="G19" s="26">
         <f t="shared" si="14"/>
         <v>134</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H19" s="22">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="I18" s="24"/>
-      <c r="J18" s="30">
+      <c r="I19" s="24"/>
+      <c r="J19" s="30">
         <v>46062</v>
       </c>
-      <c r="K18">
-        <f ca="1">ROUND(AVERAGE(L18:P18),5)</f>
-        <v>1.9E-3</v>
-      </c>
-      <c r="L18">
+      <c r="K19">
+        <f ca="1">ROUND(AVERAGE(L19:P19),5)</f>
+        <v>3.0400000000000002E-3</v>
+      </c>
+      <c r="L19">
         <f t="shared" ca="1" si="11"/>
-        <v>2.1199999999999969E-3</v>
-      </c>
-      <c r="M18">
+        <v>1.7800000000000038E-3</v>
+      </c>
+      <c r="M19">
         <f t="shared" ca="1" si="12"/>
-        <v>4.200000000000037E-4</v>
-      </c>
-      <c r="N18">
+        <v>1.8200000000000022E-3</v>
+      </c>
+      <c r="N19">
         <f t="shared" ca="1" si="7"/>
-        <v>2.9600000000000043E-3</v>
-      </c>
-      <c r="O18">
+        <v>2.2999999999999965E-3</v>
+      </c>
+      <c r="O19">
         <f t="shared" ca="1" si="8"/>
-        <v>2.0000000000000018E-3</v>
-      </c>
-      <c r="P18">
+        <v>6.2199999999999964E-3</v>
+      </c>
+      <c r="P19">
         <f t="shared" ca="1" si="9"/>
-        <v>2.0000000000000018E-3</v>
-      </c>
-      <c r="R18" s="25"/>
-      <c r="S18" s="25"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="1"/>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="22" t="s">
+        <v>3.0999999999999986E-3</v>
+      </c>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="1"/>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B20" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C20" s="22">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D20" s="25">
         <f t="shared" si="13"/>
         <v>0.44000000000000006</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E20" s="22">
         <v>0.02</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F20" s="22">
         <v>0.2</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G20" s="26">
         <f t="shared" si="14"/>
         <v>57</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H20" s="22">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="I19" s="24"/>
-      <c r="J19" s="30">
+      <c r="I20" s="24"/>
+      <c r="J20" s="30">
         <v>46133</v>
       </c>
-      <c r="K19">
+      <c r="K20">
         <f t="shared" ca="1" si="10"/>
-        <v>2.79</v>
-      </c>
-      <c r="L19">
+        <v>3.22</v>
+      </c>
+      <c r="L20">
         <f t="shared" ca="1" si="11"/>
-        <v>3.3799999999999955</v>
-      </c>
-      <c r="M19">
+        <v>2.8200000000000074</v>
+      </c>
+      <c r="M20">
         <f t="shared" ca="1" si="12"/>
-        <v>1.2400000000000091</v>
-      </c>
-      <c r="N19">
+        <v>3.3800000000000097</v>
+      </c>
+      <c r="N20">
         <f t="shared" ca="1" si="7"/>
-        <v>3.2400000000000091</v>
-      </c>
-      <c r="O19">
+        <v>2.6400000000000006</v>
+      </c>
+      <c r="O20">
         <f t="shared" ca="1" si="8"/>
-        <v>2.3600000000000136</v>
-      </c>
-      <c r="P19">
+        <v>2.8799999999999955</v>
+      </c>
+      <c r="P20">
         <f t="shared" ca="1" si="9"/>
-        <v>3.7199999999999989</v>
-      </c>
-      <c r="R19" s="25">
+        <v>4.4000000000000057</v>
+      </c>
+      <c r="R20" s="25">
         <v>-211</v>
       </c>
-      <c r="S19" s="25">
+      <c r="S20" s="25">
         <v>-701</v>
       </c>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B20" s="22" t="s">
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B21" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C21" s="22">
         <v>7.85E-2</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D21" s="25">
         <f t="shared" si="13"/>
         <v>7.8499999999999993E-3</v>
       </c>
-      <c r="E20" s="22">
+      <c r="E21" s="22">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F21" s="22">
         <v>0.05</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G21" s="26">
         <f t="shared" si="14"/>
         <v>318</v>
       </c>
-      <c r="H20" s="22">
+      <c r="H21" s="22">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="I20" s="24"/>
-      <c r="K20">
+      <c r="I21" s="24"/>
+      <c r="K21">
         <f t="shared" ca="1" si="10"/>
-        <v>127931.33</v>
-      </c>
-      <c r="L20">
+        <v>-15790.33</v>
+      </c>
+      <c r="L21">
         <f t="shared" ca="1" si="11"/>
-        <v>227546</v>
-      </c>
-      <c r="M20">
+        <v>3.6000000000000032E-2</v>
+      </c>
+      <c r="M21">
         <f t="shared" ca="1" si="12"/>
-        <v>199115.76699999999</v>
-      </c>
-      <c r="N20">
+        <v>-42426.815499999997</v>
+      </c>
+      <c r="N21">
         <f t="shared" ca="1" si="7"/>
-        <v>44982.854500000001</v>
-      </c>
-      <c r="O20">
+        <v>5.8499999999999996E-2</v>
+      </c>
+      <c r="O21">
         <f t="shared" ca="1" si="8"/>
-        <v>168012</v>
-      </c>
-      <c r="P20">
+        <v>-36525</v>
+      </c>
+      <c r="P21">
         <f t="shared" ca="1" si="9"/>
-        <v>3.1000000000000139E-2</v>
-      </c>
-      <c r="R20" s="1"/>
-      <c r="S20" s="25">
+        <v>6.4000000000000057E-2</v>
+      </c>
+      <c r="R21" s="1"/>
+      <c r="S21" s="25">
         <v>-488</v>
       </c>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-    </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B21" s="22" t="s">
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B22" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C22" s="22">
         <v>86.3</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D22" s="25">
         <f t="shared" si="13"/>
         <v>8.629999999999999</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E22" s="22">
         <v>0.5</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F22" s="22">
         <v>0.5</v>
       </c>
-      <c r="G21" s="26">
+      <c r="G22" s="26">
         <f t="shared" si="14"/>
         <v>29</v>
       </c>
-      <c r="H21" s="22">
-        <f t="shared" ref="H21:H45" si="15">ROUND(D21/E21,0)</f>
+      <c r="H22" s="22">
+        <f t="shared" ref="H22:H46" si="15">ROUND(D22/E22,0)</f>
         <v>17</v>
       </c>
-      <c r="I21" s="24"/>
-      <c r="J21" s="30">
+      <c r="I22" s="24"/>
+      <c r="J22" s="30">
         <v>46133</v>
       </c>
-      <c r="K21">
+      <c r="K22">
         <f t="shared" ca="1" si="10"/>
-        <v>67.400000000000006</v>
-      </c>
-      <c r="L21">
+        <v>102.4</v>
+      </c>
+      <c r="L22">
         <f t="shared" ca="1" si="11"/>
-        <v>118.5</v>
-      </c>
-      <c r="M21">
+        <v>104.5</v>
+      </c>
+      <c r="M22">
         <f t="shared" ca="1" si="12"/>
-        <v>27.5</v>
-      </c>
-      <c r="N21">
+        <v>132</v>
+      </c>
+      <c r="N22">
         <f t="shared" ca="1" si="7"/>
-        <v>83</v>
-      </c>
-      <c r="O21">
+        <v>104.5</v>
+      </c>
+      <c r="O22">
         <f t="shared" ca="1" si="8"/>
-        <v>67.5</v>
-      </c>
-      <c r="P21">
+        <v>72</v>
+      </c>
+      <c r="P22">
         <f t="shared" ca="1" si="9"/>
-        <v>40.5</v>
-      </c>
-      <c r="R21" s="25">
+        <v>99</v>
+      </c>
+      <c r="R22" s="25">
         <v>-741</v>
       </c>
-      <c r="S21" s="25">
+      <c r="S22" s="25">
         <v>-475</v>
       </c>
-      <c r="T21" s="29">
+      <c r="T22" s="29">
         <v>34</v>
       </c>
-      <c r="U21" s="1"/>
-    </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
+      <c r="U22" s="1"/>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>1.05</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D23" s="25">
         <f t="shared" si="1"/>
         <v>0.10500000000000001</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E23" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F23" s="1">
         <v>0.05</v>
       </c>
-      <c r="G22" s="26">
+      <c r="G23" s="26">
         <f t="shared" si="2"/>
         <v>238</v>
       </c>
-      <c r="H22" s="22">
+      <c r="H23" s="22">
         <f t="shared" si="15"/>
         <v>21</v>
       </c>
-      <c r="I22" s="23"/>
-      <c r="J22" s="30">
+      <c r="I23" s="23"/>
+      <c r="J23" s="30">
         <v>46133</v>
       </c>
-      <c r="K22">
+      <c r="K23">
         <f t="shared" ca="1" si="10"/>
-        <v>0.84</v>
-      </c>
-      <c r="L22">
+        <v>0.95</v>
+      </c>
+      <c r="L23">
         <f t="shared" ca="1" si="11"/>
-        <v>1.4500000000000028</v>
-      </c>
-      <c r="M22">
+        <v>1.0599999999999987</v>
+      </c>
+      <c r="M23">
         <f t="shared" ca="1" si="12"/>
-        <v>0.28000000000000114</v>
-      </c>
-      <c r="N22">
+        <v>0.61000000000000298</v>
+      </c>
+      <c r="N23">
         <f t="shared" ca="1" si="7"/>
-        <v>0.72499999999999787</v>
-      </c>
-      <c r="O22">
+        <v>0.78500000000000014</v>
+      </c>
+      <c r="O23">
         <f t="shared" ca="1" si="8"/>
-        <v>0.74500000000000099</v>
-      </c>
-      <c r="P22">
+        <v>0.7099999999999973</v>
+      </c>
+      <c r="P23">
         <f t="shared" ca="1" si="9"/>
-        <v>0.98499999999999943</v>
-      </c>
-      <c r="R22" s="25">
+        <v>1.5899999999999999</v>
+      </c>
+      <c r="R23" s="25">
         <v>-107</v>
       </c>
-      <c r="S22" s="25">
+      <c r="S23" s="25">
         <v>-169</v>
       </c>
-      <c r="T22" s="29">
+      <c r="T23" s="29">
         <v>24</v>
       </c>
-      <c r="U22" s="1"/>
-    </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
+      <c r="U23" s="1"/>
+    </row>
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C24" s="1">
         <v>150</v>
       </c>
-      <c r="D23" s="25">
+      <c r="D24" s="25">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E24" s="1">
         <v>0.5</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F24" s="1">
         <v>0.5</v>
       </c>
-      <c r="G23" s="26">
+      <c r="G24" s="26">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="H23" s="22">
+      <c r="H24" s="22">
         <f t="shared" si="15"/>
         <v>30</v>
       </c>
-      <c r="I23" s="23"/>
-      <c r="J23" s="30"/>
-      <c r="K23">
-        <f t="shared" ca="1" si="10"/>
-        <v>67</v>
-      </c>
-      <c r="L23">
-        <f t="shared" ca="1" si="11"/>
-        <v>74</v>
-      </c>
-      <c r="M23">
-        <f t="shared" ca="1" si="12"/>
-        <v>15</v>
-      </c>
-      <c r="N23">
-        <f t="shared" ca="1" si="7"/>
-        <v>157</v>
-      </c>
-      <c r="O23">
-        <f t="shared" ca="1" si="8"/>
-        <v>50.5</v>
-      </c>
-      <c r="P23">
-        <f t="shared" ca="1" si="9"/>
-        <v>38.5</v>
-      </c>
-      <c r="R23" s="29">
-        <v>45</v>
-      </c>
-      <c r="S23" s="29">
-        <v>10</v>
-      </c>
-      <c r="T23" s="29">
-        <v>44</v>
-      </c>
-      <c r="U23" s="1"/>
-    </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B24" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="22">
-        <v>5.7</v>
-      </c>
-      <c r="D24" s="25">
-        <f>C24/10</f>
-        <v>0.57000000000000006</v>
-      </c>
-      <c r="E24" s="22">
-        <v>0.01</v>
-      </c>
-      <c r="F24" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="G24" s="26">
-        <f>ROUND($C$4/(D24/E24*F24),0)</f>
-        <v>44</v>
-      </c>
-      <c r="H24" s="22">
-        <f t="shared" si="15"/>
-        <v>57</v>
-      </c>
-      <c r="I24" s="24"/>
+      <c r="I24" s="23"/>
       <c r="J24" s="30"/>
       <c r="K24">
         <f t="shared" ca="1" si="10"/>
-        <v>3.02</v>
+        <v>68.5</v>
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="11"/>
-        <v>4.9399999999999977</v>
+        <v>82.5</v>
       </c>
       <c r="M24">
         <f t="shared" ca="1" si="12"/>
-        <v>0.69999999999998863</v>
+        <v>52</v>
       </c>
       <c r="N24">
         <f t="shared" ca="1" si="7"/>
-        <v>3.7999999999999829</v>
+        <v>46.5</v>
       </c>
       <c r="O24">
         <f t="shared" ca="1" si="8"/>
-        <v>2.8499999999999943</v>
+        <v>68.5</v>
       </c>
       <c r="P24">
         <f t="shared" ca="1" si="9"/>
-        <v>2.8000000000000114</v>
-      </c>
-      <c r="R24" s="25">
-        <v>-146</v>
-      </c>
-      <c r="S24" s="25">
-        <v>-28</v>
+        <v>93</v>
+      </c>
+      <c r="R24" s="29">
+        <v>45</v>
+      </c>
+      <c r="S24" s="29">
+        <v>10</v>
       </c>
       <c r="T24" s="29">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="U24" s="1"/>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="22" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C25" s="22">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="D25" s="25">
-        <f t="shared" si="1"/>
-        <v>0.65</v>
+        <f>C25/10</f>
+        <v>0.57000000000000006</v>
       </c>
       <c r="E25" s="22">
         <v>0.01</v>
       </c>
       <c r="F25" s="22">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="G25" s="26">
-        <f t="shared" si="2"/>
-        <v>385</v>
+        <f>ROUND($C$4/(D25/E25*F25),0)</f>
+        <v>44</v>
       </c>
       <c r="H25" s="22">
         <f t="shared" si="15"/>
-        <v>65</v>
-      </c>
-      <c r="I25" s="23"/>
+        <v>57</v>
+      </c>
+      <c r="I25" s="24"/>
       <c r="J25" s="30"/>
       <c r="K25">
         <f t="shared" ca="1" si="10"/>
-        <v>2.3199999999999998</v>
+        <v>2.88</v>
       </c>
       <c r="L25">
         <f t="shared" ca="1" si="11"/>
-        <v>4.2899999999999991</v>
+        <v>1.6599999999999966</v>
       </c>
       <c r="M25">
         <f t="shared" ca="1" si="12"/>
-        <v>0.4199999999999946</v>
+        <v>2.9399999999999977</v>
       </c>
       <c r="N25">
         <f t="shared" ca="1" si="7"/>
-        <v>3.6799999999999997</v>
+        <v>4.25</v>
       </c>
       <c r="O25">
         <f t="shared" ca="1" si="8"/>
-        <v>1.1800000000000068</v>
+        <v>3.3499999999999943</v>
       </c>
       <c r="P25">
         <f t="shared" ca="1" si="9"/>
-        <v>2.0499999999999972</v>
+        <v>2.1799999999999784</v>
       </c>
       <c r="R25" s="25">
-        <v>-6</v>
-      </c>
-      <c r="S25" s="29">
-        <v>142</v>
+        <v>-146</v>
+      </c>
+      <c r="S25" s="25">
+        <v>-28</v>
       </c>
       <c r="T25" s="29">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="U25" s="1"/>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="1">
-        <v>4.1900000000000004</v>
+      <c r="B26" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="22">
+        <v>6.5</v>
       </c>
       <c r="D26" s="25">
         <f t="shared" si="1"/>
-        <v>0.41900000000000004</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="F26" s="1">
-        <v>0.5</v>
+        <v>0.65</v>
+      </c>
+      <c r="E26" s="22">
+        <v>0.01</v>
+      </c>
+      <c r="F26" s="22">
+        <v>0.01</v>
       </c>
       <c r="G26" s="26">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>385</v>
       </c>
       <c r="H26" s="22">
         <f t="shared" si="15"/>
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="I26" s="23"/>
-      <c r="J26" s="30">
-        <v>46063</v>
-      </c>
+      <c r="J26" s="30"/>
       <c r="K26">
         <f t="shared" ca="1" si="10"/>
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="L26">
         <f t="shared" ca="1" si="11"/>
-        <v>4.6500000000000057</v>
+        <v>3.3300000000000054</v>
       </c>
       <c r="M26">
         <f t="shared" ca="1" si="12"/>
-        <v>0.75</v>
+        <v>4.3800000000000026</v>
       </c>
       <c r="N26">
         <f t="shared" ca="1" si="7"/>
-        <v>3.0999999999999943</v>
+        <v>3.1000000000000014</v>
       </c>
       <c r="O26">
         <f t="shared" ca="1" si="8"/>
-        <v>2.5999999999999943</v>
+        <v>1.5900000000000034</v>
       </c>
       <c r="P26">
         <f t="shared" ca="1" si="9"/>
-        <v>4.6499999999999773</v>
+        <v>4.4100000000000037</v>
       </c>
       <c r="R26" s="25">
-        <v>-149</v>
+        <v>-6</v>
       </c>
       <c r="S26" s="29">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="T26" s="29">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="U26" s="1"/>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C27" s="1">
-        <v>4</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="D27" s="25">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.41900000000000004</v>
       </c>
       <c r="E27" s="1">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F27" s="1">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G27" s="26">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H27" s="22">
         <f t="shared" si="15"/>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I27" s="23"/>
-      <c r="J27" s="30"/>
+      <c r="J27" s="30">
+        <v>46063</v>
+      </c>
       <c r="K27">
         <f t="shared" ca="1" si="10"/>
-        <v>1.91</v>
+        <v>3.29</v>
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="11"/>
-        <v>3.1599999999999966</v>
+        <v>3.4499999999999886</v>
       </c>
       <c r="M27">
         <f t="shared" ca="1" si="12"/>
-        <v>0.42000000000000171</v>
+        <v>3.0500000000000114</v>
       </c>
       <c r="N27">
         <f t="shared" ca="1" si="7"/>
-        <v>1.480000000000004</v>
+        <v>2.8000000000000114</v>
       </c>
       <c r="O27">
         <f t="shared" ca="1" si="8"/>
-        <v>2.039999999999992</v>
+        <v>3.75</v>
       </c>
       <c r="P27">
         <f t="shared" ca="1" si="9"/>
-        <v>2.4599999999999937</v>
-      </c>
-      <c r="R27" s="29">
-        <v>23</v>
+        <v>3.4000000000000057</v>
+      </c>
+      <c r="R27" s="25">
+        <v>-149</v>
       </c>
       <c r="S27" s="29">
-        <v>241</v>
+        <v>46</v>
       </c>
       <c r="T27" s="29">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="U27" s="1"/>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B28" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28" s="22">
-        <v>22.54</v>
+      <c r="B28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="1">
+        <v>4</v>
       </c>
       <c r="D28" s="25">
-        <f>C28/10</f>
-        <v>2.254</v>
-      </c>
-      <c r="E28" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="F28" s="22">
-        <v>0.1</v>
+        <f t="shared" si="1"/>
+        <v>0.4</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0.2</v>
       </c>
       <c r="G28" s="26">
-        <f>ROUND($C$4/(D28/E28*F28),0)</f>
-        <v>111</v>
+        <f t="shared" si="2"/>
+        <v>63</v>
       </c>
       <c r="H28" s="22">
         <f t="shared" si="15"/>
-        <v>23</v>
-      </c>
-      <c r="I28" s="24"/>
-      <c r="J28" s="30">
-        <v>46133</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I28" s="23"/>
+      <c r="J28" s="30"/>
       <c r="K28">
         <f t="shared" ca="1" si="10"/>
-        <v>19.78</v>
+        <v>2.15</v>
       </c>
       <c r="L28">
         <f t="shared" ca="1" si="11"/>
-        <v>39.299999999999955</v>
+        <v>2.7199999999999989</v>
       </c>
       <c r="M28">
         <f t="shared" ca="1" si="12"/>
-        <v>3.2000000000000455</v>
+        <v>1.9200000000000017</v>
       </c>
       <c r="N28">
         <f t="shared" ca="1" si="7"/>
-        <v>23.299999999999955</v>
+        <v>1.6600000000000108</v>
       </c>
       <c r="O28">
         <f t="shared" ca="1" si="8"/>
-        <v>17.5</v>
+        <v>2.019999999999996</v>
       </c>
       <c r="P28">
         <f t="shared" ca="1" si="9"/>
-        <v>15.599999999999909</v>
-      </c>
-      <c r="R28" s="1"/>
+        <v>2.4200000000000017</v>
+      </c>
+      <c r="R28" s="29">
+        <v>23</v>
+      </c>
       <c r="S28" s="29">
+        <v>241</v>
+      </c>
+      <c r="T28" s="29">
+        <v>13</v>
+      </c>
+      <c r="U28" s="1"/>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B29" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="22">
+        <v>22.54</v>
+      </c>
+      <c r="D29" s="25">
+        <f>C29/10</f>
+        <v>2.254</v>
+      </c>
+      <c r="E29" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="F29" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="G29" s="26">
+        <f>ROUND($C$4/(D29/E29*F29),0)</f>
+        <v>111</v>
+      </c>
+      <c r="H29" s="22">
+        <f t="shared" si="15"/>
+        <v>23</v>
+      </c>
+      <c r="I29" s="24"/>
+      <c r="J29" s="30">
+        <v>46133</v>
+      </c>
+      <c r="K29">
+        <f t="shared" ca="1" si="10"/>
+        <v>21.62</v>
+      </c>
+      <c r="L29">
+        <f t="shared" ca="1" si="11"/>
+        <v>17.099999999999909</v>
+      </c>
+      <c r="M29">
+        <f t="shared" ca="1" si="12"/>
+        <v>21.100000000000136</v>
+      </c>
+      <c r="N29">
+        <f t="shared" ca="1" si="7"/>
+        <v>25.5</v>
+      </c>
+      <c r="O29">
+        <f t="shared" ca="1" si="8"/>
+        <v>22.400000000000091</v>
+      </c>
+      <c r="P29">
+        <f t="shared" ca="1" si="9"/>
+        <v>22</v>
+      </c>
+      <c r="R29" s="1"/>
+      <c r="S29" s="29">
         <v>55</v>
       </c>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-    </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C30" s="1">
         <v>125.5</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D30" s="25">
         <f t="shared" si="1"/>
         <v>12.55</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E30" s="1">
         <v>0.5</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F30" s="1">
         <v>0.5</v>
       </c>
-      <c r="G29" s="26">
+      <c r="G30" s="26">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="H29" s="22">
+      <c r="H30" s="22">
         <f t="shared" si="15"/>
         <v>25</v>
       </c>
-      <c r="I29" s="23"/>
-      <c r="J29" s="30">
+      <c r="I30" s="23"/>
+      <c r="J30" s="30">
         <v>46133</v>
       </c>
-      <c r="K29">
+      <c r="K30">
         <f t="shared" ca="1" si="10"/>
-        <v>117.3</v>
-      </c>
-      <c r="L29">
+        <v>96.3</v>
+      </c>
+      <c r="L30">
         <f t="shared" ca="1" si="11"/>
-        <v>164</v>
-      </c>
-      <c r="M29">
+        <v>103</v>
+      </c>
+      <c r="M30">
         <f t="shared" ca="1" si="12"/>
-        <v>28</v>
-      </c>
-      <c r="N29">
+        <v>60</v>
+      </c>
+      <c r="N30">
         <f t="shared" ca="1" si="7"/>
-        <v>249</v>
-      </c>
-      <c r="O29">
+        <v>68.5</v>
+      </c>
+      <c r="O30">
         <f t="shared" ca="1" si="8"/>
-        <v>69.5</v>
-      </c>
-      <c r="P29">
+        <v>95</v>
+      </c>
+      <c r="P30">
         <f t="shared" ca="1" si="9"/>
-        <v>76</v>
-      </c>
-      <c r="R29" s="25">
+        <v>155</v>
+      </c>
+      <c r="R30" s="25">
         <v>-6</v>
       </c>
-      <c r="S29" s="25">
+      <c r="S30" s="25">
         <v>-340</v>
       </c>
-      <c r="T29" s="29">
+      <c r="T30" s="29">
         <v>22</v>
       </c>
-      <c r="U29" s="1"/>
-    </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B30" s="22" t="s">
+      <c r="U30" s="1"/>
+    </row>
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B31" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C31" s="22">
         <v>140</v>
       </c>
-      <c r="D30" s="25">
-        <f>C30/10</f>
+      <c r="D31" s="25">
+        <f>C31/10</f>
         <v>14</v>
       </c>
-      <c r="E30" s="22">
+      <c r="E31" s="22">
         <v>0.2</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F31" s="22">
         <v>0.2</v>
       </c>
-      <c r="G30" s="26">
-        <f>ROUND($C$4/(D30/E30*F30),0)</f>
+      <c r="G31" s="26">
+        <f>ROUND($C$4/(D31/E31*F31),0)</f>
         <v>18</v>
       </c>
-      <c r="H30" s="22">
+      <c r="H31" s="22">
         <f t="shared" si="15"/>
         <v>70</v>
-      </c>
-      <c r="I30" s="24"/>
-      <c r="K30">
-        <f t="shared" ca="1" si="10"/>
-        <v>22.48</v>
-      </c>
-      <c r="L30">
-        <f t="shared" ca="1" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="M30">
-        <f t="shared" ca="1" si="12"/>
-        <v>23</v>
-      </c>
-      <c r="N30">
-        <f t="shared" ca="1" si="7"/>
-        <v>30</v>
-      </c>
-      <c r="O30">
-        <f t="shared" ca="1" si="8"/>
-        <v>12.400000000000091</v>
-      </c>
-      <c r="P30">
-        <f t="shared" ca="1" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="R30" s="1"/>
-      <c r="S30" s="25">
-        <v>-426</v>
-      </c>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-    </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B31" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="22">
-        <v>112</v>
-      </c>
-      <c r="D31" s="25">
-        <f t="shared" ref="D31:D44" si="16">C31/10</f>
-        <v>11.2</v>
-      </c>
-      <c r="E31" s="22">
-        <v>1</v>
-      </c>
-      <c r="F31" s="22">
-        <v>1</v>
-      </c>
-      <c r="G31" s="26">
-        <f t="shared" ref="G31:G44" si="17">ROUND($C$4/(D31/E31*F31),0)</f>
-        <v>22</v>
-      </c>
-      <c r="H31" s="22">
-        <f t="shared" si="15"/>
-        <v>11</v>
       </c>
       <c r="I31" s="24"/>
       <c r="K31">
         <f t="shared" ca="1" si="10"/>
-        <v>109.2</v>
+        <v>40.36</v>
       </c>
       <c r="L31">
         <f t="shared" ca="1" si="11"/>
-        <v>188</v>
+        <v>36.600000000000023</v>
       </c>
       <c r="M31">
         <f t="shared" ca="1" si="12"/>
-        <v>18</v>
+        <v>44.600000000000023</v>
       </c>
       <c r="N31">
         <f t="shared" ca="1" si="7"/>
-        <v>108</v>
+        <v>28.200000000000045</v>
       </c>
       <c r="O31">
         <f t="shared" ca="1" si="8"/>
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="P31">
         <f t="shared" ca="1" si="9"/>
-        <v>102</v>
-      </c>
-      <c r="R31" s="25">
-        <v>-31</v>
-      </c>
-      <c r="S31" s="1"/>
-      <c r="T31" s="29">
-        <v>35</v>
-      </c>
+        <v>44.399999999999977</v>
+      </c>
+      <c r="R31" s="1"/>
+      <c r="S31" s="25">
+        <v>-426</v>
+      </c>
+      <c r="T31" s="1"/>
       <c r="U31" s="1"/>
     </row>
     <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B32" s="22" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C32" s="22">
-        <v>13.12</v>
+        <v>112</v>
       </c>
       <c r="D32" s="25">
-        <f>C32/10</f>
-        <v>1.3119999999999998</v>
+        <f t="shared" ref="D32:D45" si="16">C32/10</f>
+        <v>11.2</v>
       </c>
       <c r="E32" s="22">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F32" s="22">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G32" s="26">
-        <f>ROUND($C$4/(D32/E32*F32),0)</f>
-        <v>191</v>
+        <f t="shared" ref="G32:G45" si="17">ROUND($C$4/(D32/E32*F32),0)</f>
+        <v>22</v>
       </c>
       <c r="H32" s="22">
         <f t="shared" si="15"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I32" s="24"/>
-      <c r="J32" s="30">
-        <v>46066</v>
-      </c>
       <c r="K32">
         <f t="shared" ca="1" si="10"/>
-        <v>2.46</v>
+        <v>157.4</v>
       </c>
       <c r="L32">
         <f t="shared" ca="1" si="11"/>
-        <v>3.7999999999999545</v>
+        <v>112</v>
       </c>
       <c r="M32">
         <f t="shared" ca="1" si="12"/>
-        <v>1.3999999999999773</v>
+        <v>163</v>
       </c>
       <c r="N32">
         <f t="shared" ca="1" si="7"/>
-        <v>1.8999999999999773</v>
+        <v>318</v>
       </c>
       <c r="O32">
         <f t="shared" ca="1" si="8"/>
-        <v>2.6999999999999318</v>
+        <v>91</v>
       </c>
       <c r="P32">
         <f t="shared" ca="1" si="9"/>
-        <v>2.5</v>
-      </c>
-      <c r="R32" s="1"/>
-      <c r="S32" s="29">
-        <v>61</v>
-      </c>
-      <c r="T32" s="25">
-        <v>-11</v>
+        <v>103</v>
+      </c>
+      <c r="R32" s="25">
+        <v>-31</v>
+      </c>
+      <c r="S32" s="1"/>
+      <c r="T32" s="29">
+        <v>35</v>
       </c>
       <c r="U32" s="1"/>
     </row>
     <row r="33" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B33" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="22">
+        <v>13.12</v>
+      </c>
+      <c r="D33" s="25">
+        <f>C33/10</f>
+        <v>1.3119999999999998</v>
+      </c>
+      <c r="E33" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="F33" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="G33" s="26">
+        <f>ROUND($C$4/(D33/E33*F33),0)</f>
+        <v>191</v>
+      </c>
+      <c r="H33" s="22">
+        <f t="shared" si="15"/>
+        <v>13</v>
+      </c>
+      <c r="I33" s="24"/>
+      <c r="J33" s="30">
+        <v>46066</v>
+      </c>
+      <c r="K33">
+        <f t="shared" ca="1" si="10"/>
+        <v>2.88</v>
+      </c>
+      <c r="L33">
+        <f t="shared" ca="1" si="11"/>
+        <v>2.8999999999999773</v>
+      </c>
+      <c r="M33">
+        <f t="shared" ca="1" si="12"/>
+        <v>2.5</v>
+      </c>
+      <c r="N33">
+        <f t="shared" ca="1" si="7"/>
+        <v>3.8000000000000682</v>
+      </c>
+      <c r="O33">
+        <f t="shared" ca="1" si="8"/>
+        <v>2.8999999999999773</v>
+      </c>
+      <c r="P33">
+        <f t="shared" ca="1" si="9"/>
+        <v>2.2999999999999545</v>
+      </c>
+      <c r="R33" s="1"/>
+      <c r="S33" s="29">
+        <v>61</v>
+      </c>
+      <c r="T33" s="25">
+        <v>-11</v>
+      </c>
+      <c r="U33" s="1"/>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B34" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C34" s="22">
         <v>57.2</v>
       </c>
-      <c r="D33" s="25">
+      <c r="D34" s="25">
         <f t="shared" si="16"/>
         <v>5.7200000000000006</v>
       </c>
-      <c r="E33" s="22">
+      <c r="E34" s="22">
         <v>0.2</v>
       </c>
-      <c r="F33" s="22">
+      <c r="F34" s="22">
         <v>0.2</v>
       </c>
-      <c r="G33" s="26">
+      <c r="G34" s="26">
         <f t="shared" si="17"/>
         <v>44</v>
       </c>
-      <c r="H33" s="22">
+      <c r="H34" s="22">
         <f t="shared" si="15"/>
         <v>29</v>
       </c>
-      <c r="I33" s="24"/>
-      <c r="J33" s="30">
+      <c r="I34" s="24"/>
+      <c r="J34" s="30">
         <v>46133</v>
       </c>
-      <c r="K33">
+      <c r="K34">
         <f t="shared" ca="1" si="10"/>
-        <v>42.88</v>
-      </c>
-      <c r="L33">
+        <v>36.28</v>
+      </c>
+      <c r="L34">
         <f t="shared" ca="1" si="11"/>
-        <v>32.800000000000182</v>
-      </c>
-      <c r="M33">
+        <v>27.599999999999909</v>
+      </c>
+      <c r="M34">
         <f t="shared" ca="1" si="12"/>
-        <v>11</v>
-      </c>
-      <c r="N33">
+        <v>27.800000000000182</v>
+      </c>
+      <c r="N34">
         <f t="shared" ca="1" si="7"/>
-        <v>104.40000000000009</v>
-      </c>
-      <c r="O33">
+        <v>49</v>
+      </c>
+      <c r="O34">
         <f t="shared" ca="1" si="8"/>
-        <v>30.400000000000091</v>
-      </c>
-      <c r="P33">
+        <v>44</v>
+      </c>
+      <c r="P34">
         <f t="shared" ca="1" si="9"/>
-        <v>35.800000000000182</v>
-      </c>
-      <c r="R33" s="25">
+        <v>33</v>
+      </c>
+      <c r="R34" s="25">
         <v>-68</v>
       </c>
-      <c r="S33" s="25">
+      <c r="S34" s="25">
         <v>-291</v>
       </c>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B34" s="22" t="s">
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B35" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="22">
+      <c r="C35" s="22">
         <v>10</v>
       </c>
-      <c r="D34" s="25">
+      <c r="D35" s="25">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="E34" s="22">
+      <c r="E35" s="22">
         <v>0.05</v>
       </c>
-      <c r="F34" s="22">
+      <c r="F35" s="22">
         <v>0.05</v>
       </c>
-      <c r="G34" s="26">
+      <c r="G35" s="26">
         <f t="shared" si="17"/>
         <v>250</v>
       </c>
-      <c r="H34" s="22">
+      <c r="H35" s="22">
         <f t="shared" si="15"/>
         <v>20</v>
       </c>
-      <c r="I34" s="24"/>
-      <c r="K34">
+      <c r="I35" s="24"/>
+      <c r="K35">
         <f t="shared" ca="1" si="10"/>
-        <v>3.15</v>
-      </c>
-      <c r="L34">
+        <v>4.62</v>
+      </c>
+      <c r="L35">
         <f t="shared" ca="1" si="11"/>
-        <v>2.5999999999999943</v>
-      </c>
-      <c r="M34">
+        <v>5.1000000000000085</v>
+      </c>
+      <c r="M35">
         <f t="shared" ca="1" si="12"/>
-        <v>0.94999999999998863</v>
-      </c>
-      <c r="N34">
+        <v>6.8999999999999915</v>
+      </c>
+      <c r="N35">
         <f t="shared" ca="1" si="7"/>
-        <v>6.6500000000000057</v>
-      </c>
-      <c r="O34">
+        <v>6.5</v>
+      </c>
+      <c r="O35">
         <f t="shared" ca="1" si="8"/>
-        <v>3.3499999999999943</v>
-      </c>
-      <c r="P34">
+        <v>1.7000000000000028</v>
+      </c>
+      <c r="P35">
         <f t="shared" ca="1" si="9"/>
-        <v>2.2000000000000028</v>
-      </c>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="29">
+        <v>2.9000000000000057</v>
+      </c>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="29">
         <v>33</v>
       </c>
-      <c r="U34" s="1"/>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B35" s="22" t="s">
+      <c r="U35" s="1"/>
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B36" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="22">
+      <c r="C36" s="22">
         <v>6.34</v>
       </c>
-      <c r="D35" s="25">
+      <c r="D36" s="25">
         <f t="shared" si="16"/>
         <v>0.63400000000000001</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E36" s="22">
         <v>0.05</v>
       </c>
-      <c r="F35" s="22">
+      <c r="F36" s="22">
         <v>0.05</v>
       </c>
-      <c r="G35" s="26">
+      <c r="G36" s="26">
         <f t="shared" si="17"/>
         <v>394</v>
       </c>
-      <c r="H35" s="22">
+      <c r="H36" s="22">
         <f t="shared" si="15"/>
         <v>13</v>
       </c>
-      <c r="I35" s="23"/>
-      <c r="J35" s="30">
+      <c r="I36" s="23"/>
+      <c r="J36" s="30">
         <v>46133</v>
       </c>
-      <c r="K35">
+      <c r="K36">
         <f t="shared" ca="1" si="10"/>
-        <v>7.83</v>
-      </c>
-      <c r="L35">
+        <v>7.69</v>
+      </c>
+      <c r="L36">
         <f t="shared" ca="1" si="11"/>
+        <v>12.200000000000045</v>
+      </c>
+      <c r="M36">
+        <f t="shared" ca="1" si="12"/>
         <v>8</v>
       </c>
-      <c r="M35">
-        <f t="shared" ca="1" si="12"/>
-        <v>2.3500000000000227</v>
-      </c>
-      <c r="N35">
+      <c r="N36">
         <f t="shared" ca="1" si="7"/>
-        <v>14.25</v>
-      </c>
-      <c r="O35">
+        <v>5.8000000000000114</v>
+      </c>
+      <c r="O36">
         <f t="shared" ca="1" si="8"/>
-        <v>9.1499999999999773</v>
-      </c>
-      <c r="P35">
+        <v>6.5</v>
+      </c>
+      <c r="P36">
         <f t="shared" ca="1" si="9"/>
-        <v>5.4000000000000341</v>
-      </c>
-      <c r="R35" s="29">
+        <v>5.9499999999999886</v>
+      </c>
+      <c r="R36" s="29">
         <v>342</v>
       </c>
-      <c r="S35" s="25">
+      <c r="S36" s="25">
         <v>-106</v>
       </c>
-      <c r="T35" s="25">
+      <c r="T36" s="25">
         <v>-93</v>
       </c>
-      <c r="U35" s="1"/>
-    </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B36" s="22" t="s">
+      <c r="U36" s="1"/>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B37" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C36" s="22">
+      <c r="C37" s="22">
         <v>1.1299999999999999</v>
       </c>
-      <c r="D36" s="25">
-        <f>C36/10</f>
+      <c r="D37" s="25">
+        <f>C37/10</f>
         <v>0.11299999999999999</v>
       </c>
-      <c r="E36" s="22">
+      <c r="E37" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F36" s="22">
+      <c r="F37" s="22">
         <v>0.05</v>
       </c>
-      <c r="G36" s="26">
-        <f>ROUND($C$4/(D36/E36*F36),0)</f>
+      <c r="G37" s="26">
+        <f>ROUND($C$4/(D37/E37*F37),0)</f>
         <v>221</v>
       </c>
-      <c r="H36" s="22">
+      <c r="H37" s="22">
         <f t="shared" si="15"/>
         <v>23</v>
       </c>
-      <c r="I36" s="24"/>
-      <c r="J36" s="30">
+      <c r="I37" s="24"/>
+      <c r="J37" s="30">
         <v>46133</v>
       </c>
-      <c r="K36">
+      <c r="K37">
         <f t="shared" ca="1" si="10"/>
-        <v>0.81</v>
-      </c>
-      <c r="L36">
+        <v>1.2</v>
+      </c>
+      <c r="L37">
         <f t="shared" ca="1" si="11"/>
+        <v>1.1950000000000003</v>
+      </c>
+      <c r="M37">
+        <f t="shared" ca="1" si="12"/>
+        <v>1.0350000000000037</v>
+      </c>
+      <c r="N37">
+        <f t="shared" ca="1" si="7"/>
         <v>1.0949999999999989</v>
       </c>
-      <c r="M36">
-        <f t="shared" ca="1" si="12"/>
-        <v>0.29500000000000171</v>
-      </c>
-      <c r="N36">
-        <f t="shared" ca="1" si="7"/>
-        <v>0.98000000000000398</v>
-      </c>
-      <c r="O36">
+      <c r="O37">
         <f t="shared" ca="1" si="8"/>
-        <v>0.77499999999999858</v>
-      </c>
-      <c r="P36">
+        <v>1.3349999999999937</v>
+      </c>
+      <c r="P37">
         <f t="shared" ca="1" si="9"/>
-        <v>0.92000000000000171</v>
-      </c>
-      <c r="R36" s="1"/>
-      <c r="S36" s="25">
+        <v>1.3500000000000014</v>
+      </c>
+      <c r="R37" s="1"/>
+      <c r="S37" s="25">
         <v>-143</v>
       </c>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B37" s="22" t="s">
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+    </row>
+    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B38" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="22">
+      <c r="C38" s="22">
         <v>6</v>
       </c>
-      <c r="D37" s="25">
+      <c r="D38" s="25">
         <f t="shared" si="16"/>
         <v>0.6</v>
       </c>
-      <c r="E37" s="22">
+      <c r="E38" s="22">
         <v>0.01</v>
       </c>
-      <c r="F37" s="22">
+      <c r="F38" s="22">
         <v>0.01</v>
       </c>
-      <c r="G37" s="26">
+      <c r="G38" s="26">
         <f t="shared" si="17"/>
         <v>417</v>
       </c>
-      <c r="H37" s="22">
+      <c r="H38" s="22">
         <f t="shared" si="15"/>
         <v>60</v>
       </c>
-      <c r="I37" s="23"/>
-      <c r="J37" s="30">
+      <c r="I38" s="23"/>
+      <c r="J38" s="30">
         <v>46133</v>
       </c>
-      <c r="K37">
+      <c r="K38">
         <f t="shared" ca="1" si="10"/>
-        <v>2.87</v>
-      </c>
-      <c r="L37">
+        <v>2.74</v>
+      </c>
+      <c r="L38">
         <f t="shared" ca="1" si="11"/>
-        <v>3.9399999999999977</v>
-      </c>
-      <c r="M37">
+        <v>2.1999999999999886</v>
+      </c>
+      <c r="M38">
         <f t="shared" ca="1" si="12"/>
-        <v>0.5</v>
-      </c>
-      <c r="N37">
+        <v>3.1699999999999591</v>
+      </c>
+      <c r="N38">
         <f t="shared" ca="1" si="7"/>
-        <v>3.4900000000000091</v>
-      </c>
-      <c r="O37">
+        <v>2.1300000000000523</v>
+      </c>
+      <c r="O38">
         <f t="shared" ca="1" si="8"/>
-        <v>2.4399999999999977</v>
-      </c>
-      <c r="P37">
+        <v>3.7699999999999818</v>
+      </c>
+      <c r="P38">
         <f t="shared" ca="1" si="9"/>
-        <v>3.9599999999999795</v>
-      </c>
-      <c r="R37" s="29">
+        <v>2.4499999999999886</v>
+      </c>
+      <c r="R38" s="29">
         <v>32</v>
       </c>
-      <c r="S37" s="25">
+      <c r="S38" s="25">
         <v>-139</v>
       </c>
-      <c r="T37" s="29">
+      <c r="T38" s="29">
         <v>40</v>
       </c>
-      <c r="U37" s="1"/>
-    </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B38" s="22" t="s">
+      <c r="U38" s="1"/>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B39" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="C38" s="22">
+      <c r="C39" s="22">
         <v>44.16</v>
       </c>
-      <c r="D38" s="25">
+      <c r="D39" s="25">
         <f t="shared" si="16"/>
         <v>4.4159999999999995</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E39" s="22">
         <v>0.2</v>
       </c>
-      <c r="F38" s="22">
+      <c r="F39" s="22">
         <v>0.2</v>
       </c>
-      <c r="G38" s="26">
+      <c r="G39" s="26">
         <f t="shared" si="17"/>
         <v>57</v>
       </c>
-      <c r="H38" s="22">
+      <c r="H39" s="22">
         <f t="shared" si="15"/>
         <v>22</v>
       </c>
-      <c r="I38" s="24"/>
-      <c r="J38" s="30">
+      <c r="I39" s="24"/>
+      <c r="J39" s="30">
         <v>46058</v>
       </c>
-      <c r="K38">
+      <c r="K39">
         <f t="shared" ca="1" si="10"/>
-        <v>27.28</v>
-      </c>
-      <c r="L38">
+        <v>42.36</v>
+      </c>
+      <c r="L39">
         <f t="shared" ca="1" si="11"/>
-        <v>26</v>
-      </c>
-      <c r="M38">
+        <v>54.800000000000068</v>
+      </c>
+      <c r="M39">
         <f t="shared" ca="1" si="12"/>
-        <v>12</v>
-      </c>
-      <c r="N38">
+        <v>29</v>
+      </c>
+      <c r="N39">
         <f t="shared" ca="1" si="7"/>
-        <v>24.799999999999955</v>
-      </c>
-      <c r="O38">
+        <v>7.3999999999999773</v>
+      </c>
+      <c r="O39">
         <f t="shared" ca="1" si="8"/>
-        <v>42.600000000000023</v>
-      </c>
-      <c r="P38">
+        <v>43.600000000000023</v>
+      </c>
+      <c r="P39">
         <f t="shared" ca="1" si="9"/>
-        <v>31</v>
-      </c>
-      <c r="R38" s="25">
+        <v>77</v>
+      </c>
+      <c r="R39" s="25">
         <v>-89</v>
       </c>
-      <c r="S38" s="25">
+      <c r="S39" s="25">
         <v>-300</v>
       </c>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B39" s="22" t="s">
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B40" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C39" s="22">
+      <c r="C40" s="22">
         <v>0.14000000000000001</v>
       </c>
-      <c r="D39" s="25">
-        <f>C39/10</f>
+      <c r="D40" s="25">
+        <f>C40/10</f>
         <v>1.4000000000000002E-2</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E40" s="22">
         <v>1E-3</v>
       </c>
-      <c r="F39" s="22">
+      <c r="F40" s="22">
         <v>0.1</v>
       </c>
-      <c r="G39" s="26">
-        <f>ROUND($C$4/(D39/E39*F39),0)</f>
+      <c r="G40" s="26">
+        <f>ROUND($C$4/(D40/E40*F40),0)</f>
         <v>179</v>
       </c>
-      <c r="H39" s="22">
+      <c r="H40" s="22">
         <f t="shared" si="15"/>
         <v>14</v>
-      </c>
-      <c r="I39" s="24"/>
-      <c r="K39">
-        <f t="shared" ca="1" si="10"/>
-        <v>18.05</v>
-      </c>
-      <c r="L39">
-        <f t="shared" ca="1" si="11"/>
-        <v>6.9499999999999895E-2</v>
-      </c>
-      <c r="M39">
-        <f t="shared" ca="1" si="12"/>
-        <v>1.5000000000000013E-2</v>
-      </c>
-      <c r="N39">
-        <f t="shared" ca="1" si="7"/>
-        <v>6.3999999999999946E-2</v>
-      </c>
-      <c r="O39">
-        <f t="shared" ca="1" si="8"/>
-        <v>-46021.955499999996</v>
-      </c>
-      <c r="P39">
-        <f t="shared" ca="1" si="9"/>
-        <v>46112.035499999998</v>
-      </c>
-      <c r="R39" s="29">
-        <v>71</v>
-      </c>
-      <c r="S39" s="22"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B40" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="22">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="D40" s="25">
-        <f>C40/10</f>
-        <v>1.86</v>
-      </c>
-      <c r="E40" s="22">
-        <v>0.05</v>
-      </c>
-      <c r="F40" s="22">
-        <v>0.05</v>
-      </c>
-      <c r="G40" s="26">
-        <f>ROUND($C$4/(D40/E40*F40),0)</f>
-        <v>134</v>
-      </c>
-      <c r="H40" s="22">
-        <f t="shared" si="15"/>
-        <v>37</v>
       </c>
       <c r="I40" s="24"/>
       <c r="K40">
         <f t="shared" ca="1" si="10"/>
-        <v>8.84</v>
+        <v>0.02</v>
       </c>
       <c r="L40">
         <f t="shared" ca="1" si="11"/>
-        <v>11.75</v>
+        <v>2.4500000000000077E-2</v>
       </c>
       <c r="M40">
         <f t="shared" ca="1" si="12"/>
-        <v>2.5499999999999545</v>
+        <v>1.8500000000000072E-2</v>
       </c>
       <c r="N40">
         <f t="shared" ca="1" si="7"/>
-        <v>16.450000000000045</v>
+        <v>1.6000000000000014E-2</v>
       </c>
       <c r="O40">
         <f t="shared" ca="1" si="8"/>
-        <v>8.4000000000000909</v>
+        <v>1.7500000000000071E-2</v>
       </c>
       <c r="P40">
         <f t="shared" ca="1" si="9"/>
-        <v>5.0499999999999545</v>
-      </c>
-      <c r="R40" s="25">
-        <v>-9</v>
-      </c>
-      <c r="S40" s="29">
-        <v>42</v>
-      </c>
+        <v>2.4000000000000021E-2</v>
+      </c>
+      <c r="R40" s="29">
+        <v>71</v>
+      </c>
+      <c r="S40" s="22"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
     </row>
     <row r="41" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B41" s="22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C41" s="22">
-        <v>45</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="D41" s="25">
         <f>C41/10</f>
-        <v>4.5</v>
+        <v>1.86</v>
       </c>
       <c r="E41" s="22">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="F41" s="22">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G41" s="26">
         <f>ROUND($C$4/(D41/E41*F41),0)</f>
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="H41" s="22">
         <f t="shared" si="15"/>
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I41" s="24"/>
-      <c r="J41" s="30">
-        <v>46133</v>
-      </c>
       <c r="K41">
         <f t="shared" ca="1" si="10"/>
-        <v>40.28</v>
+        <v>8.23</v>
       </c>
       <c r="L41">
         <f t="shared" ca="1" si="11"/>
-        <v>55.799999999999955</v>
+        <v>10.600000000000023</v>
       </c>
       <c r="M41">
         <f t="shared" ca="1" si="12"/>
-        <v>11.599999999999909</v>
+        <v>10</v>
       </c>
       <c r="N41">
         <f t="shared" ca="1" si="7"/>
-        <v>53.799999999999955</v>
+        <v>7.75</v>
       </c>
       <c r="O41">
         <f t="shared" ca="1" si="8"/>
-        <v>20.200000000000045</v>
+        <v>5.6000000000000227</v>
       </c>
       <c r="P41">
         <f t="shared" ca="1" si="9"/>
-        <v>60</v>
-      </c>
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="29">
-        <v>22</v>
-      </c>
+        <v>7.2000000000000455</v>
+      </c>
+      <c r="R41" s="25">
+        <v>-9</v>
+      </c>
+      <c r="S41" s="29">
+        <v>42</v>
+      </c>
+      <c r="T41" s="1"/>
       <c r="U41" s="1"/>
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B42" s="1" t="s">
-        <v>75</v>
+      <c r="B42" s="22" t="s">
+        <v>69</v>
       </c>
       <c r="C42" s="22">
-        <v>690</v>
+        <v>45</v>
       </c>
       <c r="D42" s="25">
         <f>C42/10</f>
-        <v>69</v>
+        <v>4.5</v>
       </c>
       <c r="E42" s="22">
-        <v>5.0000000000000001E-3</v>
+        <v>0.2</v>
       </c>
       <c r="F42" s="22">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G42" s="26">
         <f>ROUND($C$4/(D42/E42*F42),0)</f>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H42" s="22">
         <f t="shared" si="15"/>
-        <v>13800</v>
+        <v>23</v>
       </c>
       <c r="I42" s="24"/>
+      <c r="J42" s="30">
+        <v>46133</v>
+      </c>
       <c r="K42">
         <f t="shared" ca="1" si="10"/>
-        <v>0.27</v>
+        <v>31.84</v>
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="11"/>
-        <v>0.4599999999999973</v>
+        <v>45</v>
       </c>
       <c r="M42">
         <f t="shared" ca="1" si="12"/>
-        <v>0.14000000000000057</v>
+        <v>29</v>
       </c>
       <c r="N42">
         <f t="shared" ca="1" si="7"/>
-        <v>0.33999999999999986</v>
+        <v>23</v>
       </c>
       <c r="O42">
         <f t="shared" ca="1" si="8"/>
-        <v>0.18500000000000227</v>
+        <v>25.599999999999966</v>
       </c>
       <c r="P42">
         <f t="shared" ca="1" si="9"/>
-        <v>0.22000000000000242</v>
-      </c>
+        <v>36.600000000000023</v>
+      </c>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="29">
+        <v>22</v>
+      </c>
+      <c r="U42" s="1"/>
     </row>
     <row r="43" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="22">
+        <v>690</v>
+      </c>
+      <c r="D43" s="25">
+        <f>C43/10</f>
+        <v>69</v>
+      </c>
+      <c r="E43" s="22">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F43" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="G43" s="26">
+        <f>ROUND($C$4/(D43/E43*F43),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="22">
+        <f t="shared" si="15"/>
+        <v>13800</v>
+      </c>
+      <c r="I43" s="24"/>
+      <c r="K43">
+        <f t="shared" ca="1" si="10"/>
+        <v>-9246.34</v>
+      </c>
+      <c r="L43">
+        <f t="shared" ca="1" si="11"/>
+        <v>0.37000000000000099</v>
+      </c>
+      <c r="M43">
+        <f t="shared" ca="1" si="12"/>
+        <v>0.19500000000000028</v>
+      </c>
+      <c r="N43">
+        <f t="shared" ca="1" si="7"/>
+        <v>-46232.864999999998</v>
+      </c>
+      <c r="O43">
+        <f t="shared" ca="1" si="8"/>
+        <v>0.30000000000000071</v>
+      </c>
+      <c r="P43">
+        <f t="shared" ca="1" si="9"/>
+        <v>0.32000000000000028</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B44" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C43" s="22">
+      <c r="C44" s="22">
         <v>1.65</v>
       </c>
-      <c r="D43" s="25">
+      <c r="D44" s="25">
         <f t="shared" si="16"/>
         <v>0.16499999999999998</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E44" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F43" s="22">
+      <c r="F44" s="22">
         <v>0.05</v>
       </c>
-      <c r="G43" s="26">
+      <c r="G44" s="26">
         <f t="shared" si="17"/>
         <v>152</v>
       </c>
-      <c r="H43" s="22">
+      <c r="H44" s="22">
         <f t="shared" si="15"/>
         <v>33</v>
       </c>
-      <c r="I43" s="24"/>
-      <c r="J43" s="30">
+      <c r="I44" s="24"/>
+      <c r="J44" s="30">
         <v>46133</v>
       </c>
-      <c r="K43">
+      <c r="K44">
         <f t="shared" ca="1" si="10"/>
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="L43">
+        <v>1.03</v>
+      </c>
+      <c r="L44">
         <f t="shared" ca="1" si="11"/>
-        <v>1.240000000000002</v>
-      </c>
-      <c r="M43">
+        <v>0.73499999999999943</v>
+      </c>
+      <c r="M44">
         <f t="shared" ca="1" si="12"/>
-        <v>0.18999999999999773</v>
-      </c>
-      <c r="N43">
+        <v>0.76500000000000057</v>
+      </c>
+      <c r="N44">
         <f t="shared" ca="1" si="7"/>
-        <v>1.1749999999999972</v>
-      </c>
-      <c r="O43">
+        <v>2.1000000000000014</v>
+      </c>
+      <c r="O44">
         <f t="shared" ca="1" si="8"/>
-        <v>1.7600000000000051</v>
-      </c>
-      <c r="P43">
+        <v>0.85999999999999943</v>
+      </c>
+      <c r="P44">
         <f t="shared" ca="1" si="9"/>
-        <v>1.4200000000000017</v>
-      </c>
-      <c r="R43" s="25">
+        <v>0.66499999999999915</v>
+      </c>
+      <c r="R44" s="25">
         <v>-18</v>
       </c>
-      <c r="S43" s="25">
+      <c r="S44" s="25">
         <v>-76</v>
       </c>
-      <c r="T43" s="25">
+      <c r="T44" s="25">
         <v>-116</v>
       </c>
-      <c r="U43" s="1"/>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B44" s="22" t="s">
+      <c r="U44" s="1"/>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B45" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="22">
+      <c r="C45" s="22">
         <v>12</v>
       </c>
-      <c r="D44" s="25">
+      <c r="D45" s="25">
         <f t="shared" si="16"/>
         <v>1.2</v>
       </c>
-      <c r="E44" s="22">
+      <c r="E45" s="22">
         <v>0.1</v>
       </c>
-      <c r="F44" s="22">
+      <c r="F45" s="22">
         <v>0.1</v>
       </c>
-      <c r="G44" s="26">
+      <c r="G45" s="26">
         <f t="shared" si="17"/>
         <v>208</v>
       </c>
-      <c r="H44" s="22">
+      <c r="H45" s="22">
         <f t="shared" si="15"/>
         <v>12</v>
-      </c>
-      <c r="I44" s="24"/>
-      <c r="K44">
-        <f t="shared" ca="1" si="10"/>
-        <v>13.14</v>
-      </c>
-      <c r="L44">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B44&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B44&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>19.399999999999977</v>
-      </c>
-      <c r="M44">
-        <f t="shared" ca="1" si="12"/>
-        <v>3.6000000000000227</v>
-      </c>
-      <c r="N44">
-        <f t="shared" ca="1" si="7"/>
-        <v>19.100000000000023</v>
-      </c>
-      <c r="O44">
-        <f t="shared" ca="1" si="8"/>
-        <v>8.8999999999999773</v>
-      </c>
-      <c r="P44">
-        <f t="shared" ca="1" si="9"/>
-        <v>14.700000000000045</v>
-      </c>
-      <c r="R44" s="25">
-        <v>-114</v>
-      </c>
-      <c r="S44" s="29">
-        <v>6</v>
-      </c>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B45" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" s="22">
-        <v>6</v>
-      </c>
-      <c r="D45" s="25">
-        <f>C45/10</f>
-        <v>0.6</v>
-      </c>
-      <c r="E45" s="22">
-        <v>0.02</v>
-      </c>
-      <c r="F45" s="22">
-        <v>0.2</v>
-      </c>
-      <c r="G45" s="26">
-        <f t="shared" ref="G45:G50" si="18">ROUND($C$4/(D45/E45*F45),0)</f>
-        <v>42</v>
-      </c>
-      <c r="H45" s="22">
-        <f t="shared" si="15"/>
-        <v>30</v>
       </c>
       <c r="I45" s="24"/>
       <c r="K45">
         <f t="shared" ca="1" si="10"/>
-        <v>2.41</v>
+        <v>12.7</v>
       </c>
       <c r="L45">
-        <f t="shared" ca="1" si="11"/>
-        <v>2.8199999999999932</v>
+        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B45&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B45&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+        <v>10.799999999999955</v>
       </c>
       <c r="M45">
         <f t="shared" ca="1" si="12"/>
-        <v>0.37999999999999545</v>
+        <v>11.5</v>
       </c>
       <c r="N45">
         <f t="shared" ca="1" si="7"/>
-        <v>4.3799999999999955</v>
+        <v>11.100000000000023</v>
       </c>
       <c r="O45">
         <f t="shared" ca="1" si="8"/>
-        <v>1.5999999999999943</v>
+        <v>14.600000000000023</v>
       </c>
       <c r="P45">
         <f t="shared" ca="1" si="9"/>
-        <v>2.8799999999999955</v>
-      </c>
-      <c r="R45" s="29">
-        <v>7</v>
-      </c>
-      <c r="S45" s="25">
-        <v>-262</v>
+        <v>15.5</v>
+      </c>
+      <c r="R45" s="25">
+        <v>-114</v>
+      </c>
+      <c r="S45" s="29">
+        <v>6</v>
       </c>
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
     </row>
     <row r="46" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B46" s="22" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="C46" s="22">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="D46" s="25">
         <f>C46/10</f>
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="E46" s="22">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
       <c r="F46" s="22">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G46" s="26">
-        <f t="shared" si="18"/>
-        <v>36</v>
+        <f t="shared" ref="G46:G51" si="18">ROUND($C$4/(D46/E46*F46),0)</f>
+        <v>42</v>
       </c>
       <c r="H46" s="22">
-        <f t="shared" ref="H46:H48" si="19">ROUND(D46/E46,0)</f>
-        <v>14</v>
+        <f t="shared" si="15"/>
+        <v>30</v>
       </c>
       <c r="I46" s="24"/>
       <c r="K46">
         <f t="shared" ca="1" si="10"/>
-        <v>15.76</v>
+        <v>3.66</v>
       </c>
       <c r="L46">
         <f t="shared" ca="1" si="11"/>
-        <v>18.200000000000045</v>
+        <v>5.4200000000000017</v>
       </c>
       <c r="M46">
         <f t="shared" ca="1" si="12"/>
-        <v>6.2000000000000455</v>
+        <v>2.1400000000000006</v>
       </c>
       <c r="N46">
         <f t="shared" ca="1" si="7"/>
-        <v>22.399999999999864</v>
+        <v>3.1000000000000085</v>
       </c>
       <c r="O46">
         <f t="shared" ca="1" si="8"/>
-        <v>17.799999999999955</v>
+        <v>2.1400000000000006</v>
       </c>
       <c r="P46">
         <f t="shared" ca="1" si="9"/>
-        <v>14.200000000000045</v>
-      </c>
-      <c r="R46" s="1"/>
+        <v>5.519999999999996</v>
+      </c>
+      <c r="R46" s="29">
+        <v>7</v>
+      </c>
       <c r="S46" s="25">
-        <v>-8</v>
-      </c>
-      <c r="T46" s="29">
-        <v>5</v>
-      </c>
+        <v>-262</v>
+      </c>
+      <c r="T46" s="1"/>
       <c r="U46" s="1"/>
     </row>
     <row r="47" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B47" s="22" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C47" s="22">
-        <v>5.1400000000000001E-2</v>
+        <v>70</v>
       </c>
       <c r="D47" s="25">
-        <f>ROUND(C47/10,4)</f>
-        <v>5.1000000000000004E-3</v>
-      </c>
-      <c r="E47" s="1">
-        <v>1E-4</v>
-      </c>
-      <c r="F47" s="1">
-        <v>0.1</v>
+        <f>C47/10</f>
+        <v>7</v>
+      </c>
+      <c r="E47" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="F47" s="22">
+        <v>0.5</v>
       </c>
       <c r="G47" s="26">
         <f t="shared" si="18"/>
+        <v>36</v>
+      </c>
+      <c r="H47" s="22">
+        <f t="shared" ref="H47:H49" si="19">ROUND(D47/E47,0)</f>
+        <v>14</v>
+      </c>
+      <c r="I47" s="24"/>
+      <c r="K47">
+        <f t="shared" ca="1" si="10"/>
+        <v>25.48</v>
+      </c>
+      <c r="L47">
+        <f t="shared" ca="1" si="11"/>
+        <v>25.799999999999955</v>
+      </c>
+      <c r="M47">
+        <f t="shared" ca="1" si="12"/>
+        <v>22.599999999999909</v>
+      </c>
+      <c r="N47">
+        <f t="shared" ca="1" si="7"/>
+        <v>36</v>
+      </c>
+      <c r="O47">
+        <f t="shared" ca="1" si="8"/>
+        <v>17.799999999999955</v>
+      </c>
+      <c r="P47">
+        <f t="shared" ca="1" si="9"/>
+        <v>25.200000000000045</v>
+      </c>
+      <c r="R47" s="1"/>
+      <c r="S47" s="25">
+        <v>-8</v>
+      </c>
+      <c r="T47" s="29">
+        <v>5</v>
+      </c>
+      <c r="U47" s="1"/>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B48" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" s="22">
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="D48" s="25">
+        <f>ROUND(C48/10,4)</f>
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G48" s="26">
+        <f t="shared" si="18"/>
         <v>49</v>
       </c>
-      <c r="H47" s="22">
+      <c r="H48" s="22">
         <f t="shared" si="19"/>
         <v>51</v>
       </c>
-      <c r="I47" s="24"/>
-      <c r="J47" s="30">
+      <c r="I48" s="24"/>
+      <c r="J48" s="30">
         <v>46133</v>
       </c>
-      <c r="K47">
-        <f ca="1">ROUND(AVERAGE(L47:P47),4)</f>
-        <v>1.8800000000000001E-2</v>
-      </c>
-      <c r="L47">
+      <c r="K48">
+        <f ca="1">ROUND(AVERAGE(L48:P48),4)</f>
+        <v>4.7100000000000003E-2</v>
+      </c>
+      <c r="L48">
         <f t="shared" ca="1" si="11"/>
-        <v>1.3900000000000023E-2</v>
-      </c>
-      <c r="M47">
+        <v>2.2399999999999975E-2</v>
+      </c>
+      <c r="M48">
         <f t="shared" ca="1" si="12"/>
-        <v>2.9000000000000137E-3</v>
-      </c>
-      <c r="N47">
+        <v>4.7000000000000042E-2</v>
+      </c>
+      <c r="N48">
         <f t="shared" ca="1" si="7"/>
-        <v>3.1100000000000017E-2</v>
-      </c>
-      <c r="O47">
+        <v>2.5699999999999945E-2</v>
+      </c>
+      <c r="O48">
         <f t="shared" ca="1" si="8"/>
-        <v>2.3799999999999932E-2</v>
-      </c>
-      <c r="P47">
+        <v>3.1599999999999961E-2</v>
+      </c>
+      <c r="P48">
         <f t="shared" ca="1" si="9"/>
-        <v>2.2299999999999986E-2</v>
-      </c>
-      <c r="R47" s="1"/>
-      <c r="S47" s="22"/>
-      <c r="T47" s="22"/>
-      <c r="U47" s="1"/>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B48" s="1" t="s">
+        <v>0.1089</v>
+      </c>
+      <c r="R48" s="1"/>
+      <c r="S48" s="22"/>
+      <c r="T48" s="22"/>
+      <c r="U48" s="1"/>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C49" s="1">
         <v>8.9</v>
       </c>
-      <c r="D48" s="25">
-        <f>C48/10</f>
+      <c r="D49" s="25">
+        <f>C49/10</f>
         <v>0.89</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E49" s="1">
         <v>0.05</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F49" s="1">
         <v>0.05</v>
       </c>
-      <c r="G48" s="26">
+      <c r="G49" s="26">
         <f t="shared" si="18"/>
         <v>281</v>
       </c>
-      <c r="H48" s="22">
+      <c r="H49" s="22">
         <f t="shared" si="19"/>
         <v>18</v>
       </c>
-      <c r="I48" s="23"/>
-      <c r="J48" s="30">
+      <c r="I49" s="23"/>
+      <c r="J49" s="30">
         <v>46063</v>
       </c>
-      <c r="K48">
+      <c r="K49">
         <f t="shared" ca="1" si="10"/>
-        <v>6.07</v>
-      </c>
-      <c r="L48">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="L49">
         <f t="shared" ca="1" si="11"/>
-        <v>10.399999999999977</v>
-      </c>
-      <c r="M48">
+        <v>8.8000000000000114</v>
+      </c>
+      <c r="M49">
         <f t="shared" ca="1" si="12"/>
-        <v>1.6000000000000227</v>
-      </c>
-      <c r="N48">
+        <v>8.5499999999999829</v>
+      </c>
+      <c r="N49">
         <f t="shared" ca="1" si="7"/>
-        <v>8.4999999999999716</v>
-      </c>
-      <c r="O48">
+        <v>7.0500000000000114</v>
+      </c>
+      <c r="O49">
         <f t="shared" ca="1" si="8"/>
-        <v>5.5999999999999659</v>
-      </c>
-      <c r="P48">
+        <v>11.550000000000011</v>
+      </c>
+      <c r="P49">
         <f t="shared" ca="1" si="9"/>
-        <v>4.25</v>
-      </c>
-      <c r="R48" s="1"/>
-      <c r="S48" s="29">
+        <v>7.1500000000000057</v>
+      </c>
+      <c r="R49" s="1"/>
+      <c r="S49" s="29">
         <v>24</v>
       </c>
-      <c r="T48" s="1"/>
-      <c r="U48" s="1"/>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>77</v>
       </c>
-      <c r="B49" s="22" t="s">
+      <c r="B50" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C49" s="22">
+      <c r="C50" s="22">
         <v>2.71</v>
       </c>
-      <c r="D49" s="25">
-        <f>C49/10</f>
+      <c r="D50" s="25">
+        <f>C50/10</f>
         <v>0.27100000000000002</v>
       </c>
-      <c r="E49" s="22">
+      <c r="E50" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F49" s="22">
+      <c r="F50" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G49" s="26">
+      <c r="G50" s="26">
         <f t="shared" si="18"/>
         <v>923</v>
       </c>
-      <c r="H49" s="22">
-        <f>ROUND(D49/E49,0)</f>
+      <c r="H50" s="22">
+        <f>ROUND(D50/E50,0)</f>
         <v>54</v>
       </c>
-      <c r="I49" s="24"/>
-      <c r="J49" s="30">
+      <c r="I50" s="24"/>
+      <c r="J50" s="30">
         <v>46069</v>
       </c>
-      <c r="K49">
+      <c r="K50">
         <f t="shared" ca="1" si="10"/>
-        <v>1.78</v>
-      </c>
-      <c r="L49">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="L50">
         <f t="shared" ca="1" si="11"/>
-        <v>2.2800000000000011</v>
-      </c>
-      <c r="M49">
+        <v>2.7750000000000057</v>
+      </c>
+      <c r="M50">
         <f t="shared" ca="1" si="12"/>
-        <v>0.40999999999999659</v>
-      </c>
-      <c r="N49">
+        <v>2.0949999999999989</v>
+      </c>
+      <c r="N50">
         <f t="shared" ca="1" si="7"/>
-        <v>1.5600000000000023</v>
-      </c>
-      <c r="O49">
+        <v>2.1799999999999926</v>
+      </c>
+      <c r="O50">
         <f t="shared" ca="1" si="8"/>
-        <v>1.5400000000000063</v>
-      </c>
-      <c r="P49">
+        <v>5.9300000000000068</v>
+      </c>
+      <c r="P50">
         <f t="shared" ca="1" si="9"/>
-        <v>3.125</v>
-      </c>
-      <c r="R49" s="29">
+        <v>11.484999999999999</v>
+      </c>
+      <c r="R50" s="29">
         <v>19</v>
       </c>
-      <c r="S49" s="29">
+      <c r="S50" s="29">
         <v>122</v>
       </c>
-      <c r="T49" s="1"/>
-      <c r="U49" s="1"/>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B50" s="1" t="s">
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B51" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C50" s="22">
+      <c r="C51" s="22">
         <v>46.6</v>
       </c>
-      <c r="D50" s="25">
-        <f>C50/10</f>
+      <c r="D51" s="25">
+        <f>C51/10</f>
         <v>4.66</v>
       </c>
-      <c r="E50" s="22">
+      <c r="E51" s="22">
         <v>0.5</v>
       </c>
-      <c r="F50" s="22">
+      <c r="F51" s="22">
         <v>0.5</v>
       </c>
-      <c r="G50" s="26">
+      <c r="G51" s="26">
         <f t="shared" si="18"/>
         <v>54</v>
       </c>
-      <c r="H50" s="22">
-        <f>ROUND(D50/E50,0)</f>
+      <c r="H51" s="22">
+        <f>ROUND(D51/E51,0)</f>
         <v>9</v>
       </c>
-      <c r="I50" s="24"/>
-      <c r="J50" s="30">
-        <v>46133</v>
-      </c>
-      <c r="K50">
-        <f t="shared" ca="1" si="10"/>
-        <v>26</v>
-      </c>
-      <c r="L50">
-        <f t="shared" ca="1" si="11"/>
-        <v>40.5</v>
-      </c>
-      <c r="M50">
-        <f t="shared" ca="1" si="12"/>
-        <v>12.5</v>
-      </c>
-      <c r="N50">
-        <f t="shared" ca="1" si="7"/>
-        <v>40</v>
-      </c>
-      <c r="O50">
-        <f t="shared" ca="1" si="8"/>
-        <v>18.5</v>
-      </c>
-      <c r="P50">
-        <f t="shared" ca="1" si="9"/>
-        <v>18.5</v>
-      </c>
-      <c r="R50" s="1"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="1"/>
-      <c r="U50" s="1"/>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B51" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C51" s="1">
-        <v>120.3</v>
-      </c>
-      <c r="D51" s="25">
-        <f t="shared" ref="D51:D54" si="20">C51/10</f>
-        <v>12.03</v>
-      </c>
-      <c r="E51" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="F51" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="G51" s="26">
-        <f t="shared" ref="G51:G54" si="21">ROUND($C$4/(D51/E51*F51),0)</f>
-        <v>21</v>
-      </c>
-      <c r="H51" s="22">
-        <f t="shared" ref="H51:H54" si="22">ROUND(D51/E51,0)</f>
-        <v>24</v>
-      </c>
-      <c r="I51" s="23"/>
+      <c r="I51" s="24"/>
       <c r="J51" s="30">
         <v>46133</v>
       </c>
       <c r="K51">
         <f t="shared" ca="1" si="10"/>
-        <v>90.4</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="L51">
         <f t="shared" ca="1" si="11"/>
-        <v>140.5</v>
+        <v>25</v>
       </c>
       <c r="M51">
         <f t="shared" ca="1" si="12"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N51">
         <f t="shared" ca="1" si="7"/>
-        <v>167</v>
+        <v>29</v>
       </c>
       <c r="O51">
         <f t="shared" ca="1" si="8"/>
-        <v>64.5</v>
+        <v>49.5</v>
       </c>
       <c r="P51">
         <f t="shared" ca="1" si="9"/>
-        <v>56</v>
-      </c>
-      <c r="R51" s="1">
+        <v>49.5</v>
+      </c>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B52" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52" s="1">
+        <v>120.3</v>
+      </c>
+      <c r="D52" s="25">
+        <f t="shared" ref="D52:D55" si="20">C52/10</f>
+        <v>12.03</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G52" s="26">
+        <f t="shared" ref="G52:G55" si="21">ROUND($C$4/(D52/E52*F52),0)</f>
+        <v>21</v>
+      </c>
+      <c r="H52" s="22">
+        <f t="shared" ref="H52:H55" si="22">ROUND(D52/E52,0)</f>
+        <v>24</v>
+      </c>
+      <c r="I52" s="23"/>
+      <c r="J52" s="30">
+        <v>46133</v>
+      </c>
+      <c r="K52">
+        <f t="shared" ca="1" si="10"/>
+        <v>65.2</v>
+      </c>
+      <c r="L52">
+        <f t="shared" ca="1" si="11"/>
+        <v>64</v>
+      </c>
+      <c r="M52">
+        <f t="shared" ca="1" si="12"/>
+        <v>38</v>
+      </c>
+      <c r="N52">
+        <f t="shared" ca="1" si="7"/>
+        <v>46</v>
+      </c>
+      <c r="O52">
+        <f t="shared" ca="1" si="8"/>
+        <v>115.5</v>
+      </c>
+      <c r="P52">
+        <f t="shared" ca="1" si="9"/>
+        <v>62.5</v>
+      </c>
+      <c r="R52" s="1">
         <v>-97</v>
       </c>
-      <c r="S51" s="25">
+      <c r="S52" s="25">
         <v>-176</v>
       </c>
-      <c r="T51" s="29">
+      <c r="T52" s="29">
         <v>11</v>
       </c>
-      <c r="U51" s="1"/>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B52" s="27" t="s">
+      <c r="U52" s="1"/>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B53" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="C52" s="22">
+      <c r="C53" s="22">
         <v>60</v>
       </c>
-      <c r="D52" s="25">
+      <c r="D53" s="25">
         <f t="shared" si="20"/>
         <v>6</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E53" s="1">
         <v>0.05</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F53" s="1">
         <v>0.5</v>
       </c>
-      <c r="G52" s="26">
+      <c r="G53" s="26">
         <f t="shared" si="21"/>
         <v>4</v>
       </c>
-      <c r="H52" s="22">
+      <c r="H53" s="22">
         <f t="shared" si="22"/>
         <v>120</v>
       </c>
-      <c r="I52" s="23"/>
-      <c r="R52" s="1"/>
-      <c r="S52" s="25">
+      <c r="I53" s="23"/>
+      <c r="R53" s="1"/>
+      <c r="S53" s="25">
         <v>-489</v>
       </c>
-      <c r="T52" s="29">
+      <c r="T53" s="29">
         <v>255</v>
       </c>
-      <c r="U52" s="1"/>
-    </row>
-    <row r="53" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="27" t="s">
+      <c r="U53" s="1"/>
+    </row>
+    <row r="54" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C53" s="22">
+      <c r="C54" s="22">
         <v>0.1</v>
       </c>
-      <c r="D53" s="25">
+      <c r="D54" s="25">
         <f t="shared" si="20"/>
         <v>0.01</v>
       </c>
-      <c r="E53" s="22">
+      <c r="E54" s="22">
         <v>1E-3</v>
       </c>
-      <c r="F53" s="22">
+      <c r="F54" s="22">
         <v>1</v>
       </c>
-      <c r="G53" s="26">
+      <c r="G54" s="26">
         <f t="shared" si="21"/>
         <v>25</v>
       </c>
-      <c r="H53" s="22">
+      <c r="H54" s="22">
         <f t="shared" si="22"/>
         <v>10</v>
       </c>
-      <c r="I53" s="24"/>
-      <c r="R53" s="29">
+      <c r="I54" s="24"/>
+      <c r="R54" s="29">
         <v>445</v>
       </c>
-      <c r="S53" s="25">
+      <c r="S54" s="25">
         <v>-21</v>
       </c>
-      <c r="T53" s="29">
+      <c r="T54" s="29">
         <v>125</v>
       </c>
-      <c r="U53" s="1"/>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B54" s="27" t="s">
+      <c r="U54" s="1"/>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B55" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="C54" s="22">
+      <c r="C55" s="22">
         <v>550</v>
       </c>
-      <c r="D54" s="25">
+      <c r="D55" s="25">
         <f t="shared" si="20"/>
         <v>55</v>
       </c>
-      <c r="E54" s="22">
+      <c r="E55" s="22">
         <v>1</v>
       </c>
-      <c r="F54" s="22">
+      <c r="F55" s="22">
         <v>1</v>
       </c>
-      <c r="G54" s="26">
+      <c r="G55" s="26">
         <f t="shared" si="21"/>
         <v>5</v>
       </c>
-      <c r="H54" s="22">
+      <c r="H55" s="22">
         <f t="shared" si="22"/>
         <v>55</v>
       </c>
-      <c r="I54" s="24"/>
-      <c r="M54" t="e">
-        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/futures/markets/forts/securities/"&amp;B54&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/futures/markets/forts/securities/"&amp;B54&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
+      <c r="I55" s="24"/>
+      <c r="M55" t="e">
+        <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/futures/markets/forts/securities/"&amp;B55&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/futures/markets/forts/securities/"&amp;B55&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R54" s="29">
+      <c r="R55" s="29">
         <v>459</v>
       </c>
-      <c r="S54" s="29">
+      <c r="S55" s="29">
         <v>596</v>
       </c>
-      <c r="T54" s="25">
+      <c r="T55" s="25">
         <v>-455</v>
       </c>
-      <c r="U54" s="1"/>
+      <c r="U55" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4710,7 +4771,7 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C2" s="34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D2" s="34"/>
       <c r="E2" s="34"/>
@@ -4752,7 +4813,9 @@
       <c r="I3" s="33">
         <v>46135</v>
       </c>
-      <c r="J3" s="1"/>
+      <c r="J3" s="33">
+        <v>46148</v>
+      </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -4770,7 +4833,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" s="1">
         <v>46</v>
@@ -4788,7 +4851,9 @@
       <c r="I4" s="1">
         <v>46</v>
       </c>
-      <c r="J4" s="1"/>
+      <c r="J4" s="1">
+        <v>132</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -4803,10 +4868,10 @@
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5" s="1">
         <v>50</v>
@@ -4818,7 +4883,9 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+      <c r="J5" s="1">
+        <v>48</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -4833,10 +4900,10 @@
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="1">
         <v>60</v>
@@ -4852,7 +4919,9 @@
         <v>45</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+      <c r="J6" s="1">
+        <v>42</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -4870,7 +4939,7 @@
         <v>73</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D7" s="1">
         <v>61</v>
@@ -4900,7 +4969,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1">
@@ -4932,7 +5001,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -4959,10 +5028,10 @@
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>

--- a/calc.xlsx
+++ b/calc.xlsx
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M6" s="5" t="str">
         <f ca="1">TEXT(M7,"ддд")</f>
-        <v>Пт</v>
+        <v>Ср</v>
       </c>
       <c r="N6" s="5" t="str">
         <f t="shared" ref="N6:P6" ca="1" si="0">TEXT(N7,"ддд")</f>
-        <v>Пн</v>
+        <v>Вт</v>
       </c>
       <c r="O6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Ср</v>
+        <v>Пн</v>
       </c>
       <c r="P6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Вт</v>
+        <v>Пт</v>
       </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.25">
@@ -1889,24 +1889,24 @@
         <v>78</v>
       </c>
       <c r="L7" s="1" t="str">
-        <f ca="1">TEXT(TODAY()-5, "ГГГГ-ММ-ДД")</f>
-        <v>2026-05-28</v>
+        <f ca="1">TEXT(TODAY()-1, "ГГГГ-ММ-ДД")</f>
+        <v>2026-07-23</v>
       </c>
       <c r="M7" s="1" t="str">
+        <f ca="1">TEXT(TODAY()-2, "ГГГГ-ММ-ДД")</f>
+        <v>2026-07-22</v>
+      </c>
+      <c r="N7" s="1" t="str">
+        <f ca="1">TEXT(TODAY()-3, "ГГГГ-ММ-ДД")</f>
+        <v>2026-07-21</v>
+      </c>
+      <c r="O7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-4, "ГГГГ-ММ-ДД")</f>
-        <v>2026-05-29</v>
-      </c>
-      <c r="N7" s="1" t="str">
-        <f ca="1">TEXT(TODAY()-1, "ГГГГ-ММ-ДД")</f>
-        <v>2026-06-01</v>
-      </c>
-      <c r="O7" s="1" t="str">
-        <f ca="1">TEXT(TODAY()-6, "ГГГГ-ММ-ДД")</f>
-        <v>2026-05-27</v>
+        <v>2026-07-20</v>
       </c>
       <c r="P7" s="1" t="str">
         <f ca="1">TEXT(TODAY()-7, "ГГГГ-ММ-ДД")</f>
-        <v>2026-05-26</v>
+        <v>2026-07-17</v>
       </c>
       <c r="R7" s="28">
         <v>45566</v>
@@ -1926,11 +1926,11 @@
         <v>46</v>
       </c>
       <c r="C8" s="22">
-        <v>0.35</v>
+        <v>0.8</v>
       </c>
       <c r="D8" s="25">
         <f t="shared" ref="D8:D30" si="1">C8/10</f>
-        <v>3.4999999999999996E-2</v>
+        <v>0.08</v>
       </c>
       <c r="E8" s="22">
         <v>1E-3</v>
@@ -1940,39 +1940,39 @@
       </c>
       <c r="G8" s="26">
         <f t="shared" ref="G8:G30" si="2">ROUND($C$4/(D8/E8*F8),0)</f>
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="H8" s="22">
         <f t="shared" ref="H8:H21" si="3">ROUND(D8/E8,0)</f>
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="30">
-        <v>46135</v>
+        <v>46227</v>
       </c>
       <c r="K8">
         <f t="shared" ref="K8:K13" ca="1" si="4">ROUND(AVERAGE(L8:P8),2)</f>
-        <v>5895.08</v>
+        <v>9229.2199999999993</v>
       </c>
       <c r="L8">
         <f t="shared" ref="L8:L13" ca="1" si="5">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.90200000000000102</v>
+        <v>46142.569000000003</v>
       </c>
       <c r="M8">
         <f t="shared" ref="M8:M13" ca="1" si="6">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>-16729.837</v>
+        <v>0.60800000000000054</v>
       </c>
       <c r="N8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>46203.107000000004</v>
+        <v>0.74600000000000044</v>
       </c>
       <c r="O8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.46200000000000152</v>
+        <v>1.2939999999999996</v>
       </c>
       <c r="P8">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B8&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.77500000000000036</v>
+        <v>0.90599999999999881</v>
       </c>
       <c r="R8" s="29">
         <v>54</v>
@@ -2016,27 +2016,27 @@
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="4"/>
-        <v>1.51</v>
+        <v>-9275.27</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="5"/>
-        <v>1.0399999999999991</v>
+        <v>1.1600000000000001</v>
       </c>
       <c r="M9">
         <f t="shared" ca="1" si="6"/>
-        <v>2.5200000000000031</v>
+        <v>-46354.28</v>
       </c>
       <c r="N9">
         <f t="shared" ref="N9:N52" ca="1" si="7">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$N$7&amp;"&amp;till="&amp;$N$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.5300000000000011</v>
+        <v>1.509999999999998</v>
       </c>
       <c r="O9">
         <f t="shared" ref="O9:O52" ca="1" si="8">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$O$7&amp;"&amp;till="&amp;$O$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>0.94000000000000483</v>
+        <v>-46199.87</v>
       </c>
       <c r="P9">
         <f t="shared" ref="P9:P52" ca="1" si="9">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B9&amp;"/candles.xml?from="&amp;$P$7&amp;"&amp;till="&amp;$P$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>1.5300000000000011</v>
+        <v>46175.15</v>
       </c>
       <c r="R9" s="25">
         <v>-30</v>
@@ -2077,27 +2077,27 @@
       <c r="I10" s="24"/>
       <c r="K10">
         <f t="shared" ca="1" si="4"/>
-        <v>9180.76</v>
+        <v>1.89</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="5"/>
-        <v>1.1999999999999993</v>
+        <v>1.5599999999999987</v>
       </c>
       <c r="M10">
         <f t="shared" ca="1" si="6"/>
-        <v>1.4200000000000017</v>
+        <v>1.0599999999999987</v>
       </c>
       <c r="N10">
         <f t="shared" ca="1" si="7"/>
-        <v>46053.59</v>
+        <v>2.91</v>
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="8"/>
-        <v>-153</v>
+        <v>3.09</v>
       </c>
       <c r="P10">
         <f t="shared" ca="1" si="9"/>
-        <v>0.58000000000000185</v>
+        <v>0.80999999999999872</v>
       </c>
       <c r="R10" s="29">
         <v>39</v>
@@ -2141,27 +2141,27 @@
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="4"/>
-        <v>15.63</v>
+        <v>20.74</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="5"/>
-        <v>2.25</v>
+        <v>11.849999999999994</v>
       </c>
       <c r="M11">
         <f t="shared" ca="1" si="6"/>
-        <v>12.550000000000011</v>
+        <v>11.800000000000011</v>
       </c>
       <c r="N11">
         <f t="shared" ca="1" si="7"/>
-        <v>51.849999999999994</v>
+        <v>29.649999999999977</v>
       </c>
       <c r="O11">
         <f t="shared" ca="1" si="8"/>
-        <v>5.75</v>
+        <v>30.649999999999977</v>
       </c>
       <c r="P11">
         <f t="shared" ca="1" si="9"/>
-        <v>5.75</v>
+        <v>19.750000000000014</v>
       </c>
       <c r="R11" s="29"/>
       <c r="S11" s="29"/>
@@ -2199,27 +2199,27 @@
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="4"/>
-        <v>4.29</v>
+        <v>16.32</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="5"/>
-        <v>6.589999999999975</v>
+        <v>9.0999999999999943</v>
       </c>
       <c r="M12">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>7.9699999999999989</v>
       </c>
       <c r="N12">
         <f t="shared" ca="1" si="7"/>
-        <v>2.3899999999999864</v>
+        <v>14.200000000000017</v>
       </c>
       <c r="O12">
         <f t="shared" ca="1" si="8"/>
-        <v>3.8100000000000023</v>
+        <v>29.319999999999993</v>
       </c>
       <c r="P12">
         <f t="shared" ca="1" si="9"/>
-        <v>5.6700000000000159</v>
+        <v>21</v>
       </c>
       <c r="R12" s="29"/>
       <c r="S12" s="29"/>
@@ -2257,27 +2257,27 @@
       </c>
       <c r="K13" s="24">
         <f t="shared" ca="1" si="4"/>
-        <v>1.46</v>
+        <v>-18472.43</v>
       </c>
       <c r="L13" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>1.8500000000000014</v>
       </c>
       <c r="M13" s="24">
         <f t="shared" ca="1" si="6"/>
-        <v>0.54999999999999716</v>
+        <v>2.7999999999999972</v>
       </c>
       <c r="N13" s="24">
         <f t="shared" ca="1" si="7"/>
-        <v>2.7999999999999972</v>
+        <v>2.6499999999999986</v>
       </c>
       <c r="O13" s="24">
         <f t="shared" ca="1" si="8"/>
-        <v>0.75</v>
+        <v>-46229.9</v>
       </c>
       <c r="P13" s="24">
         <f t="shared" ca="1" si="9"/>
-        <v>2.1999999999999957</v>
+        <v>-46139.55</v>
       </c>
       <c r="R13" s="29"/>
       <c r="S13" s="29"/>
@@ -2289,11 +2289,11 @@
         <v>43</v>
       </c>
       <c r="C14" s="1">
-        <v>20</v>
+        <v>32.6</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3.2600000000000002</v>
       </c>
       <c r="E14" s="1">
         <v>0.2</v>
@@ -2303,39 +2303,39 @@
       </c>
       <c r="G14" s="26">
         <f t="shared" si="2"/>
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="H14" s="22">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I14" s="23"/>
       <c r="J14" s="30">
-        <v>46135</v>
+        <v>46227</v>
       </c>
       <c r="K14">
         <f t="shared" ref="K14:K52" ca="1" si="10">ROUND(AVERAGE(L14:P14),2)</f>
-        <v>18.079999999999998</v>
+        <v>33.04</v>
       </c>
       <c r="L14">
         <f t="shared" ref="L14:L52" ca="1" si="11">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>24</v>
+        <v>27.399999999999977</v>
       </c>
       <c r="M14">
         <f t="shared" ref="M14:M52" ca="1" si="12">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B14&amp;"/candles.xml?from="&amp;$M$7&amp;"&amp;till="&amp;$M$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>12.399999999999977</v>
+        <v>28.600000000000023</v>
       </c>
       <c r="N14">
         <f t="shared" ca="1" si="7"/>
-        <v>14</v>
+        <v>34.799999999999955</v>
       </c>
       <c r="O14">
         <f t="shared" ca="1" si="8"/>
-        <v>13.200000000000045</v>
+        <v>47</v>
       </c>
       <c r="P14">
         <f t="shared" ca="1" si="9"/>
-        <v>26.799999999999955</v>
+        <v>27.399999999999977</v>
       </c>
       <c r="R14" s="29">
         <v>80</v>
@@ -2379,27 +2379,27 @@
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="10"/>
-        <v>47.64</v>
+        <v>83.8</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="11"/>
-        <v>57.800000000000182</v>
+        <v>32.5</v>
       </c>
       <c r="M15">
         <f t="shared" ca="1" si="12"/>
-        <v>48.599999999999909</v>
+        <v>48.900000000000091</v>
       </c>
       <c r="N15">
         <f t="shared" ca="1" si="7"/>
-        <v>21.599999999999909</v>
+        <v>75.400000000000091</v>
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="8"/>
-        <v>47.300000000000182</v>
+        <v>177.80000000000018</v>
       </c>
       <c r="P15">
         <f t="shared" ca="1" si="9"/>
-        <v>62.900000000000091</v>
+        <v>84.399999999999864</v>
       </c>
       <c r="R15" s="22"/>
       <c r="S15" s="22"/>
@@ -2434,27 +2434,27 @@
       <c r="I16" s="24"/>
       <c r="K16">
         <f t="shared" ca="1" si="10"/>
-        <v>2.37</v>
+        <v>5.31</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="11"/>
-        <v>1.8199999999999932</v>
+        <v>5.1900000000000119</v>
       </c>
       <c r="M16">
         <f t="shared" ca="1" si="12"/>
-        <v>2.7599999999999909</v>
+        <v>4.1099999999999994</v>
       </c>
       <c r="N16">
         <f t="shared" ca="1" si="7"/>
-        <v>2.4699999999999989</v>
+        <v>5.3400000000000034</v>
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="8"/>
-        <v>2.4300000000000068</v>
+        <v>7.6899999999999977</v>
       </c>
       <c r="P16">
         <f t="shared" ca="1" si="9"/>
-        <v>2.3599999999999994</v>
+        <v>4.1999999999999957</v>
       </c>
       <c r="R16" s="29">
         <v>27</v>
@@ -2493,27 +2493,27 @@
       <c r="I17" s="23"/>
       <c r="K17">
         <f t="shared" ca="1" si="10"/>
-        <v>2.19</v>
+        <v>12.77</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="11"/>
-        <v>2.3499999999999943</v>
+        <v>12.5</v>
       </c>
       <c r="M17">
         <f t="shared" ca="1" si="12"/>
-        <v>2.6500000000000057</v>
+        <v>5.8500000000000014</v>
       </c>
       <c r="N17">
         <f t="shared" ca="1" si="7"/>
-        <v>2.1000000000000085</v>
+        <v>15.049999999999997</v>
       </c>
       <c r="O17">
         <f t="shared" ca="1" si="8"/>
-        <v>1.5999999999999943</v>
+        <v>24.799999999999997</v>
       </c>
       <c r="P17">
         <f t="shared" ca="1" si="9"/>
-        <v>2.25</v>
+        <v>5.6499999999999986</v>
       </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
@@ -2551,27 +2551,27 @@
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="10"/>
-        <v>1.84</v>
+        <v>5.77</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="11"/>
-        <v>1.6299999999999955</v>
+        <v>2.9099999999999966</v>
       </c>
       <c r="M18">
         <f t="shared" ca="1" si="12"/>
-        <v>1.8999999999999915</v>
+        <v>6.9099999999999966</v>
       </c>
       <c r="N18">
         <f t="shared" ca="1" si="7"/>
-        <v>1.8400000000000034</v>
+        <v>4.4599999999999937</v>
       </c>
       <c r="O18">
         <f t="shared" ca="1" si="8"/>
-        <v>1.9500000000000028</v>
+        <v>7.1599999999999966</v>
       </c>
       <c r="P18">
         <f t="shared" ca="1" si="9"/>
-        <v>1.9000000000000057</v>
+        <v>7.4000000000000057</v>
       </c>
       <c r="R18" s="25">
         <v>-2</v>
@@ -2615,27 +2615,27 @@
       </c>
       <c r="K19">
         <f ca="1">ROUND(AVERAGE(L19:P19),5)</f>
-        <v>3.0400000000000002E-3</v>
+        <v>3.0100000000000001E-3</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="11"/>
-        <v>1.7800000000000038E-3</v>
+        <v>2.020000000000001E-3</v>
       </c>
       <c r="M19">
         <f t="shared" ca="1" si="12"/>
-        <v>1.8200000000000022E-3</v>
+        <v>3.5400000000000015E-3</v>
       </c>
       <c r="N19">
         <f t="shared" ca="1" si="7"/>
-        <v>2.2999999999999965E-3</v>
+        <v>3.599999999999999E-3</v>
       </c>
       <c r="O19">
         <f t="shared" ca="1" si="8"/>
-        <v>6.2199999999999964E-3</v>
+        <v>3.819999999999997E-3</v>
       </c>
       <c r="P19">
         <f t="shared" ca="1" si="9"/>
-        <v>3.0999999999999986E-3</v>
+        <v>2.0599999999999993E-3</v>
       </c>
       <c r="R19" s="25"/>
       <c r="S19" s="25"/>
@@ -2647,11 +2647,11 @@
         <v>56</v>
       </c>
       <c r="C20" s="22">
-        <v>4.4000000000000004</v>
+        <v>6.73</v>
       </c>
       <c r="D20" s="25">
         <f t="shared" si="13"/>
-        <v>0.44000000000000006</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="E20" s="22">
         <v>0.02</v>
@@ -2661,39 +2661,39 @@
       </c>
       <c r="G20" s="26">
         <f t="shared" si="14"/>
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="H20" s="22">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I20" s="24"/>
       <c r="J20" s="30">
-        <v>46133</v>
+        <v>46227</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="10"/>
-        <v>3.22</v>
+        <v>6.73</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="11"/>
-        <v>2.8200000000000074</v>
+        <v>5.1400000000000006</v>
       </c>
       <c r="M20">
         <f t="shared" ca="1" si="12"/>
-        <v>3.3800000000000097</v>
+        <v>5.9000000000000057</v>
       </c>
       <c r="N20">
         <f t="shared" ca="1" si="7"/>
-        <v>2.6400000000000006</v>
+        <v>6.1599999999999966</v>
       </c>
       <c r="O20">
         <f t="shared" ca="1" si="8"/>
-        <v>2.8799999999999955</v>
+        <v>9.6199999999999903</v>
       </c>
       <c r="P20">
         <f t="shared" ca="1" si="9"/>
-        <v>4.4000000000000057</v>
+        <v>6.8400000000000034</v>
       </c>
       <c r="R20" s="25">
         <v>-211</v>
@@ -2732,27 +2732,27 @@
       <c r="I21" s="24"/>
       <c r="K21">
         <f t="shared" ca="1" si="10"/>
-        <v>-15790.33</v>
+        <v>33949.839999999997</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="11"/>
-        <v>3.6000000000000032E-2</v>
+        <v>-392270</v>
       </c>
       <c r="M21">
         <f t="shared" ca="1" si="12"/>
-        <v>-42426.815499999997</v>
+        <v>398115</v>
       </c>
       <c r="N21">
         <f t="shared" ca="1" si="7"/>
-        <v>5.8499999999999996E-2</v>
+        <v>0.1339999999999999</v>
       </c>
       <c r="O21">
         <f t="shared" ca="1" si="8"/>
-        <v>-36525</v>
+        <v>210045.908</v>
       </c>
       <c r="P21">
         <f t="shared" ca="1" si="9"/>
-        <v>6.4000000000000057E-2</v>
+        <v>-46141.828999999998</v>
       </c>
       <c r="R21" s="1"/>
       <c r="S21" s="25">
@@ -2766,11 +2766,11 @@
         <v>55</v>
       </c>
       <c r="C22" s="22">
-        <v>86.3</v>
+        <v>280</v>
       </c>
       <c r="D22" s="25">
         <f t="shared" si="13"/>
-        <v>8.629999999999999</v>
+        <v>28</v>
       </c>
       <c r="E22" s="22">
         <v>0.5</v>
@@ -2780,39 +2780,39 @@
       </c>
       <c r="G22" s="26">
         <f t="shared" si="14"/>
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="H22" s="22">
         <f t="shared" ref="H22:H46" si="15">ROUND(D22/E22,0)</f>
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="I22" s="24"/>
       <c r="J22" s="30">
-        <v>46133</v>
+        <v>46227</v>
       </c>
       <c r="K22">
         <f t="shared" ca="1" si="10"/>
-        <v>102.4</v>
+        <v>280.60000000000002</v>
       </c>
       <c r="L22">
         <f t="shared" ca="1" si="11"/>
-        <v>104.5</v>
+        <v>247</v>
       </c>
       <c r="M22">
         <f t="shared" ca="1" si="12"/>
-        <v>132</v>
+        <v>325</v>
       </c>
       <c r="N22">
         <f t="shared" ca="1" si="7"/>
-        <v>104.5</v>
+        <v>217</v>
       </c>
       <c r="O22">
         <f t="shared" ca="1" si="8"/>
-        <v>72</v>
+        <v>321.5</v>
       </c>
       <c r="P22">
         <f t="shared" ca="1" si="9"/>
-        <v>99</v>
+        <v>292.5</v>
       </c>
       <c r="R22" s="25">
         <v>-741</v>
@@ -2852,31 +2852,31 @@
       </c>
       <c r="I23" s="23"/>
       <c r="J23" s="30">
-        <v>46133</v>
+        <v>46227</v>
       </c>
       <c r="K23">
         <f t="shared" ca="1" si="10"/>
-        <v>0.95</v>
+        <v>18458.02</v>
       </c>
       <c r="L23">
         <f t="shared" ca="1" si="11"/>
-        <v>1.0599999999999987</v>
+        <v>1.0450000000000017</v>
       </c>
       <c r="M23">
         <f t="shared" ca="1" si="12"/>
-        <v>0.61000000000000298</v>
+        <v>1.0500000000000007</v>
       </c>
       <c r="N23">
         <f t="shared" ca="1" si="7"/>
-        <v>0.78500000000000014</v>
+        <v>46113.025000000001</v>
       </c>
       <c r="O23">
         <f t="shared" ca="1" si="8"/>
-        <v>0.7099999999999973</v>
+        <v>46174.084999999999</v>
       </c>
       <c r="P23">
         <f t="shared" ca="1" si="9"/>
-        <v>1.5899999999999999</v>
+        <v>0.87499999999999822</v>
       </c>
       <c r="R23" s="25">
         <v>-107</v>
@@ -2918,27 +2918,27 @@
       <c r="J24" s="30"/>
       <c r="K24">
         <f t="shared" ca="1" si="10"/>
-        <v>68.5</v>
+        <v>138.69999999999999</v>
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="11"/>
-        <v>82.5</v>
+        <v>91</v>
       </c>
       <c r="M24">
         <f t="shared" ca="1" si="12"/>
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="N24">
         <f t="shared" ca="1" si="7"/>
-        <v>46.5</v>
+        <v>138.5</v>
       </c>
       <c r="O24">
         <f t="shared" ca="1" si="8"/>
-        <v>68.5</v>
+        <v>178.5</v>
       </c>
       <c r="P24">
         <f t="shared" ca="1" si="9"/>
-        <v>93</v>
+        <v>194.5</v>
       </c>
       <c r="R24" s="29">
         <v>45</v>
@@ -2980,27 +2980,27 @@
       <c r="J25" s="30"/>
       <c r="K25">
         <f t="shared" ca="1" si="10"/>
-        <v>2.88</v>
+        <v>6.68</v>
       </c>
       <c r="L25">
         <f t="shared" ca="1" si="11"/>
-        <v>1.6599999999999966</v>
+        <v>5.1000000000000227</v>
       </c>
       <c r="M25">
         <f t="shared" ca="1" si="12"/>
-        <v>2.9399999999999977</v>
+        <v>5.2400000000000091</v>
       </c>
       <c r="N25">
         <f t="shared" ca="1" si="7"/>
-        <v>4.25</v>
+        <v>6.6599999999999966</v>
       </c>
       <c r="O25">
         <f t="shared" ca="1" si="8"/>
-        <v>3.3499999999999943</v>
+        <v>11.379999999999995</v>
       </c>
       <c r="P25">
         <f t="shared" ca="1" si="9"/>
-        <v>2.1799999999999784</v>
+        <v>5</v>
       </c>
       <c r="R25" s="25">
         <v>-146</v>
@@ -3042,27 +3042,27 @@
       <c r="J26" s="30"/>
       <c r="K26">
         <f t="shared" ca="1" si="10"/>
-        <v>3.36</v>
+        <v>-18464.97</v>
       </c>
       <c r="L26">
         <f t="shared" ca="1" si="11"/>
-        <v>3.3300000000000054</v>
+        <v>2.8100000000000023</v>
       </c>
       <c r="M26">
         <f t="shared" ca="1" si="12"/>
-        <v>4.3800000000000026</v>
+        <v>2.3699999999999974</v>
       </c>
       <c r="N26">
         <f t="shared" ca="1" si="7"/>
-        <v>3.1000000000000014</v>
+        <v>4.8999999999999986</v>
       </c>
       <c r="O26">
         <f t="shared" ca="1" si="8"/>
-        <v>1.5900000000000034</v>
+        <v>-46195.6</v>
       </c>
       <c r="P26">
         <f t="shared" ca="1" si="9"/>
-        <v>4.4100000000000037</v>
+        <v>-46139.33</v>
       </c>
       <c r="R26" s="25">
         <v>-6</v>
@@ -3106,27 +3106,27 @@
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="10"/>
-        <v>3.29</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="11"/>
-        <v>3.4499999999999886</v>
+        <v>7.0500000000000114</v>
       </c>
       <c r="M27">
         <f t="shared" ca="1" si="12"/>
-        <v>3.0500000000000114</v>
+        <v>6.4499999999999886</v>
       </c>
       <c r="N27">
         <f t="shared" ca="1" si="7"/>
-        <v>2.8000000000000114</v>
+        <v>11.550000000000011</v>
       </c>
       <c r="O27">
         <f t="shared" ca="1" si="8"/>
-        <v>3.75</v>
+        <v>10.349999999999994</v>
       </c>
       <c r="P27">
         <f t="shared" ca="1" si="9"/>
-        <v>3.4000000000000057</v>
+        <v>10.699999999999989</v>
       </c>
       <c r="R27" s="25">
         <v>-149</v>
@@ -3168,27 +3168,27 @@
       <c r="J28" s="30"/>
       <c r="K28">
         <f t="shared" ca="1" si="10"/>
-        <v>2.15</v>
+        <v>3.85</v>
       </c>
       <c r="L28">
         <f t="shared" ca="1" si="11"/>
-        <v>2.7199999999999989</v>
+        <v>3.6799999999999997</v>
       </c>
       <c r="M28">
         <f t="shared" ca="1" si="12"/>
-        <v>1.9200000000000017</v>
+        <v>2.8200000000000074</v>
       </c>
       <c r="N28">
         <f t="shared" ca="1" si="7"/>
-        <v>1.6600000000000108</v>
+        <v>3.240000000000002</v>
       </c>
       <c r="O28">
         <f t="shared" ca="1" si="8"/>
-        <v>2.019999999999996</v>
+        <v>5.9799999999999969</v>
       </c>
       <c r="P28">
         <f t="shared" ca="1" si="9"/>
-        <v>2.4200000000000017</v>
+        <v>3.5399999999999991</v>
       </c>
       <c r="R28" s="29">
         <v>23</v>
@@ -3206,11 +3206,11 @@
         <v>66</v>
       </c>
       <c r="C29" s="22">
-        <v>22.54</v>
+        <v>52</v>
       </c>
       <c r="D29" s="25">
         <f>C29/10</f>
-        <v>2.254</v>
+        <v>5.2</v>
       </c>
       <c r="E29" s="22">
         <v>0.1</v>
@@ -3220,11 +3220,11 @@
       </c>
       <c r="G29" s="26">
         <f>ROUND($C$4/(D29/E29*F29),0)</f>
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="H29" s="22">
         <f t="shared" si="15"/>
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="I29" s="24"/>
       <c r="J29" s="30">
@@ -3232,27 +3232,27 @@
       </c>
       <c r="K29">
         <f t="shared" ca="1" si="10"/>
-        <v>21.62</v>
+        <v>53.02</v>
       </c>
       <c r="L29">
         <f t="shared" ca="1" si="11"/>
-        <v>17.099999999999909</v>
+        <v>54.199999999999932</v>
       </c>
       <c r="M29">
         <f t="shared" ca="1" si="12"/>
-        <v>21.100000000000136</v>
+        <v>56</v>
       </c>
       <c r="N29">
         <f t="shared" ca="1" si="7"/>
-        <v>25.5</v>
+        <v>42</v>
       </c>
       <c r="O29">
         <f t="shared" ca="1" si="8"/>
-        <v>22.400000000000091</v>
+        <v>61</v>
       </c>
       <c r="P29">
         <f t="shared" ca="1" si="9"/>
-        <v>22</v>
+        <v>51.899999999999977</v>
       </c>
       <c r="R29" s="1"/>
       <c r="S29" s="29">
@@ -3292,27 +3292,27 @@
       </c>
       <c r="K30">
         <f t="shared" ca="1" si="10"/>
-        <v>96.3</v>
+        <v>227.1</v>
       </c>
       <c r="L30">
         <f t="shared" ca="1" si="11"/>
-        <v>103</v>
+        <v>121.5</v>
       </c>
       <c r="M30">
         <f t="shared" ca="1" si="12"/>
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="N30">
         <f t="shared" ca="1" si="7"/>
-        <v>68.5</v>
+        <v>164.5</v>
       </c>
       <c r="O30">
         <f t="shared" ca="1" si="8"/>
-        <v>95</v>
+        <v>465.5</v>
       </c>
       <c r="P30">
         <f t="shared" ca="1" si="9"/>
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="R30" s="25">
         <v>-6</v>
@@ -3353,27 +3353,27 @@
       <c r="I31" s="24"/>
       <c r="K31">
         <f t="shared" ca="1" si="10"/>
-        <v>40.36</v>
+        <v>65.760000000000005</v>
       </c>
       <c r="L31">
         <f t="shared" ca="1" si="11"/>
-        <v>36.600000000000023</v>
+        <v>43</v>
       </c>
       <c r="M31">
         <f t="shared" ca="1" si="12"/>
-        <v>44.600000000000023</v>
+        <v>65.799999999999955</v>
       </c>
       <c r="N31">
         <f t="shared" ca="1" si="7"/>
-        <v>28.200000000000045</v>
+        <v>85.199999999999932</v>
       </c>
       <c r="O31">
         <f t="shared" ca="1" si="8"/>
-        <v>48</v>
+        <v>91.800000000000068</v>
       </c>
       <c r="P31">
         <f t="shared" ca="1" si="9"/>
-        <v>44.399999999999977</v>
+        <v>43</v>
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="25">
@@ -3410,27 +3410,27 @@
       <c r="I32" s="24"/>
       <c r="K32">
         <f t="shared" ca="1" si="10"/>
-        <v>157.4</v>
+        <v>296.60000000000002</v>
       </c>
       <c r="L32">
         <f t="shared" ca="1" si="11"/>
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="M32">
         <f t="shared" ca="1" si="12"/>
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="N32">
         <f t="shared" ca="1" si="7"/>
-        <v>318</v>
+        <v>287</v>
       </c>
       <c r="O32">
         <f t="shared" ca="1" si="8"/>
-        <v>91</v>
+        <v>546</v>
       </c>
       <c r="P32">
         <f t="shared" ca="1" si="9"/>
-        <v>103</v>
+        <v>247</v>
       </c>
       <c r="R32" s="25">
         <v>-31</v>
@@ -3472,27 +3472,27 @@
       </c>
       <c r="K33">
         <f t="shared" ca="1" si="10"/>
-        <v>2.88</v>
+        <v>26.94</v>
       </c>
       <c r="L33">
         <f t="shared" ca="1" si="11"/>
-        <v>2.8999999999999773</v>
+        <v>29.5</v>
       </c>
       <c r="M33">
         <f t="shared" ca="1" si="12"/>
-        <v>2.5</v>
+        <v>14.600000000000023</v>
       </c>
       <c r="N33">
         <f t="shared" ca="1" si="7"/>
-        <v>3.8000000000000682</v>
+        <v>21.100000000000023</v>
       </c>
       <c r="O33">
         <f t="shared" ca="1" si="8"/>
-        <v>2.8999999999999773</v>
+        <v>41.699999999999932</v>
       </c>
       <c r="P33">
         <f t="shared" ca="1" si="9"/>
-        <v>2.2999999999999545</v>
+        <v>27.799999999999955</v>
       </c>
       <c r="R33" s="1"/>
       <c r="S33" s="29">
@@ -3508,11 +3508,11 @@
         <v>58</v>
       </c>
       <c r="C34" s="22">
-        <v>57.2</v>
+        <v>130</v>
       </c>
       <c r="D34" s="25">
         <f t="shared" si="16"/>
-        <v>5.7200000000000006</v>
+        <v>13</v>
       </c>
       <c r="E34" s="22">
         <v>0.2</v>
@@ -3522,39 +3522,39 @@
       </c>
       <c r="G34" s="26">
         <f t="shared" si="17"/>
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="H34" s="22">
         <f t="shared" si="15"/>
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="I34" s="24"/>
       <c r="J34" s="30">
-        <v>46133</v>
+        <v>46227</v>
       </c>
       <c r="K34">
         <f t="shared" ca="1" si="10"/>
-        <v>36.28</v>
+        <v>130.80000000000001</v>
       </c>
       <c r="L34">
         <f t="shared" ca="1" si="11"/>
-        <v>27.599999999999909</v>
+        <v>89.400000000000091</v>
       </c>
       <c r="M34">
         <f t="shared" ca="1" si="12"/>
-        <v>27.800000000000182</v>
+        <v>186.20000000000005</v>
       </c>
       <c r="N34">
         <f t="shared" ca="1" si="7"/>
-        <v>49</v>
+        <v>128.60000000000014</v>
       </c>
       <c r="O34">
         <f t="shared" ca="1" si="8"/>
-        <v>44</v>
+        <v>108.40000000000009</v>
       </c>
       <c r="P34">
         <f t="shared" ca="1" si="9"/>
-        <v>33</v>
+        <v>141.40000000000009</v>
       </c>
       <c r="R34" s="25">
         <v>-68</v>
@@ -3593,27 +3593,27 @@
       <c r="I35" s="24"/>
       <c r="K35">
         <f t="shared" ca="1" si="10"/>
-        <v>4.62</v>
+        <v>5.8</v>
       </c>
       <c r="L35">
         <f t="shared" ca="1" si="11"/>
-        <v>5.1000000000000085</v>
+        <v>5.8500000000000085</v>
       </c>
       <c r="M35">
         <f t="shared" ca="1" si="12"/>
-        <v>6.8999999999999915</v>
+        <v>6.0499999999999972</v>
       </c>
       <c r="N35">
         <f t="shared" ca="1" si="7"/>
-        <v>6.5</v>
+        <v>5.9000000000000057</v>
       </c>
       <c r="O35">
         <f t="shared" ca="1" si="8"/>
-        <v>1.7000000000000028</v>
+        <v>7.1000000000000085</v>
       </c>
       <c r="P35">
         <f t="shared" ca="1" si="9"/>
-        <v>2.9000000000000057</v>
+        <v>4.1000000000000085</v>
       </c>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
@@ -3627,11 +3627,11 @@
         <v>49</v>
       </c>
       <c r="C36" s="22">
-        <v>6.34</v>
+        <v>20.29</v>
       </c>
       <c r="D36" s="25">
         <f t="shared" si="16"/>
-        <v>0.63400000000000001</v>
+        <v>2.0289999999999999</v>
       </c>
       <c r="E36" s="22">
         <v>0.05</v>
@@ -3641,39 +3641,39 @@
       </c>
       <c r="G36" s="26">
         <f t="shared" si="17"/>
-        <v>394</v>
+        <v>123</v>
       </c>
       <c r="H36" s="22">
         <f t="shared" si="15"/>
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="I36" s="23"/>
       <c r="J36" s="30">
-        <v>46133</v>
+        <v>46227</v>
       </c>
       <c r="K36">
         <f t="shared" ca="1" si="10"/>
-        <v>7.69</v>
+        <v>20.29</v>
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="11"/>
-        <v>12.200000000000045</v>
+        <v>14.800000000000011</v>
       </c>
       <c r="M36">
         <f t="shared" ca="1" si="12"/>
-        <v>8</v>
+        <v>28.649999999999977</v>
       </c>
       <c r="N36">
         <f t="shared" ca="1" si="7"/>
-        <v>5.8000000000000114</v>
+        <v>16.550000000000011</v>
       </c>
       <c r="O36">
         <f t="shared" ca="1" si="8"/>
-        <v>6.5</v>
+        <v>26.75</v>
       </c>
       <c r="P36">
         <f t="shared" ca="1" si="9"/>
-        <v>5.9499999999999886</v>
+        <v>14.699999999999989</v>
       </c>
       <c r="R36" s="29">
         <v>342</v>
@@ -3717,27 +3717,27 @@
       </c>
       <c r="K37">
         <f t="shared" ca="1" si="10"/>
-        <v>1.2</v>
+        <v>18476.87</v>
       </c>
       <c r="L37">
         <f t="shared" ca="1" si="11"/>
-        <v>1.1950000000000003</v>
+        <v>0.96499999999999986</v>
       </c>
       <c r="M37">
         <f t="shared" ca="1" si="12"/>
-        <v>1.0350000000000037</v>
+        <v>46113.165000000001</v>
       </c>
       <c r="N37">
         <f t="shared" ca="1" si="7"/>
-        <v>1.0949999999999989</v>
+        <v>1.5700000000000003</v>
       </c>
       <c r="O37">
         <f t="shared" ca="1" si="8"/>
-        <v>1.3349999999999937</v>
+        <v>2.745000000000001</v>
       </c>
       <c r="P37">
         <f t="shared" ca="1" si="9"/>
-        <v>1.3500000000000014</v>
+        <v>46265.885000000002</v>
       </c>
       <c r="R37" s="1"/>
       <c r="S37" s="25">
@@ -3751,11 +3751,11 @@
         <v>48</v>
       </c>
       <c r="C38" s="22">
-        <v>6</v>
+        <v>6.1999999999999886</v>
       </c>
       <c r="D38" s="25">
         <f t="shared" si="16"/>
-        <v>0.6</v>
+        <v>0.61999999999999889</v>
       </c>
       <c r="E38" s="22">
         <v>0.01</v>
@@ -3765,39 +3765,39 @@
       </c>
       <c r="G38" s="26">
         <f t="shared" si="17"/>
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="H38" s="22">
         <f t="shared" si="15"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I38" s="23"/>
       <c r="J38" s="30">
-        <v>46133</v>
+        <v>46197</v>
       </c>
       <c r="K38">
         <f t="shared" ca="1" si="10"/>
-        <v>2.74</v>
+        <v>9.59</v>
       </c>
       <c r="L38">
         <f t="shared" ca="1" si="11"/>
-        <v>2.1999999999999886</v>
+        <v>4.0600000000000023</v>
       </c>
       <c r="M38">
         <f t="shared" ca="1" si="12"/>
-        <v>3.1699999999999591</v>
+        <v>6.1999999999999886</v>
       </c>
       <c r="N38">
         <f t="shared" ca="1" si="7"/>
-        <v>2.1300000000000523</v>
+        <v>10.650000000000034</v>
       </c>
       <c r="O38">
         <f t="shared" ca="1" si="8"/>
-        <v>3.7699999999999818</v>
+        <v>17.370000000000005</v>
       </c>
       <c r="P38">
         <f t="shared" ca="1" si="9"/>
-        <v>2.4499999999999886</v>
+        <v>9.6700000000000159</v>
       </c>
       <c r="R38" s="29">
         <v>32</v>
@@ -3841,27 +3841,27 @@
       </c>
       <c r="K39">
         <f t="shared" ca="1" si="10"/>
-        <v>42.36</v>
+        <v>90.8</v>
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="11"/>
-        <v>54.800000000000068</v>
+        <v>32.799999999999955</v>
       </c>
       <c r="M39">
         <f t="shared" ca="1" si="12"/>
-        <v>29</v>
+        <v>59.800000000000011</v>
       </c>
       <c r="N39">
         <f t="shared" ca="1" si="7"/>
-        <v>7.3999999999999773</v>
+        <v>136.59999999999997</v>
       </c>
       <c r="O39">
         <f t="shared" ca="1" si="8"/>
-        <v>43.600000000000023</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="P39">
         <f t="shared" ca="1" si="9"/>
-        <v>77</v>
+        <v>72.600000000000023</v>
       </c>
       <c r="R39" s="25">
         <v>-89</v>
@@ -3900,27 +3900,27 @@
       <c r="I40" s="24"/>
       <c r="K40">
         <f t="shared" ca="1" si="10"/>
-        <v>0.02</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L40">
         <f t="shared" ca="1" si="11"/>
-        <v>2.4500000000000077E-2</v>
+        <v>4.4999999999999984E-2</v>
       </c>
       <c r="M40">
         <f t="shared" ca="1" si="12"/>
-        <v>1.8500000000000072E-2</v>
+        <v>3.0999999999999972E-2</v>
       </c>
       <c r="N40">
         <f t="shared" ca="1" si="7"/>
-        <v>1.6000000000000014E-2</v>
+        <v>7.6500000000000012E-2</v>
       </c>
       <c r="O40">
         <f t="shared" ca="1" si="8"/>
-        <v>1.7500000000000071E-2</v>
+        <v>0.10600000000000004</v>
       </c>
       <c r="P40">
         <f t="shared" ca="1" si="9"/>
-        <v>2.4000000000000021E-2</v>
+        <v>6.6500000000000004E-2</v>
       </c>
       <c r="R40" s="29">
         <v>71</v>
@@ -3957,27 +3957,27 @@
       <c r="I41" s="24"/>
       <c r="K41">
         <f t="shared" ca="1" si="10"/>
-        <v>8.23</v>
+        <v>21.21</v>
       </c>
       <c r="L41">
         <f t="shared" ca="1" si="11"/>
-        <v>10.600000000000023</v>
+        <v>13.100000000000023</v>
       </c>
       <c r="M41">
         <f t="shared" ca="1" si="12"/>
-        <v>10</v>
+        <v>26.949999999999989</v>
       </c>
       <c r="N41">
         <f t="shared" ca="1" si="7"/>
-        <v>7.75</v>
+        <v>17.800000000000011</v>
       </c>
       <c r="O41">
         <f t="shared" ca="1" si="8"/>
-        <v>5.6000000000000227</v>
+        <v>26.600000000000023</v>
       </c>
       <c r="P41">
         <f t="shared" ca="1" si="9"/>
-        <v>7.2000000000000455</v>
+        <v>21.600000000000023</v>
       </c>
       <c r="R41" s="25">
         <v>-9</v>
@@ -3993,11 +3993,11 @@
         <v>69</v>
       </c>
       <c r="C42" s="22">
-        <v>45</v>
+        <v>38.28</v>
       </c>
       <c r="D42" s="25">
         <f>C42/10</f>
-        <v>4.5</v>
+        <v>3.8280000000000003</v>
       </c>
       <c r="E42" s="22">
         <v>0.2</v>
@@ -4007,39 +4007,39 @@
       </c>
       <c r="G42" s="26">
         <f>ROUND($C$4/(D42/E42*F42),0)</f>
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H42" s="22">
         <f t="shared" si="15"/>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I42" s="24"/>
       <c r="J42" s="30">
-        <v>46133</v>
+        <v>46227</v>
       </c>
       <c r="K42">
         <f t="shared" ca="1" si="10"/>
-        <v>31.84</v>
+        <v>38.28</v>
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="11"/>
-        <v>45</v>
+        <v>23.399999999999977</v>
       </c>
       <c r="M42">
         <f t="shared" ca="1" si="12"/>
-        <v>29</v>
+        <v>30.199999999999989</v>
       </c>
       <c r="N42">
         <f t="shared" ca="1" si="7"/>
-        <v>23</v>
+        <v>63.800000000000011</v>
       </c>
       <c r="O42">
         <f t="shared" ca="1" si="8"/>
-        <v>25.599999999999966</v>
+        <v>47.399999999999977</v>
       </c>
       <c r="P42">
         <f t="shared" ca="1" si="9"/>
-        <v>36.600000000000023</v>
+        <v>26.599999999999994</v>
       </c>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
@@ -4076,27 +4076,27 @@
       <c r="I43" s="24"/>
       <c r="K43">
         <f t="shared" ca="1" si="10"/>
-        <v>-9246.34</v>
+        <v>0.85</v>
       </c>
       <c r="L43">
         <f t="shared" ca="1" si="11"/>
-        <v>0.37000000000000099</v>
+        <v>0.66999999999999993</v>
       </c>
       <c r="M43">
         <f t="shared" ca="1" si="12"/>
-        <v>0.19500000000000028</v>
+        <v>0.8149999999999995</v>
       </c>
       <c r="N43">
         <f t="shared" ca="1" si="7"/>
-        <v>-46232.864999999998</v>
+        <v>0.63500000000000156</v>
       </c>
       <c r="O43">
         <f t="shared" ca="1" si="8"/>
-        <v>0.30000000000000071</v>
+        <v>1.3200000000000003</v>
       </c>
       <c r="P43">
         <f t="shared" ca="1" si="9"/>
-        <v>0.32000000000000028</v>
+        <v>0.82499999999999929</v>
       </c>
     </row>
     <row r="44" spans="2:21" x14ac:dyDescent="0.25">
@@ -4126,31 +4126,31 @@
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="30">
-        <v>46133</v>
+        <v>46227</v>
       </c>
       <c r="K44">
         <f t="shared" ca="1" si="10"/>
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="L44">
         <f t="shared" ca="1" si="11"/>
-        <v>0.73499999999999943</v>
+        <v>1.1099999999999994</v>
       </c>
       <c r="M44">
         <f t="shared" ca="1" si="12"/>
-        <v>0.76500000000000057</v>
+        <v>1.1849999999999952</v>
       </c>
       <c r="N44">
         <f t="shared" ca="1" si="7"/>
-        <v>2.1000000000000014</v>
+        <v>1.3299999999999983</v>
       </c>
       <c r="O44">
         <f t="shared" ca="1" si="8"/>
-        <v>0.85999999999999943</v>
+        <v>2.105000000000004</v>
       </c>
       <c r="P44">
         <f t="shared" ca="1" si="9"/>
-        <v>0.66499999999999915</v>
+        <v>2.1749999999999972</v>
       </c>
       <c r="R44" s="25">
         <v>-18</v>
@@ -4191,27 +4191,27 @@
       <c r="I45" s="24"/>
       <c r="K45">
         <f t="shared" ca="1" si="10"/>
-        <v>12.7</v>
+        <v>34.82</v>
       </c>
       <c r="L45">
         <f ca="1">VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B45&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@high"),".",","))-VALUE(SUBSTITUTE(_xlfn.FILTERXML(_xlfn.WEBSERVICE("https://iss.moex.com/iss/engines/stock/markets/shares/securities/"&amp;B45&amp;"/candles.xml?from="&amp;$L$7&amp;"&amp;till="&amp;$L$7&amp;"&amp;interval=24"),"//document//data//rows//row/@low"),".",","))</f>
-        <v>10.799999999999955</v>
+        <v>33.599999999999966</v>
       </c>
       <c r="M45">
         <f t="shared" ca="1" si="12"/>
-        <v>11.5</v>
+        <v>38.100000000000023</v>
       </c>
       <c r="N45">
         <f t="shared" ca="1" si="7"/>
-        <v>11.100000000000023</v>
+        <v>28.5</v>
       </c>
       <c r="O45">
         <f t="shared" ca="1" si="8"/>
-        <v>14.600000000000023</v>
+        <v>34.900000000000034</v>
       </c>
       <c r="P45">
         <f t="shared" ca="1" si="9"/>
-        <v>15.5</v>
+        <v>39</v>
       </c>
       <c r="R45" s="25">
         <v>-114</v>
@@ -4250,27 +4250,27 @@
       <c r="I46" s="24"/>
       <c r="K46">
         <f t="shared" ca="1" si="10"/>
-        <v>3.66</v>
+        <v>6.12</v>
       </c>
       <c r="L46">
         <f t="shared" ca="1" si="11"/>
-        <v>5.4200000000000017</v>
+        <v>3.9799999999999969</v>
       </c>
       <c r="M46">
         <f t="shared" ca="1" si="12"/>
-        <v>2.1400000000000006</v>
+        <v>4.4799999999999969</v>
       </c>
       <c r="N46">
         <f t="shared" ca="1" si="7"/>
-        <v>3.1000000000000085</v>
+        <v>7.2800000000000011</v>
       </c>
       <c r="O46">
         <f t="shared" ca="1" si="8"/>
-        <v>2.1400000000000006</v>
+        <v>9.68</v>
       </c>
       <c r="P46">
         <f t="shared" ca="1" si="9"/>
-        <v>5.519999999999996</v>
+        <v>5.1599999999999966</v>
       </c>
       <c r="R46" s="29">
         <v>7</v>
@@ -4309,27 +4309,27 @@
       <c r="I47" s="24"/>
       <c r="K47">
         <f t="shared" ca="1" si="10"/>
-        <v>25.48</v>
+        <v>56.16</v>
       </c>
       <c r="L47">
         <f t="shared" ca="1" si="11"/>
-        <v>25.799999999999955</v>
+        <v>24.799999999999955</v>
       </c>
       <c r="M47">
         <f t="shared" ca="1" si="12"/>
-        <v>22.599999999999909</v>
+        <v>29.799999999999955</v>
       </c>
       <c r="N47">
         <f t="shared" ca="1" si="7"/>
-        <v>36</v>
+        <v>47.599999999999909</v>
       </c>
       <c r="O47">
         <f t="shared" ca="1" si="8"/>
-        <v>17.799999999999955</v>
+        <v>69.999999999999886</v>
       </c>
       <c r="P47">
         <f t="shared" ca="1" si="9"/>
-        <v>25.200000000000045</v>
+        <v>108.59999999999991</v>
       </c>
       <c r="R47" s="1"/>
       <c r="S47" s="25">
@@ -4345,11 +4345,11 @@
         <v>80</v>
       </c>
       <c r="C48" s="22">
-        <v>5.1400000000000001E-2</v>
+        <v>2.7799999999999998E-2</v>
       </c>
       <c r="D48" s="25">
         <f>ROUND(C48/10,4)</f>
-        <v>5.1000000000000004E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="E48" s="1">
         <v>1E-4</v>
@@ -4359,39 +4359,39 @@
       </c>
       <c r="G48" s="26">
         <f t="shared" si="18"/>
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H48" s="22">
         <f t="shared" si="19"/>
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="I48" s="24"/>
       <c r="J48" s="30">
-        <v>46133</v>
+        <v>46227</v>
       </c>
       <c r="K48">
         <f ca="1">ROUND(AVERAGE(L48:P48),4)</f>
-        <v>4.7100000000000003E-2</v>
+        <v>2.7799999999999998E-2</v>
       </c>
       <c r="L48">
         <f t="shared" ca="1" si="11"/>
-        <v>2.2399999999999975E-2</v>
+        <v>1.8299999999999983E-2</v>
       </c>
       <c r="M48">
         <f t="shared" ca="1" si="12"/>
-        <v>4.7000000000000042E-2</v>
+        <v>2.3599999999999954E-2</v>
       </c>
       <c r="N48">
         <f t="shared" ca="1" si="7"/>
-        <v>2.5699999999999945E-2</v>
+        <v>1.7800000000000038E-2</v>
       </c>
       <c r="O48">
         <f t="shared" ca="1" si="8"/>
-        <v>3.1599999999999961E-2</v>
+        <v>3.3399999999999985E-2</v>
       </c>
       <c r="P48">
         <f t="shared" ca="1" si="9"/>
-        <v>0.1089</v>
+        <v>4.5699999999999963E-2</v>
       </c>
       <c r="R48" s="1"/>
       <c r="S48" s="22"/>
@@ -4429,27 +4429,27 @@
       </c>
       <c r="K49">
         <f t="shared" ca="1" si="10"/>
-        <v>8.6199999999999992</v>
+        <v>13.66</v>
       </c>
       <c r="L49">
         <f t="shared" ca="1" si="11"/>
-        <v>8.8000000000000114</v>
+        <v>9.9000000000000057</v>
       </c>
       <c r="M49">
         <f t="shared" ca="1" si="12"/>
-        <v>8.5499999999999829</v>
+        <v>7.1999999999999886</v>
       </c>
       <c r="N49">
         <f t="shared" ca="1" si="7"/>
-        <v>7.0500000000000114</v>
+        <v>15.550000000000011</v>
       </c>
       <c r="O49">
         <f t="shared" ca="1" si="8"/>
-        <v>11.550000000000011</v>
+        <v>23.600000000000009</v>
       </c>
       <c r="P49">
         <f t="shared" ca="1" si="9"/>
-        <v>7.1500000000000057</v>
+        <v>12.049999999999997</v>
       </c>
       <c r="R49" s="1"/>
       <c r="S49" s="29">
@@ -4466,11 +4466,11 @@
         <v>59</v>
       </c>
       <c r="C50" s="22">
-        <v>2.71</v>
+        <v>3.88</v>
       </c>
       <c r="D50" s="25">
         <f>C50/10</f>
-        <v>0.27100000000000002</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="E50" s="22">
         <v>5.0000000000000001E-3</v>
@@ -4480,39 +4480,39 @@
       </c>
       <c r="G50" s="26">
         <f t="shared" si="18"/>
-        <v>923</v>
+        <v>644</v>
       </c>
       <c r="H50" s="22">
         <f>ROUND(D50/E50,0)</f>
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="I50" s="24"/>
       <c r="J50" s="30">
-        <v>46069</v>
+        <v>46227</v>
       </c>
       <c r="K50">
         <f t="shared" ca="1" si="10"/>
-        <v>4.8899999999999997</v>
+        <v>3.88</v>
       </c>
       <c r="L50">
         <f t="shared" ca="1" si="11"/>
-        <v>2.7750000000000057</v>
+        <v>2.259999999999998</v>
       </c>
       <c r="M50">
         <f t="shared" ca="1" si="12"/>
-        <v>2.0949999999999989</v>
+        <v>3.375</v>
       </c>
       <c r="N50">
         <f t="shared" ca="1" si="7"/>
-        <v>2.1799999999999926</v>
+        <v>3.240000000000002</v>
       </c>
       <c r="O50">
         <f t="shared" ca="1" si="8"/>
-        <v>5.9300000000000068</v>
+        <v>6.4100000000000037</v>
       </c>
       <c r="P50">
         <f t="shared" ca="1" si="9"/>
-        <v>11.484999999999999</v>
+        <v>4.1000000000000014</v>
       </c>
       <c r="R50" s="29">
         <v>19</v>
@@ -4554,27 +4554,27 @@
       </c>
       <c r="K51">
         <f t="shared" ca="1" si="10"/>
-        <v>35.200000000000003</v>
+        <v>66.5</v>
       </c>
       <c r="L51">
         <f t="shared" ca="1" si="11"/>
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="M51">
         <f t="shared" ca="1" si="12"/>
-        <v>23</v>
+        <v>44.5</v>
       </c>
       <c r="N51">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="O51">
         <f t="shared" ca="1" si="8"/>
-        <v>49.5</v>
+        <v>135</v>
       </c>
       <c r="P51">
         <f t="shared" ca="1" si="9"/>
-        <v>49.5</v>
+        <v>55</v>
       </c>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
@@ -4586,11 +4586,11 @@
         <v>37</v>
       </c>
       <c r="C52" s="1">
-        <v>120.3</v>
+        <v>206.6</v>
       </c>
       <c r="D52" s="25">
         <f t="shared" ref="D52:D55" si="20">C52/10</f>
-        <v>12.03</v>
+        <v>20.66</v>
       </c>
       <c r="E52" s="1">
         <v>0.5</v>
@@ -4600,39 +4600,39 @@
       </c>
       <c r="G52" s="26">
         <f t="shared" ref="G52:G55" si="21">ROUND($C$4/(D52/E52*F52),0)</f>
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H52" s="22">
         <f t="shared" ref="H52:H55" si="22">ROUND(D52/E52,0)</f>
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I52" s="23"/>
       <c r="J52" s="30">
-        <v>46133</v>
+        <v>46227</v>
       </c>
       <c r="K52">
         <f t="shared" ca="1" si="10"/>
-        <v>65.2</v>
+        <v>206.6</v>
       </c>
       <c r="L52">
         <f t="shared" ca="1" si="11"/>
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="M52">
         <f t="shared" ca="1" si="12"/>
-        <v>38</v>
+        <v>167.5</v>
       </c>
       <c r="N52">
         <f t="shared" ca="1" si="7"/>
-        <v>46</v>
+        <v>212.5</v>
       </c>
       <c r="O52">
         <f t="shared" ca="1" si="8"/>
-        <v>115.5</v>
+        <v>295</v>
       </c>
       <c r="P52">
         <f t="shared" ca="1" si="9"/>
-        <v>62.5</v>
+        <v>266</v>
       </c>
       <c r="R52" s="1">
         <v>-97</v>
